--- a/results/Dommages.xlsx
+++ b/results/Dommages.xlsx
@@ -12,15 +12,16 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5890" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dommages" sheetId="1" r:id="rId1"/>
-    <sheet name="Graphique1" sheetId="2" r:id="rId2"/>
+    <sheet name="Décompo" sheetId="1" r:id="rId1"/>
+    <sheet name="Gr Décompo" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,12 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Dommages</t>
-  </si>
-  <si>
-    <t>Température</t>
   </si>
   <si>
     <t>Chaîne logistique</t>
@@ -43,13 +41,20 @@
   <si>
     <t>Autres risques</t>
   </si>
+  <si>
+    <t>Rendements agricoles</t>
+  </si>
+  <si>
+    <t>Température de l'air</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -80,11 +85,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -188,7 +194,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dommages!$A$7</c:f>
+              <c:f>Décompo!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -208,10 +214,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Dommages!$B$6:$BE$6</c:f>
+              <c:f>Décompo!$B$7:$AZ$7</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>42005</c:v>
                 </c:pt>
@@ -364,198 +370,168 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>60268</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>60633</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>60998</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>61363</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61729</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>62094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dommages!$B$7:$BE$7</c:f>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-1.266072864198553E-3</c:v>
+                  <c:v>1.3538601712600906E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.5917392506271675E-3</c:v>
+                  <c:v>1.6912679139984843E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4.0326000639545612E-3</c:v>
+                  <c:v>2.0115560050032899E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.5398882267881921E-3</c:v>
+                  <c:v>2.2943774039713705E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-7.0753521544256737E-3</c:v>
+                  <c:v>2.5425308096377663E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-8.6109377713811108E-3</c:v>
+                  <c:v>2.7611418605846372E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.0144740729668866E-2</c:v>
+                  <c:v>2.9576927112697438E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.1647558849598894E-2</c:v>
+                  <c:v>3.1353239073615535E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1.3108699732437334E-2</c:v>
+                  <c:v>3.2985843392642766E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.4521609586762518E-2</c:v>
+                  <c:v>3.4516237501799885E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.5879614421541621E-2</c:v>
+                  <c:v>3.6927247035058564E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.7246794912863739E-2</c:v>
+                  <c:v>3.7901004681047845E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.856728984472833E-2</c:v>
+                  <c:v>3.8748605891280929E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1.9840005510711523E-2</c:v>
+                  <c:v>3.9477051314678935E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2.1064153683655107E-2</c:v>
+                  <c:v>4.0116488877360634E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2.2240101557918446E-2</c:v>
+                  <c:v>4.0694640941231978E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2.3427369804605025E-2</c:v>
+                  <c:v>4.1277964002331198E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2.4576642800835713E-2</c:v>
+                  <c:v>4.1849741026071745E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2.5689675345346386E-2</c:v>
+                  <c:v>4.2425458296820991E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2.6767820412278209E-2</c:v>
+                  <c:v>4.3016340742832782E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2.7815086689841229E-2</c:v>
+                  <c:v>4.3633104309372284E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-2.8827773151122837E-2</c:v>
+                  <c:v>4.427314031618601E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-2.9810370857266899E-2</c:v>
+                  <c:v>4.4941592404026176E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-3.0765609291796503E-2</c:v>
+                  <c:v>4.563947337910957E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-3.1696101481516137E-2</c:v>
+                  <c:v>4.6365522950460585E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-3.261048090505636E-2</c:v>
+                  <c:v>4.7123697653551948E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-3.3479270837039277E-2</c:v>
+                  <c:v>4.788032119780028E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-3.43266459642948E-2</c:v>
+                  <c:v>4.8649621572917197E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-3.5156542306031047E-2</c:v>
+                  <c:v>4.9429610515789646E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-3.5972365891299485E-2</c:v>
+                  <c:v>5.0218084317584018E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-3.677661276628974E-2</c:v>
+                  <c:v>5.1012621214923663E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-3.7560475373298097E-2</c:v>
+                  <c:v>5.1800471640880197E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-3.8333996431981987E-2</c:v>
+                  <c:v>5.2587995224248063E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-3.9097743338236013E-2</c:v>
+                  <c:v>5.337331162577863E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-3.9852007191780725E-2</c:v>
+                  <c:v>5.4154996240649018E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-4.0596735508986799E-2</c:v>
+                  <c:v>5.4931913241978665E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-4.1246932839789426E-2</c:v>
+                  <c:v>5.5612806592488247E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-4.1875993547512709E-2</c:v>
+                  <c:v>5.6273572035804416E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-4.2484618386982136E-2</c:v>
+                  <c:v>5.6914643529708646E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-4.3075432912364493E-2</c:v>
+                  <c:v>5.753897634474104E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-4.3651236796108946E-2</c:v>
+                  <c:v>5.8149801082812758E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-4.42014486513208E-2</c:v>
+                  <c:v>5.8735596987392939E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-4.4738996919088558E-2</c:v>
+                  <c:v>5.9311343796265348E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-4.5265541607199984E-2</c:v>
+                  <c:v>5.9879563848025723E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-4.5781799152661673E-2</c:v>
+                  <c:v>6.0442828733665251E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-4.6288400899773825E-2</c:v>
+                  <c:v>6.1003296850866917E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-4.6744839222177322E-2</c:v>
+                  <c:v>6.1513652453118454E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-4.7186985694255945E-2</c:v>
+                  <c:v>6.2016559531788203E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-4.7616235314381417E-2</c:v>
+                  <c:v>6.251429610217496E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-4.8034529350900357E-2</c:v>
+                  <c:v>6.3009329761051225E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-4.8443625976066669E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>-4.8820978767775906E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>-4.9188573097843073E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>-4.9548004893138382E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>-4.9901043179792381E-2</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>-5.0249201356903479E-2</c:v>
+                  <c:v>6.3503741189399388E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -571,11 +547,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dommages!$A$8</c:f>
+              <c:f>Décompo!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Température</c:v>
+                  <c:v>Rendements agricoles</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -591,10 +567,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Dommages!$B$6:$BE$6</c:f>
+              <c:f>Décompo!$B$7:$AZ$7</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>42005</c:v>
                 </c:pt>
@@ -747,198 +723,168 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>60268</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>60633</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>60998</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>61363</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61729</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>62094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dommages!$B$8:$BE$8</c:f>
+              <c:f>Décompo!$B$9:$AZ$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-9.7918243057160126E-6</c:v>
+                  <c:v>2.7840212279017784E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.808163346990078E-5</c:v>
+                  <c:v>5.224525962783666E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5.1425394389958967E-5</c:v>
+                  <c:v>6.9534022194739364E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-7.6835517343942783E-5</c:v>
+                  <c:v>8.0445679314089524E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.0307311318846768E-4</c:v>
+                  <c:v>8.7831374153535258E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.3017207009036191E-4</c:v>
+                  <c:v>9.4332704387400934E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.5893840397063208E-4</c:v>
+                  <c:v>1.0147871066616965E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.900957509812784E-4</c:v>
+                  <c:v>1.0972397702284642E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-2.2405515147039257E-4</c:v>
+                  <c:v>1.189922651713915E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2.6120984226385424E-4</c:v>
+                  <c:v>1.289820743303971E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-3.0136230370669814E-4</c:v>
+                  <c:v>1.3906185439738206E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-3.4507215634838051E-4</c:v>
+                  <c:v>1.5004994437428643E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-3.9191995531873136E-4</c:v>
+                  <c:v>1.6132898073157875E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-4.4114990896770845E-4</c:v>
+                  <c:v>1.7274126835205017E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.9215842053884629E-4</c:v>
+                  <c:v>1.8416524130396919E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-5.4467441744643352E-4</c:v>
+                  <c:v>1.9553201850748408E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-5.9988147260625624E-4</c:v>
+                  <c:v>2.0706062263154898E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-6.5783344658254528E-4</c:v>
+                  <c:v>2.1869310298537961E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-7.1810884898160232E-4</c:v>
+                  <c:v>2.303463453985799E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-7.8037089716820329E-4</c:v>
+                  <c:v>2.4194115546302061E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-8.444333458824671E-4</c:v>
+                  <c:v>2.5337376518913615E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-9.1049501542794786E-4</c:v>
+                  <c:v>2.647006054314123E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-9.7870515529852042E-4</c:v>
+                  <c:v>2.7587936974806659E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.049388186096234E-3</c:v>
+                  <c:v>2.8691627555110649E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.1227904989230542E-3</c:v>
+                  <c:v>2.9782513372484942E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-1.1986558011504167E-3</c:v>
+                  <c:v>3.0845426854701E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-1.2764895022373546E-3</c:v>
+                  <c:v>3.1893081092998557E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-1.3560705527247974E-3</c:v>
+                  <c:v>3.2922830336853323E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-1.437541955118915E-3</c:v>
+                  <c:v>3.3939862645634492E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-1.5210217514883828E-3</c:v>
+                  <c:v>3.4949579534206826E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-1.6064580242231008E-3</c:v>
+                  <c:v>3.5956227016033029E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-1.6932692563298435E-3</c:v>
+                  <c:v>3.6957206085608263E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-1.7812715975512664E-3</c:v>
+                  <c:v>3.7954412599580031E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.8704921625820603E-3</c:v>
+                  <c:v>3.8950323936456296E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-1.9609740786158472E-3</c:v>
+                  <c:v>3.9947226290580826E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-2.052726693418272E-3</c:v>
+                  <c:v>4.0946887554384886E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-2.1415867908399708E-3</c:v>
+                  <c:v>4.1900888256526311E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-2.2277185472585614E-3</c:v>
+                  <c:v>4.2817482682538863E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-2.3130713765548983E-3</c:v>
+                  <c:v>4.371267291225292E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-2.399165040325002E-3</c:v>
+                  <c:v>4.4602334244469993E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-2.4865986947451013E-3</c:v>
+                  <c:v>4.5497829812162216E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-2.574581717191618E-3</c:v>
+                  <c:v>4.6398338524992269E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-2.6627405756573033E-3</c:v>
+                  <c:v>4.7306407184012356E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-2.751034449388623E-3</c:v>
+                  <c:v>4.822557023581038E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-2.8395133235213851E-3</c:v>
+                  <c:v>4.915672562974531E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-2.928251737951193E-3</c:v>
+                  <c:v>5.0100464855701299E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-3.0148603633889312E-3</c:v>
+                  <c:v>5.1035559964569613E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-3.0994813738940419E-3</c:v>
+                  <c:v>5.1962276094394896E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-3.1834509889060517E-3</c:v>
+                  <c:v>5.2888830168641432E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-3.2678653013855641E-3</c:v>
+                  <c:v>5.3824060842524446E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-3.3532388624071124E-3</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>-3.4380184925244528E-3</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>-3.5220648948561945E-3</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>-3.6059800267032038E-3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>-3.6902752450919049E-3</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>-3.775179817056544E-3</c:v>
+                  <c:v>5.477488980923928E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -954,11 +900,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dommages!$A$9</c:f>
+              <c:f>Décompo!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Autres risques</c:v>
+                  <c:v>Température de l'air</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -966,6 +912,359 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Décompo!$B$7:$AZ$7</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>42005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42370</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42736</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43466</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43831</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44197</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44562</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44927</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45292</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46388</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46753</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>47119</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>47484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>47849</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48214</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48580</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48945</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>49310</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>49675</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>50406</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50771</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>51136</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51502</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>51867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>52232</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>52597</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>52963</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53328</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53693</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>54058</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>54424</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>54789</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>55154</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>55519</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>55885</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>56250</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>56615</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>56980</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>57346</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>57711</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>58076</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>58441</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>58807</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>59172</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>59537</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>59902</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>60268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Décompo!$B$10:$AZ$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>6.168779579696082E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2415006617638724E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6806397964841402E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9533471300470229E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1561527487090615E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3723164204614289E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6463511131902262E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9862186944706881E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.3781094304263792E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.8015762570164924E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.2303960818368402E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.6827398521953612E-4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.1421941050267678E-4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.604412600280842E-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.0684488432372063E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.5365284502870435E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.0237722578869038E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.5342635216713028E-4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.066844280045643E-4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.6201393587105601E-4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>9.1932180070708469E-4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9.7881014286314849E-4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.0405195746674423E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.1045060634298359E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.170796694930927E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.2390978049161561E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3090452237356359E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.3804602482122633E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.4534740382222619E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.5281965357031371E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.6046269659593104E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.6822930112380188E-3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.761106602276255E-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.8411538530372987E-3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.9225128302719011E-3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.0052168885985669E-3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.0854399887522135E-3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.1632975700532908E-3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.2405688385811404E-3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.3186284023730755E-3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.3979986580122681E-3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.4779283908153982E-3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.5580341694070308E-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.6382558313923221E-3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2.7186220593600208E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.7991866626791984E-3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.8777843676351944E-3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.9544839735867745E-3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.0305233494897221E-3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.106923302080733E-3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.1841664268963399E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0B97-4EC8-8433-CD6511F1540E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Décompo!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Autres risques</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -974,10 +1273,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Dommages!$B$6:$BE$6</c:f>
+              <c:f>Décompo!$B$7:$AZ$7</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
                   <c:v>42005</c:v>
                 </c:pt>
@@ -1130,205 +1429,175 @@
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>60268</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>60633</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>60998</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>61363</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>61729</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>62094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dommages!$B$9:$BE$9</c:f>
+              <c:f>Décompo!$B$11:$AZ$11</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-2.8767437052490408E-6</c:v>
+                  <c:v>-7.2669652130707973E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.6996036485477148E-6</c:v>
+                  <c:v>-7.879551575240562E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.3528907525373057E-5</c:v>
+                  <c:v>-8.7302778841835682E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.9801261958773964E-5</c:v>
+                  <c:v>-9.7772507465898606E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2.6119598913743047E-5</c:v>
+                  <c:v>-1.0843370503699212E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-3.2083843975572179E-5</c:v>
+                  <c:v>-1.175582647838791E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3.6954970511149376E-5</c:v>
+                  <c:v>-1.2430022394416262E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-4.0289119702885401E-5</c:v>
+                  <c:v>-1.2860406736370233E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.223457660024188E-5</c:v>
+                  <c:v>-1.3112928915759436E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-4.2707972871203204E-5</c:v>
+                  <c:v>-1.3312405400012217E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-4.3030631782681183E-5</c:v>
+                  <c:v>-1.3557234589245404E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.3118690705390428E-5</c:v>
+                  <c:v>-1.3984670744315864E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.3503423099222616E-5</c:v>
+                  <c:v>-1.4546917841518764E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-4.438984078114494E-5</c:v>
+                  <c:v>-1.520626001153616E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.593109875450363E-5</c:v>
+                  <c:v>-1.5909555991312774E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-4.8243963762795161E-5</c:v>
+                  <c:v>-1.66077867519758E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-5.1435177144898425E-5</c:v>
+                  <c:v>-1.7285141273948312E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-5.5684867826810702E-5</c:v>
+                  <c:v>-1.79035250725261E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-6.0834283375221787E-5</c:v>
+                  <c:v>-1.84520800972858E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-6.6685293010126934E-5</c:v>
+                  <c:v>-1.8927222727184445E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-7.2785899666971687E-5</c:v>
+                  <c:v>-1.9342556341384737E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-7.9434000149869455E-5</c:v>
+                  <c:v>-1.9685611233777323E-4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-8.6276343460700566E-5</c:v>
+                  <c:v>-1.9975510404212499E-4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-9.3321111052757644E-5</c:v>
+                  <c:v>-2.0224006395475058E-4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.0078355224740765E-4</c:v>
+                  <c:v>-2.0441808520754029E-4</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-1.0811630780882542E-4</c:v>
+                  <c:v>-2.0670360937535825E-4</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-1.1657258102559798E-4</c:v>
+                  <c:v>-2.0859936724437061E-4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-1.2548500949127739E-4</c:v>
+                  <c:v>-2.10377166453668E-4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-1.3453573633059879E-4</c:v>
+                  <c:v>-2.1209909277342121E-4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-1.4339361988013888E-4</c:v>
+                  <c:v>-2.1380935684255781E-4</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-1.5180230519962201E-4</c:v>
+                  <c:v>-2.1552686643211416E-4</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-1.5958921700154338E-4</c:v>
+                  <c:v>-2.1719691109545886E-4</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-1.6663922126813197E-4</c:v>
+                  <c:v>-2.1884168707887036E-4</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.7299561583250522E-4</c:v>
+                  <c:v>-2.2043630044332047E-4</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-1.7875910808606149E-4</c:v>
+                  <c:v>-2.2195763552824987E-4</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-1.8405739646330799E-4</c:v>
+                  <c:v>-2.2337942252437237E-4</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-1.8875378573913332E-4</c:v>
+                  <c:v>-2.2427381890066656E-4</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-1.9271771197747894E-4</c:v>
+                  <c:v>-2.2489407428549074E-4</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-1.9625133834611647E-4</c:v>
+                  <c:v>-2.2524427262649027E-4</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-1.9963216349482699E-4</c:v>
+                  <c:v>-2.2536862792232881E-4</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-2.0306784493927948E-4</c:v>
+                  <c:v>-2.253060154772113E-4</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-2.0667942651330512E-4</c:v>
+                  <c:v>-2.2500744033948639E-4</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-2.104643640076162E-4</c:v>
+                  <c:v>-2.2454337015731518E-4</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-2.144920037425585E-4</c:v>
+                  <c:v>-2.2392253051151112E-4</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-2.1882182280963391E-4</c:v>
+                  <c:v>-2.2315218908330881E-4</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-2.235034261962518E-4</c:v>
+                  <c:v>-2.2223241794816495E-4</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-2.2856850453423228E-4</c:v>
+                  <c:v>-2.2090510750294445E-4</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-2.337926166070467E-4</c:v>
+                  <c:v>-2.1935469415590436E-4</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-2.393172554430098E-4</c:v>
+                  <c:v>-2.1759224127337884E-4</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-2.4528627438380468E-4</c:v>
+                  <c:v>-2.1564078073721404E-4</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-2.51812905748168E-4</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>-2.589500631655639E-4</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>-2.6658755750685187E-4</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>-2.7481049540266367E-4</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>-2.836954198700628E-4</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>-2.9330113904658256E-4</c:v>
+                  <c:v>-2.135171994367413E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0B97-4EC8-8433-CD6511F1540E}"/>
+              <c16:uniqueId val="{00000000-7EC6-4E26-91E0-1E0153E07C27}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2103,7 +2372,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9291053" cy="6060351"/>
+    <xdr:ext cx="9297358" cy="6074434"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1"/>
@@ -2155,344 +2424,159 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4">
-            <v>42005</v>
-          </cell>
-          <cell r="D4">
-            <v>42370</v>
-          </cell>
-          <cell r="E4">
-            <v>42736</v>
-          </cell>
-          <cell r="F4">
-            <v>43101</v>
-          </cell>
-          <cell r="G4">
-            <v>43466</v>
-          </cell>
-          <cell r="H4">
-            <v>43831</v>
-          </cell>
-          <cell r="I4">
-            <v>44197</v>
-          </cell>
-          <cell r="J4">
-            <v>44562</v>
-          </cell>
-          <cell r="K4">
-            <v>44927</v>
-          </cell>
-          <cell r="L4">
-            <v>45292</v>
-          </cell>
-          <cell r="M4">
-            <v>45658</v>
-          </cell>
-          <cell r="N4">
-            <v>46023</v>
-          </cell>
-          <cell r="O4">
-            <v>46388</v>
-          </cell>
-          <cell r="P4">
-            <v>46753</v>
-          </cell>
-          <cell r="Q4">
-            <v>47119</v>
-          </cell>
-          <cell r="R4">
-            <v>47484</v>
-          </cell>
-          <cell r="S4">
-            <v>47849</v>
-          </cell>
-          <cell r="T4">
-            <v>48214</v>
-          </cell>
-          <cell r="U4">
-            <v>48580</v>
-          </cell>
-          <cell r="V4">
-            <v>48945</v>
-          </cell>
-          <cell r="W4">
-            <v>49310</v>
-          </cell>
-          <cell r="X4">
-            <v>49675</v>
-          </cell>
-          <cell r="Y4">
-            <v>50041</v>
-          </cell>
-          <cell r="Z4">
-            <v>50406</v>
-          </cell>
-          <cell r="AA4">
-            <v>50771</v>
-          </cell>
-          <cell r="AB4">
-            <v>51136</v>
-          </cell>
-          <cell r="AC4">
-            <v>51502</v>
-          </cell>
-          <cell r="AD4">
-            <v>51867</v>
-          </cell>
-          <cell r="AE4">
-            <v>52232</v>
-          </cell>
-          <cell r="AF4">
-            <v>52597</v>
-          </cell>
-          <cell r="AG4">
-            <v>52963</v>
-          </cell>
-          <cell r="AH4">
-            <v>53328</v>
-          </cell>
-          <cell r="AI4">
-            <v>53693</v>
-          </cell>
-          <cell r="AJ4">
-            <v>54058</v>
-          </cell>
-          <cell r="AK4">
-            <v>54424</v>
-          </cell>
-          <cell r="AL4">
-            <v>54789</v>
-          </cell>
-          <cell r="AM4">
-            <v>55154</v>
-          </cell>
-          <cell r="AN4">
-            <v>55519</v>
-          </cell>
-          <cell r="AO4">
-            <v>55885</v>
-          </cell>
-          <cell r="AP4">
-            <v>56250</v>
-          </cell>
-          <cell r="AQ4">
-            <v>56615</v>
-          </cell>
-          <cell r="AR4">
-            <v>56980</v>
-          </cell>
-          <cell r="AS4">
-            <v>57346</v>
-          </cell>
-          <cell r="AT4">
-            <v>57711</v>
-          </cell>
-          <cell r="AU4">
-            <v>58076</v>
-          </cell>
-          <cell r="AV4">
-            <v>58441</v>
-          </cell>
-          <cell r="AW4">
-            <v>58807</v>
-          </cell>
-          <cell r="AX4">
-            <v>59172</v>
-          </cell>
-          <cell r="AY4">
-            <v>59537</v>
-          </cell>
-          <cell r="AZ4">
-            <v>59902</v>
-          </cell>
-          <cell r="BA4">
-            <v>60268</v>
-          </cell>
-          <cell r="BB4">
-            <v>60633</v>
-          </cell>
-          <cell r="BC4">
-            <v>60998</v>
-          </cell>
-          <cell r="BD4">
-            <v>61363</v>
-          </cell>
-          <cell r="BE4">
-            <v>61729</v>
-          </cell>
-          <cell r="BF4">
-            <v>62094</v>
-          </cell>
-        </row>
         <row r="5">
           <cell r="C5">
-            <v>-0.12787414322095181</v>
+            <v>-1.3538601712600906</v>
           </cell>
           <cell r="D5">
-            <v>-0.2627520487745616</v>
+            <v>-1.6912679139984843</v>
           </cell>
           <cell r="E5">
-            <v>-0.40975543658698932</v>
+            <v>-2.0115560050032899</v>
           </cell>
           <cell r="F5">
-            <v>-0.56365250060909089</v>
+            <v>-2.2943774039713705</v>
           </cell>
           <cell r="G5">
-            <v>-0.72045448665278844</v>
+            <v>-2.5425308096377663</v>
           </cell>
           <cell r="H5">
-            <v>-0.87731936854470449</v>
+            <v>-2.7611418605846372</v>
           </cell>
           <cell r="I5">
-            <v>-1.0340634104150648</v>
+            <v>-2.9576927112697438</v>
           </cell>
           <cell r="J5">
-            <v>-1.1877943720283057</v>
+            <v>-3.1353239073615535</v>
           </cell>
           <cell r="K5">
-            <v>-1.3374989460507969</v>
+            <v>-3.2985843392642766</v>
           </cell>
           <cell r="L5">
-            <v>-1.4825527401897576</v>
+            <v>-3.4516237501799885</v>
           </cell>
           <cell r="M5">
-            <v>-1.6224007357031001</v>
+            <v>-3.6927247035058564</v>
           </cell>
           <cell r="N5">
-            <v>-1.763498575991751</v>
+            <v>-3.7901004681047845</v>
           </cell>
           <cell r="O5">
-            <v>-1.9002713223146284</v>
+            <v>-3.8748605891280929</v>
           </cell>
           <cell r="P5">
-            <v>-2.0325545260460376</v>
+            <v>-3.9477051314678935</v>
           </cell>
           <cell r="Q5">
-            <v>-2.1602243202948457</v>
+            <v>-4.0116488877360634</v>
           </cell>
           <cell r="R5">
-            <v>-2.2833019939127674</v>
+            <v>-4.0694640941231981</v>
           </cell>
           <cell r="S5">
-            <v>-2.407868645435618</v>
+            <v>-4.1277964002331196</v>
           </cell>
           <cell r="T5">
-            <v>-2.5290161115245069</v>
+            <v>-4.1849741026071747</v>
           </cell>
           <cell r="U5">
-            <v>-2.646861847770321</v>
+            <v>-4.2425458296820988</v>
           </cell>
           <cell r="V5">
-            <v>-2.761487660245654</v>
+            <v>-4.3016340742832782</v>
           </cell>
           <cell r="W5">
-            <v>-2.8732305935390667</v>
+            <v>-4.3633104309372284</v>
           </cell>
           <cell r="X5">
-            <v>-2.9817702166700655</v>
+            <v>-4.427314031618601</v>
           </cell>
           <cell r="Y5">
-            <v>-3.087535235602612</v>
+            <v>-4.4941592404026176</v>
           </cell>
           <cell r="Z5">
-            <v>-3.1908318588945495</v>
+            <v>-4.5639473379109567</v>
           </cell>
           <cell r="AA5">
-            <v>-3.2919675532686599</v>
+            <v>-4.6365522950460587</v>
           </cell>
           <cell r="AB5">
-            <v>-3.3917253014015603</v>
+            <v>-4.712369765355195</v>
           </cell>
           <cell r="AC5">
-            <v>-3.4872332920302229</v>
+            <v>-4.788032119780028</v>
           </cell>
           <cell r="AD5">
-            <v>-3.5808201526510874</v>
+            <v>-4.8649621572917194</v>
           </cell>
           <cell r="AE5">
-            <v>-3.672861999748056</v>
+            <v>-4.9429610515789646</v>
           </cell>
           <cell r="AF5">
-            <v>-3.7636781262668006</v>
+            <v>-5.0218084317584015</v>
           </cell>
           <cell r="AG5">
-            <v>-3.8534873095712463</v>
+            <v>-5.1012621214923666</v>
           </cell>
           <cell r="AH5">
-            <v>-3.9413333846629484</v>
+            <v>-5.1800471640880197</v>
           </cell>
           <cell r="AI5">
-            <v>-4.0281907250801385</v>
+            <v>-5.2587995224248063</v>
           </cell>
           <cell r="AJ5">
-            <v>-4.1141231116650578</v>
+            <v>-5.337331162577863</v>
           </cell>
           <cell r="AK5">
-            <v>-4.1991740378482634</v>
+            <v>-5.4154996240649016</v>
           </cell>
           <cell r="AL5">
-            <v>-4.2833519598868381</v>
+            <v>-5.4931913241978663</v>
           </cell>
           <cell r="AM5">
-            <v>-4.3577273416368527</v>
+            <v>-5.5612806592488244</v>
           </cell>
           <cell r="AN5">
-            <v>-4.4296429806748749</v>
+            <v>-5.6273572035804413</v>
           </cell>
           <cell r="AO5">
-            <v>-4.499394110188315</v>
+            <v>-5.6914643529708648</v>
           </cell>
           <cell r="AP5">
-            <v>-4.5674230116184322</v>
+            <v>-5.7538976344741037</v>
           </cell>
           <cell r="AQ5">
-            <v>-4.6340903335793326</v>
+            <v>-5.8149801082812758</v>
           </cell>
           <cell r="AR5">
-            <v>-4.6982709795025723</v>
+            <v>-5.8735596987392942</v>
           </cell>
           <cell r="AS5">
-            <v>-4.7612201858753478</v>
+            <v>-5.9311343796265348</v>
           </cell>
           <cell r="AT5">
-            <v>-4.8231068060331168</v>
+            <v>-5.9879563848025725</v>
           </cell>
           <cell r="AU5">
-            <v>-4.8840134298992695</v>
+            <v>-6.0442828733665248</v>
           </cell>
           <cell r="AV5">
-            <v>-4.944015606392127</v>
+            <v>-6.1003296850866917</v>
           </cell>
           <cell r="AW5">
-            <v>-4.9988268090100485</v>
+            <v>-6.1513652453118457</v>
           </cell>
           <cell r="AX5">
-            <v>-5.0520259684757036</v>
+            <v>-6.20165595317882</v>
           </cell>
           <cell r="AY5">
-            <v>-5.1039003558730478</v>
+            <v>-6.251429610217496</v>
           </cell>
           <cell r="AZ5">
-            <v>-5.1547680926669726</v>
+            <v>-6.3009329761051225</v>
           </cell>
           <cell r="BA5">
-            <v>-5.2048677744221949</v>
-          </cell>
-          <cell r="BB5">
-            <v>-5.2517947323465926</v>
-          </cell>
-          <cell r="BC5">
-            <v>-5.297722555020612</v>
-          </cell>
-          <cell r="BD5">
-            <v>-5.3428795415244252</v>
-          </cell>
-          <cell r="BE5">
-            <v>-5.3875013844754349</v>
-          </cell>
-          <cell r="BF5">
-            <v>-5.4317682313006603</v>
+            <v>-6.3503741189399392</v>
           </cell>
         </row>
       </sheetData>
@@ -2532,172 +2616,157 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-0.1275864688504269</v>
+            <v>-1.3817003835391084</v>
           </cell>
           <cell r="D5">
-            <v>-0.26198208840970683</v>
+            <v>-1.743513173626321</v>
           </cell>
           <cell r="E5">
-            <v>-0.40840254583445201</v>
+            <v>-2.0810900271980293</v>
           </cell>
           <cell r="F5">
-            <v>-0.56167237441321349</v>
+            <v>-2.37482308328546</v>
           </cell>
           <cell r="G5">
-            <v>-0.71784252676141413</v>
+            <v>-2.6303621837913016</v>
           </cell>
           <cell r="H5">
-            <v>-0.87411098414714727</v>
+            <v>-2.8554745649720381</v>
           </cell>
           <cell r="I5">
-            <v>-1.0303679133639498</v>
+            <v>-3.0591714219359134</v>
           </cell>
           <cell r="J5">
-            <v>-1.1837654600580172</v>
+            <v>-3.2450478843843999</v>
           </cell>
           <cell r="K5">
-            <v>-1.3332754883907727</v>
+            <v>-3.4175766044356681</v>
           </cell>
           <cell r="L5">
-            <v>-1.4782819429026373</v>
+            <v>-3.5806058245103856</v>
           </cell>
           <cell r="M5">
-            <v>-1.6180976725248319</v>
+            <v>-3.8317865579032384</v>
           </cell>
           <cell r="N5">
-            <v>-1.7591867069212119</v>
+            <v>-3.9401504124790709</v>
           </cell>
           <cell r="O5">
-            <v>-1.8959209800047061</v>
+            <v>-4.0361895698596717</v>
           </cell>
           <cell r="P5">
-            <v>-2.0281155419679231</v>
+            <v>-4.1204463998199437</v>
           </cell>
           <cell r="Q5">
-            <v>-2.1556312104193953</v>
+            <v>-4.1958141290400324</v>
           </cell>
           <cell r="R5">
-            <v>-2.2784775975364879</v>
+            <v>-4.2649961126306817</v>
           </cell>
           <cell r="S5">
-            <v>-2.4027251277211281</v>
+            <v>-4.3348570228646688</v>
           </cell>
           <cell r="T5">
-            <v>-2.5234476247418258</v>
+            <v>-4.4036672055925541</v>
           </cell>
           <cell r="U5">
-            <v>-2.6407784194327988</v>
+            <v>-4.4728921750806787</v>
           </cell>
           <cell r="V5">
-            <v>-2.7548191309446413</v>
+            <v>-4.543575229746299</v>
           </cell>
           <cell r="W5">
-            <v>-2.8659520035723696</v>
+            <v>-4.6166841961263643</v>
           </cell>
           <cell r="X5">
-            <v>-2.9738268166550785</v>
+            <v>-4.6920146370500131</v>
           </cell>
           <cell r="Y5">
-            <v>-3.0789076012565419</v>
+            <v>-4.7700386101506842</v>
           </cell>
           <cell r="Z5">
-            <v>-3.1814997477892737</v>
+            <v>-4.8508636134620637</v>
           </cell>
           <cell r="AA5">
-            <v>-3.2818891980439191</v>
+            <v>-4.9343774287709081</v>
           </cell>
           <cell r="AB5">
-            <v>-3.3809136706206777</v>
+            <v>-5.0208240339022048</v>
           </cell>
           <cell r="AC5">
-            <v>-3.4755760339276631</v>
+            <v>-5.1069629307100133</v>
           </cell>
           <cell r="AD5">
-            <v>-3.5682716517019597</v>
+            <v>-5.1941904606602529</v>
           </cell>
           <cell r="AE5">
-            <v>-3.6594084261149962</v>
+            <v>-5.2823596780353093</v>
           </cell>
           <cell r="AF5">
-            <v>-3.7493387642787868</v>
+            <v>-5.3713042271004703</v>
           </cell>
           <cell r="AG5">
-            <v>-3.8383070790512841</v>
+            <v>-5.4608243916526966</v>
           </cell>
           <cell r="AH5">
-            <v>-3.925374462962794</v>
+            <v>-5.5496192249441023</v>
           </cell>
           <cell r="AI5">
-            <v>-4.0115268029533251</v>
+            <v>-5.6383436484206069</v>
           </cell>
           <cell r="AJ5">
-            <v>-4.0968235500818073</v>
+            <v>-5.7268344019424262</v>
           </cell>
           <cell r="AK5">
-            <v>-4.181298127039657</v>
+            <v>-5.8149718869707101</v>
           </cell>
           <cell r="AL5">
-            <v>-4.2649462202405068</v>
+            <v>-5.9026601997417156</v>
           </cell>
           <cell r="AM5">
-            <v>-4.3388519630629396</v>
+            <v>-5.9802895418140878</v>
           </cell>
           <cell r="AN5">
-            <v>-4.4103712094771268</v>
+            <v>-6.0555320304058302</v>
           </cell>
           <cell r="AO5">
-            <v>-4.4797689763537036</v>
+            <v>-6.1285910820933935</v>
           </cell>
           <cell r="AP5">
-            <v>-4.5474597952689493</v>
+            <v>-6.1999209769188042</v>
           </cell>
           <cell r="AQ5">
-            <v>-4.6137835490854044</v>
+            <v>-6.2699584064028979</v>
           </cell>
           <cell r="AR5">
-            <v>-4.6776030368512416</v>
+            <v>-6.3375430839892166</v>
           </cell>
           <cell r="AS5">
-            <v>-4.7401737494745859</v>
+            <v>-6.4041984514666588</v>
           </cell>
           <cell r="AT5">
-            <v>-4.8016576056588605</v>
+            <v>-6.4702120871606761</v>
           </cell>
           <cell r="AU5">
-            <v>-4.8621312476183061</v>
+            <v>-6.5358501296639782</v>
           </cell>
           <cell r="AV5">
-            <v>-4.9216652637725016</v>
+            <v>-6.6013343336437043</v>
           </cell>
           <cell r="AW5">
-            <v>-4.9759699585566253</v>
+            <v>-6.6617208449575411</v>
           </cell>
           <cell r="AX5">
-            <v>-5.0286467068149987</v>
+            <v>-6.7212787141227697</v>
           </cell>
           <cell r="AY5">
-            <v>-5.0799686303287466</v>
+            <v>-6.7803179119039108</v>
           </cell>
           <cell r="AZ5">
-            <v>-5.1302394652285921</v>
+            <v>-6.8391735845303669</v>
           </cell>
           <cell r="BA5">
-            <v>-5.1796864838473784</v>
-          </cell>
-          <cell r="BB5">
-            <v>-5.2258997260300362</v>
-          </cell>
-          <cell r="BC5">
-            <v>-5.2710637992699265</v>
-          </cell>
-          <cell r="BD5">
-            <v>-5.3153984919841584</v>
-          </cell>
-          <cell r="BE5">
-            <v>-5.3591318424884289</v>
-          </cell>
-          <cell r="BF5">
-            <v>-5.4024381173960023</v>
+            <v>-6.8981230170323311</v>
           </cell>
         </row>
       </sheetData>
@@ -2735,174 +2804,504 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>42005</v>
+          </cell>
+          <cell r="D4">
+            <v>42370</v>
+          </cell>
+          <cell r="E4">
+            <v>42736</v>
+          </cell>
+          <cell r="F4">
+            <v>43101</v>
+          </cell>
+          <cell r="G4">
+            <v>43466</v>
+          </cell>
+          <cell r="H4">
+            <v>43831</v>
+          </cell>
+          <cell r="I4">
+            <v>44197</v>
+          </cell>
+          <cell r="J4">
+            <v>44562</v>
+          </cell>
+          <cell r="K4">
+            <v>44927</v>
+          </cell>
+          <cell r="L4">
+            <v>45292</v>
+          </cell>
+          <cell r="M4">
+            <v>45658</v>
+          </cell>
+          <cell r="N4">
+            <v>46023</v>
+          </cell>
+          <cell r="O4">
+            <v>46388</v>
+          </cell>
+          <cell r="P4">
+            <v>46753</v>
+          </cell>
+          <cell r="Q4">
+            <v>47119</v>
+          </cell>
+          <cell r="R4">
+            <v>47484</v>
+          </cell>
+          <cell r="S4">
+            <v>47849</v>
+          </cell>
+          <cell r="T4">
+            <v>48214</v>
+          </cell>
+          <cell r="U4">
+            <v>48580</v>
+          </cell>
+          <cell r="V4">
+            <v>48945</v>
+          </cell>
+          <cell r="W4">
+            <v>49310</v>
+          </cell>
+          <cell r="X4">
+            <v>49675</v>
+          </cell>
+          <cell r="Y4">
+            <v>50041</v>
+          </cell>
+          <cell r="Z4">
+            <v>50406</v>
+          </cell>
+          <cell r="AA4">
+            <v>50771</v>
+          </cell>
+          <cell r="AB4">
+            <v>51136</v>
+          </cell>
+          <cell r="AC4">
+            <v>51502</v>
+          </cell>
+          <cell r="AD4">
+            <v>51867</v>
+          </cell>
+          <cell r="AE4">
+            <v>52232</v>
+          </cell>
+          <cell r="AF4">
+            <v>52597</v>
+          </cell>
+          <cell r="AG4">
+            <v>52963</v>
+          </cell>
+          <cell r="AH4">
+            <v>53328</v>
+          </cell>
+          <cell r="AI4">
+            <v>53693</v>
+          </cell>
+          <cell r="AJ4">
+            <v>54058</v>
+          </cell>
+          <cell r="AK4">
+            <v>54424</v>
+          </cell>
+          <cell r="AL4">
+            <v>54789</v>
+          </cell>
+          <cell r="AM4">
+            <v>55154</v>
+          </cell>
+          <cell r="AN4">
+            <v>55519</v>
+          </cell>
+          <cell r="AO4">
+            <v>55885</v>
+          </cell>
+          <cell r="AP4">
+            <v>56250</v>
+          </cell>
+          <cell r="AQ4">
+            <v>56615</v>
+          </cell>
+          <cell r="AR4">
+            <v>56980</v>
+          </cell>
+          <cell r="AS4">
+            <v>57346</v>
+          </cell>
+          <cell r="AT4">
+            <v>57711</v>
+          </cell>
+          <cell r="AU4">
+            <v>58076</v>
+          </cell>
+          <cell r="AV4">
+            <v>58441</v>
+          </cell>
+          <cell r="AW4">
+            <v>58807</v>
+          </cell>
+          <cell r="AX4">
+            <v>59172</v>
+          </cell>
+          <cell r="AY4">
+            <v>59537</v>
+          </cell>
+          <cell r="AZ4">
+            <v>59902</v>
+          </cell>
+          <cell r="BA4">
+            <v>60268</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
-            <v>-0.1266072864198553</v>
+            <v>-1.3806021979057337</v>
           </cell>
           <cell r="D5">
-            <v>-0.25917392506271675</v>
+            <v>-1.7480486286687191</v>
           </cell>
           <cell r="E5">
-            <v>-0.40326000639545612</v>
+            <v>-2.0891661472786871</v>
           </cell>
           <cell r="F5">
-            <v>-0.55398882267881921</v>
+            <v>-2.3845793038393404</v>
           </cell>
           <cell r="G5">
-            <v>-0.70753521544256737</v>
+            <v>-2.641080340774693</v>
           </cell>
           <cell r="H5">
-            <v>-0.86109377713811108</v>
+            <v>-2.8674419026982645</v>
           </cell>
           <cell r="I5">
-            <v>-1.0144740729668866</v>
+            <v>-3.0732049106733994</v>
           </cell>
           <cell r="J5">
-            <v>-1.1647558849598894</v>
+            <v>-3.2620496645927366</v>
           </cell>
           <cell r="K5">
-            <v>-1.3108699732437334</v>
+            <v>-3.4382447698241725</v>
           </cell>
           <cell r="L5">
-            <v>-1.4521609586762518</v>
+            <v>-3.6053091816805383</v>
           </cell>
           <cell r="M5">
-            <v>-1.5879614421541621</v>
+            <v>-3.8605332841323614</v>
           </cell>
           <cell r="N5">
-            <v>-1.7246794912863739</v>
+            <v>-3.9729931402567087</v>
           </cell>
           <cell r="O5">
-            <v>-1.856728984472833</v>
+            <v>-4.0730645930684206</v>
           </cell>
           <cell r="P5">
-            <v>-1.9840005510711523</v>
+            <v>-4.1612842658112159</v>
           </cell>
           <cell r="Q5">
-            <v>-2.1064153683655107</v>
+            <v>-4.2405890614810922</v>
           </cell>
           <cell r="R5">
-            <v>-2.2240101557918446</v>
+            <v>-4.3137536103815766</v>
           </cell>
           <cell r="S5">
-            <v>-2.3427369804605025</v>
+            <v>-4.3878096041695898</v>
           </cell>
           <cell r="T5">
-            <v>-2.4576642800835713</v>
+            <v>-4.4611063157367408</v>
           </cell>
           <cell r="U5">
-            <v>-2.5689675345346386</v>
+            <v>-4.5351085377838496</v>
           </cell>
           <cell r="V5">
-            <v>-2.6767820412278209</v>
+            <v>-4.6108494006062202</v>
           </cell>
           <cell r="W5">
-            <v>-2.7815086689841229</v>
+            <v>-4.6892738198556883</v>
           </cell>
           <cell r="X5">
-            <v>-2.8827773151122837</v>
+            <v>-4.7702100401025511</v>
           </cell>
           <cell r="Y5">
-            <v>-2.9810370857266899</v>
+            <v>-4.8541150572132157</v>
           </cell>
           <cell r="Z5">
-            <v>-3.0765609291796503</v>
+            <v>-4.9410902134095718</v>
           </cell>
           <cell r="AA5">
-            <v>-3.1696101481516137</v>
+            <v>-5.0310152897432463</v>
           </cell>
           <cell r="AB5">
-            <v>-3.261048090505636</v>
+            <v>-5.1240634534562846</v>
           </cell>
           <cell r="AC5">
-            <v>-3.3479270837039277</v>
+            <v>-5.2170075163591401</v>
           </cell>
           <cell r="AD5">
-            <v>-3.43266459642948</v>
+            <v>-5.3111987688361122</v>
           </cell>
           <cell r="AE5">
-            <v>-3.5156542306031047</v>
+            <v>-5.4064971725801936</v>
           </cell>
           <cell r="AF5">
-            <v>-3.5972365891299485</v>
+            <v>-5.5027429449865277</v>
           </cell>
           <cell r="AG5">
-            <v>-3.677661276628974</v>
+            <v>-5.5997344016054162</v>
           </cell>
           <cell r="AH5">
-            <v>-3.7560475373298097</v>
+            <v>-5.6961288349583583</v>
           </cell>
           <cell r="AI5">
-            <v>-3.8333996431981987</v>
+            <v>-5.7925701399403451</v>
           </cell>
           <cell r="AJ5">
-            <v>-3.9097743338236013</v>
+            <v>-5.8889061572018235</v>
           </cell>
           <cell r="AK5">
-            <v>-3.9852007191780725</v>
+            <v>-5.9850274064450755</v>
           </cell>
           <cell r="AL5">
-            <v>-4.0596735508986797</v>
+            <v>-6.0808439463491348</v>
           </cell>
           <cell r="AM5">
-            <v>-4.1246932839789423</v>
+            <v>-6.1664061587992425</v>
           </cell>
           <cell r="AN5">
-            <v>-4.1875993547512707</v>
+            <v>-6.24937237998261</v>
           </cell>
           <cell r="AO5">
-            <v>-4.2484618386982138</v>
+            <v>-6.3301235386888592</v>
           </cell>
           <cell r="AP5">
-            <v>-4.3075432912364491</v>
+            <v>-6.4092469543638781</v>
           </cell>
           <cell r="AQ5">
-            <v>-4.3651236796108943</v>
+            <v>-6.487227670656404</v>
           </cell>
           <cell r="AR5">
-            <v>-4.4201448651320803</v>
+            <v>-6.5628351790368082</v>
           </cell>
           <cell r="AS5">
-            <v>-4.4738996919088558</v>
+            <v>-6.6375475313916299</v>
           </cell>
           <cell r="AT5">
-            <v>-4.5265541607199982</v>
+            <v>-6.7116454172487572</v>
           </cell>
           <cell r="AU5">
-            <v>-4.5781799152661673</v>
+            <v>-6.7853971166916498</v>
           </cell>
           <cell r="AV5">
-            <v>-4.6288400899773823</v>
+            <v>-6.859029758116808</v>
           </cell>
           <cell r="AW5">
-            <v>-4.6744839222177319</v>
+            <v>-6.9274087709707661</v>
           </cell>
           <cell r="AX5">
-            <v>-4.7186985694255945</v>
+            <v>-6.9947916420658558</v>
           </cell>
           <cell r="AY5">
-            <v>-4.7616235314381417</v>
+            <v>-7.0616110227255451</v>
           </cell>
           <cell r="AZ5">
-            <v>-4.8034529350900357</v>
+            <v>-7.1283018366647184</v>
           </cell>
           <cell r="BA5">
-            <v>-4.8443625976066667</v>
-          </cell>
-          <cell r="BB5">
-            <v>-4.8820978767775909</v>
-          </cell>
-          <cell r="BC5">
-            <v>-4.9188573097843076</v>
-          </cell>
-          <cell r="BD5">
-            <v>-4.954800489313838</v>
-          </cell>
-          <cell r="BE5">
-            <v>-4.9901043179792381</v>
-          </cell>
-          <cell r="BF5">
-            <v>-5.0249201356903477</v>
+            <v>-7.1951879397782914</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Données"/>
+      <sheetName val="Gr Macro"/>
+      <sheetName val="Gr inflation"/>
+      <sheetName val="Gr émissions"/>
+      <sheetName val="Gr conso éner"/>
+      <sheetName val="GR macro ener"/>
+      <sheetName val="Gr éner prim"/>
+      <sheetName val="BUIL (class,base)"/>
+      <sheetName val="BUIL (class,shock)"/>
+      <sheetName val="Auto (class,base)"/>
+      <sheetName val="Auto (class,shock)"/>
+      <sheetName val="Auto (ener,shock)"/>
+      <sheetName val="Auto (ener,base)"/>
+      <sheetName val="Employment"/>
+      <sheetName val="Investment"/>
+      <sheetName val="Firms' emissions"/>
+      <sheetName val="Capital intensity"/>
+      <sheetName val="Energy intensity"/>
+      <sheetName val="Gr VA secteurs (% dev)"/>
+      <sheetName val="Gr VA secteurs (% share)"/>
+      <sheetName val="Gr Y secteurs (% dev)"/>
+      <sheetName val="Gr Y secteurs (% share)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="C5">
+            <v>-1.3878691631188045</v>
+          </cell>
+          <cell r="D5">
+            <v>-1.7559281802439597</v>
+          </cell>
+          <cell r="E5">
+            <v>-2.0978964251628707</v>
+          </cell>
+          <cell r="F5">
+            <v>-2.3943565545859302</v>
+          </cell>
+          <cell r="G5">
+            <v>-2.6519237112783922</v>
+          </cell>
+          <cell r="H5">
+            <v>-2.8791977291766524</v>
+          </cell>
+          <cell r="I5">
+            <v>-3.0856349330678157</v>
+          </cell>
+          <cell r="J5">
+            <v>-3.2749100713291068</v>
+          </cell>
+          <cell r="K5">
+            <v>-3.4513576987399319</v>
+          </cell>
+          <cell r="L5">
+            <v>-3.6186215870805505</v>
+          </cell>
+          <cell r="M5">
+            <v>-3.8740905187216068</v>
+          </cell>
+          <cell r="N5">
+            <v>-3.9869778110010246</v>
+          </cell>
+          <cell r="O5">
+            <v>-4.0876115109099391</v>
+          </cell>
+          <cell r="P5">
+            <v>-4.1764905258227518</v>
+          </cell>
+          <cell r="Q5">
+            <v>-4.2564986174724044</v>
+          </cell>
+          <cell r="R5">
+            <v>-4.3303613971335526</v>
+          </cell>
+          <cell r="S5">
+            <v>-4.4050947454435381</v>
+          </cell>
+          <cell r="T5">
+            <v>-4.4790098408092671</v>
+          </cell>
+          <cell r="U5">
+            <v>-4.5535606178811356</v>
+          </cell>
+          <cell r="V5">
+            <v>-4.6297766233334041</v>
+          </cell>
+          <cell r="W5">
+            <v>-4.7086163761970727</v>
+          </cell>
+          <cell r="X5">
+            <v>-4.7898956513363284</v>
+          </cell>
+          <cell r="Y5">
+            <v>-4.8740905676174284</v>
+          </cell>
+          <cell r="Z5">
+            <v>-4.9613142198050468</v>
+          </cell>
+          <cell r="AA5">
+            <v>-5.0514570982640006</v>
+          </cell>
+          <cell r="AB5">
+            <v>-5.1447338143938204</v>
+          </cell>
+          <cell r="AC5">
+            <v>-5.2378674530835774</v>
+          </cell>
+          <cell r="AD5">
+            <v>-5.332236485481479</v>
+          </cell>
+          <cell r="AE5">
+            <v>-5.4277070818575357</v>
+          </cell>
+          <cell r="AF5">
+            <v>-5.5241238806707837</v>
+          </cell>
+          <cell r="AG5">
+            <v>-5.6212870882486277</v>
+          </cell>
+          <cell r="AH5">
+            <v>-5.7178485260679039</v>
+          </cell>
+          <cell r="AI5">
+            <v>-5.8144543086482319</v>
+          </cell>
+          <cell r="AJ5">
+            <v>-5.9109497872461558</v>
+          </cell>
+          <cell r="AK5">
+            <v>-6.0072231699979</v>
+          </cell>
+          <cell r="AL5">
+            <v>-6.1031818886015721</v>
+          </cell>
+          <cell r="AM5">
+            <v>-6.1888335406893091</v>
+          </cell>
+          <cell r="AN5">
+            <v>-6.2718617874111597</v>
+          </cell>
+          <cell r="AO5">
+            <v>-6.3526479659515083</v>
+          </cell>
+          <cell r="AP5">
+            <v>-6.431783817156111</v>
+          </cell>
+          <cell r="AQ5">
+            <v>-6.5097582722041247</v>
+          </cell>
+          <cell r="AR5">
+            <v>-6.5853359230707564</v>
+          </cell>
+          <cell r="AS5">
+            <v>-6.6600018684073614</v>
+          </cell>
+          <cell r="AT5">
+            <v>-6.7340376702999087</v>
+          </cell>
+          <cell r="AU5">
+            <v>-6.8077123355999802</v>
+          </cell>
+          <cell r="AV5">
+            <v>-6.8812529999116245</v>
+          </cell>
+          <cell r="AW5">
+            <v>-6.949499281721061</v>
+          </cell>
+          <cell r="AX5">
+            <v>-7.0167271114814467</v>
+          </cell>
+          <cell r="AY5">
+            <v>-7.0833702468528825</v>
+          </cell>
+          <cell r="AZ5">
+            <v>-7.1498659147384398</v>
+          </cell>
+          <cell r="BA5">
+            <v>-7.2165396597219651</v>
           </cell>
         </row>
       </sheetData>
@@ -3174,1836 +3573,2099 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BE9"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
-        <f>[1]Données!C4</f>
+        <f>[3]Données!C4</f>
         <v>42005</v>
       </c>
       <c r="C1" s="1">
-        <f>[1]Données!D4</f>
+        <f>[3]Données!D4</f>
         <v>42370</v>
       </c>
       <c r="D1" s="1">
-        <f>[1]Données!E4</f>
+        <f>[3]Données!E4</f>
         <v>42736</v>
       </c>
       <c r="E1" s="1">
-        <f>[1]Données!F4</f>
+        <f>[3]Données!F4</f>
         <v>43101</v>
       </c>
       <c r="F1" s="1">
-        <f>[1]Données!G4</f>
+        <f>[3]Données!G4</f>
         <v>43466</v>
       </c>
       <c r="G1" s="1">
-        <f>[1]Données!H4</f>
+        <f>[3]Données!H4</f>
         <v>43831</v>
       </c>
       <c r="H1" s="1">
-        <f>[1]Données!I4</f>
+        <f>[3]Données!I4</f>
         <v>44197</v>
       </c>
       <c r="I1" s="1">
-        <f>[1]Données!J4</f>
+        <f>[3]Données!J4</f>
         <v>44562</v>
       </c>
       <c r="J1" s="1">
-        <f>[1]Données!K4</f>
+        <f>[3]Données!K4</f>
         <v>44927</v>
       </c>
       <c r="K1" s="1">
-        <f>[1]Données!L4</f>
+        <f>[3]Données!L4</f>
         <v>45292</v>
       </c>
       <c r="L1" s="1">
-        <f>[1]Données!M4</f>
+        <f>[3]Données!M4</f>
         <v>45658</v>
       </c>
       <c r="M1" s="1">
-        <f>[1]Données!N4</f>
+        <f>[3]Données!N4</f>
         <v>46023</v>
       </c>
       <c r="N1" s="1">
-        <f>[1]Données!O4</f>
+        <f>[3]Données!O4</f>
         <v>46388</v>
       </c>
       <c r="O1" s="1">
-        <f>[1]Données!P4</f>
+        <f>[3]Données!P4</f>
         <v>46753</v>
       </c>
       <c r="P1" s="1">
-        <f>[1]Données!Q4</f>
+        <f>[3]Données!Q4</f>
         <v>47119</v>
       </c>
       <c r="Q1" s="1">
-        <f>[1]Données!R4</f>
+        <f>[3]Données!R4</f>
         <v>47484</v>
       </c>
       <c r="R1" s="1">
-        <f>[1]Données!S4</f>
+        <f>[3]Données!S4</f>
         <v>47849</v>
       </c>
       <c r="S1" s="1">
-        <f>[1]Données!T4</f>
+        <f>[3]Données!T4</f>
         <v>48214</v>
       </c>
       <c r="T1" s="1">
-        <f>[1]Données!U4</f>
+        <f>[3]Données!U4</f>
         <v>48580</v>
       </c>
       <c r="U1" s="1">
-        <f>[1]Données!V4</f>
+        <f>[3]Données!V4</f>
         <v>48945</v>
       </c>
       <c r="V1" s="1">
-        <f>[1]Données!W4</f>
+        <f>[3]Données!W4</f>
         <v>49310</v>
       </c>
       <c r="W1" s="1">
-        <f>[1]Données!X4</f>
+        <f>[3]Données!X4</f>
         <v>49675</v>
       </c>
       <c r="X1" s="1">
-        <f>[1]Données!Y4</f>
+        <f>[3]Données!Y4</f>
         <v>50041</v>
       </c>
       <c r="Y1" s="1">
-        <f>[1]Données!Z4</f>
+        <f>[3]Données!Z4</f>
         <v>50406</v>
       </c>
       <c r="Z1" s="1">
-        <f>[1]Données!AA4</f>
+        <f>[3]Données!AA4</f>
         <v>50771</v>
       </c>
       <c r="AA1" s="1">
-        <f>[1]Données!AB4</f>
+        <f>[3]Données!AB4</f>
         <v>51136</v>
       </c>
       <c r="AB1" s="1">
-        <f>[1]Données!AC4</f>
+        <f>[3]Données!AC4</f>
         <v>51502</v>
       </c>
       <c r="AC1" s="1">
-        <f>[1]Données!AD4</f>
+        <f>[3]Données!AD4</f>
         <v>51867</v>
       </c>
       <c r="AD1" s="1">
-        <f>[1]Données!AE4</f>
+        <f>[3]Données!AE4</f>
         <v>52232</v>
       </c>
       <c r="AE1" s="1">
-        <f>[1]Données!AF4</f>
+        <f>[3]Données!AF4</f>
         <v>52597</v>
       </c>
       <c r="AF1" s="1">
-        <f>[1]Données!AG4</f>
+        <f>[3]Données!AG4</f>
         <v>52963</v>
       </c>
       <c r="AG1" s="1">
-        <f>[1]Données!AH4</f>
+        <f>[3]Données!AH4</f>
         <v>53328</v>
       </c>
       <c r="AH1" s="1">
-        <f>[1]Données!AI4</f>
+        <f>[3]Données!AI4</f>
         <v>53693</v>
       </c>
       <c r="AI1" s="1">
-        <f>[1]Données!AJ4</f>
+        <f>[3]Données!AJ4</f>
         <v>54058</v>
       </c>
       <c r="AJ1" s="1">
-        <f>[1]Données!AK4</f>
+        <f>[3]Données!AK4</f>
         <v>54424</v>
       </c>
       <c r="AK1" s="1">
-        <f>[1]Données!AL4</f>
+        <f>[3]Données!AL4</f>
         <v>54789</v>
       </c>
       <c r="AL1" s="1">
-        <f>[1]Données!AM4</f>
+        <f>[3]Données!AM4</f>
         <v>55154</v>
       </c>
       <c r="AM1" s="1">
-        <f>[1]Données!AN4</f>
+        <f>[3]Données!AN4</f>
         <v>55519</v>
       </c>
       <c r="AN1" s="1">
-        <f>[1]Données!AO4</f>
+        <f>[3]Données!AO4</f>
         <v>55885</v>
       </c>
       <c r="AO1" s="1">
-        <f>[1]Données!AP4</f>
+        <f>[3]Données!AP4</f>
         <v>56250</v>
       </c>
       <c r="AP1" s="1">
-        <f>[1]Données!AQ4</f>
+        <f>[3]Données!AQ4</f>
         <v>56615</v>
       </c>
       <c r="AQ1" s="1">
-        <f>[1]Données!AR4</f>
+        <f>[3]Données!AR4</f>
         <v>56980</v>
       </c>
       <c r="AR1" s="1">
-        <f>[1]Données!AS4</f>
+        <f>[3]Données!AS4</f>
         <v>57346</v>
       </c>
       <c r="AS1" s="1">
-        <f>[1]Données!AT4</f>
+        <f>[3]Données!AT4</f>
         <v>57711</v>
       </c>
       <c r="AT1" s="1">
-        <f>[1]Données!AU4</f>
+        <f>[3]Données!AU4</f>
         <v>58076</v>
       </c>
       <c r="AU1" s="1">
-        <f>[1]Données!AV4</f>
+        <f>[3]Données!AV4</f>
         <v>58441</v>
       </c>
       <c r="AV1" s="1">
-        <f>[1]Données!AW4</f>
+        <f>[3]Données!AW4</f>
         <v>58807</v>
       </c>
       <c r="AW1" s="1">
-        <f>[1]Données!AX4</f>
+        <f>[3]Données!AX4</f>
         <v>59172</v>
       </c>
       <c r="AX1" s="1">
-        <f>[1]Données!AY4</f>
+        <f>[3]Données!AY4</f>
         <v>59537</v>
       </c>
       <c r="AY1" s="1">
-        <f>[1]Données!AZ4</f>
+        <f>[3]Données!AZ4</f>
         <v>59902</v>
       </c>
       <c r="AZ1" s="1">
-        <f>[1]Données!BA4</f>
+        <f>[3]Données!BA4</f>
         <v>60268</v>
       </c>
-      <c r="BA1" s="1">
-        <f>[1]Données!BB4</f>
-        <v>60633</v>
-      </c>
-      <c r="BB1" s="1">
-        <f>[1]Données!BC4</f>
-        <v>60998</v>
-      </c>
-      <c r="BC1" s="1">
-        <f>[1]Données!BD4</f>
-        <v>61363</v>
-      </c>
-      <c r="BD1" s="1">
-        <f>[1]Données!BE4</f>
-        <v>61729</v>
-      </c>
-      <c r="BE1" s="1">
-        <f>[1]Données!BF4</f>
-        <v>62094</v>
-      </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
-        <f>([3]Données!C5)/100</f>
-        <v>-1.266072864198553E-3</v>
+        <f>(([1]Données!C5)/100)*-1</f>
+        <v>1.3538601712600906E-2</v>
       </c>
       <c r="C2" s="2">
-        <f>([3]Données!D5)/100</f>
-        <v>-2.5917392506271675E-3</v>
+        <f>(([1]Données!D5)/100)*-1</f>
+        <v>1.6912679139984843E-2</v>
       </c>
       <c r="D2" s="2">
-        <f>([3]Données!E5)/100</f>
-        <v>-4.0326000639545612E-3</v>
+        <f>(([1]Données!E5)/100)*-1</f>
+        <v>2.0115560050032899E-2</v>
       </c>
       <c r="E2" s="2">
-        <f>([3]Données!F5)/100</f>
-        <v>-5.5398882267881921E-3</v>
+        <f>(([1]Données!F5)/100)*-1</f>
+        <v>2.2943774039713705E-2</v>
       </c>
       <c r="F2" s="2">
-        <f>([3]Données!G5)/100</f>
-        <v>-7.0753521544256737E-3</v>
+        <f>(([1]Données!G5)/100)*-1</f>
+        <v>2.5425308096377663E-2</v>
       </c>
       <c r="G2" s="2">
-        <f>([3]Données!H5)/100</f>
-        <v>-8.6109377713811108E-3</v>
+        <f>(([1]Données!H5)/100)*-1</f>
+        <v>2.7611418605846372E-2</v>
       </c>
       <c r="H2" s="2">
-        <f>([3]Données!I5)/100</f>
-        <v>-1.0144740729668866E-2</v>
+        <f>(([1]Données!I5)/100)*-1</f>
+        <v>2.9576927112697438E-2</v>
       </c>
       <c r="I2" s="2">
-        <f>([3]Données!J5)/100</f>
-        <v>-1.1647558849598894E-2</v>
+        <f>(([1]Données!J5)/100)*-1</f>
+        <v>3.1353239073615535E-2</v>
       </c>
       <c r="J2" s="2">
-        <f>([3]Données!K5)/100</f>
-        <v>-1.3108699732437334E-2</v>
+        <f>(([1]Données!K5)/100)*-1</f>
+        <v>3.2985843392642766E-2</v>
       </c>
       <c r="K2" s="2">
-        <f>([3]Données!L5)/100</f>
-        <v>-1.4521609586762518E-2</v>
+        <f>(([1]Données!L5)/100)*-1</f>
+        <v>3.4516237501799885E-2</v>
       </c>
       <c r="L2" s="2">
-        <f>([3]Données!M5)/100</f>
-        <v>-1.5879614421541621E-2</v>
+        <f>(([1]Données!M5)/100)*-1</f>
+        <v>3.6927247035058564E-2</v>
       </c>
       <c r="M2" s="2">
-        <f>([3]Données!N5)/100</f>
-        <v>-1.7246794912863739E-2</v>
+        <f>(([1]Données!N5)/100)*-1</f>
+        <v>3.7901004681047845E-2</v>
       </c>
       <c r="N2" s="2">
-        <f>([3]Données!O5)/100</f>
-        <v>-1.856728984472833E-2</v>
+        <f>(([1]Données!O5)/100)*-1</f>
+        <v>3.8748605891280929E-2</v>
       </c>
       <c r="O2" s="2">
-        <f>([3]Données!P5)/100</f>
-        <v>-1.9840005510711523E-2</v>
+        <f>(([1]Données!P5)/100)*-1</f>
+        <v>3.9477051314678935E-2</v>
       </c>
       <c r="P2" s="2">
-        <f>([3]Données!Q5)/100</f>
-        <v>-2.1064153683655107E-2</v>
+        <f>(([1]Données!Q5)/100)*-1</f>
+        <v>4.0116488877360634E-2</v>
       </c>
       <c r="Q2" s="2">
-        <f>([3]Données!R5)/100</f>
-        <v>-2.2240101557918446E-2</v>
+        <f>(([1]Données!R5)/100)*-1</f>
+        <v>4.0694640941231978E-2</v>
       </c>
       <c r="R2" s="2">
-        <f>([3]Données!S5)/100</f>
-        <v>-2.3427369804605025E-2</v>
+        <f>(([1]Données!S5)/100)*-1</f>
+        <v>4.1277964002331198E-2</v>
       </c>
       <c r="S2" s="2">
-        <f>([3]Données!T5)/100</f>
-        <v>-2.4576642800835713E-2</v>
+        <f>(([1]Données!T5)/100)*-1</f>
+        <v>4.1849741026071745E-2</v>
       </c>
       <c r="T2" s="2">
-        <f>([3]Données!U5)/100</f>
-        <v>-2.5689675345346386E-2</v>
+        <f>(([1]Données!U5)/100)*-1</f>
+        <v>4.2425458296820991E-2</v>
       </c>
       <c r="U2" s="2">
-        <f>([3]Données!V5)/100</f>
-        <v>-2.6767820412278209E-2</v>
+        <f>(([1]Données!V5)/100)*-1</f>
+        <v>4.3016340742832782E-2</v>
       </c>
       <c r="V2" s="2">
-        <f>([3]Données!W5)/100</f>
-        <v>-2.7815086689841229E-2</v>
+        <f>(([1]Données!W5)/100)*-1</f>
+        <v>4.3633104309372284E-2</v>
       </c>
       <c r="W2" s="2">
-        <f>([3]Données!X5)/100</f>
-        <v>-2.8827773151122837E-2</v>
+        <f>(([1]Données!X5)/100)*-1</f>
+        <v>4.427314031618601E-2</v>
       </c>
       <c r="X2" s="2">
-        <f>([3]Données!Y5)/100</f>
-        <v>-2.9810370857266899E-2</v>
+        <f>(([1]Données!Y5)/100)*-1</f>
+        <v>4.4941592404026176E-2</v>
       </c>
       <c r="Y2" s="2">
-        <f>([3]Données!Z5)/100</f>
-        <v>-3.0765609291796503E-2</v>
+        <f>(([1]Données!Z5)/100)*-1</f>
+        <v>4.563947337910957E-2</v>
       </c>
       <c r="Z2" s="2">
-        <f>([3]Données!AA5)/100</f>
-        <v>-3.1696101481516137E-2</v>
+        <f>(([1]Données!AA5)/100)*-1</f>
+        <v>4.6365522950460585E-2</v>
       </c>
       <c r="AA2" s="2">
-        <f>([3]Données!AB5)/100</f>
-        <v>-3.261048090505636E-2</v>
+        <f>(([1]Données!AB5)/100)*-1</f>
+        <v>4.7123697653551948E-2</v>
       </c>
       <c r="AB2" s="2">
-        <f>([3]Données!AC5)/100</f>
-        <v>-3.3479270837039277E-2</v>
+        <f>(([1]Données!AC5)/100)*-1</f>
+        <v>4.788032119780028E-2</v>
       </c>
       <c r="AC2" s="2">
-        <f>([3]Données!AD5)/100</f>
-        <v>-3.43266459642948E-2</v>
+        <f>(([1]Données!AD5)/100)*-1</f>
+        <v>4.8649621572917197E-2</v>
       </c>
       <c r="AD2" s="2">
-        <f>([3]Données!AE5)/100</f>
-        <v>-3.5156542306031047E-2</v>
+        <f>(([1]Données!AE5)/100)*-1</f>
+        <v>4.9429610515789646E-2</v>
       </c>
       <c r="AE2" s="2">
-        <f>([3]Données!AF5)/100</f>
-        <v>-3.5972365891299485E-2</v>
+        <f>(([1]Données!AF5)/100)*-1</f>
+        <v>5.0218084317584018E-2</v>
       </c>
       <c r="AF2" s="2">
-        <f>([3]Données!AG5)/100</f>
-        <v>-3.677661276628974E-2</v>
+        <f>(([1]Données!AG5)/100)*-1</f>
+        <v>5.1012621214923663E-2</v>
       </c>
       <c r="AG2" s="2">
-        <f>([3]Données!AH5)/100</f>
-        <v>-3.7560475373298097E-2</v>
+        <f>(([1]Données!AH5)/100)*-1</f>
+        <v>5.1800471640880197E-2</v>
       </c>
       <c r="AH2" s="2">
-        <f>([3]Données!AI5)/100</f>
-        <v>-3.8333996431981987E-2</v>
+        <f>(([1]Données!AI5)/100)*-1</f>
+        <v>5.2587995224248063E-2</v>
       </c>
       <c r="AI2" s="2">
-        <f>([3]Données!AJ5)/100</f>
-        <v>-3.9097743338236013E-2</v>
+        <f>(([1]Données!AJ5)/100)*-1</f>
+        <v>5.337331162577863E-2</v>
       </c>
       <c r="AJ2" s="2">
-        <f>([3]Données!AK5)/100</f>
-        <v>-3.9852007191780725E-2</v>
+        <f>(([1]Données!AK5)/100)*-1</f>
+        <v>5.4154996240649018E-2</v>
       </c>
       <c r="AK2" s="2">
-        <f>([3]Données!AL5)/100</f>
-        <v>-4.0596735508986799E-2</v>
+        <f>(([1]Données!AL5)/100)*-1</f>
+        <v>5.4931913241978665E-2</v>
       </c>
       <c r="AL2" s="2">
-        <f>([3]Données!AM5)/100</f>
-        <v>-4.1246932839789426E-2</v>
+        <f>(([1]Données!AM5)/100)*-1</f>
+        <v>5.5612806592488247E-2</v>
       </c>
       <c r="AM2" s="2">
-        <f>([3]Données!AN5)/100</f>
-        <v>-4.1875993547512709E-2</v>
+        <f>(([1]Données!AN5)/100)*-1</f>
+        <v>5.6273572035804416E-2</v>
       </c>
       <c r="AN2" s="2">
-        <f>([3]Données!AO5)/100</f>
-        <v>-4.2484618386982136E-2</v>
+        <f>(([1]Données!AO5)/100)*-1</f>
+        <v>5.6914643529708646E-2</v>
       </c>
       <c r="AO2" s="2">
-        <f>([3]Données!AP5)/100</f>
-        <v>-4.3075432912364493E-2</v>
+        <f>(([1]Données!AP5)/100)*-1</f>
+        <v>5.753897634474104E-2</v>
       </c>
       <c r="AP2" s="2">
-        <f>([3]Données!AQ5)/100</f>
-        <v>-4.3651236796108946E-2</v>
+        <f>(([1]Données!AQ5)/100)*-1</f>
+        <v>5.8149801082812758E-2</v>
       </c>
       <c r="AQ2" s="2">
-        <f>([3]Données!AR5)/100</f>
-        <v>-4.42014486513208E-2</v>
+        <f>(([1]Données!AR5)/100)*-1</f>
+        <v>5.8735596987392939E-2</v>
       </c>
       <c r="AR2" s="2">
-        <f>([3]Données!AS5)/100</f>
-        <v>-4.4738996919088558E-2</v>
+        <f>(([1]Données!AS5)/100)*-1</f>
+        <v>5.9311343796265348E-2</v>
       </c>
       <c r="AS2" s="2">
-        <f>([3]Données!AT5)/100</f>
-        <v>-4.5265541607199984E-2</v>
+        <f>(([1]Données!AT5)/100)*-1</f>
+        <v>5.9879563848025723E-2</v>
       </c>
       <c r="AT2" s="2">
-        <f>([3]Données!AU5)/100</f>
-        <v>-4.5781799152661673E-2</v>
+        <f>(([1]Données!AU5)/100)*-1</f>
+        <v>6.0442828733665251E-2</v>
       </c>
       <c r="AU2" s="2">
-        <f>([3]Données!AV5)/100</f>
-        <v>-4.6288400899773825E-2</v>
+        <f>(([1]Données!AV5)/100)*-1</f>
+        <v>6.1003296850866917E-2</v>
       </c>
       <c r="AV2" s="2">
-        <f>([3]Données!AW5)/100</f>
-        <v>-4.6744839222177322E-2</v>
+        <f>(([1]Données!AW5)/100)*-1</f>
+        <v>6.1513652453118454E-2</v>
       </c>
       <c r="AW2" s="2">
-        <f>([3]Données!AX5)/100</f>
-        <v>-4.7186985694255945E-2</v>
+        <f>(([1]Données!AX5)/100)*-1</f>
+        <v>6.2016559531788203E-2</v>
       </c>
       <c r="AX2" s="2">
-        <f>([3]Données!AY5)/100</f>
-        <v>-4.7616235314381417E-2</v>
+        <f>(([1]Données!AY5)/100)*-1</f>
+        <v>6.251429610217496E-2</v>
       </c>
       <c r="AY2" s="2">
-        <f>([3]Données!AZ5)/100</f>
-        <v>-4.8034529350900357E-2</v>
-      </c>
-      <c r="AZ2" s="2">
-        <f>([3]Données!BA5)/100</f>
-        <v>-4.8443625976066669E-2</v>
-      </c>
-      <c r="BA2" s="2">
-        <f>([3]Données!BB5)/100</f>
-        <v>-4.8820978767775906E-2</v>
-      </c>
-      <c r="BB2" s="2">
-        <f>([3]Données!BC5)/100</f>
-        <v>-4.9188573097843073E-2</v>
-      </c>
-      <c r="BC2" s="2">
-        <f>([3]Données!BD5)/100</f>
-        <v>-4.9548004893138382E-2</v>
-      </c>
-      <c r="BD2" s="2">
-        <f>([3]Données!BE5)/100</f>
-        <v>-4.9901043179792381E-2</v>
-      </c>
-      <c r="BE2" s="2">
-        <f>([3]Données!BF5)/100</f>
-        <v>-5.0249201356903479E-2</v>
+        <f>(([1]Données!AZ5)/100)*-1</f>
+        <v>6.3009329761051225E-2</v>
+      </c>
+      <c r="AZ2" s="4">
+        <f>(([1]Données!BA5)/100)*-1</f>
+        <v>6.3503741189399388E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
-        <f>([2]Données!C5)/100</f>
-        <v>-1.275864688504269E-3</v>
+        <f>(([2]Données!C5)/100)*-1</f>
+        <v>1.3817003835391084E-2</v>
       </c>
       <c r="C3" s="2">
-        <f>([2]Données!D5)/100</f>
-        <v>-2.6198208840970683E-3</v>
+        <f>(([2]Données!D5)/100)*-1</f>
+        <v>1.743513173626321E-2</v>
       </c>
       <c r="D3" s="2">
-        <f>([2]Données!E5)/100</f>
-        <v>-4.0840254583445201E-3</v>
+        <f>(([2]Données!E5)/100)*-1</f>
+        <v>2.0810900271980293E-2</v>
       </c>
       <c r="E3" s="2">
-        <f>([2]Données!F5)/100</f>
-        <v>-5.6167237441321349E-3</v>
+        <f>(([2]Données!F5)/100)*-1</f>
+        <v>2.37482308328546E-2</v>
       </c>
       <c r="F3" s="2">
-        <f>([2]Données!G5)/100</f>
-        <v>-7.1784252676141413E-3</v>
+        <f>(([2]Données!G5)/100)*-1</f>
+        <v>2.6303621837913016E-2</v>
       </c>
       <c r="G3" s="2">
-        <f>([2]Données!H5)/100</f>
-        <v>-8.7411098414714727E-3</v>
+        <f>(([2]Données!H5)/100)*-1</f>
+        <v>2.8554745649720381E-2</v>
       </c>
       <c r="H3" s="2">
-        <f>([2]Données!I5)/100</f>
-        <v>-1.0303679133639498E-2</v>
+        <f>(([2]Données!I5)/100)*-1</f>
+        <v>3.0591714219359134E-2</v>
       </c>
       <c r="I3" s="2">
-        <f>([2]Données!J5)/100</f>
-        <v>-1.1837654600580172E-2</v>
+        <f>(([2]Données!J5)/100)*-1</f>
+        <v>3.2450478843843999E-2</v>
       </c>
       <c r="J3" s="2">
-        <f>([2]Données!K5)/100</f>
-        <v>-1.3332754883907727E-2</v>
+        <f>(([2]Données!K5)/100)*-1</f>
+        <v>3.4175766044356681E-2</v>
       </c>
       <c r="K3" s="2">
-        <f>([2]Données!L5)/100</f>
-        <v>-1.4782819429026373E-2</v>
+        <f>(([2]Données!L5)/100)*-1</f>
+        <v>3.5806058245103856E-2</v>
       </c>
       <c r="L3" s="2">
-        <f>([2]Données!M5)/100</f>
-        <v>-1.6180976725248319E-2</v>
+        <f>(([2]Données!M5)/100)*-1</f>
+        <v>3.8317865579032384E-2</v>
       </c>
       <c r="M3" s="2">
-        <f>([2]Données!N5)/100</f>
-        <v>-1.7591867069212119E-2</v>
+        <f>(([2]Données!N5)/100)*-1</f>
+        <v>3.9401504124790709E-2</v>
       </c>
       <c r="N3" s="2">
-        <f>([2]Données!O5)/100</f>
-        <v>-1.8959209800047061E-2</v>
+        <f>(([2]Données!O5)/100)*-1</f>
+        <v>4.0361895698596717E-2</v>
       </c>
       <c r="O3" s="2">
-        <f>([2]Données!P5)/100</f>
-        <v>-2.0281155419679231E-2</v>
+        <f>(([2]Données!P5)/100)*-1</f>
+        <v>4.1204463998199437E-2</v>
       </c>
       <c r="P3" s="2">
-        <f>([2]Données!Q5)/100</f>
-        <v>-2.1556312104193953E-2</v>
+        <f>(([2]Données!Q5)/100)*-1</f>
+        <v>4.1958141290400326E-2</v>
       </c>
       <c r="Q3" s="2">
-        <f>([2]Données!R5)/100</f>
-        <v>-2.2784775975364879E-2</v>
+        <f>(([2]Données!R5)/100)*-1</f>
+        <v>4.2649961126306819E-2</v>
       </c>
       <c r="R3" s="2">
-        <f>([2]Données!S5)/100</f>
-        <v>-2.4027251277211281E-2</v>
+        <f>(([2]Données!S5)/100)*-1</f>
+        <v>4.3348570228646688E-2</v>
       </c>
       <c r="S3" s="2">
-        <f>([2]Données!T5)/100</f>
-        <v>-2.5234476247418258E-2</v>
+        <f>(([2]Données!T5)/100)*-1</f>
+        <v>4.4036672055925541E-2</v>
       </c>
       <c r="T3" s="2">
-        <f>([2]Données!U5)/100</f>
-        <v>-2.6407784194327988E-2</v>
+        <f>(([2]Données!U5)/100)*-1</f>
+        <v>4.472892175080679E-2</v>
       </c>
       <c r="U3" s="2">
-        <f>([2]Données!V5)/100</f>
-        <v>-2.7548191309446413E-2</v>
+        <f>(([2]Données!V5)/100)*-1</f>
+        <v>4.5435752297462988E-2</v>
       </c>
       <c r="V3" s="2">
-        <f>([2]Données!W5)/100</f>
-        <v>-2.8659520035723696E-2</v>
+        <f>(([2]Données!W5)/100)*-1</f>
+        <v>4.6166841961263645E-2</v>
       </c>
       <c r="W3" s="2">
-        <f>([2]Données!X5)/100</f>
-        <v>-2.9738268166550785E-2</v>
+        <f>(([2]Données!X5)/100)*-1</f>
+        <v>4.6920146370500133E-2</v>
       </c>
       <c r="X3" s="2">
-        <f>([2]Données!Y5)/100</f>
-        <v>-3.0789076012565419E-2</v>
+        <f>(([2]Données!Y5)/100)*-1</f>
+        <v>4.7700386101506842E-2</v>
       </c>
       <c r="Y3" s="2">
-        <f>([2]Données!Z5)/100</f>
-        <v>-3.1814997477892737E-2</v>
+        <f>(([2]Données!Z5)/100)*-1</f>
+        <v>4.8508636134620635E-2</v>
       </c>
       <c r="Z3" s="2">
-        <f>([2]Données!AA5)/100</f>
-        <v>-3.2818891980439191E-2</v>
+        <f>(([2]Données!AA5)/100)*-1</f>
+        <v>4.9343774287709079E-2</v>
       </c>
       <c r="AA3" s="2">
-        <f>([2]Données!AB5)/100</f>
-        <v>-3.3809136706206777E-2</v>
+        <f>(([2]Données!AB5)/100)*-1</f>
+        <v>5.0208240339022048E-2</v>
       </c>
       <c r="AB3" s="2">
-        <f>([2]Données!AC5)/100</f>
-        <v>-3.4755760339276631E-2</v>
+        <f>(([2]Données!AC5)/100)*-1</f>
+        <v>5.1069629307100135E-2</v>
       </c>
       <c r="AC3" s="2">
-        <f>([2]Données!AD5)/100</f>
-        <v>-3.5682716517019597E-2</v>
+        <f>(([2]Données!AD5)/100)*-1</f>
+        <v>5.1941904606602529E-2</v>
       </c>
       <c r="AD3" s="2">
-        <f>([2]Données!AE5)/100</f>
-        <v>-3.6594084261149962E-2</v>
+        <f>(([2]Données!AE5)/100)*-1</f>
+        <v>5.2823596780353095E-2</v>
       </c>
       <c r="AE3" s="2">
-        <f>([2]Données!AF5)/100</f>
-        <v>-3.7493387642787868E-2</v>
+        <f>(([2]Données!AF5)/100)*-1</f>
+        <v>5.37130422710047E-2</v>
       </c>
       <c r="AF3" s="2">
-        <f>([2]Données!AG5)/100</f>
-        <v>-3.8383070790512841E-2</v>
+        <f>(([2]Données!AG5)/100)*-1</f>
+        <v>5.4608243916526966E-2</v>
       </c>
       <c r="AG3" s="2">
-        <f>([2]Données!AH5)/100</f>
-        <v>-3.925374462962794E-2</v>
+        <f>(([2]Données!AH5)/100)*-1</f>
+        <v>5.5496192249441023E-2</v>
       </c>
       <c r="AH3" s="2">
-        <f>([2]Données!AI5)/100</f>
-        <v>-4.0115268029533253E-2</v>
+        <f>(([2]Données!AI5)/100)*-1</f>
+        <v>5.6383436484206066E-2</v>
       </c>
       <c r="AI3" s="2">
-        <f>([2]Données!AJ5)/100</f>
-        <v>-4.0968235500818073E-2</v>
+        <f>(([2]Données!AJ5)/100)*-1</f>
+        <v>5.726834401942426E-2</v>
       </c>
       <c r="AJ3" s="2">
-        <f>([2]Données!AK5)/100</f>
-        <v>-4.1812981270396572E-2</v>
+        <f>(([2]Données!AK5)/100)*-1</f>
+        <v>5.8149718869707101E-2</v>
       </c>
       <c r="AK3" s="2">
-        <f>([2]Données!AL5)/100</f>
-        <v>-4.2649462202405071E-2</v>
+        <f>(([2]Données!AL5)/100)*-1</f>
+        <v>5.9026601997417154E-2</v>
       </c>
       <c r="AL3" s="2">
-        <f>([2]Données!AM5)/100</f>
-        <v>-4.3388519630629396E-2</v>
+        <f>(([2]Données!AM5)/100)*-1</f>
+        <v>5.9802895418140878E-2</v>
       </c>
       <c r="AM3" s="2">
-        <f>([2]Données!AN5)/100</f>
-        <v>-4.410371209477127E-2</v>
+        <f>(([2]Données!AN5)/100)*-1</f>
+        <v>6.0555320304058302E-2</v>
       </c>
       <c r="AN3" s="2">
-        <f>([2]Données!AO5)/100</f>
-        <v>-4.4797689763537034E-2</v>
+        <f>(([2]Données!AO5)/100)*-1</f>
+        <v>6.1285910820933938E-2</v>
       </c>
       <c r="AO3" s="2">
-        <f>([2]Données!AP5)/100</f>
-        <v>-4.5474597952689495E-2</v>
+        <f>(([2]Données!AP5)/100)*-1</f>
+        <v>6.1999209769188039E-2</v>
       </c>
       <c r="AP3" s="2">
-        <f>([2]Données!AQ5)/100</f>
-        <v>-4.6137835490854047E-2</v>
+        <f>(([2]Données!AQ5)/100)*-1</f>
+        <v>6.2699584064028979E-2</v>
       </c>
       <c r="AQ3" s="2">
-        <f>([2]Données!AR5)/100</f>
-        <v>-4.6776030368512418E-2</v>
+        <f>(([2]Données!AR5)/100)*-1</f>
+        <v>6.3375430839892166E-2</v>
       </c>
       <c r="AR3" s="2">
-        <f>([2]Données!AS5)/100</f>
-        <v>-4.7401737494745862E-2</v>
+        <f>(([2]Données!AS5)/100)*-1</f>
+        <v>6.4041984514666583E-2</v>
       </c>
       <c r="AS3" s="2">
-        <f>([2]Données!AT5)/100</f>
-        <v>-4.8016576056588607E-2</v>
+        <f>(([2]Données!AT5)/100)*-1</f>
+        <v>6.4702120871606761E-2</v>
       </c>
       <c r="AT3" s="2">
-        <f>([2]Données!AU5)/100</f>
-        <v>-4.8621312476183058E-2</v>
+        <f>(([2]Données!AU5)/100)*-1</f>
+        <v>6.5358501296639782E-2</v>
       </c>
       <c r="AU3" s="2">
-        <f>([2]Données!AV5)/100</f>
-        <v>-4.9216652637725018E-2</v>
+        <f>(([2]Données!AV5)/100)*-1</f>
+        <v>6.6013343336437047E-2</v>
       </c>
       <c r="AV3" s="2">
-        <f>([2]Données!AW5)/100</f>
-        <v>-4.9759699585566253E-2</v>
+        <f>(([2]Données!AW5)/100)*-1</f>
+        <v>6.6617208449575416E-2</v>
       </c>
       <c r="AW3" s="2">
-        <f>([2]Données!AX5)/100</f>
-        <v>-5.0286467068149987E-2</v>
+        <f>(([2]Données!AX5)/100)*-1</f>
+        <v>6.7212787141227692E-2</v>
       </c>
       <c r="AX3" s="2">
-        <f>([2]Données!AY5)/100</f>
-        <v>-5.0799686303287468E-2</v>
+        <f>(([2]Données!AY5)/100)*-1</f>
+        <v>6.7803179119039103E-2</v>
       </c>
       <c r="AY3" s="2">
-        <f>([2]Données!AZ5)/100</f>
-        <v>-5.1302394652285921E-2</v>
-      </c>
-      <c r="AZ3" s="2">
-        <f>([2]Données!BA5)/100</f>
-        <v>-5.1796864838473781E-2</v>
-      </c>
-      <c r="BA3" s="2">
-        <f>([2]Données!BB5)/100</f>
-        <v>-5.2258997260300359E-2</v>
-      </c>
-      <c r="BB3" s="2">
-        <f>([2]Données!BC5)/100</f>
-        <v>-5.2710637992699268E-2</v>
-      </c>
-      <c r="BC3" s="2">
-        <f>([2]Données!BD5)/100</f>
-        <v>-5.3153984919841586E-2</v>
-      </c>
-      <c r="BD3" s="2">
-        <f>([2]Données!BE5)/100</f>
-        <v>-5.3591318424884286E-2</v>
-      </c>
-      <c r="BE3" s="2">
-        <f>([2]Données!BF5)/100</f>
-        <v>-5.4024381173960023E-2</v>
+        <f>(([2]Données!AZ5)/100)*-1</f>
+        <v>6.8391735845303669E-2</v>
+      </c>
+      <c r="AZ3" s="4">
+        <f>(([2]Données!BA5)/100)*-1</f>
+        <v>6.8981230170323315E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <f>([4]Données!C5/100)*-1</f>
+        <v>1.3878691631188045E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <f>([4]Données!D5/100)*-1</f>
+        <v>1.7559281802439597E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <f>([4]Données!E5/100)*-1</f>
+        <v>2.0978964251628707E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <f>([4]Données!F5/100)*-1</f>
+        <v>2.3943565545859302E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <f>([4]Données!G5/100)*-1</f>
+        <v>2.6519237112783922E-2</v>
+      </c>
+      <c r="G4" s="2">
+        <f>([4]Données!H5/100)*-1</f>
+        <v>2.8791977291766524E-2</v>
+      </c>
+      <c r="H4" s="2">
+        <f>([4]Données!I5/100)*-1</f>
+        <v>3.0856349330678157E-2</v>
+      </c>
+      <c r="I4" s="2">
+        <f>([4]Données!J5/100)*-1</f>
+        <v>3.2749100713291068E-2</v>
+      </c>
+      <c r="J4" s="2">
+        <f>([4]Données!K5/100)*-1</f>
+        <v>3.4513576987399319E-2</v>
+      </c>
+      <c r="K4" s="2">
+        <f>([4]Données!L5/100)*-1</f>
+        <v>3.6186215870805505E-2</v>
+      </c>
+      <c r="L4" s="2">
+        <f>([4]Données!M5/100)*-1</f>
+        <v>3.8740905187216068E-2</v>
+      </c>
+      <c r="M4" s="2">
+        <f>([4]Données!N5/100)*-1</f>
+        <v>3.9869778110010246E-2</v>
+      </c>
+      <c r="N4" s="2">
+        <f>([4]Données!O5/100)*-1</f>
+        <v>4.0876115109099394E-2</v>
+      </c>
+      <c r="O4" s="2">
+        <f>([4]Données!P5/100)*-1</f>
+        <v>4.1764905258227521E-2</v>
+      </c>
+      <c r="P4" s="2">
+        <f>([4]Données!Q5/100)*-1</f>
+        <v>4.2564986174724047E-2</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>([4]Données!R5/100)*-1</f>
+        <v>4.3303613971335524E-2</v>
+      </c>
+      <c r="R4" s="2">
+        <f>([4]Données!S5/100)*-1</f>
+        <v>4.4050947454435378E-2</v>
+      </c>
+      <c r="S4" s="2">
+        <f>([4]Données!T5/100)*-1</f>
+        <v>4.4790098408092671E-2</v>
+      </c>
+      <c r="T4" s="2">
+        <f>([4]Données!U5/100)*-1</f>
+        <v>4.5535606178811354E-2</v>
+      </c>
+      <c r="U4" s="2">
+        <f>([4]Données!V5/100)*-1</f>
+        <v>4.6297766233334044E-2</v>
+      </c>
+      <c r="V4" s="2">
+        <f>([4]Données!W5/100)*-1</f>
+        <v>4.708616376197073E-2</v>
+      </c>
+      <c r="W4" s="2">
+        <f>([4]Données!X5/100)*-1</f>
+        <v>4.7898956513363282E-2</v>
+      </c>
+      <c r="X4" s="2">
+        <f>([4]Données!Y5/100)*-1</f>
+        <v>4.8740905676174284E-2</v>
+      </c>
+      <c r="Y4" s="2">
+        <f>([4]Données!Z5/100)*-1</f>
+        <v>4.9613142198050471E-2</v>
+      </c>
+      <c r="Z4" s="2">
+        <f>([4]Données!AA5/100)*-1</f>
+        <v>5.0514570982640006E-2</v>
+      </c>
+      <c r="AA4" s="2">
+        <f>([4]Données!AB5/100)*-1</f>
+        <v>5.1447338143938204E-2</v>
+      </c>
+      <c r="AB4" s="2">
+        <f>([4]Données!AC5/100)*-1</f>
+        <v>5.2378674530835771E-2</v>
+      </c>
+      <c r="AC4" s="2">
+        <f>([4]Données!AD5/100)*-1</f>
+        <v>5.3322364854814792E-2</v>
+      </c>
+      <c r="AD4" s="2">
+        <f>([4]Données!AE5/100)*-1</f>
+        <v>5.4277070818575357E-2</v>
+      </c>
+      <c r="AE4" s="2">
+        <f>([4]Données!AF5/100)*-1</f>
+        <v>5.5241238806707837E-2</v>
+      </c>
+      <c r="AF4" s="2">
+        <f>([4]Données!AG5/100)*-1</f>
+        <v>5.6212870882486277E-2</v>
+      </c>
+      <c r="AG4" s="2">
+        <f>([4]Données!AH5/100)*-1</f>
+        <v>5.7178485260679042E-2</v>
+      </c>
+      <c r="AH4" s="2">
+        <f>([4]Données!AI5/100)*-1</f>
+        <v>5.8144543086482321E-2</v>
+      </c>
+      <c r="AI4" s="2">
+        <f>([4]Données!AJ5/100)*-1</f>
+        <v>5.9109497872461558E-2</v>
+      </c>
+      <c r="AJ4" s="2">
+        <f>([4]Données!AK5/100)*-1</f>
+        <v>6.0072231699979002E-2</v>
+      </c>
+      <c r="AK4" s="2">
+        <f>([4]Données!AL5/100)*-1</f>
+        <v>6.1031818886015721E-2</v>
+      </c>
+      <c r="AL4" s="2">
+        <f>([4]Données!AM5/100)*-1</f>
+        <v>6.1888335406893091E-2</v>
+      </c>
+      <c r="AM4" s="2">
+        <f>([4]Données!AN5/100)*-1</f>
+        <v>6.2718617874111593E-2</v>
+      </c>
+      <c r="AN4" s="2">
+        <f>([4]Données!AO5/100)*-1</f>
+        <v>6.3526479659515078E-2</v>
+      </c>
+      <c r="AO4" s="2">
+        <f>([4]Données!AP5/100)*-1</f>
+        <v>6.4317838171561115E-2</v>
+      </c>
+      <c r="AP4" s="2">
+        <f>([4]Données!AQ5/100)*-1</f>
+        <v>6.5097582722041247E-2</v>
+      </c>
+      <c r="AQ4" s="2">
+        <f>([4]Données!AR5/100)*-1</f>
+        <v>6.5853359230707564E-2</v>
+      </c>
+      <c r="AR4" s="2">
+        <f>([4]Données!AS5/100)*-1</f>
+        <v>6.6600018684073614E-2</v>
+      </c>
+      <c r="AS4" s="2">
+        <f>([4]Données!AT5/100)*-1</f>
+        <v>6.7340376702999083E-2</v>
+      </c>
+      <c r="AT4" s="2">
+        <f>([4]Données!AU5/100)*-1</f>
+        <v>6.8077123355999802E-2</v>
+      </c>
+      <c r="AU4" s="2">
+        <f>([4]Données!AV5/100)*-1</f>
+        <v>6.8812529999116245E-2</v>
+      </c>
+      <c r="AV4" s="2">
+        <f>([4]Données!AW5/100)*-1</f>
+        <v>6.949499281721061E-2</v>
+      </c>
+      <c r="AW4" s="2">
+        <f>([4]Données!AX5/100)*-1</f>
+        <v>7.0167271114814467E-2</v>
+      </c>
+      <c r="AX4" s="2">
+        <f>([4]Données!AY5/100)*-1</f>
+        <v>7.0833702468528825E-2</v>
+      </c>
+      <c r="AY4" s="2">
+        <f>([4]Données!AZ5/100)*-1</f>
+        <v>7.1498659147384402E-2</v>
+      </c>
+      <c r="AZ4" s="4">
+        <f>([4]Données!BA5/100)*-1</f>
+        <v>7.2165396597219655E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2">
-        <f>([1]Données!C5)/100</f>
-        <v>-1.2787414322095181E-3</v>
-      </c>
-      <c r="C4" s="2">
-        <f>([1]Données!D5)/100</f>
-        <v>-2.627520487745616E-3</v>
-      </c>
-      <c r="D4" s="2">
-        <f>([1]Données!E5)/100</f>
-        <v>-4.0975543658698932E-3</v>
-      </c>
-      <c r="E4" s="2">
-        <f>([1]Données!F5)/100</f>
-        <v>-5.6365250060909089E-3</v>
-      </c>
-      <c r="F4" s="2">
-        <f>([1]Données!G5)/100</f>
-        <v>-7.2045448665278844E-3</v>
-      </c>
-      <c r="G4" s="2">
-        <f>([1]Données!H5)/100</f>
-        <v>-8.7731936854470449E-3</v>
-      </c>
-      <c r="H4" s="2">
-        <f>([1]Données!I5)/100</f>
-        <v>-1.0340634104150648E-2</v>
-      </c>
-      <c r="I4" s="2">
-        <f>([1]Données!J5)/100</f>
-        <v>-1.1877943720283057E-2</v>
-      </c>
-      <c r="J4" s="2">
-        <f>([1]Données!K5)/100</f>
-        <v>-1.3374989460507969E-2</v>
-      </c>
-      <c r="K4" s="2">
-        <f>([1]Données!L5)/100</f>
-        <v>-1.4825527401897576E-2</v>
-      </c>
-      <c r="L4" s="2">
-        <f>([1]Données!M5)/100</f>
-        <v>-1.6224007357031001E-2</v>
-      </c>
-      <c r="M4" s="2">
-        <f>([1]Données!N5)/100</f>
-        <v>-1.763498575991751E-2</v>
-      </c>
-      <c r="N4" s="2">
-        <f>([1]Données!O5)/100</f>
-        <v>-1.9002713223146284E-2</v>
-      </c>
-      <c r="O4" s="2">
-        <f>([1]Données!P5)/100</f>
-        <v>-2.0325545260460376E-2</v>
-      </c>
-      <c r="P4" s="2">
-        <f>([1]Données!Q5)/100</f>
-        <v>-2.1602243202948457E-2</v>
-      </c>
-      <c r="Q4" s="2">
-        <f>([1]Données!R5)/100</f>
-        <v>-2.2833019939127674E-2</v>
-      </c>
-      <c r="R4" s="2">
-        <f>([1]Données!S5)/100</f>
-        <v>-2.407868645435618E-2</v>
-      </c>
-      <c r="S4" s="2">
-        <f>([1]Données!T5)/100</f>
-        <v>-2.5290161115245069E-2</v>
-      </c>
-      <c r="T4" s="2">
-        <f>([1]Données!U5)/100</f>
-        <v>-2.646861847770321E-2</v>
-      </c>
-      <c r="U4" s="2">
-        <f>([1]Données!V5)/100</f>
-        <v>-2.761487660245654E-2</v>
-      </c>
-      <c r="V4" s="2">
-        <f>([1]Données!W5)/100</f>
-        <v>-2.8732305935390667E-2</v>
-      </c>
-      <c r="W4" s="2">
-        <f>([1]Données!X5)/100</f>
-        <v>-2.9817702166700655E-2</v>
-      </c>
-      <c r="X4" s="2">
-        <f>([1]Données!Y5)/100</f>
-        <v>-3.087535235602612E-2</v>
-      </c>
-      <c r="Y4" s="2">
-        <f>([1]Données!Z5)/100</f>
-        <v>-3.1908318588945495E-2</v>
-      </c>
-      <c r="Z4" s="2">
-        <f>([1]Données!AA5)/100</f>
-        <v>-3.2919675532686599E-2</v>
-      </c>
-      <c r="AA4" s="2">
-        <f>([1]Données!AB5)/100</f>
-        <v>-3.3917253014015603E-2</v>
-      </c>
-      <c r="AB4" s="2">
-        <f>([1]Données!AC5)/100</f>
-        <v>-3.4872332920302229E-2</v>
-      </c>
-      <c r="AC4" s="2">
-        <f>([1]Données!AD5)/100</f>
-        <v>-3.5808201526510874E-2</v>
-      </c>
-      <c r="AD4" s="2">
-        <f>([1]Données!AE5)/100</f>
-        <v>-3.672861999748056E-2</v>
-      </c>
-      <c r="AE4" s="2">
-        <f>([1]Données!AF5)/100</f>
-        <v>-3.7636781262668006E-2</v>
-      </c>
-      <c r="AF4" s="2">
-        <f>([1]Données!AG5)/100</f>
-        <v>-3.8534873095712463E-2</v>
-      </c>
-      <c r="AG4" s="2">
-        <f>([1]Données!AH5)/100</f>
-        <v>-3.9413333846629484E-2</v>
-      </c>
-      <c r="AH4" s="2">
-        <f>([1]Données!AI5)/100</f>
-        <v>-4.0281907250801385E-2</v>
-      </c>
-      <c r="AI4" s="2">
-        <f>([1]Données!AJ5)/100</f>
-        <v>-4.1141231116650578E-2</v>
-      </c>
-      <c r="AJ4" s="2">
-        <f>([1]Données!AK5)/100</f>
-        <v>-4.1991740378482634E-2</v>
-      </c>
-      <c r="AK4" s="2">
-        <f>([1]Données!AL5)/100</f>
-        <v>-4.2833519598868379E-2</v>
-      </c>
-      <c r="AL4" s="2">
-        <f>([1]Données!AM5)/100</f>
-        <v>-4.357727341636853E-2</v>
-      </c>
-      <c r="AM4" s="2">
-        <f>([1]Données!AN5)/100</f>
-        <v>-4.4296429806748749E-2</v>
-      </c>
-      <c r="AN4" s="2">
-        <f>([1]Données!AO5)/100</f>
-        <v>-4.499394110188315E-2</v>
-      </c>
-      <c r="AO4" s="2">
-        <f>([1]Données!AP5)/100</f>
-        <v>-4.5674230116184322E-2</v>
-      </c>
-      <c r="AP4" s="2">
-        <f>([1]Données!AQ5)/100</f>
-        <v>-4.6340903335793326E-2</v>
-      </c>
-      <c r="AQ4" s="2">
-        <f>([1]Données!AR5)/100</f>
-        <v>-4.6982709795025723E-2</v>
-      </c>
-      <c r="AR4" s="2">
-        <f>([1]Données!AS5)/100</f>
-        <v>-4.7612201858753478E-2</v>
-      </c>
-      <c r="AS4" s="2">
-        <f>([1]Données!AT5)/100</f>
-        <v>-4.8231068060331166E-2</v>
-      </c>
-      <c r="AT4" s="2">
-        <f>([1]Données!AU5)/100</f>
-        <v>-4.8840134298992692E-2</v>
-      </c>
-      <c r="AU4" s="2">
-        <f>([1]Données!AV5)/100</f>
-        <v>-4.944015606392127E-2</v>
-      </c>
-      <c r="AV4" s="2">
-        <f>([1]Données!AW5)/100</f>
-        <v>-4.9988268090100485E-2</v>
-      </c>
-      <c r="AW4" s="2">
-        <f>([1]Données!AX5)/100</f>
-        <v>-5.0520259684757034E-2</v>
-      </c>
-      <c r="AX4" s="2">
-        <f>([1]Données!AY5)/100</f>
-        <v>-5.1039003558730478E-2</v>
-      </c>
-      <c r="AY4" s="2">
-        <f>([1]Données!AZ5)/100</f>
-        <v>-5.1547680926669726E-2</v>
-      </c>
-      <c r="AZ4" s="2">
-        <f>([1]Données!BA5)/100</f>
-        <v>-5.2048677744221949E-2</v>
-      </c>
-      <c r="BA4" s="2">
-        <f>([1]Données!BB5)/100</f>
-        <v>-5.2517947323465923E-2</v>
-      </c>
-      <c r="BB4" s="2">
-        <f>([1]Données!BC5)/100</f>
-        <v>-5.297722555020612E-2</v>
-      </c>
-      <c r="BC4" s="2">
-        <f>([1]Données!BD5)/100</f>
-        <v>-5.342879541524425E-2</v>
-      </c>
-      <c r="BD4" s="2">
-        <f>([1]Données!BE5)/100</f>
-        <v>-5.3875013844754349E-2</v>
-      </c>
-      <c r="BE4" s="2">
-        <f>([1]Données!BF5)/100</f>
-        <v>-5.4317682313006606E-2</v>
+      <c r="B5" s="2">
+        <f>(([3]Données!C5)/100)*-1</f>
+        <v>1.3806021979057337E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <f>(([3]Données!D5)/100)*-1</f>
+        <v>1.7480486286687191E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <f>(([3]Données!E5)/100)*-1</f>
+        <v>2.0891661472786871E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <f>(([3]Données!F5)/100)*-1</f>
+        <v>2.3845793038393404E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <f>(([3]Données!G5)/100)*-1</f>
+        <v>2.641080340774693E-2</v>
+      </c>
+      <c r="G5" s="2">
+        <f>(([3]Données!H5)/100)*-1</f>
+        <v>2.8674419026982645E-2</v>
+      </c>
+      <c r="H5" s="2">
+        <f>(([3]Données!I5)/100)*-1</f>
+        <v>3.0732049106733994E-2</v>
+      </c>
+      <c r="I5" s="2">
+        <f>(([3]Données!J5)/100)*-1</f>
+        <v>3.2620496645927366E-2</v>
+      </c>
+      <c r="J5" s="2">
+        <f>(([3]Données!K5)/100)*-1</f>
+        <v>3.4382447698241725E-2</v>
+      </c>
+      <c r="K5" s="2">
+        <f>(([3]Données!L5)/100)*-1</f>
+        <v>3.6053091816805383E-2</v>
+      </c>
+      <c r="L5" s="2">
+        <f>(([3]Données!M5)/100)*-1</f>
+        <v>3.8605332841323614E-2</v>
+      </c>
+      <c r="M5" s="2">
+        <f>(([3]Données!N5)/100)*-1</f>
+        <v>3.9729931402567087E-2</v>
+      </c>
+      <c r="N5" s="2">
+        <f>(([3]Données!O5)/100)*-1</f>
+        <v>4.0730645930684206E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <f>(([3]Données!P5)/100)*-1</f>
+        <v>4.1612842658112159E-2</v>
+      </c>
+      <c r="P5" s="2">
+        <f>(([3]Données!Q5)/100)*-1</f>
+        <v>4.2405890614810919E-2</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>(([3]Données!R5)/100)*-1</f>
+        <v>4.3137536103815766E-2</v>
+      </c>
+      <c r="R5" s="2">
+        <f>(([3]Données!S5)/100)*-1</f>
+        <v>4.3878096041695895E-2</v>
+      </c>
+      <c r="S5" s="2">
+        <f>(([3]Données!T5)/100)*-1</f>
+        <v>4.461106315736741E-2</v>
+      </c>
+      <c r="T5" s="2">
+        <f>(([3]Données!U5)/100)*-1</f>
+        <v>4.5351085377838496E-2</v>
+      </c>
+      <c r="U5" s="2">
+        <f>(([3]Données!V5)/100)*-1</f>
+        <v>4.6108494006062199E-2</v>
+      </c>
+      <c r="V5" s="2">
+        <f>(([3]Données!W5)/100)*-1</f>
+        <v>4.6892738198556883E-2</v>
+      </c>
+      <c r="W5" s="2">
+        <f>(([3]Données!X5)/100)*-1</f>
+        <v>4.7702100401025509E-2</v>
+      </c>
+      <c r="X5" s="2">
+        <f>(([3]Données!Y5)/100)*-1</f>
+        <v>4.8541150572132159E-2</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>(([3]Données!Z5)/100)*-1</f>
+        <v>4.941090213409572E-2</v>
+      </c>
+      <c r="Z5" s="2">
+        <f>(([3]Données!AA5)/100)*-1</f>
+        <v>5.0310152897432465E-2</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>(([3]Données!AB5)/100)*-1</f>
+        <v>5.1240634534562846E-2</v>
+      </c>
+      <c r="AB5" s="2">
+        <f>(([3]Données!AC5)/100)*-1</f>
+        <v>5.2170075163591401E-2</v>
+      </c>
+      <c r="AC5" s="2">
+        <f>(([3]Données!AD5)/100)*-1</f>
+        <v>5.3111987688361124E-2</v>
+      </c>
+      <c r="AD5" s="2">
+        <f>(([3]Données!AE5)/100)*-1</f>
+        <v>5.4064971725801936E-2</v>
+      </c>
+      <c r="AE5" s="2">
+        <f>(([3]Données!AF5)/100)*-1</f>
+        <v>5.502742944986528E-2</v>
+      </c>
+      <c r="AF5" s="2">
+        <f>(([3]Données!AG5)/100)*-1</f>
+        <v>5.5997344016054162E-2</v>
+      </c>
+      <c r="AG5" s="2">
+        <f>(([3]Données!AH5)/100)*-1</f>
+        <v>5.6961288349583583E-2</v>
+      </c>
+      <c r="AH5" s="2">
+        <f>(([3]Données!AI5)/100)*-1</f>
+        <v>5.7925701399403451E-2</v>
+      </c>
+      <c r="AI5" s="2">
+        <f>(([3]Données!AJ5)/100)*-1</f>
+        <v>5.8889061572018238E-2</v>
+      </c>
+      <c r="AJ5" s="2">
+        <f>(([3]Données!AK5)/100)*-1</f>
+        <v>5.9850274064450752E-2</v>
+      </c>
+      <c r="AK5" s="2">
+        <f>(([3]Données!AL5)/100)*-1</f>
+        <v>6.0808439463491348E-2</v>
+      </c>
+      <c r="AL5" s="2">
+        <f>(([3]Données!AM5)/100)*-1</f>
+        <v>6.1664061587992425E-2</v>
+      </c>
+      <c r="AM5" s="2">
+        <f>(([3]Données!AN5)/100)*-1</f>
+        <v>6.2493723799826102E-2</v>
+      </c>
+      <c r="AN5" s="2">
+        <f>(([3]Données!AO5)/100)*-1</f>
+        <v>6.3301235386888588E-2</v>
+      </c>
+      <c r="AO5" s="2">
+        <f>(([3]Données!AP5)/100)*-1</f>
+        <v>6.4092469543638786E-2</v>
+      </c>
+      <c r="AP5" s="2">
+        <f>(([3]Données!AQ5)/100)*-1</f>
+        <v>6.4872276706564036E-2</v>
+      </c>
+      <c r="AQ5" s="2">
+        <f>(([3]Données!AR5)/100)*-1</f>
+        <v>6.5628351790368078E-2</v>
+      </c>
+      <c r="AR5" s="2">
+        <f>(([3]Données!AS5)/100)*-1</f>
+        <v>6.6375475313916299E-2</v>
+      </c>
+      <c r="AS5" s="2">
+        <f>(([3]Données!AT5)/100)*-1</f>
+        <v>6.7116454172487572E-2</v>
+      </c>
+      <c r="AT5" s="2">
+        <f>(([3]Données!AU5)/100)*-1</f>
+        <v>6.7853971166916494E-2</v>
+      </c>
+      <c r="AU5" s="2">
+        <f>(([3]Données!AV5)/100)*-1</f>
+        <v>6.859029758116808E-2</v>
+      </c>
+      <c r="AV5" s="2">
+        <f>(([3]Données!AW5)/100)*-1</f>
+        <v>6.9274087709707666E-2</v>
+      </c>
+      <c r="AW5" s="2">
+        <f>(([3]Données!AX5)/100)*-1</f>
+        <v>6.9947916420658562E-2</v>
+      </c>
+      <c r="AX5" s="2">
+        <f>(([3]Données!AY5)/100)*-1</f>
+        <v>7.0616110227255446E-2</v>
+      </c>
+      <c r="AY5" s="2">
+        <f>(([3]Données!AZ5)/100)*-1</f>
+        <v>7.1283018366647188E-2</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f>(([3]Données!BA5)/100)*-1</f>
+        <v>7.1951879397782914E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.35">
-      <c r="B6" s="1">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
         <f>B1</f>
         <v>42005</v>
       </c>
-      <c r="C6" s="1">
-        <f t="shared" ref="C6:BE6" si="0">C1</f>
+      <c r="C7" s="1">
+        <f t="shared" ref="C7:AZ7" si="0">C1</f>
         <v>42370</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>42736</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
         <v>43101</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>43466</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>43831</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>44197</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I7" s="1">
         <f t="shared" si="0"/>
         <v>44562</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J7" s="1">
         <f t="shared" si="0"/>
         <v>44927</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K7" s="1">
         <f t="shared" si="0"/>
         <v>45292</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L7" s="1">
         <f t="shared" si="0"/>
         <v>45658</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>46023</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N7" s="1">
         <f t="shared" si="0"/>
         <v>46388</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O7" s="1">
         <f t="shared" si="0"/>
         <v>46753</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P7" s="1">
         <f t="shared" si="0"/>
         <v>47119</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q7" s="1">
         <f t="shared" si="0"/>
         <v>47484</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R7" s="1">
         <f t="shared" si="0"/>
         <v>47849</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S7" s="1">
         <f t="shared" si="0"/>
         <v>48214</v>
       </c>
-      <c r="T6" s="1">
+      <c r="T7" s="1">
         <f t="shared" si="0"/>
         <v>48580</v>
       </c>
-      <c r="U6" s="1">
+      <c r="U7" s="1">
         <f t="shared" si="0"/>
         <v>48945</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V7" s="1">
         <f t="shared" si="0"/>
         <v>49310</v>
       </c>
-      <c r="W6" s="1">
+      <c r="W7" s="1">
         <f t="shared" si="0"/>
         <v>49675</v>
       </c>
-      <c r="X6" s="1">
+      <c r="X7" s="1">
         <f t="shared" si="0"/>
         <v>50041</v>
       </c>
-      <c r="Y6" s="1">
+      <c r="Y7" s="1">
         <f t="shared" si="0"/>
         <v>50406</v>
       </c>
-      <c r="Z6" s="1">
+      <c r="Z7" s="1">
         <f t="shared" si="0"/>
         <v>50771</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="AA7" s="1">
         <f t="shared" si="0"/>
         <v>51136</v>
       </c>
-      <c r="AB6" s="1">
+      <c r="AB7" s="1">
         <f t="shared" si="0"/>
         <v>51502</v>
       </c>
-      <c r="AC6" s="1">
+      <c r="AC7" s="1">
         <f t="shared" si="0"/>
         <v>51867</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AD7" s="1">
         <f t="shared" si="0"/>
         <v>52232</v>
       </c>
-      <c r="AE6" s="1">
+      <c r="AE7" s="1">
         <f t="shared" si="0"/>
         <v>52597</v>
       </c>
-      <c r="AF6" s="1">
+      <c r="AF7" s="1">
         <f t="shared" si="0"/>
         <v>52963</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AG7" s="1">
         <f t="shared" si="0"/>
         <v>53328</v>
       </c>
-      <c r="AH6" s="1">
+      <c r="AH7" s="1">
         <f t="shared" si="0"/>
         <v>53693</v>
       </c>
-      <c r="AI6" s="1">
+      <c r="AI7" s="1">
         <f t="shared" si="0"/>
         <v>54058</v>
       </c>
-      <c r="AJ6" s="1">
+      <c r="AJ7" s="1">
         <f t="shared" si="0"/>
         <v>54424</v>
       </c>
-      <c r="AK6" s="1">
+      <c r="AK7" s="1">
         <f t="shared" si="0"/>
         <v>54789</v>
       </c>
-      <c r="AL6" s="1">
+      <c r="AL7" s="1">
         <f t="shared" si="0"/>
         <v>55154</v>
       </c>
-      <c r="AM6" s="1">
+      <c r="AM7" s="1">
         <f t="shared" si="0"/>
         <v>55519</v>
       </c>
-      <c r="AN6" s="1">
+      <c r="AN7" s="1">
         <f t="shared" si="0"/>
         <v>55885</v>
       </c>
-      <c r="AO6" s="1">
+      <c r="AO7" s="1">
         <f t="shared" si="0"/>
         <v>56250</v>
       </c>
-      <c r="AP6" s="1">
+      <c r="AP7" s="1">
         <f t="shared" si="0"/>
         <v>56615</v>
       </c>
-      <c r="AQ6" s="1">
+      <c r="AQ7" s="1">
         <f t="shared" si="0"/>
         <v>56980</v>
       </c>
-      <c r="AR6" s="1">
+      <c r="AR7" s="1">
         <f t="shared" si="0"/>
         <v>57346</v>
       </c>
-      <c r="AS6" s="1">
+      <c r="AS7" s="1">
         <f t="shared" si="0"/>
         <v>57711</v>
       </c>
-      <c r="AT6" s="1">
+      <c r="AT7" s="1">
         <f t="shared" si="0"/>
         <v>58076</v>
       </c>
-      <c r="AU6" s="1">
+      <c r="AU7" s="1">
         <f t="shared" si="0"/>
         <v>58441</v>
       </c>
-      <c r="AV6" s="1">
+      <c r="AV7" s="1">
         <f t="shared" si="0"/>
         <v>58807</v>
       </c>
-      <c r="AW6" s="1">
+      <c r="AW7" s="1">
         <f t="shared" si="0"/>
         <v>59172</v>
       </c>
-      <c r="AX6" s="1">
+      <c r="AX7" s="1">
         <f t="shared" si="0"/>
         <v>59537</v>
       </c>
-      <c r="AY6" s="1">
+      <c r="AY7" s="1">
         <f t="shared" si="0"/>
         <v>59902</v>
       </c>
-      <c r="AZ6" s="1">
+      <c r="AZ7" s="1">
         <f t="shared" si="0"/>
         <v>60268</v>
       </c>
-      <c r="BA6" s="1">
-        <f t="shared" si="0"/>
-        <v>60633</v>
-      </c>
-      <c r="BB6" s="1">
-        <f t="shared" si="0"/>
-        <v>60998</v>
-      </c>
-      <c r="BC6" s="1">
-        <f t="shared" si="0"/>
-        <v>61363</v>
-      </c>
-      <c r="BD6" s="1">
-        <f t="shared" si="0"/>
-        <v>61729</v>
-      </c>
-      <c r="BE6" s="1">
-        <f t="shared" si="0"/>
-        <v>62094</v>
-      </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3">
-        <f>B2</f>
-        <v>-1.266072864198553E-3</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" ref="C7:BE7" si="1">C2</f>
-        <v>-2.5917392506271675E-3</v>
-      </c>
-      <c r="D7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.0326000639545612E-3</v>
-      </c>
-      <c r="E7" s="3">
-        <f t="shared" si="1"/>
-        <v>-5.5398882267881921E-3</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="1"/>
-        <v>-7.0753521544256737E-3</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>-8.6109377713811108E-3</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.0144740729668866E-2</v>
-      </c>
-      <c r="I7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.1647558849598894E-2</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.3108699732437334E-2</v>
-      </c>
-      <c r="K7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.4521609586762518E-2</v>
-      </c>
-      <c r="L7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.5879614421541621E-2</v>
-      </c>
-      <c r="M7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.7246794912863739E-2</v>
-      </c>
-      <c r="N7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.856728984472833E-2</v>
-      </c>
-      <c r="O7" s="3">
-        <f t="shared" si="1"/>
-        <v>-1.9840005510711523E-2</v>
-      </c>
-      <c r="P7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.1064153683655107E-2</v>
-      </c>
-      <c r="Q7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.2240101557918446E-2</v>
-      </c>
-      <c r="R7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.3427369804605025E-2</v>
-      </c>
-      <c r="S7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.4576642800835713E-2</v>
-      </c>
-      <c r="T7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.5689675345346386E-2</v>
-      </c>
-      <c r="U7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.6767820412278209E-2</v>
-      </c>
-      <c r="V7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.7815086689841229E-2</v>
-      </c>
-      <c r="W7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.8827773151122837E-2</v>
-      </c>
-      <c r="X7" s="3">
-        <f t="shared" si="1"/>
-        <v>-2.9810370857266899E-2</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.0765609291796503E-2</v>
-      </c>
-      <c r="Z7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.1696101481516137E-2</v>
-      </c>
-      <c r="AA7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.261048090505636E-2</v>
-      </c>
-      <c r="AB7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.3479270837039277E-2</v>
-      </c>
-      <c r="AC7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.43266459642948E-2</v>
-      </c>
-      <c r="AD7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.5156542306031047E-2</v>
-      </c>
-      <c r="AE7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.5972365891299485E-2</v>
-      </c>
-      <c r="AF7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.677661276628974E-2</v>
-      </c>
-      <c r="AG7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.7560475373298097E-2</v>
-      </c>
-      <c r="AH7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.8333996431981987E-2</v>
-      </c>
-      <c r="AI7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.9097743338236013E-2</v>
-      </c>
-      <c r="AJ7" s="3">
-        <f t="shared" si="1"/>
-        <v>-3.9852007191780725E-2</v>
-      </c>
-      <c r="AK7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.0596735508986799E-2</v>
-      </c>
-      <c r="AL7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.1246932839789426E-2</v>
-      </c>
-      <c r="AM7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.1875993547512709E-2</v>
-      </c>
-      <c r="AN7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.2484618386982136E-2</v>
-      </c>
-      <c r="AO7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.3075432912364493E-2</v>
-      </c>
-      <c r="AP7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.3651236796108946E-2</v>
-      </c>
-      <c r="AQ7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.42014486513208E-2</v>
-      </c>
-      <c r="AR7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.4738996919088558E-2</v>
-      </c>
-      <c r="AS7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.5265541607199984E-2</v>
-      </c>
-      <c r="AT7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.5781799152661673E-2</v>
-      </c>
-      <c r="AU7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.6288400899773825E-2</v>
-      </c>
-      <c r="AV7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.6744839222177322E-2</v>
-      </c>
-      <c r="AW7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.7186985694255945E-2</v>
-      </c>
-      <c r="AX7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.7616235314381417E-2</v>
-      </c>
-      <c r="AY7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.8034529350900357E-2</v>
-      </c>
-      <c r="AZ7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.8443625976066669E-2</v>
-      </c>
-      <c r="BA7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.8820978767775906E-2</v>
-      </c>
-      <c r="BB7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.9188573097843073E-2</v>
-      </c>
-      <c r="BC7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.9548004893138382E-2</v>
-      </c>
-      <c r="BD7" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.9901043179792381E-2</v>
-      </c>
-      <c r="BE7" s="3">
-        <f t="shared" si="1"/>
-        <v>-5.0249201356903479E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="3">
-        <f>B3-B2</f>
-        <v>-9.7918243057160126E-6</v>
+        <f>B2</f>
+        <v>1.3538601712600906E-2</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" ref="C8:BE8" si="2">C3-C2</f>
-        <v>-2.808163346990078E-5</v>
+        <f t="shared" ref="C8:AZ8" si="1">C2</f>
+        <v>1.6912679139984843E-2</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="2"/>
-        <v>-5.1425394389958967E-5</v>
+        <f t="shared" si="1"/>
+        <v>2.0115560050032899E-2</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="2"/>
-        <v>-7.6835517343942783E-5</v>
+        <f t="shared" si="1"/>
+        <v>2.2943774039713705E-2</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.0307311318846768E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.5425308096377663E-2</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.3017207009036191E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.7611418605846372E-2</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.5893840397063208E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.9576927112697438E-2</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.900957509812784E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.1353239073615535E-2</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.2405515147039257E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.2985843392642766E-2</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.6120984226385424E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.4516237501799885E-2</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.0136230370669814E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.6927247035058564E-2</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.4507215634838051E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.7901004681047845E-2</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.9191995531873136E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.8748605891280929E-2</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" si="2"/>
-        <v>-4.4114990896770845E-4</v>
+        <f t="shared" si="1"/>
+        <v>3.9477051314678935E-2</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="2"/>
-        <v>-4.9215842053884629E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.0116488877360634E-2</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="2"/>
-        <v>-5.4467441744643352E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.0694640941231978E-2</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="2"/>
-        <v>-5.9988147260625624E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.1277964002331198E-2</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="2"/>
-        <v>-6.5783344658254528E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.1849741026071745E-2</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="2"/>
-        <v>-7.1810884898160232E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.2425458296820991E-2</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" si="2"/>
-        <v>-7.8037089716820329E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.3016340742832782E-2</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" si="2"/>
-        <v>-8.444333458824671E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.3633104309372284E-2</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" si="2"/>
-        <v>-9.1049501542794786E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.427314031618601E-2</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="2"/>
-        <v>-9.7870515529852042E-4</v>
+        <f t="shared" si="1"/>
+        <v>4.4941592404026176E-2</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.049388186096234E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.563947337910957E-2</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.1227904989230542E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.6365522950460585E-2</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.1986558011504167E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.7123697653551948E-2</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.2764895022373546E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.788032119780028E-2</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.3560705527247974E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.8649621572917197E-2</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.437541955118915E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.9429610515789646E-2</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.5210217514883828E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.0218084317584018E-2</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.6064580242231008E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.1012621214923663E-2</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.6932692563298435E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.1800471640880197E-2</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.7812715975512664E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.2587995224248063E-2</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.8704921625820603E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.337331162577863E-2</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="2"/>
-        <v>-1.9609740786158472E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.4154996240649018E-2</v>
       </c>
       <c r="AK8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.052726693418272E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.4931913241978665E-2</v>
       </c>
       <c r="AL8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.1415867908399708E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.5612806592488247E-2</v>
       </c>
       <c r="AM8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.2277185472585614E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.6273572035804416E-2</v>
       </c>
       <c r="AN8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.3130713765548983E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.6914643529708646E-2</v>
       </c>
       <c r="AO8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.399165040325002E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.753897634474104E-2</v>
       </c>
       <c r="AP8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.4865986947451013E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.8149801082812758E-2</v>
       </c>
       <c r="AQ8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.574581717191618E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.8735596987392939E-2</v>
       </c>
       <c r="AR8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.6627405756573033E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.9311343796265348E-2</v>
       </c>
       <c r="AS8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.751034449388623E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.9879563848025723E-2</v>
       </c>
       <c r="AT8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.8395133235213851E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.0442828733665251E-2</v>
       </c>
       <c r="AU8" s="3">
-        <f t="shared" si="2"/>
-        <v>-2.928251737951193E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.1003296850866917E-2</v>
       </c>
       <c r="AV8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.0148603633889312E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.1513652453118454E-2</v>
       </c>
       <c r="AW8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.0994813738940419E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.2016559531788203E-2</v>
       </c>
       <c r="AX8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.1834509889060517E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.251429610217496E-2</v>
       </c>
       <c r="AY8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.2678653013855641E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.3009329761051225E-2</v>
       </c>
       <c r="AZ8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.3532388624071124E-3</v>
-      </c>
-      <c r="BA8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.4380184925244528E-3</v>
-      </c>
-      <c r="BB8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.5220648948561945E-3</v>
-      </c>
-      <c r="BC8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.6059800267032038E-3</v>
-      </c>
-      <c r="BD8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.6902752450919049E-3</v>
-      </c>
-      <c r="BE8" s="3">
-        <f t="shared" si="2"/>
-        <v>-3.775179817056544E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.3503741189399388E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="3">
+        <f>B3-B2</f>
+        <v>2.7840212279017784E-4</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" ref="C9:AZ9" si="2">C3-C2</f>
+        <v>5.224525962783666E-4</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="2"/>
+        <v>6.9534022194739364E-4</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="2"/>
+        <v>8.0445679314089524E-4</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="2"/>
+        <v>8.7831374153535258E-4</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="2"/>
+        <v>9.4332704387400934E-4</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0147871066616965E-3</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0972397702284642E-3</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.189922651713915E-3</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.289820743303971E-3</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3906185439738206E-3</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.5004994437428643E-3</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.6132898073157875E-3</v>
+      </c>
+      <c r="O9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.7274126835205017E-3</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8416524130396919E-3</v>
+      </c>
+      <c r="Q9" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9553201850748408E-3</v>
+      </c>
+      <c r="R9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.0706062263154898E-3</v>
+      </c>
+      <c r="S9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1869310298537961E-3</v>
+      </c>
+      <c r="T9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.303463453985799E-3</v>
+      </c>
+      <c r="U9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4194115546302061E-3</v>
+      </c>
+      <c r="V9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5337376518913615E-3</v>
+      </c>
+      <c r="W9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.647006054314123E-3</v>
+      </c>
+      <c r="X9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7587936974806659E-3</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.8691627555110649E-3</v>
+      </c>
+      <c r="Z9" s="3">
+        <f t="shared" si="2"/>
+        <v>2.9782513372484942E-3</v>
+      </c>
+      <c r="AA9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.0845426854701E-3</v>
+      </c>
+      <c r="AB9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.1893081092998557E-3</v>
+      </c>
+      <c r="AC9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.2922830336853323E-3</v>
+      </c>
+      <c r="AD9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.3939862645634492E-3</v>
+      </c>
+      <c r="AE9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.4949579534206826E-3</v>
+      </c>
+      <c r="AF9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.5956227016033029E-3</v>
+      </c>
+      <c r="AG9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.6957206085608263E-3</v>
+      </c>
+      <c r="AH9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.7954412599580031E-3</v>
+      </c>
+      <c r="AI9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.8950323936456296E-3</v>
+      </c>
+      <c r="AJ9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.9947226290580826E-3</v>
+      </c>
+      <c r="AK9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.0946887554384886E-3</v>
+      </c>
+      <c r="AL9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.1900888256526311E-3</v>
+      </c>
+      <c r="AM9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2817482682538863E-3</v>
+      </c>
+      <c r="AN9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.371267291225292E-3</v>
+      </c>
+      <c r="AO9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.4602334244469993E-3</v>
+      </c>
+      <c r="AP9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.5497829812162216E-3</v>
+      </c>
+      <c r="AQ9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.6398338524992269E-3</v>
+      </c>
+      <c r="AR9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.7306407184012356E-3</v>
+      </c>
+      <c r="AS9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.822557023581038E-3</v>
+      </c>
+      <c r="AT9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.915672562974531E-3</v>
+      </c>
+      <c r="AU9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.0100464855701299E-3</v>
+      </c>
+      <c r="AV9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.1035559964569613E-3</v>
+      </c>
+      <c r="AW9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.1962276094394896E-3</v>
+      </c>
+      <c r="AX9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.2888830168641432E-3</v>
+      </c>
+      <c r="AY9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.3824060842524446E-3</v>
+      </c>
+      <c r="AZ9" s="3">
+        <f t="shared" si="2"/>
+        <v>5.477488980923928E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3">
         <f>B4-B3</f>
-        <v>-2.8767437052490408E-6</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" ref="C9:BE9" si="3">C4-C3</f>
-        <v>-7.6996036485477148E-6</v>
-      </c>
-      <c r="D9" s="3">
+        <v>6.168779579696082E-5</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" ref="C10:AZ10" si="3">C4-C3</f>
+        <v>1.2415006617638724E-4</v>
+      </c>
+      <c r="D10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.3528907525373057E-5</v>
-      </c>
-      <c r="E9" s="3">
+        <v>1.6806397964841402E-4</v>
+      </c>
+      <c r="E10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.9801261958773964E-5</v>
-      </c>
-      <c r="F9" s="3">
+        <v>1.9533471300470229E-4</v>
+      </c>
+      <c r="F10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.6119598913743047E-5</v>
-      </c>
-      <c r="G9" s="3">
+        <v>2.1561527487090615E-4</v>
+      </c>
+      <c r="G10" s="3">
         <f t="shared" si="3"/>
-        <v>-3.2083843975572179E-5</v>
-      </c>
-      <c r="H9" s="3">
+        <v>2.3723164204614289E-4</v>
+      </c>
+      <c r="H10" s="3">
         <f t="shared" si="3"/>
-        <v>-3.6954970511149376E-5</v>
-      </c>
-      <c r="I9" s="3">
+        <v>2.6463511131902262E-4</v>
+      </c>
+      <c r="I10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.0289119702885401E-5</v>
-      </c>
-      <c r="J9" s="3">
+        <v>2.9862186944706881E-4</v>
+      </c>
+      <c r="J10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.223457660024188E-5</v>
-      </c>
-      <c r="K9" s="3">
+        <v>3.3781094304263792E-4</v>
+      </c>
+      <c r="K10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.2707972871203204E-5</v>
-      </c>
-      <c r="L9" s="3">
+        <v>3.8015762570164924E-4</v>
+      </c>
+      <c r="L10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.3030631782681183E-5</v>
-      </c>
-      <c r="M9" s="3">
+        <v>4.2303960818368402E-4</v>
+      </c>
+      <c r="M10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.3118690705390428E-5</v>
-      </c>
-      <c r="N9" s="3">
+        <v>4.6827398521953612E-4</v>
+      </c>
+      <c r="N10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.3503423099222616E-5</v>
-      </c>
-      <c r="O9" s="3">
+        <v>5.1421941050267678E-4</v>
+      </c>
+      <c r="O10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.438984078114494E-5</v>
-      </c>
-      <c r="P9" s="3">
+        <v>5.604412600280842E-4</v>
+      </c>
+      <c r="P10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.593109875450363E-5</v>
-      </c>
-      <c r="Q9" s="3">
+        <v>6.0684488432372063E-4</v>
+      </c>
+      <c r="Q10" s="3">
         <f t="shared" si="3"/>
-        <v>-4.8243963762795161E-5</v>
-      </c>
-      <c r="R9" s="3">
+        <v>6.5365284502870435E-4</v>
+      </c>
+      <c r="R10" s="3">
         <f t="shared" si="3"/>
-        <v>-5.1435177144898425E-5</v>
-      </c>
-      <c r="S9" s="3">
+        <v>7.0237722578869038E-4</v>
+      </c>
+      <c r="S10" s="3">
         <f t="shared" si="3"/>
-        <v>-5.5684867826810702E-5</v>
-      </c>
-      <c r="T9" s="3">
+        <v>7.5342635216713028E-4</v>
+      </c>
+      <c r="T10" s="3">
         <f t="shared" si="3"/>
-        <v>-6.0834283375221787E-5</v>
-      </c>
-      <c r="U9" s="3">
+        <v>8.066844280045643E-4</v>
+      </c>
+      <c r="U10" s="3">
         <f t="shared" si="3"/>
-        <v>-6.6685293010126934E-5</v>
-      </c>
-      <c r="V9" s="3">
+        <v>8.6201393587105601E-4</v>
+      </c>
+      <c r="V10" s="3">
         <f t="shared" si="3"/>
-        <v>-7.2785899666971687E-5</v>
-      </c>
-      <c r="W9" s="3">
+        <v>9.1932180070708469E-4</v>
+      </c>
+      <c r="W10" s="3">
         <f t="shared" si="3"/>
-        <v>-7.9434000149869455E-5</v>
-      </c>
-      <c r="X9" s="3">
+        <v>9.7881014286314849E-4</v>
+      </c>
+      <c r="X10" s="3">
         <f t="shared" si="3"/>
-        <v>-8.6276343460700566E-5</v>
-      </c>
-      <c r="Y9" s="3">
+        <v>1.0405195746674423E-3</v>
+      </c>
+      <c r="Y10" s="3">
         <f t="shared" si="3"/>
-        <v>-9.3321111052757644E-5</v>
-      </c>
-      <c r="Z9" s="3">
+        <v>1.1045060634298359E-3</v>
+      </c>
+      <c r="Z10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.0078355224740765E-4</v>
-      </c>
-      <c r="AA9" s="3">
+        <v>1.170796694930927E-3</v>
+      </c>
+      <c r="AA10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.0811630780882542E-4</v>
-      </c>
-      <c r="AB9" s="3">
+        <v>1.2390978049161561E-3</v>
+      </c>
+      <c r="AB10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.1657258102559798E-4</v>
-      </c>
-      <c r="AC9" s="3">
+        <v>1.3090452237356359E-3</v>
+      </c>
+      <c r="AC10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.2548500949127739E-4</v>
-      </c>
-      <c r="AD9" s="3">
+        <v>1.3804602482122633E-3</v>
+      </c>
+      <c r="AD10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.3453573633059879E-4</v>
-      </c>
-      <c r="AE9" s="3">
+        <v>1.4534740382222619E-3</v>
+      </c>
+      <c r="AE10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.4339361988013888E-4</v>
-      </c>
-      <c r="AF9" s="3">
+        <v>1.5281965357031371E-3</v>
+      </c>
+      <c r="AF10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.5180230519962201E-4</v>
-      </c>
-      <c r="AG9" s="3">
+        <v>1.6046269659593104E-3</v>
+      </c>
+      <c r="AG10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.5958921700154338E-4</v>
-      </c>
-      <c r="AH9" s="3">
+        <v>1.6822930112380188E-3</v>
+      </c>
+      <c r="AH10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.6663922126813197E-4</v>
-      </c>
-      <c r="AI9" s="3">
+        <v>1.761106602276255E-3</v>
+      </c>
+      <c r="AI10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.7299561583250522E-4</v>
-      </c>
-      <c r="AJ9" s="3">
+        <v>1.8411538530372987E-3</v>
+      </c>
+      <c r="AJ10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.7875910808606149E-4</v>
-      </c>
-      <c r="AK9" s="3">
+        <v>1.9225128302719011E-3</v>
+      </c>
+      <c r="AK10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.8405739646330799E-4</v>
-      </c>
-      <c r="AL9" s="3">
+        <v>2.0052168885985669E-3</v>
+      </c>
+      <c r="AL10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.8875378573913332E-4</v>
-      </c>
-      <c r="AM9" s="3">
+        <v>2.0854399887522135E-3</v>
+      </c>
+      <c r="AM10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.9271771197747894E-4</v>
-      </c>
-      <c r="AN9" s="3">
+        <v>2.1632975700532908E-3</v>
+      </c>
+      <c r="AN10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.9625133834611647E-4</v>
-      </c>
-      <c r="AO9" s="3">
+        <v>2.2405688385811404E-3</v>
+      </c>
+      <c r="AO10" s="3">
         <f t="shared" si="3"/>
-        <v>-1.9963216349482699E-4</v>
-      </c>
-      <c r="AP9" s="3">
+        <v>2.3186284023730755E-3</v>
+      </c>
+      <c r="AP10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.0306784493927948E-4</v>
-      </c>
-      <c r="AQ9" s="3">
+        <v>2.3979986580122681E-3</v>
+      </c>
+      <c r="AQ10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.0667942651330512E-4</v>
-      </c>
-      <c r="AR9" s="3">
+        <v>2.4779283908153982E-3</v>
+      </c>
+      <c r="AR10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.104643640076162E-4</v>
-      </c>
-      <c r="AS9" s="3">
+        <v>2.5580341694070308E-3</v>
+      </c>
+      <c r="AS10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.144920037425585E-4</v>
-      </c>
-      <c r="AT9" s="3">
+        <v>2.6382558313923221E-3</v>
+      </c>
+      <c r="AT10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.1882182280963391E-4</v>
-      </c>
-      <c r="AU9" s="3">
+        <v>2.7186220593600208E-3</v>
+      </c>
+      <c r="AU10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.235034261962518E-4</v>
-      </c>
-      <c r="AV9" s="3">
+        <v>2.7991866626791984E-3</v>
+      </c>
+      <c r="AV10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.2856850453423228E-4</v>
-      </c>
-      <c r="AW9" s="3">
+        <v>2.8777843676351944E-3</v>
+      </c>
+      <c r="AW10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.337926166070467E-4</v>
-      </c>
-      <c r="AX9" s="3">
+        <v>2.9544839735867745E-3</v>
+      </c>
+      <c r="AX10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.393172554430098E-4</v>
-      </c>
-      <c r="AY9" s="3">
+        <v>3.0305233494897221E-3</v>
+      </c>
+      <c r="AY10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.4528627438380468E-4</v>
-      </c>
-      <c r="AZ9" s="3">
+        <v>3.106923302080733E-3</v>
+      </c>
+      <c r="AZ10" s="3">
         <f t="shared" si="3"/>
-        <v>-2.51812905748168E-4</v>
-      </c>
-      <c r="BA9" s="3">
-        <f t="shared" si="3"/>
-        <v>-2.589500631655639E-4</v>
-      </c>
-      <c r="BB9" s="3">
-        <f t="shared" si="3"/>
-        <v>-2.6658755750685187E-4</v>
-      </c>
-      <c r="BC9" s="3">
-        <f t="shared" si="3"/>
-        <v>-2.7481049540266367E-4</v>
-      </c>
-      <c r="BD9" s="3">
-        <f t="shared" si="3"/>
-        <v>-2.836954198700628E-4</v>
-      </c>
-      <c r="BE9" s="3">
-        <f t="shared" si="3"/>
-        <v>-2.9330113904658256E-4</v>
+        <v>3.1841664268963399E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3">
+        <f>B5-B4</f>
+        <v>-7.2669652130707973E-5</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" ref="C11:AZ11" si="4">C5-C4</f>
+        <v>-7.879551575240562E-5</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="4"/>
+        <v>-8.7302778841835682E-5</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="4"/>
+        <v>-9.7772507465898606E-5</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.0843370503699212E-4</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.175582647838791E-4</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.2430022394416262E-4</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.2860406736370233E-4</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.3112928915759436E-4</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.3312405400012217E-4</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.3557234589245404E-4</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.3984670744315864E-4</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.4546917841518764E-4</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.520626001153616E-4</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.5909555991312774E-4</v>
+      </c>
+      <c r="Q11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.66077867519758E-4</v>
+      </c>
+      <c r="R11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.7285141273948312E-4</v>
+      </c>
+      <c r="S11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.79035250725261E-4</v>
+      </c>
+      <c r="T11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.84520800972858E-4</v>
+      </c>
+      <c r="U11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.8927222727184445E-4</v>
+      </c>
+      <c r="V11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.9342556341384737E-4</v>
+      </c>
+      <c r="W11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.9685611233777323E-4</v>
+      </c>
+      <c r="X11" s="3">
+        <f t="shared" si="4"/>
+        <v>-1.9975510404212499E-4</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.0224006395475058E-4</v>
+      </c>
+      <c r="Z11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.0441808520754029E-4</v>
+      </c>
+      <c r="AA11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.0670360937535825E-4</v>
+      </c>
+      <c r="AB11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.0859936724437061E-4</v>
+      </c>
+      <c r="AC11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.10377166453668E-4</v>
+      </c>
+      <c r="AD11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1209909277342121E-4</v>
+      </c>
+      <c r="AE11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1380935684255781E-4</v>
+      </c>
+      <c r="AF11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1552686643211416E-4</v>
+      </c>
+      <c r="AG11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1719691109545886E-4</v>
+      </c>
+      <c r="AH11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1884168707887036E-4</v>
+      </c>
+      <c r="AI11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2043630044332047E-4</v>
+      </c>
+      <c r="AJ11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2195763552824987E-4</v>
+      </c>
+      <c r="AK11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2337942252437237E-4</v>
+      </c>
+      <c r="AL11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2427381890066656E-4</v>
+      </c>
+      <c r="AM11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2489407428549074E-4</v>
+      </c>
+      <c r="AN11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2524427262649027E-4</v>
+      </c>
+      <c r="AO11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2536862792232881E-4</v>
+      </c>
+      <c r="AP11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.253060154772113E-4</v>
+      </c>
+      <c r="AQ11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2500744033948639E-4</v>
+      </c>
+      <c r="AR11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2454337015731518E-4</v>
+      </c>
+      <c r="AS11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2392253051151112E-4</v>
+      </c>
+      <c r="AT11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2315218908330881E-4</v>
+      </c>
+      <c r="AU11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2223241794816495E-4</v>
+      </c>
+      <c r="AV11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.2090510750294445E-4</v>
+      </c>
+      <c r="AW11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1935469415590436E-4</v>
+      </c>
+      <c r="AX11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1759224127337884E-4</v>
+      </c>
+      <c r="AY11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.1564078073721404E-4</v>
+      </c>
+      <c r="AZ11" s="3">
+        <f t="shared" si="4"/>
+        <v>-2.135171994367413E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="B14">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/results/Dommages.xlsx
+++ b/results/Dommages.xlsx
@@ -20,6 +20,7 @@
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>Dommages</t>
   </si>
@@ -47,6 +48,9 @@
   <si>
     <t>Température de l'air</t>
   </si>
+  <si>
+    <t>Mer et inondations</t>
+  </si>
 </sst>
 </file>
 
@@ -54,7 +58,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -90,7 +94,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -194,7 +198,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Décompo!$A$8</c:f>
+              <c:f>Décompo!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -214,7 +218,7 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Décompo!$B$7:$AZ$7</c:f>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="51"/>
@@ -376,7 +380,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Décompo!$B$8:$AZ$8</c:f>
+              <c:f>Décompo!$B$9:$AZ$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
@@ -390,7 +394,7 @@
                   <c:v>2.0115560050032899E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2943774039713705E-2</c:v>
+                  <c:v>2.2943774902325131E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2.5425308096377663E-2</c:v>
@@ -399,7 +403,7 @@
                   <c:v>2.7611418605846372E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.9576927112697438E-2</c:v>
+                  <c:v>2.9576927529626262E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3.1353239073615535E-2</c:v>
@@ -411,7 +415,7 @@
                   <c:v>3.4516237501799885E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.6927247035058564E-2</c:v>
+                  <c:v>3.6927247412231856E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.7901004681047845E-2</c:v>
@@ -420,7 +424,7 @@
                   <c:v>3.8748605891280929E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.9477051314678935E-2</c:v>
+                  <c:v>3.9477051688237563E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>4.0116488877360634E-2</c:v>
@@ -447,13 +451,13 @@
                   <c:v>4.427314031618601E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.4941592404026176E-2</c:v>
+                  <c:v>4.4941592729452529E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>4.563947337910957E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.6365522950460585E-2</c:v>
+                  <c:v>4.6365523266142288E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>4.7123697653551948E-2</c:v>
@@ -471,7 +475,7 @@
                   <c:v>5.0218084317584018E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.1012621214923663E-2</c:v>
+                  <c:v>5.1012621505727829E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>5.1800471640880197E-2</c:v>
@@ -480,13 +484,13 @@
                   <c:v>5.2587995224248063E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.337331162577863E-2</c:v>
+                  <c:v>5.33733113615723E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>5.4154996240649018E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.4931913241978665E-2</c:v>
+                  <c:v>5.4931912985350273E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>5.5612806592488247E-2</c:v>
@@ -501,7 +505,7 @@
                   <c:v>5.753897634474104E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.8149801082812758E-2</c:v>
+                  <c:v>5.8149801337017311E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>5.8735596987392939E-2</c:v>
@@ -510,7 +514,7 @@
                   <c:v>5.9311343796265348E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5.9879563848025723E-2</c:v>
+                  <c:v>5.9879563862663465E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>6.0442828733665251E-2</c:v>
@@ -519,19 +523,19 @@
                   <c:v>6.1003296850866917E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.1513652453118454E-2</c:v>
+                  <c:v>6.1513652688195419E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>6.2016559531788203E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6.251429610217496E-2</c:v>
+                  <c:v>6.2514296331188435E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.3009329761051225E-2</c:v>
+                  <c:v>6.3009329987089857E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.3503741189399388E-2</c:v>
+                  <c:v>6.3503741412501813E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -547,7 +551,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Décompo!$A$9</c:f>
+              <c:f>Décompo!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -558,7 +562,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:srgbClr val="00B050"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -567,7 +571,7 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Décompo!$B$7:$AZ$7</c:f>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="51"/>
@@ -729,162 +733,162 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Décompo!$B$9:$AZ$9</c:f>
+              <c:f>Décompo!$B$10:$AZ$10</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>2.7840212279017784E-4</c:v>
+                  <c:v>1.3438789375808113E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.224525962783666E-4</c:v>
+                  <c:v>2.6181616621756554E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.9534022194739364E-4</c:v>
+                  <c:v>3.621163355573831E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.0445679314089524E-4</c:v>
+                  <c:v>4.3724432175051842E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.7831374153535258E-4</c:v>
+                  <c:v>4.9908398422249256E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.4332704387400934E-4</c:v>
+                  <c:v>5.5892513906752317E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0147871066616965E-3</c:v>
+                  <c:v>6.2275232294828342E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0972397702284642E-3</c:v>
+                  <c:v>6.9139740652446324E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.189922651713915E-3</c:v>
+                  <c:v>7.6394908653598659E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.289820743303971E-3</c:v>
+                  <c:v>8.3886924188336653E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.3906185439738206E-3</c:v>
+                  <c:v>9.1286593600881094E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5004994437428643E-3</c:v>
+                  <c:v>9.9162630619664682E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.6132898073157875E-3</c:v>
+                  <c:v>1.0720241721557944E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.7274126835205017E-3</c:v>
+                  <c:v>1.1535640345473608E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.8416524130396919E-3</c:v>
+                  <c:v>1.2358563924219634E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.9553201850748408E-3</c:v>
+                  <c:v>1.3187051360760219E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.0706062263154898E-3</c:v>
+                  <c:v>1.4037302002539651E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.1869310298537961E-3</c:v>
+                  <c:v>1.4906360662765294E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.303463453985799E-3</c:v>
+                  <c:v>1.5789080261373531E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.4194115546302061E-3</c:v>
+                  <c:v>1.6679755653525863E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.5337376518913615E-3</c:v>
+                  <c:v>1.7571472529557333E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.647006054314123E-3</c:v>
+                  <c:v>1.8463864538693642E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.7587936974806659E-3</c:v>
+                  <c:v>1.9353816062881446E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.8691627555110649E-3</c:v>
+                  <c:v>2.024025037136272E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.9782513372484942E-3</c:v>
+                  <c:v>2.1122705465630581E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.0845426854701E-3</c:v>
+                  <c:v>2.1993524566710221E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3.1893081092998557E-3</c:v>
+                  <c:v>2.2852918106983644E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.2922830336853323E-3</c:v>
+                  <c:v>2.3700224069685902E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3.3939862645634492E-3</c:v>
+                  <c:v>2.4537980799140754E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.4949579534206826E-3</c:v>
+                  <c:v>2.5369167545655699E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.5956227016033029E-3</c:v>
+                  <c:v>2.6196162716446356E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.6957206085608263E-3</c:v>
+                  <c:v>2.7016507745774021E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>3.7954412599580031E-3</c:v>
+                  <c:v>2.7831101864821406E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.8950323936456296E-3</c:v>
+                  <c:v>2.8641228855196335E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>3.9947226290580826E-3</c:v>
+                  <c:v>2.9448077328281183E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.0946887554384886E-3</c:v>
+                  <c:v>3.0252520047377995E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.1900888256526311E-3</c:v>
+                  <c:v>3.1020826789411871E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.2817482682538863E-3</c:v>
+                  <c:v>3.1756576366343964E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.371267291225292E-3</c:v>
+                  <c:v>3.2469566266472086E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4.4602334244469993E-3</c:v>
+                  <c:v>3.3169858002710662E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.5497829812162216E-3</c:v>
+                  <c:v>3.3864791738471567E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4.6398338524992269E-3</c:v>
+                  <c:v>3.4553360584705928E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4.7306407184012356E-3</c:v>
+                  <c:v>3.5237223017656749E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>4.822557023581038E-3</c:v>
+                  <c:v>3.5918993111437869E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>4.915672562974531E-3</c:v>
+                  <c:v>3.6598822236594206E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5.0100464855701299E-3</c:v>
+                  <c:v>3.7276654590847613E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>5.1035559964569613E-3</c:v>
+                  <c:v>3.7936479530592537E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>5.1962276094394896E-3</c:v>
+                  <c:v>3.8578144973709858E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>5.2888830168641432E-3</c:v>
+                  <c:v>3.9206724280951288E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>5.3824060842524446E-3</c:v>
+                  <c:v>3.9827770538726215E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5.477488980923928E-3</c:v>
+                  <c:v>4.0445557140917909E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -900,7 +904,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Décompo!$A$10</c:f>
+              <c:f>Décompo!$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -911,7 +915,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln w="25400">
               <a:noFill/>
@@ -920,7 +924,7 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Décompo!$B$7:$AZ$7</c:f>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="51"/>
@@ -1082,162 +1086,162 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Décompo!$B$10:$AZ$10</c:f>
+              <c:f>Décompo!$B$11:$AZ$11</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>6.168779579696082E-5</c:v>
+                  <c:v>6.166325736678413E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2415006617638724E-4</c:v>
+                  <c:v>1.2406974180489971E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6806397964841402E-4</c:v>
+                  <c:v>1.6798032322717926E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9533471300470229E-4</c:v>
+                  <c:v>1.9531726047739006E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.1561527487090615E-4</c:v>
+                  <c:v>2.157012436457828E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.3723164204614289E-4</c:v>
+                  <c:v>2.3742380955982245E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.6463511131902262E-4</c:v>
+                  <c:v>2.6492154138157975E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.9862186944706881E-4</c:v>
+                  <c:v>2.9898978713482904E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3781094304263792E-4</c:v>
+                  <c:v>3.3825210997651123E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.8015762570164924E-4</c:v>
+                  <c:v>3.8067326778778998E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.2303960818368402E-4</c:v>
+                  <c:v>4.2363293529634749E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.6827398521953612E-4</c:v>
+                  <c:v>4.6895746744057831E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.1421941050267678E-4</c:v>
+                  <c:v>5.1500073576260519E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.604412600280842E-4</c:v>
+                  <c:v>5.6134116250994986E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.0684488432372063E-4</c:v>
+                  <c:v>6.0785770713067677E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.5365284502870435E-4</c:v>
+                  <c:v>6.5476914563755706E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.0237722578869038E-4</c:v>
+                  <c:v>7.0358864451414149E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.5342635216713028E-4</c:v>
+                  <c:v>7.547237955446498E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.066844280045643E-4</c:v>
+                  <c:v>8.0806122963938271E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.6201393587105601E-4</c:v>
+                  <c:v>8.6346503463374802E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.1932180070708469E-4</c:v>
+                  <c:v>9.2084637913879275E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.7881014286314849E-4</c:v>
+                  <c:v>9.80411257173186E-4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0405195746674423E-3</c:v>
+                  <c:v>1.0422023538963973E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1045060634298359E-3</c:v>
+                  <c:v>1.1062791825026189E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.170796694930927E-3</c:v>
+                  <c:v>1.1726705813077665E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.2390978049161561E-3</c:v>
+                  <c:v>1.2410816766340663E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.3090452237356359E-3</c:v>
+                  <c:v>1.3111531910162746E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.3804602482122633E-3</c:v>
+                  <c:v>1.3827054202674091E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.4534740382222619E-3</c:v>
+                  <c:v>1.4558694544935108E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.5281965357031371E-3</c:v>
+                  <c:v>1.5307536879812858E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.6046269659593104E-3</c:v>
+                  <c:v>1.6073581983827648E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.6822930112380188E-3</c:v>
+                  <c:v>1.6852278177769062E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.761106602276255E-3</c:v>
+                  <c:v>1.7642629577990718E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.8411538530372987E-3</c:v>
+                  <c:v>1.8445390925142593E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.9225128302719011E-3</c:v>
+                  <c:v>1.9261368756108357E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.0052168885985669E-3</c:v>
+                  <c:v>2.0090918360936641E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.0854399887522135E-3</c:v>
+                  <c:v>2.0895786394496824E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.1632975700532908E-3</c:v>
+                  <c:v>2.1677130334341044E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.2405688385811404E-3</c:v>
+                  <c:v>2.2452746057254266E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.3186284023730755E-3</c:v>
+                  <c:v>2.3236380363928985E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.3979986580122681E-3</c:v>
+                  <c:v>2.4033272925388857E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.4779283908153982E-3</c:v>
+                  <c:v>2.4835948887653794E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.5580341694070308E-3</c:v>
+                  <c:v>2.5640596761753454E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.6382558313923221E-3</c:v>
+                  <c:v>2.6446648633973169E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.7186220593600208E-3</c:v>
+                  <c:v>2.7254406205889925E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.7991866626791984E-3</c:v>
+                  <c:v>2.8064438176084172E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.8777843676351944E-3</c:v>
+                  <c:v>2.8855094665938275E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.9544839735867745E-3</c:v>
+                  <c:v>2.9627060505986735E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.0305233494897221E-3</c:v>
+                  <c:v>3.0392718891184556E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.106923302080733E-3</c:v>
+                  <c:v>3.1162286409965878E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.1841664268963399E-3</c:v>
+                  <c:v>3.1940607928172549E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1253,18 +1257,373 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Décompo!$A$11</c:f>
+              <c:f>Décompo!$A$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Autres risques</c:v>
+                  <c:v>Mer et inondations</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>42005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42370</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42736</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43466</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43831</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44197</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44562</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44927</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45292</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46388</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46753</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>47119</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>47484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>47849</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48214</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48580</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48945</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>49310</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>49675</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>50406</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50771</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>51136</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>51502</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>51867</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>52232</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>52597</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>52963</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53328</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53693</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>54058</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>54424</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>54789</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>55154</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>55519</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>55885</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>56250</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>56615</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>56980</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>57346</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>57711</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>58076</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>58441</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>58807</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>59172</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>59537</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>59902</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>60268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Décompo!$B$12:$AZ$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>3.9972466572613108E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.3665455638706181E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.8740654790432352E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.8671582443389241E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5367439926474784E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9974471688657474E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0331032043029431E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0575416159764872E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0763834282041529E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0921056494282988E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1057368566246284E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1209628843252828E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1381882674956767E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1575790415513307E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.1792015706788561E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2030059910806898E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.2301343960197109E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2598800045520164E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2918136021887808E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.32561429079181E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3620583709840275E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3985062787638114E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.4361223895582725E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.4747510826485996E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5142564547891979E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.5576401966460596E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.5983562067459697E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.6387247227599502E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.6787970840530519E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.7186206553632052E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.7582305817761545E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.7972845889957581E-3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.8359746195955109E-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.8744092420992509E-3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.9126703151580646E-3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.9508234414471401E-3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.9863117217567908E-3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.0196579110873872E-3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.0516174003635326E-3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.082670029862066E-3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.1131576966908483E-3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.1427704929819491E-3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.1719688309533858E-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.2010336584927792E-3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2.2301641625331881E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.2595033146388666E-3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.2871013262685258E-3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.3140186070349511E-3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.3407144772028543E-3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.3674681380444484E-3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.3944577475761841E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7EC6-4E26-91E0-1E0153E07C27}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Décompo!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Autres risques</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1273,7 +1632,7 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Décompo!$B$7:$AZ$7</c:f>
+              <c:f>Décompo!$B$8:$AZ$8</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="51"/>
@@ -1435,169 +1794,169 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Décompo!$B$11:$AZ$11</c:f>
+              <c:f>Décompo!$B$13:$AZ$13</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>-7.2669652130707973E-5</c:v>
+                  <c:v>2.2223002079790888E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.879551575240562E-5</c:v>
+                  <c:v>4.2433615243542278E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-8.7302778841835682E-5</c:v>
+                  <c:v>5.460484776365071E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-9.7772507465898606E-5</c:v>
+                  <c:v>6.0582705880252163E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.0843370503699212E-4</c:v>
+                  <c:v>6.2931765114337956E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.175582647838791E-4</c:v>
+                  <c:v>6.3797201827009431E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.2430022394416262E-4</c:v>
+                  <c:v>6.4523020353712823E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.2860406736370233E-4</c:v>
+                  <c:v>6.5651380013864724E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1.3112928915759436E-4</c:v>
+                  <c:v>6.7277674351318151E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.3312405400012217E-4</c:v>
+                  <c:v>6.9236716254850172E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.3557234589245404E-4</c:v>
+                  <c:v>7.1186858567295203E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.3984670744315864E-4</c:v>
+                  <c:v>7.339265242249926E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.4546917841518764E-4</c:v>
+                  <c:v>7.5574492127428172E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1.520626001153616E-4</c:v>
+                  <c:v>7.7685716043829345E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1.5909555991312774E-4</c:v>
+                  <c:v>7.9714597830683048E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1.66077867519758E-4</c:v>
+                  <c:v>8.1669863298294842E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1.7285141273948312E-4</c:v>
+                  <c:v>8.3644969196160907E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1.79035250725261E-4</c:v>
+                  <c:v>8.5642039832490441E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.84520800972858E-4</c:v>
+                  <c:v>8.7634582048701226E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1.8927222727184445E-4</c:v>
+                  <c:v>8.9598727931495398E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1.9342556341384737E-4</c:v>
+                  <c:v>9.1503285465011075E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-1.9685611233777323E-4</c:v>
+                  <c:v>9.335953487628057E-4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1.9975510404212499E-4</c:v>
+                  <c:v>9.5171367511747568E-4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-2.0224006395475058E-4</c:v>
+                  <c:v>9.6935188907742997E-4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-2.0441808520754029E-4</c:v>
+                  <c:v>9.8651373350443911E-4</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-2.0670360937535825E-4</c:v>
+                  <c:v>1.0025299021160228E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-2.0859936724437061E-4</c:v>
+                  <c:v>1.0178720288839191E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-2.10377166453668E-4</c:v>
+                  <c:v>1.0326582515052252E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-2.1209909277342121E-4</c:v>
+                  <c:v>1.0470512460817247E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-2.1380935684255781E-4</c:v>
+                  <c:v>1.0612214383433072E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-2.1552686643211416E-4</c:v>
+                  <c:v>1.0753090623075723E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-2.1719691109545886E-4</c:v>
+                  <c:v>1.0892942806112194E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-2.1884168707887036E-4</c:v>
+                  <c:v>1.1032629738735311E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-2.2043630044332047E-4</c:v>
+                  <c:v>1.1173722355650589E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-2.2195763552824987E-4</c:v>
+                  <c:v>1.1317584707346562E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-2.2337942252437237E-4</c:v>
+                  <c:v>1.1465471099495472E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-2.2427381890066656E-4</c:v>
+                  <c:v>1.1606241133053086E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-2.2489407428549074E-4</c:v>
+                  <c:v>1.1741412275859675E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-2.2524427262649027E-4</c:v>
+                  <c:v>1.1878206457391904E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-2.2536862792232881E-4</c:v>
+                  <c:v>1.2022725018577818E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-2.253060154772113E-4</c:v>
+                  <c:v>1.2179150664397564E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-2.2500744033948639E-4</c:v>
+                  <c:v>1.2348353848774529E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-2.2454337015731518E-4</c:v>
+                  <c:v>1.2530988614173344E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-2.2392253051151112E-4</c:v>
+                  <c:v>1.2728268323418668E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-2.2315218908330881E-4</c:v>
+                  <c:v>1.2941191998472323E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-2.2223241794816495E-4</c:v>
+                  <c:v>1.3170632297310192E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-2.2090510750294445E-4</c:v>
+                  <c:v>1.3413303100763274E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-2.1935469415590436E-4</c:v>
+                  <c:v>1.366829348992793E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-2.1759224127337884E-4</c:v>
+                  <c:v>1.3938871094382188E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-2.1564078073721404E-4</c:v>
+                  <c:v>1.4228244530135603E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-2.135171994367413E-4</c:v>
+                  <c:v>1.4538930628853475E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7EC6-4E26-91E0-1E0153E07C27}"/>
+              <c16:uniqueId val="{00000000-EFD4-4220-87B3-3326FFCAFB75}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1774,10 +2133,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -2372,7 +2728,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297358" cy="6074434"/>
+    <xdr:ext cx="9291053" cy="6060351"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Graphique 1"/>
@@ -2424,159 +2780,314 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>42005</v>
+          </cell>
+          <cell r="D4">
+            <v>42370</v>
+          </cell>
+          <cell r="E4">
+            <v>42736</v>
+          </cell>
+          <cell r="F4">
+            <v>43101</v>
+          </cell>
+          <cell r="G4">
+            <v>43466</v>
+          </cell>
+          <cell r="H4">
+            <v>43831</v>
+          </cell>
+          <cell r="I4">
+            <v>44197</v>
+          </cell>
+          <cell r="J4">
+            <v>44562</v>
+          </cell>
+          <cell r="K4">
+            <v>44927</v>
+          </cell>
+          <cell r="L4">
+            <v>45292</v>
+          </cell>
+          <cell r="M4">
+            <v>45658</v>
+          </cell>
+          <cell r="N4">
+            <v>46023</v>
+          </cell>
+          <cell r="O4">
+            <v>46388</v>
+          </cell>
+          <cell r="P4">
+            <v>46753</v>
+          </cell>
+          <cell r="Q4">
+            <v>47119</v>
+          </cell>
+          <cell r="R4">
+            <v>47484</v>
+          </cell>
+          <cell r="S4">
+            <v>47849</v>
+          </cell>
+          <cell r="T4">
+            <v>48214</v>
+          </cell>
+          <cell r="U4">
+            <v>48580</v>
+          </cell>
+          <cell r="V4">
+            <v>48945</v>
+          </cell>
+          <cell r="W4">
+            <v>49310</v>
+          </cell>
+          <cell r="X4">
+            <v>49675</v>
+          </cell>
+          <cell r="Y4">
+            <v>50041</v>
+          </cell>
+          <cell r="Z4">
+            <v>50406</v>
+          </cell>
+          <cell r="AA4">
+            <v>50771</v>
+          </cell>
+          <cell r="AB4">
+            <v>51136</v>
+          </cell>
+          <cell r="AC4">
+            <v>51502</v>
+          </cell>
+          <cell r="AD4">
+            <v>51867</v>
+          </cell>
+          <cell r="AE4">
+            <v>52232</v>
+          </cell>
+          <cell r="AF4">
+            <v>52597</v>
+          </cell>
+          <cell r="AG4">
+            <v>52963</v>
+          </cell>
+          <cell r="AH4">
+            <v>53328</v>
+          </cell>
+          <cell r="AI4">
+            <v>53693</v>
+          </cell>
+          <cell r="AJ4">
+            <v>54058</v>
+          </cell>
+          <cell r="AK4">
+            <v>54424</v>
+          </cell>
+          <cell r="AL4">
+            <v>54789</v>
+          </cell>
+          <cell r="AM4">
+            <v>55154</v>
+          </cell>
+          <cell r="AN4">
+            <v>55519</v>
+          </cell>
+          <cell r="AO4">
+            <v>55885</v>
+          </cell>
+          <cell r="AP4">
+            <v>56250</v>
+          </cell>
+          <cell r="AQ4">
+            <v>56615</v>
+          </cell>
+          <cell r="AR4">
+            <v>56980</v>
+          </cell>
+          <cell r="AS4">
+            <v>57346</v>
+          </cell>
+          <cell r="AT4">
+            <v>57711</v>
+          </cell>
+          <cell r="AU4">
+            <v>58076</v>
+          </cell>
+          <cell r="AV4">
+            <v>58441</v>
+          </cell>
+          <cell r="AW4">
+            <v>58807</v>
+          </cell>
+          <cell r="AX4">
+            <v>59172</v>
+          </cell>
+          <cell r="AY4">
+            <v>59537</v>
+          </cell>
+          <cell r="AZ4">
+            <v>59902</v>
+          </cell>
+          <cell r="BA4">
+            <v>60268</v>
+          </cell>
+        </row>
         <row r="5">
           <cell r="C5">
-            <v>-1.3538601712600906</v>
+            <v>-1.4356607550249811</v>
           </cell>
           <cell r="D5">
-            <v>-1.6912679139984843</v>
+            <v>-1.8359555756829793</v>
           </cell>
           <cell r="E5">
-            <v>-2.0115560050032899</v>
+            <v>-2.1979111734358292</v>
           </cell>
           <cell r="F5">
-            <v>-2.2943774039713705</v>
+            <v>-2.5068879367789454</v>
           </cell>
           <cell r="G5">
-            <v>-2.5425308096377663</v>
+            <v>-2.7723085374654066</v>
           </cell>
           <cell r="H5">
-            <v>-2.7611418605846372</v>
+            <v>-3.0045484289630386</v>
           </cell>
           <cell r="I5">
-            <v>-2.9576927112697438</v>
+            <v>-3.2142934801796197</v>
           </cell>
           <cell r="J5">
-            <v>-3.1353239073615535</v>
+            <v>-3.4057681683389962</v>
           </cell>
           <cell r="K5">
-            <v>-3.2985843392642766</v>
+            <v>-3.5837204760872599</v>
           </cell>
           <cell r="L5">
-            <v>-3.4516237501799885</v>
+            <v>-3.7520252823447842</v>
           </cell>
           <cell r="M5">
-            <v>-3.6927247035058564</v>
+            <v>-4.0081351725834597</v>
           </cell>
           <cell r="N5">
-            <v>-3.7901004681047845</v>
+            <v>-4.1216477863235346</v>
           </cell>
           <cell r="O5">
-            <v>-3.8748605891280929</v>
+            <v>-4.2229563987969287</v>
           </cell>
           <cell r="P5">
-            <v>-3.9477051314678935</v>
+            <v>-4.3126393087284498</v>
           </cell>
           <cell r="Q5">
-            <v>-4.0116488877360634</v>
+            <v>-4.3936550525898959</v>
           </cell>
           <cell r="R5">
-            <v>-4.0694640941231981</v>
+            <v>-4.4687819847009198</v>
           </cell>
           <cell r="S5">
-            <v>-4.1277964002331196</v>
+            <v>-4.5451866935080627</v>
           </cell>
           <cell r="T5">
-            <v>-4.1849741026071747</v>
+            <v>-4.6211401290769842</v>
           </cell>
           <cell r="U5">
-            <v>-4.2425458296820988</v>
+            <v>-4.6980586975273519</v>
           </cell>
           <cell r="V5">
-            <v>-4.3016340742832782</v>
+            <v>-4.7769382912925877</v>
           </cell>
           <cell r="W5">
-            <v>-4.3633104309372284</v>
+            <v>-4.8588189167100948</v>
           </cell>
           <cell r="X5">
-            <v>-4.427314031618601</v>
+            <v>-4.9432039654755178</v>
           </cell>
           <cell r="Y5">
-            <v>-4.4941592404026176</v>
+            <v>-5.0307012754312819</v>
           </cell>
           <cell r="Z5">
-            <v>-4.5639473379109567</v>
+            <v>-5.121388057047449</v>
           </cell>
           <cell r="AA5">
-            <v>-4.6365522950460587</v>
+            <v>-5.2151234582306749</v>
           </cell>
           <cell r="AB5">
-            <v>-4.712369765355195</v>
+            <v>-5.3124301885619118</v>
           </cell>
           <cell r="AC5">
-            <v>-4.788032119780028</v>
+            <v>-5.409299443514481</v>
           </cell>
           <cell r="AD5">
-            <v>-4.8649621572917194</v>
+            <v>-5.5073732374418372</v>
           </cell>
           <cell r="AE5">
-            <v>-4.9429610515789646</v>
+            <v>-5.6065126380332009</v>
           </cell>
           <cell r="AF5">
-            <v>-5.0218084317584015</v>
+            <v>-5.7065596853837386</v>
           </cell>
           <cell r="AG5">
-            <v>-5.1012621214923666</v>
+            <v>-5.8073135619838956</v>
           </cell>
           <cell r="AH5">
-            <v>-5.1800471640880197</v>
+            <v>-5.9073929102841483</v>
           </cell>
           <cell r="AI5">
-            <v>-5.2587995224248063</v>
+            <v>-6.0074605961998317</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.337331162577863</v>
+            <v>-6.1073754817270505</v>
           </cell>
           <cell r="AK5">
-            <v>-5.4154996240649016</v>
+            <v>-6.2070369634980693</v>
           </cell>
           <cell r="AL5">
-            <v>-5.4931913241978663</v>
+            <v>-6.3063627377578424</v>
           </cell>
           <cell r="AM5">
-            <v>-5.5612806592488244</v>
+            <v>-6.3951403745941215</v>
           </cell>
           <cell r="AN5">
-            <v>-5.6273572035804413</v>
+            <v>-6.4810741844546271</v>
           </cell>
           <cell r="AO5">
-            <v>-5.6914643529708648</v>
+            <v>-6.5646312808184</v>
           </cell>
           <cell r="AP5">
-            <v>-5.7538976344741037</v>
+            <v>-6.6464542713124857</v>
           </cell>
           <cell r="AQ5">
-            <v>-5.8149801082812758</v>
+            <v>-6.7270680566533958</v>
           </cell>
           <cell r="AR5">
-            <v>-5.8735596987392942</v>
+            <v>-6.8052133812488318</v>
           </cell>
           <cell r="AS5">
-            <v>-5.9311343796265348</v>
+            <v>-6.8824193466577093</v>
           </cell>
           <cell r="AT5">
-            <v>-5.9879563848025725</v>
+            <v>-6.9589988528039211</v>
           </cell>
           <cell r="AU5">
-            <v>-6.0442828733665248</v>
+            <v>-7.0352434940294089</v>
           </cell>
           <cell r="AV5">
-            <v>-6.1003296850866917</v>
+            <v>-7.1113972671929986</v>
           </cell>
           <cell r="AW5">
-            <v>-6.1513652453118457</v>
+            <v>-7.1821241744193358</v>
           </cell>
           <cell r="AX5">
-            <v>-6.20165595317882</v>
+            <v>-7.2517928035785602</v>
           </cell>
           <cell r="AY5">
-            <v>-6.251429610217496</v>
+            <v>-7.3208842235043097</v>
           </cell>
           <cell r="AZ5">
-            <v>-6.3009329761051225</v>
+            <v>-7.3898628273017071</v>
           </cell>
           <cell r="BA5">
-            <v>-6.3503741189399392</v>
+            <v>-7.4590708729872386</v>
           </cell>
         </row>
       </sheetData>
@@ -2616,157 +3127,157 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.3817003835391084</v>
+            <v>-1.3538601712600906</v>
           </cell>
           <cell r="D5">
-            <v>-1.743513173626321</v>
+            <v>-1.6912679139984843</v>
           </cell>
           <cell r="E5">
-            <v>-2.0810900271980293</v>
+            <v>-2.0115560050032899</v>
           </cell>
           <cell r="F5">
-            <v>-2.37482308328546</v>
+            <v>-2.2943774902325131</v>
           </cell>
           <cell r="G5">
-            <v>-2.6303621837913016</v>
+            <v>-2.5425308096377663</v>
           </cell>
           <cell r="H5">
-            <v>-2.8554745649720381</v>
+            <v>-2.7611418605846372</v>
           </cell>
           <cell r="I5">
-            <v>-3.0591714219359134</v>
+            <v>-2.9576927529626262</v>
           </cell>
           <cell r="J5">
-            <v>-3.2450478843843999</v>
+            <v>-3.1353239073615535</v>
           </cell>
           <cell r="K5">
-            <v>-3.4175766044356681</v>
+            <v>-3.2985843392642766</v>
           </cell>
           <cell r="L5">
-            <v>-3.5806058245103856</v>
+            <v>-3.4516237501799885</v>
           </cell>
           <cell r="M5">
-            <v>-3.8317865579032384</v>
+            <v>-3.6927247412231856</v>
           </cell>
           <cell r="N5">
-            <v>-3.9401504124790709</v>
+            <v>-3.7901004681047845</v>
           </cell>
           <cell r="O5">
-            <v>-4.0361895698596717</v>
+            <v>-3.8748605891280929</v>
           </cell>
           <cell r="P5">
-            <v>-4.1204463998199437</v>
+            <v>-3.9477051688237563</v>
           </cell>
           <cell r="Q5">
-            <v>-4.1958141290400324</v>
+            <v>-4.0116488877360634</v>
           </cell>
           <cell r="R5">
-            <v>-4.2649961126306817</v>
+            <v>-4.0694640941231981</v>
           </cell>
           <cell r="S5">
-            <v>-4.3348570228646688</v>
+            <v>-4.1277964002331196</v>
           </cell>
           <cell r="T5">
-            <v>-4.4036672055925541</v>
+            <v>-4.1849741026071747</v>
           </cell>
           <cell r="U5">
-            <v>-4.4728921750806787</v>
+            <v>-4.2425458296820988</v>
           </cell>
           <cell r="V5">
-            <v>-4.543575229746299</v>
+            <v>-4.3016340742832782</v>
           </cell>
           <cell r="W5">
-            <v>-4.6166841961263643</v>
+            <v>-4.3633104309372284</v>
           </cell>
           <cell r="X5">
-            <v>-4.6920146370500131</v>
+            <v>-4.427314031618601</v>
           </cell>
           <cell r="Y5">
-            <v>-4.7700386101506842</v>
+            <v>-4.4941592729452529</v>
           </cell>
           <cell r="Z5">
-            <v>-4.8508636134620637</v>
+            <v>-4.5639473379109567</v>
           </cell>
           <cell r="AA5">
-            <v>-4.9343774287709081</v>
+            <v>-4.636552326614229</v>
           </cell>
           <cell r="AB5">
-            <v>-5.0208240339022048</v>
+            <v>-4.712369765355195</v>
           </cell>
           <cell r="AC5">
-            <v>-5.1069629307100133</v>
+            <v>-4.788032119780028</v>
           </cell>
           <cell r="AD5">
-            <v>-5.1941904606602529</v>
+            <v>-4.8649621572917194</v>
           </cell>
           <cell r="AE5">
-            <v>-5.2823596780353093</v>
+            <v>-4.9429610515789646</v>
           </cell>
           <cell r="AF5">
-            <v>-5.3713042271004703</v>
+            <v>-5.0218084317584015</v>
           </cell>
           <cell r="AG5">
-            <v>-5.4608243916526966</v>
+            <v>-5.1012621505727829</v>
           </cell>
           <cell r="AH5">
-            <v>-5.5496192249441023</v>
+            <v>-5.1800471640880197</v>
           </cell>
           <cell r="AI5">
-            <v>-5.6383436484206069</v>
+            <v>-5.2587995224248063</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.7268344019424262</v>
+            <v>-5.3373311361572302</v>
           </cell>
           <cell r="AK5">
-            <v>-5.8149718869707101</v>
+            <v>-5.4154996240649016</v>
           </cell>
           <cell r="AL5">
-            <v>-5.9026601997417156</v>
+            <v>-5.4931912985350273</v>
           </cell>
           <cell r="AM5">
-            <v>-5.9802895418140878</v>
+            <v>-5.5612806592488244</v>
           </cell>
           <cell r="AN5">
-            <v>-6.0555320304058302</v>
+            <v>-5.6273572035804413</v>
           </cell>
           <cell r="AO5">
-            <v>-6.1285910820933935</v>
+            <v>-5.6914643529708648</v>
           </cell>
           <cell r="AP5">
-            <v>-6.1999209769188042</v>
+            <v>-5.7538976344741037</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.2699584064028979</v>
+            <v>-5.8149801337017308</v>
           </cell>
           <cell r="AR5">
-            <v>-6.3375430839892166</v>
+            <v>-5.8735596987392942</v>
           </cell>
           <cell r="AS5">
-            <v>-6.4041984514666588</v>
+            <v>-5.9311343796265348</v>
           </cell>
           <cell r="AT5">
-            <v>-6.4702120871606761</v>
+            <v>-5.9879563862663465</v>
           </cell>
           <cell r="AU5">
-            <v>-6.5358501296639782</v>
+            <v>-6.0442828733665248</v>
           </cell>
           <cell r="AV5">
-            <v>-6.6013343336437043</v>
+            <v>-6.1003296850866917</v>
           </cell>
           <cell r="AW5">
-            <v>-6.6617208449575411</v>
+            <v>-6.1513652688195419</v>
           </cell>
           <cell r="AX5">
-            <v>-6.7212787141227697</v>
+            <v>-6.20165595317882</v>
           </cell>
           <cell r="AY5">
-            <v>-6.7803179119039108</v>
+            <v>-6.2514296331188435</v>
           </cell>
           <cell r="AZ5">
-            <v>-6.8391735845303669</v>
+            <v>-6.3009329987089853</v>
           </cell>
           <cell r="BA5">
-            <v>-6.8981230170323311</v>
+            <v>-6.3503741412501817</v>
           </cell>
         </row>
       </sheetData>
@@ -2804,314 +3315,159 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4">
-            <v>42005</v>
-          </cell>
-          <cell r="D4">
-            <v>42370</v>
-          </cell>
-          <cell r="E4">
-            <v>42736</v>
-          </cell>
-          <cell r="F4">
-            <v>43101</v>
-          </cell>
-          <cell r="G4">
-            <v>43466</v>
-          </cell>
-          <cell r="H4">
-            <v>43831</v>
-          </cell>
-          <cell r="I4">
-            <v>44197</v>
-          </cell>
-          <cell r="J4">
-            <v>44562</v>
-          </cell>
-          <cell r="K4">
-            <v>44927</v>
-          </cell>
-          <cell r="L4">
-            <v>45292</v>
-          </cell>
-          <cell r="M4">
-            <v>45658</v>
-          </cell>
-          <cell r="N4">
-            <v>46023</v>
-          </cell>
-          <cell r="O4">
-            <v>46388</v>
-          </cell>
-          <cell r="P4">
-            <v>46753</v>
-          </cell>
-          <cell r="Q4">
-            <v>47119</v>
-          </cell>
-          <cell r="R4">
-            <v>47484</v>
-          </cell>
-          <cell r="S4">
-            <v>47849</v>
-          </cell>
-          <cell r="T4">
-            <v>48214</v>
-          </cell>
-          <cell r="U4">
-            <v>48580</v>
-          </cell>
-          <cell r="V4">
-            <v>48945</v>
-          </cell>
-          <cell r="W4">
-            <v>49310</v>
-          </cell>
-          <cell r="X4">
-            <v>49675</v>
-          </cell>
-          <cell r="Y4">
-            <v>50041</v>
-          </cell>
-          <cell r="Z4">
-            <v>50406</v>
-          </cell>
-          <cell r="AA4">
-            <v>50771</v>
-          </cell>
-          <cell r="AB4">
-            <v>51136</v>
-          </cell>
-          <cell r="AC4">
-            <v>51502</v>
-          </cell>
-          <cell r="AD4">
-            <v>51867</v>
-          </cell>
-          <cell r="AE4">
-            <v>52232</v>
-          </cell>
-          <cell r="AF4">
-            <v>52597</v>
-          </cell>
-          <cell r="AG4">
-            <v>52963</v>
-          </cell>
-          <cell r="AH4">
-            <v>53328</v>
-          </cell>
-          <cell r="AI4">
-            <v>53693</v>
-          </cell>
-          <cell r="AJ4">
-            <v>54058</v>
-          </cell>
-          <cell r="AK4">
-            <v>54424</v>
-          </cell>
-          <cell r="AL4">
-            <v>54789</v>
-          </cell>
-          <cell r="AM4">
-            <v>55154</v>
-          </cell>
-          <cell r="AN4">
-            <v>55519</v>
-          </cell>
-          <cell r="AO4">
-            <v>55885</v>
-          </cell>
-          <cell r="AP4">
-            <v>56250</v>
-          </cell>
-          <cell r="AQ4">
-            <v>56615</v>
-          </cell>
-          <cell r="AR4">
-            <v>56980</v>
-          </cell>
-          <cell r="AS4">
-            <v>57346</v>
-          </cell>
-          <cell r="AT4">
-            <v>57711</v>
-          </cell>
-          <cell r="AU4">
-            <v>58076</v>
-          </cell>
-          <cell r="AV4">
-            <v>58441</v>
-          </cell>
-          <cell r="AW4">
-            <v>58807</v>
-          </cell>
-          <cell r="AX4">
-            <v>59172</v>
-          </cell>
-          <cell r="AY4">
-            <v>59537</v>
-          </cell>
-          <cell r="AZ4">
-            <v>59902</v>
-          </cell>
-          <cell r="BA4">
-            <v>60268</v>
-          </cell>
-        </row>
         <row r="5">
           <cell r="C5">
-            <v>-1.3806021979057337</v>
+            <v>-1.3672989606358987</v>
           </cell>
           <cell r="D5">
-            <v>-1.7480486286687191</v>
+            <v>-1.7174495306202409</v>
           </cell>
           <cell r="E5">
-            <v>-2.0891661472786871</v>
+            <v>-2.0477676385590282</v>
           </cell>
           <cell r="F5">
-            <v>-2.3845793038393404</v>
+            <v>-2.338101922407565</v>
           </cell>
           <cell r="G5">
-            <v>-2.641080340774693</v>
+            <v>-2.5924392080600156</v>
           </cell>
           <cell r="H5">
-            <v>-2.8674419026982645</v>
+            <v>-2.8170343744913895</v>
           </cell>
           <cell r="I5">
-            <v>-3.0732049106733994</v>
+            <v>-3.0199679852574546</v>
           </cell>
           <cell r="J5">
-            <v>-3.2620496645927366</v>
+            <v>-3.2044636480139999</v>
           </cell>
           <cell r="K5">
-            <v>-3.4382447698241725</v>
+            <v>-3.3749792479178753</v>
           </cell>
           <cell r="L5">
-            <v>-3.6053091816805383</v>
+            <v>-3.5355106743683251</v>
           </cell>
           <cell r="M5">
-            <v>-3.8605332841323614</v>
+            <v>-3.7840113348240667</v>
           </cell>
           <cell r="N5">
-            <v>-3.9729931402567087</v>
+            <v>-3.8892630987244492</v>
           </cell>
           <cell r="O5">
-            <v>-4.0730645930684206</v>
+            <v>-3.9820630063436724</v>
           </cell>
           <cell r="P5">
-            <v>-4.1612842658112159</v>
+            <v>-4.0630615722784924</v>
           </cell>
           <cell r="Q5">
-            <v>-4.2405890614810922</v>
+            <v>-4.1352345269782598</v>
           </cell>
           <cell r="R5">
-            <v>-4.3137536103815766</v>
+            <v>-4.2013346077308</v>
           </cell>
           <cell r="S5">
-            <v>-4.3878096041695898</v>
+            <v>-4.2681694202585163</v>
           </cell>
           <cell r="T5">
-            <v>-4.4611063157367408</v>
+            <v>-4.3340377092348277</v>
           </cell>
           <cell r="U5">
-            <v>-4.5351085377838496</v>
+            <v>-4.4004366322958344</v>
           </cell>
           <cell r="V5">
-            <v>-4.6108494006062202</v>
+            <v>-4.4684316308185368</v>
           </cell>
           <cell r="W5">
-            <v>-4.6892738198556883</v>
+            <v>-4.5390251562328015</v>
           </cell>
           <cell r="X5">
-            <v>-4.7702100401025511</v>
+            <v>-4.6119526770055375</v>
           </cell>
           <cell r="Y5">
-            <v>-4.8541150572132157</v>
+            <v>-4.6876974335740673</v>
           </cell>
           <cell r="Z5">
-            <v>-4.9410902134095718</v>
+            <v>-4.7663498416245842</v>
           </cell>
           <cell r="AA5">
-            <v>-5.0310152897432463</v>
+            <v>-4.8477793812705343</v>
           </cell>
           <cell r="AB5">
-            <v>-5.1240634534562846</v>
+            <v>-4.9323050110222972</v>
           </cell>
           <cell r="AC5">
-            <v>-5.2170075163591401</v>
+            <v>-5.0165613008498644</v>
           </cell>
           <cell r="AD5">
-            <v>-5.3111987688361122</v>
+            <v>-5.1019643979885787</v>
           </cell>
           <cell r="AE5">
-            <v>-5.4064971725801936</v>
+            <v>-5.1883408595703724</v>
           </cell>
           <cell r="AF5">
-            <v>-5.5027429449865277</v>
+            <v>-5.2755001072149588</v>
           </cell>
           <cell r="AG5">
-            <v>-5.5997344016054162</v>
+            <v>-5.3632237777372467</v>
           </cell>
           <cell r="AH5">
-            <v>-5.6961288349583583</v>
+            <v>-5.4502122415457599</v>
           </cell>
           <cell r="AI5">
-            <v>-5.7925701399403451</v>
+            <v>-5.5371105410730204</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.8889061572018235</v>
+            <v>-5.6237434247091933</v>
           </cell>
           <cell r="AK5">
-            <v>-5.9850274064450755</v>
+            <v>-5.7099803973477137</v>
           </cell>
           <cell r="AL5">
-            <v>-6.0808439463491348</v>
+            <v>-5.7957164990088073</v>
           </cell>
           <cell r="AM5">
-            <v>-6.1664061587992425</v>
+            <v>-5.8714889271429431</v>
           </cell>
           <cell r="AN5">
-            <v>-6.24937237998261</v>
+            <v>-5.9449229672438815</v>
           </cell>
           <cell r="AO5">
-            <v>-6.3301235386888592</v>
+            <v>-6.0161600156355854</v>
           </cell>
           <cell r="AP5">
-            <v>-6.4092469543638781</v>
+            <v>-6.0855962145012104</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.487227670656404</v>
+            <v>-6.1536280510864465</v>
           </cell>
           <cell r="AR5">
-            <v>-6.5628351790368082</v>
+            <v>-6.2190933045863535</v>
           </cell>
           <cell r="AS5">
-            <v>-6.6375475313916299</v>
+            <v>-6.2835066098031023</v>
           </cell>
           <cell r="AT5">
-            <v>-6.7116454172487572</v>
+            <v>-6.3471463173807248</v>
           </cell>
           <cell r="AU5">
-            <v>-6.7853971166916498</v>
+            <v>-6.4102710957324671</v>
           </cell>
           <cell r="AV5">
-            <v>-6.859029758116808</v>
+            <v>-6.4730962309951678</v>
           </cell>
           <cell r="AW5">
-            <v>-6.9274087709707661</v>
+            <v>-6.5307300641254677</v>
           </cell>
           <cell r="AX5">
-            <v>-6.9947916420658558</v>
+            <v>-6.5874374029159188</v>
           </cell>
           <cell r="AY5">
-            <v>-7.0616110227255451</v>
+            <v>-6.6434968759283564</v>
           </cell>
           <cell r="AZ5">
-            <v>-7.1283018366647184</v>
+            <v>-6.6992107040962479</v>
           </cell>
           <cell r="BA5">
-            <v>-7.1951879397782914</v>
+            <v>-6.7548297126593599</v>
           </cell>
         </row>
       </sheetData>
@@ -3151,157 +3507,368 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.3878691631188045</v>
+            <v>-1.3734652863725771</v>
           </cell>
           <cell r="D5">
-            <v>-1.7559281802439597</v>
+            <v>-1.7298565048007308</v>
           </cell>
           <cell r="E5">
-            <v>-2.0978964251628707</v>
+            <v>-2.0645656708817461</v>
           </cell>
           <cell r="F5">
-            <v>-2.3943565545859302</v>
+            <v>-2.357633648455304</v>
           </cell>
           <cell r="G5">
-            <v>-2.6519237112783922</v>
+            <v>-2.6140093324245939</v>
           </cell>
           <cell r="H5">
-            <v>-2.8791977291766524</v>
+            <v>-2.8407767554473717</v>
           </cell>
           <cell r="I5">
-            <v>-3.0856349330678157</v>
+            <v>-3.0464601393956126</v>
           </cell>
           <cell r="J5">
-            <v>-3.2749100713291068</v>
+            <v>-3.2343626267274828</v>
           </cell>
           <cell r="K5">
-            <v>-3.4513576987399319</v>
+            <v>-3.4088044589155264</v>
           </cell>
           <cell r="L5">
-            <v>-3.6186215870805505</v>
+            <v>-3.5735780011471041</v>
           </cell>
           <cell r="M5">
-            <v>-3.8740905187216068</v>
+            <v>-3.8263746283537015</v>
           </cell>
           <cell r="N5">
-            <v>-3.9869778110010246</v>
+            <v>-3.936158845468507</v>
           </cell>
           <cell r="O5">
-            <v>-4.0876115109099391</v>
+            <v>-4.0335630799199329</v>
           </cell>
           <cell r="P5">
-            <v>-4.1764905258227518</v>
+            <v>-4.1191956885294871</v>
           </cell>
           <cell r="Q5">
-            <v>-4.2564986174724044</v>
+            <v>-4.1960202976913274</v>
           </cell>
           <cell r="R5">
-            <v>-4.3303613971335526</v>
+            <v>-4.2668115222945557</v>
           </cell>
           <cell r="S5">
-            <v>-4.4050947454435381</v>
+            <v>-4.3385282847099305</v>
           </cell>
           <cell r="T5">
-            <v>-4.4790098408092671</v>
+            <v>-4.4095100887892924</v>
           </cell>
           <cell r="U5">
-            <v>-4.5535606178811356</v>
+            <v>-4.4812427552597729</v>
           </cell>
           <cell r="V5">
-            <v>-4.6297766233334041</v>
+            <v>-4.5547781342819116</v>
           </cell>
           <cell r="W5">
-            <v>-4.7086163761970727</v>
+            <v>-4.6311097941466812</v>
           </cell>
           <cell r="X5">
-            <v>-4.7898956513363284</v>
+            <v>-4.7099938027228561</v>
           </cell>
           <cell r="Y5">
-            <v>-4.8740905676174284</v>
+            <v>-4.7919176689637073</v>
           </cell>
           <cell r="Z5">
-            <v>-4.9613142198050468</v>
+            <v>-4.8769777598748458</v>
           </cell>
           <cell r="AA5">
-            <v>-5.0514570982640006</v>
+            <v>-4.965046439401311</v>
           </cell>
           <cell r="AB5">
-            <v>-5.1447338143938204</v>
+            <v>-5.0564131786857036</v>
           </cell>
           <cell r="AC5">
-            <v>-5.2378674530835774</v>
+            <v>-5.1476766199514916</v>
           </cell>
           <cell r="AD5">
-            <v>-5.332236485481479</v>
+            <v>-5.2402349400153199</v>
           </cell>
           <cell r="AE5">
-            <v>-5.4277070818575357</v>
+            <v>-5.333927805019723</v>
           </cell>
           <cell r="AF5">
-            <v>-5.5241238806707837</v>
+            <v>-5.4285754760130871</v>
           </cell>
           <cell r="AG5">
-            <v>-5.6212870882486277</v>
+            <v>-5.5239595975755229</v>
           </cell>
           <cell r="AH5">
-            <v>-5.7178485260679039</v>
+            <v>-5.6187350233234508</v>
           </cell>
           <cell r="AI5">
-            <v>-5.8144543086482319</v>
+            <v>-5.7135368368529278</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.9109497872461558</v>
+            <v>-5.808197333960619</v>
           </cell>
           <cell r="AK5">
-            <v>-6.0072231699979</v>
+            <v>-5.902594084908797</v>
           </cell>
           <cell r="AL5">
-            <v>-6.1031818886015721</v>
+            <v>-5.9966256826181734</v>
           </cell>
           <cell r="AM5">
-            <v>-6.1888335406893091</v>
+            <v>-6.0804467910879119</v>
           </cell>
           <cell r="AN5">
-            <v>-6.2718617874111597</v>
+            <v>-6.1616942705872919</v>
           </cell>
           <cell r="AO5">
-            <v>-6.3526479659515083</v>
+            <v>-6.2406874762081284</v>
           </cell>
           <cell r="AP5">
-            <v>-6.431783817156111</v>
+            <v>-6.3179600181405</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.5097582722041247</v>
+            <v>-6.3939607803403353</v>
           </cell>
           <cell r="AR5">
-            <v>-6.5853359230707564</v>
+            <v>-6.4674527934628916</v>
           </cell>
           <cell r="AS5">
-            <v>-6.6600018684073614</v>
+            <v>-6.5399125774206368</v>
           </cell>
           <cell r="AT5">
-            <v>-6.7340376702999087</v>
+            <v>-6.6116128037204565</v>
           </cell>
           <cell r="AU5">
-            <v>-6.8077123355999802</v>
+            <v>-6.6828151577913664</v>
           </cell>
           <cell r="AV5">
-            <v>-6.8812529999116245</v>
+            <v>-6.75374061275601</v>
           </cell>
           <cell r="AW5">
-            <v>-6.949499281721061</v>
+            <v>-6.8192810107848505</v>
           </cell>
           <cell r="AX5">
-            <v>-7.0167271114814467</v>
+            <v>-6.8837080079757857</v>
           </cell>
           <cell r="AY5">
-            <v>-7.0833702468528825</v>
+            <v>-6.9474240648402024</v>
           </cell>
           <cell r="AZ5">
-            <v>-7.1498659147384398</v>
+            <v>-7.0108335681959062</v>
           </cell>
           <cell r="BA5">
-            <v>-7.2165396597219651</v>
+            <v>-7.0742357919410859</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Données"/>
+      <sheetName val="Gr Macro"/>
+      <sheetName val="Gr inflation"/>
+      <sheetName val="Gr émissions"/>
+      <sheetName val="Gr conso éner"/>
+      <sheetName val="GR macro ener"/>
+      <sheetName val="Gr éner prim"/>
+      <sheetName val="BUIL (class,base)"/>
+      <sheetName val="BUIL (class,shock)"/>
+      <sheetName val="Auto (class,base)"/>
+      <sheetName val="Auto (class,shock)"/>
+      <sheetName val="Auto (ener,shock)"/>
+      <sheetName val="Auto (ener,base)"/>
+      <sheetName val="Employment"/>
+      <sheetName val="Investment"/>
+      <sheetName val="Firms' emissions"/>
+      <sheetName val="Capital intensity"/>
+      <sheetName val="Energy intensity"/>
+      <sheetName val="Gr VA secteurs (% dev)"/>
+      <sheetName val="Gr VA secteurs (% share)"/>
+      <sheetName val="Gr Y secteurs (% dev)"/>
+      <sheetName val="Gr Y secteurs (% share)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="C5">
+            <v>-1.4134377529451903</v>
+          </cell>
+          <cell r="D5">
+            <v>-1.793521960439437</v>
+          </cell>
+          <cell r="E5">
+            <v>-2.1433063256721785</v>
+          </cell>
+          <cell r="F5">
+            <v>-2.4463052308986932</v>
+          </cell>
+          <cell r="G5">
+            <v>-2.7093767723510687</v>
+          </cell>
+          <cell r="H5">
+            <v>-2.9407512271360292</v>
+          </cell>
+          <cell r="I5">
+            <v>-3.1497704598259069</v>
+          </cell>
+          <cell r="J5">
+            <v>-3.3401167883251315</v>
+          </cell>
+          <cell r="K5">
+            <v>-3.5164428017359417</v>
+          </cell>
+          <cell r="L5">
+            <v>-3.682788566089934</v>
+          </cell>
+          <cell r="M5">
+            <v>-3.9369483140161643</v>
+          </cell>
+          <cell r="N5">
+            <v>-4.0482551339010353</v>
+          </cell>
+          <cell r="O5">
+            <v>-4.1473819066695006</v>
+          </cell>
+          <cell r="P5">
+            <v>-4.2349535926846205</v>
+          </cell>
+          <cell r="Q5">
+            <v>-4.3139404547592131</v>
+          </cell>
+          <cell r="R5">
+            <v>-4.387112121402625</v>
+          </cell>
+          <cell r="S5">
+            <v>-4.4615417243119015</v>
+          </cell>
+          <cell r="T5">
+            <v>-4.535498089244494</v>
+          </cell>
+          <cell r="U5">
+            <v>-4.6104241154786507</v>
+          </cell>
+          <cell r="V5">
+            <v>-4.6873395633610926</v>
+          </cell>
+          <cell r="W5">
+            <v>-4.7673156312450837</v>
+          </cell>
+          <cell r="X5">
+            <v>-4.8498444305992372</v>
+          </cell>
+          <cell r="Y5">
+            <v>-4.9355299079195341</v>
+          </cell>
+          <cell r="Z5">
+            <v>-5.024452868139706</v>
+          </cell>
+          <cell r="AA5">
+            <v>-5.1164720848802308</v>
+          </cell>
+          <cell r="AB5">
+            <v>-5.2121771983503091</v>
+          </cell>
+          <cell r="AC5">
+            <v>-5.3075122406260888</v>
+          </cell>
+          <cell r="AD5">
+            <v>-5.4041074122913146</v>
+          </cell>
+          <cell r="AE5">
+            <v>-5.5018075134250282</v>
+          </cell>
+          <cell r="AF5">
+            <v>-5.6004375415494074</v>
+          </cell>
+          <cell r="AG5">
+            <v>-5.6997826557531379</v>
+          </cell>
+          <cell r="AH5">
+            <v>-5.7984634822230259</v>
+          </cell>
+          <cell r="AI5">
+            <v>-5.8971342988124782</v>
+          </cell>
+          <cell r="AJ5">
+            <v>-5.9956382581705441</v>
+          </cell>
+          <cell r="AK5">
+            <v>-6.0938611164246037</v>
+          </cell>
+          <cell r="AL5">
+            <v>-6.1917080267628872</v>
+          </cell>
+          <cell r="AM5">
+            <v>-6.2790779632635907</v>
+          </cell>
+          <cell r="AN5">
+            <v>-6.3636600616960308</v>
+          </cell>
+          <cell r="AO5">
+            <v>-6.4458492162444809</v>
+          </cell>
+          <cell r="AP5">
+            <v>-6.5262270211267071</v>
+          </cell>
+          <cell r="AQ5">
+            <v>-6.6052765500094202</v>
+          </cell>
+          <cell r="AR5">
+            <v>-6.6817298427610865</v>
+          </cell>
+          <cell r="AS5">
+            <v>-6.7571094605159754</v>
+          </cell>
+          <cell r="AT5">
+            <v>-6.8317161695697344</v>
+          </cell>
+          <cell r="AU5">
+            <v>-6.9058315740446847</v>
+          </cell>
+          <cell r="AV5">
+            <v>-6.9796909442198967</v>
+          </cell>
+          <cell r="AW5">
+            <v>-7.0479911434117026</v>
+          </cell>
+          <cell r="AX5">
+            <v>-7.1151098686792817</v>
+          </cell>
+          <cell r="AY5">
+            <v>-7.1814955125604873</v>
+          </cell>
+          <cell r="AZ5">
+            <v>-7.2475803820003515</v>
+          </cell>
+          <cell r="BA5">
+            <v>-7.3136815666987047</v>
           </cell>
         </row>
       </sheetData>
@@ -3573,7 +4140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" customWidth="1"/>
@@ -3581,207 +4148,207 @@
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
-        <f>[3]Données!C4</f>
+        <f>[1]Données!C4</f>
         <v>42005</v>
       </c>
       <c r="C1" s="1">
-        <f>[3]Données!D4</f>
+        <f>[1]Données!D4</f>
         <v>42370</v>
       </c>
       <c r="D1" s="1">
-        <f>[3]Données!E4</f>
+        <f>[1]Données!E4</f>
         <v>42736</v>
       </c>
       <c r="E1" s="1">
-        <f>[3]Données!F4</f>
+        <f>[1]Données!F4</f>
         <v>43101</v>
       </c>
       <c r="F1" s="1">
-        <f>[3]Données!G4</f>
+        <f>[1]Données!G4</f>
         <v>43466</v>
       </c>
       <c r="G1" s="1">
-        <f>[3]Données!H4</f>
+        <f>[1]Données!H4</f>
         <v>43831</v>
       </c>
       <c r="H1" s="1">
-        <f>[3]Données!I4</f>
+        <f>[1]Données!I4</f>
         <v>44197</v>
       </c>
       <c r="I1" s="1">
-        <f>[3]Données!J4</f>
+        <f>[1]Données!J4</f>
         <v>44562</v>
       </c>
       <c r="J1" s="1">
-        <f>[3]Données!K4</f>
+        <f>[1]Données!K4</f>
         <v>44927</v>
       </c>
       <c r="K1" s="1">
-        <f>[3]Données!L4</f>
+        <f>[1]Données!L4</f>
         <v>45292</v>
       </c>
       <c r="L1" s="1">
-        <f>[3]Données!M4</f>
+        <f>[1]Données!M4</f>
         <v>45658</v>
       </c>
       <c r="M1" s="1">
-        <f>[3]Données!N4</f>
+        <f>[1]Données!N4</f>
         <v>46023</v>
       </c>
       <c r="N1" s="1">
-        <f>[3]Données!O4</f>
+        <f>[1]Données!O4</f>
         <v>46388</v>
       </c>
       <c r="O1" s="1">
-        <f>[3]Données!P4</f>
+        <f>[1]Données!P4</f>
         <v>46753</v>
       </c>
       <c r="P1" s="1">
-        <f>[3]Données!Q4</f>
+        <f>[1]Données!Q4</f>
         <v>47119</v>
       </c>
       <c r="Q1" s="1">
-        <f>[3]Données!R4</f>
+        <f>[1]Données!R4</f>
         <v>47484</v>
       </c>
       <c r="R1" s="1">
-        <f>[3]Données!S4</f>
+        <f>[1]Données!S4</f>
         <v>47849</v>
       </c>
       <c r="S1" s="1">
-        <f>[3]Données!T4</f>
+        <f>[1]Données!T4</f>
         <v>48214</v>
       </c>
       <c r="T1" s="1">
-        <f>[3]Données!U4</f>
+        <f>[1]Données!U4</f>
         <v>48580</v>
       </c>
       <c r="U1" s="1">
-        <f>[3]Données!V4</f>
+        <f>[1]Données!V4</f>
         <v>48945</v>
       </c>
       <c r="V1" s="1">
-        <f>[3]Données!W4</f>
+        <f>[1]Données!W4</f>
         <v>49310</v>
       </c>
       <c r="W1" s="1">
-        <f>[3]Données!X4</f>
+        <f>[1]Données!X4</f>
         <v>49675</v>
       </c>
       <c r="X1" s="1">
-        <f>[3]Données!Y4</f>
+        <f>[1]Données!Y4</f>
         <v>50041</v>
       </c>
       <c r="Y1" s="1">
-        <f>[3]Données!Z4</f>
+        <f>[1]Données!Z4</f>
         <v>50406</v>
       </c>
       <c r="Z1" s="1">
-        <f>[3]Données!AA4</f>
+        <f>[1]Données!AA4</f>
         <v>50771</v>
       </c>
       <c r="AA1" s="1">
-        <f>[3]Données!AB4</f>
+        <f>[1]Données!AB4</f>
         <v>51136</v>
       </c>
       <c r="AB1" s="1">
-        <f>[3]Données!AC4</f>
+        <f>[1]Données!AC4</f>
         <v>51502</v>
       </c>
       <c r="AC1" s="1">
-        <f>[3]Données!AD4</f>
+        <f>[1]Données!AD4</f>
         <v>51867</v>
       </c>
       <c r="AD1" s="1">
-        <f>[3]Données!AE4</f>
+        <f>[1]Données!AE4</f>
         <v>52232</v>
       </c>
       <c r="AE1" s="1">
-        <f>[3]Données!AF4</f>
+        <f>[1]Données!AF4</f>
         <v>52597</v>
       </c>
       <c r="AF1" s="1">
-        <f>[3]Données!AG4</f>
+        <f>[1]Données!AG4</f>
         <v>52963</v>
       </c>
       <c r="AG1" s="1">
-        <f>[3]Données!AH4</f>
+        <f>[1]Données!AH4</f>
         <v>53328</v>
       </c>
       <c r="AH1" s="1">
-        <f>[3]Données!AI4</f>
+        <f>[1]Données!AI4</f>
         <v>53693</v>
       </c>
       <c r="AI1" s="1">
-        <f>[3]Données!AJ4</f>
+        <f>[1]Données!AJ4</f>
         <v>54058</v>
       </c>
       <c r="AJ1" s="1">
-        <f>[3]Données!AK4</f>
+        <f>[1]Données!AK4</f>
         <v>54424</v>
       </c>
       <c r="AK1" s="1">
-        <f>[3]Données!AL4</f>
+        <f>[1]Données!AL4</f>
         <v>54789</v>
       </c>
       <c r="AL1" s="1">
-        <f>[3]Données!AM4</f>
+        <f>[1]Données!AM4</f>
         <v>55154</v>
       </c>
       <c r="AM1" s="1">
-        <f>[3]Données!AN4</f>
+        <f>[1]Données!AN4</f>
         <v>55519</v>
       </c>
       <c r="AN1" s="1">
-        <f>[3]Données!AO4</f>
+        <f>[1]Données!AO4</f>
         <v>55885</v>
       </c>
       <c r="AO1" s="1">
-        <f>[3]Données!AP4</f>
+        <f>[1]Données!AP4</f>
         <v>56250</v>
       </c>
       <c r="AP1" s="1">
-        <f>[3]Données!AQ4</f>
+        <f>[1]Données!AQ4</f>
         <v>56615</v>
       </c>
       <c r="AQ1" s="1">
-        <f>[3]Données!AR4</f>
+        <f>[1]Données!AR4</f>
         <v>56980</v>
       </c>
       <c r="AR1" s="1">
-        <f>[3]Données!AS4</f>
+        <f>[1]Données!AS4</f>
         <v>57346</v>
       </c>
       <c r="AS1" s="1">
-        <f>[3]Données!AT4</f>
+        <f>[1]Données!AT4</f>
         <v>57711</v>
       </c>
       <c r="AT1" s="1">
-        <f>[3]Données!AU4</f>
+        <f>[1]Données!AU4</f>
         <v>58076</v>
       </c>
       <c r="AU1" s="1">
-        <f>[3]Données!AV4</f>
+        <f>[1]Données!AV4</f>
         <v>58441</v>
       </c>
       <c r="AV1" s="1">
-        <f>[3]Données!AW4</f>
+        <f>[1]Données!AW4</f>
         <v>58807</v>
       </c>
       <c r="AW1" s="1">
-        <f>[3]Données!AX4</f>
+        <f>[1]Données!AX4</f>
         <v>59172</v>
       </c>
       <c r="AX1" s="1">
-        <f>[3]Données!AY4</f>
+        <f>[1]Données!AY4</f>
         <v>59537</v>
       </c>
       <c r="AY1" s="1">
-        <f>[3]Données!AZ4</f>
+        <f>[1]Données!AZ4</f>
         <v>59902</v>
       </c>
       <c r="AZ1" s="1">
-        <f>[3]Données!BA4</f>
+        <f>[1]Données!BA4</f>
         <v>60268</v>
       </c>
     </row>
@@ -3790,208 +4357,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <f>(([1]Données!C5)/100)*-1</f>
+        <f>(([2]Données!C5)/100)*-1</f>
         <v>1.3538601712600906E-2</v>
       </c>
       <c r="C2" s="2">
-        <f>(([1]Données!D5)/100)*-1</f>
+        <f>(([2]Données!D5)/100)*-1</f>
         <v>1.6912679139984843E-2</v>
       </c>
       <c r="D2" s="2">
-        <f>(([1]Données!E5)/100)*-1</f>
+        <f>(([2]Données!E5)/100)*-1</f>
         <v>2.0115560050032899E-2</v>
       </c>
       <c r="E2" s="2">
-        <f>(([1]Données!F5)/100)*-1</f>
-        <v>2.2943774039713705E-2</v>
+        <f>(([2]Données!F5)/100)*-1</f>
+        <v>2.2943774902325131E-2</v>
       </c>
       <c r="F2" s="2">
-        <f>(([1]Données!G5)/100)*-1</f>
+        <f>(([2]Données!G5)/100)*-1</f>
         <v>2.5425308096377663E-2</v>
       </c>
       <c r="G2" s="2">
-        <f>(([1]Données!H5)/100)*-1</f>
+        <f>(([2]Données!H5)/100)*-1</f>
         <v>2.7611418605846372E-2</v>
       </c>
       <c r="H2" s="2">
-        <f>(([1]Données!I5)/100)*-1</f>
-        <v>2.9576927112697438E-2</v>
+        <f>(([2]Données!I5)/100)*-1</f>
+        <v>2.9576927529626262E-2</v>
       </c>
       <c r="I2" s="2">
-        <f>(([1]Données!J5)/100)*-1</f>
+        <f>(([2]Données!J5)/100)*-1</f>
         <v>3.1353239073615535E-2</v>
       </c>
       <c r="J2" s="2">
-        <f>(([1]Données!K5)/100)*-1</f>
+        <f>(([2]Données!K5)/100)*-1</f>
         <v>3.2985843392642766E-2</v>
       </c>
       <c r="K2" s="2">
-        <f>(([1]Données!L5)/100)*-1</f>
+        <f>(([2]Données!L5)/100)*-1</f>
         <v>3.4516237501799885E-2</v>
       </c>
       <c r="L2" s="2">
-        <f>(([1]Données!M5)/100)*-1</f>
-        <v>3.6927247035058564E-2</v>
+        <f>(([2]Données!M5)/100)*-1</f>
+        <v>3.6927247412231856E-2</v>
       </c>
       <c r="M2" s="2">
-        <f>(([1]Données!N5)/100)*-1</f>
+        <f>(([2]Données!N5)/100)*-1</f>
         <v>3.7901004681047845E-2</v>
       </c>
       <c r="N2" s="2">
-        <f>(([1]Données!O5)/100)*-1</f>
+        <f>(([2]Données!O5)/100)*-1</f>
         <v>3.8748605891280929E-2</v>
       </c>
       <c r="O2" s="2">
-        <f>(([1]Données!P5)/100)*-1</f>
-        <v>3.9477051314678935E-2</v>
+        <f>(([2]Données!P5)/100)*-1</f>
+        <v>3.9477051688237563E-2</v>
       </c>
       <c r="P2" s="2">
-        <f>(([1]Données!Q5)/100)*-1</f>
+        <f>(([2]Données!Q5)/100)*-1</f>
         <v>4.0116488877360634E-2</v>
       </c>
       <c r="Q2" s="2">
-        <f>(([1]Données!R5)/100)*-1</f>
+        <f>(([2]Données!R5)/100)*-1</f>
         <v>4.0694640941231978E-2</v>
       </c>
       <c r="R2" s="2">
-        <f>(([1]Données!S5)/100)*-1</f>
+        <f>(([2]Données!S5)/100)*-1</f>
         <v>4.1277964002331198E-2</v>
       </c>
       <c r="S2" s="2">
-        <f>(([1]Données!T5)/100)*-1</f>
+        <f>(([2]Données!T5)/100)*-1</f>
         <v>4.1849741026071745E-2</v>
       </c>
       <c r="T2" s="2">
-        <f>(([1]Données!U5)/100)*-1</f>
+        <f>(([2]Données!U5)/100)*-1</f>
         <v>4.2425458296820991E-2</v>
       </c>
       <c r="U2" s="2">
-        <f>(([1]Données!V5)/100)*-1</f>
+        <f>(([2]Données!V5)/100)*-1</f>
         <v>4.3016340742832782E-2</v>
       </c>
       <c r="V2" s="2">
-        <f>(([1]Données!W5)/100)*-1</f>
+        <f>(([2]Données!W5)/100)*-1</f>
         <v>4.3633104309372284E-2</v>
       </c>
       <c r="W2" s="2">
-        <f>(([1]Données!X5)/100)*-1</f>
+        <f>(([2]Données!X5)/100)*-1</f>
         <v>4.427314031618601E-2</v>
       </c>
       <c r="X2" s="2">
-        <f>(([1]Données!Y5)/100)*-1</f>
-        <v>4.4941592404026176E-2</v>
+        <f>(([2]Données!Y5)/100)*-1</f>
+        <v>4.4941592729452529E-2</v>
       </c>
       <c r="Y2" s="2">
-        <f>(([1]Données!Z5)/100)*-1</f>
+        <f>(([2]Données!Z5)/100)*-1</f>
         <v>4.563947337910957E-2</v>
       </c>
       <c r="Z2" s="2">
-        <f>(([1]Données!AA5)/100)*-1</f>
-        <v>4.6365522950460585E-2</v>
+        <f>(([2]Données!AA5)/100)*-1</f>
+        <v>4.6365523266142288E-2</v>
       </c>
       <c r="AA2" s="2">
-        <f>(([1]Données!AB5)/100)*-1</f>
+        <f>(([2]Données!AB5)/100)*-1</f>
         <v>4.7123697653551948E-2</v>
       </c>
       <c r="AB2" s="2">
-        <f>(([1]Données!AC5)/100)*-1</f>
+        <f>(([2]Données!AC5)/100)*-1</f>
         <v>4.788032119780028E-2</v>
       </c>
       <c r="AC2" s="2">
-        <f>(([1]Données!AD5)/100)*-1</f>
+        <f>(([2]Données!AD5)/100)*-1</f>
         <v>4.8649621572917197E-2</v>
       </c>
       <c r="AD2" s="2">
-        <f>(([1]Données!AE5)/100)*-1</f>
+        <f>(([2]Données!AE5)/100)*-1</f>
         <v>4.9429610515789646E-2</v>
       </c>
       <c r="AE2" s="2">
-        <f>(([1]Données!AF5)/100)*-1</f>
+        <f>(([2]Données!AF5)/100)*-1</f>
         <v>5.0218084317584018E-2</v>
       </c>
       <c r="AF2" s="2">
-        <f>(([1]Données!AG5)/100)*-1</f>
-        <v>5.1012621214923663E-2</v>
+        <f>(([2]Données!AG5)/100)*-1</f>
+        <v>5.1012621505727829E-2</v>
       </c>
       <c r="AG2" s="2">
-        <f>(([1]Données!AH5)/100)*-1</f>
+        <f>(([2]Données!AH5)/100)*-1</f>
         <v>5.1800471640880197E-2</v>
       </c>
       <c r="AH2" s="2">
-        <f>(([1]Données!AI5)/100)*-1</f>
+        <f>(([2]Données!AI5)/100)*-1</f>
         <v>5.2587995224248063E-2</v>
       </c>
       <c r="AI2" s="2">
-        <f>(([1]Données!AJ5)/100)*-1</f>
-        <v>5.337331162577863E-2</v>
+        <f>(([2]Données!AJ5)/100)*-1</f>
+        <v>5.33733113615723E-2</v>
       </c>
       <c r="AJ2" s="2">
-        <f>(([1]Données!AK5)/100)*-1</f>
+        <f>(([2]Données!AK5)/100)*-1</f>
         <v>5.4154996240649018E-2</v>
       </c>
       <c r="AK2" s="2">
-        <f>(([1]Données!AL5)/100)*-1</f>
-        <v>5.4931913241978665E-2</v>
+        <f>(([2]Données!AL5)/100)*-1</f>
+        <v>5.4931912985350273E-2</v>
       </c>
       <c r="AL2" s="2">
-        <f>(([1]Données!AM5)/100)*-1</f>
+        <f>(([2]Données!AM5)/100)*-1</f>
         <v>5.5612806592488247E-2</v>
       </c>
       <c r="AM2" s="2">
-        <f>(([1]Données!AN5)/100)*-1</f>
+        <f>(([2]Données!AN5)/100)*-1</f>
         <v>5.6273572035804416E-2</v>
       </c>
       <c r="AN2" s="2">
-        <f>(([1]Données!AO5)/100)*-1</f>
+        <f>(([2]Données!AO5)/100)*-1</f>
         <v>5.6914643529708646E-2</v>
       </c>
       <c r="AO2" s="2">
-        <f>(([1]Données!AP5)/100)*-1</f>
+        <f>(([2]Données!AP5)/100)*-1</f>
         <v>5.753897634474104E-2</v>
       </c>
       <c r="AP2" s="2">
-        <f>(([1]Données!AQ5)/100)*-1</f>
-        <v>5.8149801082812758E-2</v>
+        <f>(([2]Données!AQ5)/100)*-1</f>
+        <v>5.8149801337017311E-2</v>
       </c>
       <c r="AQ2" s="2">
-        <f>(([1]Données!AR5)/100)*-1</f>
+        <f>(([2]Données!AR5)/100)*-1</f>
         <v>5.8735596987392939E-2</v>
       </c>
       <c r="AR2" s="2">
-        <f>(([1]Données!AS5)/100)*-1</f>
+        <f>(([2]Données!AS5)/100)*-1</f>
         <v>5.9311343796265348E-2</v>
       </c>
       <c r="AS2" s="2">
-        <f>(([1]Données!AT5)/100)*-1</f>
-        <v>5.9879563848025723E-2</v>
+        <f>(([2]Données!AT5)/100)*-1</f>
+        <v>5.9879563862663465E-2</v>
       </c>
       <c r="AT2" s="2">
-        <f>(([1]Données!AU5)/100)*-1</f>
+        <f>(([2]Données!AU5)/100)*-1</f>
         <v>6.0442828733665251E-2</v>
       </c>
       <c r="AU2" s="2">
-        <f>(([1]Données!AV5)/100)*-1</f>
+        <f>(([2]Données!AV5)/100)*-1</f>
         <v>6.1003296850866917E-2</v>
       </c>
       <c r="AV2" s="2">
-        <f>(([1]Données!AW5)/100)*-1</f>
-        <v>6.1513652453118454E-2</v>
+        <f>(([2]Données!AW5)/100)*-1</f>
+        <v>6.1513652688195419E-2</v>
       </c>
       <c r="AW2" s="2">
-        <f>(([1]Données!AX5)/100)*-1</f>
+        <f>(([2]Données!AX5)/100)*-1</f>
         <v>6.2016559531788203E-2</v>
       </c>
       <c r="AX2" s="2">
-        <f>(([1]Données!AY5)/100)*-1</f>
-        <v>6.251429610217496E-2</v>
+        <f>(([2]Données!AY5)/100)*-1</f>
+        <v>6.2514296331188435E-2</v>
       </c>
       <c r="AY2" s="2">
-        <f>(([1]Données!AZ5)/100)*-1</f>
-        <v>6.3009329761051225E-2</v>
+        <f>(([2]Données!AZ5)/100)*-1</f>
+        <v>6.3009329987089857E-2</v>
       </c>
       <c r="AZ2" s="4">
-        <f>(([1]Données!BA5)/100)*-1</f>
-        <v>6.3503741189399388E-2</v>
+        <f>(([2]Données!BA5)/100)*-1</f>
+        <v>6.3503741412501813E-2</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.35">
@@ -3999,208 +4566,208 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <f>(([2]Données!C5)/100)*-1</f>
-        <v>1.3817003835391084E-2</v>
+        <f>(([3]Données!C5)/100)*-1</f>
+        <v>1.3672989606358987E-2</v>
       </c>
       <c r="C3" s="2">
-        <f>(([2]Données!D5)/100)*-1</f>
-        <v>1.743513173626321E-2</v>
+        <f>(([3]Données!D5)/100)*-1</f>
+        <v>1.7174495306202409E-2</v>
       </c>
       <c r="D3" s="2">
-        <f>(([2]Données!E5)/100)*-1</f>
-        <v>2.0810900271980293E-2</v>
+        <f>(([3]Données!E5)/100)*-1</f>
+        <v>2.0477676385590282E-2</v>
       </c>
       <c r="E3" s="2">
-        <f>(([2]Données!F5)/100)*-1</f>
-        <v>2.37482308328546E-2</v>
+        <f>(([3]Données!F5)/100)*-1</f>
+        <v>2.338101922407565E-2</v>
       </c>
       <c r="F3" s="2">
-        <f>(([2]Données!G5)/100)*-1</f>
-        <v>2.6303621837913016E-2</v>
+        <f>(([3]Données!G5)/100)*-1</f>
+        <v>2.5924392080600156E-2</v>
       </c>
       <c r="G3" s="2">
-        <f>(([2]Données!H5)/100)*-1</f>
-        <v>2.8554745649720381E-2</v>
+        <f>(([3]Données!H5)/100)*-1</f>
+        <v>2.8170343744913895E-2</v>
       </c>
       <c r="H3" s="2">
-        <f>(([2]Données!I5)/100)*-1</f>
-        <v>3.0591714219359134E-2</v>
+        <f>(([3]Données!I5)/100)*-1</f>
+        <v>3.0199679852574546E-2</v>
       </c>
       <c r="I3" s="2">
-        <f>(([2]Données!J5)/100)*-1</f>
-        <v>3.2450478843843999E-2</v>
+        <f>(([3]Données!J5)/100)*-1</f>
+        <v>3.2044636480139999E-2</v>
       </c>
       <c r="J3" s="2">
-        <f>(([2]Données!K5)/100)*-1</f>
-        <v>3.4175766044356681E-2</v>
+        <f>(([3]Données!K5)/100)*-1</f>
+        <v>3.3749792479178753E-2</v>
       </c>
       <c r="K3" s="2">
-        <f>(([2]Données!L5)/100)*-1</f>
-        <v>3.5806058245103856E-2</v>
+        <f>(([3]Données!L5)/100)*-1</f>
+        <v>3.5355106743683251E-2</v>
       </c>
       <c r="L3" s="2">
-        <f>(([2]Données!M5)/100)*-1</f>
-        <v>3.8317865579032384E-2</v>
+        <f>(([3]Données!M5)/100)*-1</f>
+        <v>3.7840113348240667E-2</v>
       </c>
       <c r="M3" s="2">
-        <f>(([2]Données!N5)/100)*-1</f>
-        <v>3.9401504124790709E-2</v>
+        <f>(([3]Données!N5)/100)*-1</f>
+        <v>3.8892630987244492E-2</v>
       </c>
       <c r="N3" s="2">
-        <f>(([2]Données!O5)/100)*-1</f>
-        <v>4.0361895698596717E-2</v>
+        <f>(([3]Données!O5)/100)*-1</f>
+        <v>3.9820630063436724E-2</v>
       </c>
       <c r="O3" s="2">
-        <f>(([2]Données!P5)/100)*-1</f>
-        <v>4.1204463998199437E-2</v>
+        <f>(([3]Données!P5)/100)*-1</f>
+        <v>4.0630615722784924E-2</v>
       </c>
       <c r="P3" s="2">
-        <f>(([2]Données!Q5)/100)*-1</f>
-        <v>4.1958141290400326E-2</v>
+        <f>(([3]Données!Q5)/100)*-1</f>
+        <v>4.1352345269782598E-2</v>
       </c>
       <c r="Q3" s="2">
-        <f>(([2]Données!R5)/100)*-1</f>
-        <v>4.2649961126306819E-2</v>
+        <f>(([3]Données!R5)/100)*-1</f>
+        <v>4.2013346077308E-2</v>
       </c>
       <c r="R3" s="2">
-        <f>(([2]Données!S5)/100)*-1</f>
-        <v>4.3348570228646688E-2</v>
+        <f>(([3]Données!S5)/100)*-1</f>
+        <v>4.2681694202585163E-2</v>
       </c>
       <c r="S3" s="2">
-        <f>(([2]Données!T5)/100)*-1</f>
-        <v>4.4036672055925541E-2</v>
+        <f>(([3]Données!T5)/100)*-1</f>
+        <v>4.3340377092348274E-2</v>
       </c>
       <c r="T3" s="2">
-        <f>(([2]Données!U5)/100)*-1</f>
-        <v>4.472892175080679E-2</v>
+        <f>(([3]Données!U5)/100)*-1</f>
+        <v>4.4004366322958344E-2</v>
       </c>
       <c r="U3" s="2">
-        <f>(([2]Données!V5)/100)*-1</f>
-        <v>4.5435752297462988E-2</v>
+        <f>(([3]Données!V5)/100)*-1</f>
+        <v>4.4684316308185368E-2</v>
       </c>
       <c r="V3" s="2">
-        <f>(([2]Données!W5)/100)*-1</f>
-        <v>4.6166841961263645E-2</v>
+        <f>(([3]Données!W5)/100)*-1</f>
+        <v>4.5390251562328017E-2</v>
       </c>
       <c r="W3" s="2">
-        <f>(([2]Données!X5)/100)*-1</f>
-        <v>4.6920146370500133E-2</v>
+        <f>(([3]Données!X5)/100)*-1</f>
+        <v>4.6119526770055375E-2</v>
       </c>
       <c r="X3" s="2">
-        <f>(([2]Données!Y5)/100)*-1</f>
-        <v>4.7700386101506842E-2</v>
+        <f>(([3]Données!Y5)/100)*-1</f>
+        <v>4.6876974335740673E-2</v>
       </c>
       <c r="Y3" s="2">
-        <f>(([2]Données!Z5)/100)*-1</f>
-        <v>4.8508636134620635E-2</v>
+        <f>(([3]Données!Z5)/100)*-1</f>
+        <v>4.7663498416245842E-2</v>
       </c>
       <c r="Z3" s="2">
-        <f>(([2]Données!AA5)/100)*-1</f>
-        <v>4.9343774287709079E-2</v>
+        <f>(([3]Données!AA5)/100)*-1</f>
+        <v>4.8477793812705346E-2</v>
       </c>
       <c r="AA3" s="2">
-        <f>(([2]Données!AB5)/100)*-1</f>
-        <v>5.0208240339022048E-2</v>
+        <f>(([3]Données!AB5)/100)*-1</f>
+        <v>4.932305011022297E-2</v>
       </c>
       <c r="AB3" s="2">
-        <f>(([2]Données!AC5)/100)*-1</f>
-        <v>5.1069629307100135E-2</v>
+        <f>(([3]Données!AC5)/100)*-1</f>
+        <v>5.0165613008498644E-2</v>
       </c>
       <c r="AC3" s="2">
-        <f>(([2]Données!AD5)/100)*-1</f>
-        <v>5.1941904606602529E-2</v>
+        <f>(([3]Données!AD5)/100)*-1</f>
+        <v>5.1019643979885787E-2</v>
       </c>
       <c r="AD3" s="2">
-        <f>(([2]Données!AE5)/100)*-1</f>
-        <v>5.2823596780353095E-2</v>
+        <f>(([3]Données!AE5)/100)*-1</f>
+        <v>5.1883408595703721E-2</v>
       </c>
       <c r="AE3" s="2">
-        <f>(([2]Données!AF5)/100)*-1</f>
-        <v>5.37130422710047E-2</v>
+        <f>(([3]Données!AF5)/100)*-1</f>
+        <v>5.2755001072149588E-2</v>
       </c>
       <c r="AF3" s="2">
-        <f>(([2]Données!AG5)/100)*-1</f>
-        <v>5.4608243916526966E-2</v>
+        <f>(([3]Données!AG5)/100)*-1</f>
+        <v>5.3632237777372464E-2</v>
       </c>
       <c r="AG3" s="2">
-        <f>(([2]Données!AH5)/100)*-1</f>
-        <v>5.5496192249441023E-2</v>
+        <f>(([3]Données!AH5)/100)*-1</f>
+        <v>5.4502122415457599E-2</v>
       </c>
       <c r="AH3" s="2">
-        <f>(([2]Données!AI5)/100)*-1</f>
-        <v>5.6383436484206066E-2</v>
+        <f>(([3]Données!AI5)/100)*-1</f>
+        <v>5.5371105410730204E-2</v>
       </c>
       <c r="AI3" s="2">
-        <f>(([2]Données!AJ5)/100)*-1</f>
-        <v>5.726834401942426E-2</v>
+        <f>(([3]Données!AJ5)/100)*-1</f>
+        <v>5.6237434247091933E-2</v>
       </c>
       <c r="AJ3" s="2">
-        <f>(([2]Données!AK5)/100)*-1</f>
-        <v>5.8149718869707101E-2</v>
+        <f>(([3]Données!AK5)/100)*-1</f>
+        <v>5.7099803973477137E-2</v>
       </c>
       <c r="AK3" s="2">
-        <f>(([2]Données!AL5)/100)*-1</f>
-        <v>5.9026601997417154E-2</v>
+        <f>(([3]Données!AL5)/100)*-1</f>
+        <v>5.7957164990088073E-2</v>
       </c>
       <c r="AL3" s="2">
-        <f>(([2]Données!AM5)/100)*-1</f>
-        <v>5.9802895418140878E-2</v>
+        <f>(([3]Données!AM5)/100)*-1</f>
+        <v>5.8714889271429434E-2</v>
       </c>
       <c r="AM3" s="2">
-        <f>(([2]Données!AN5)/100)*-1</f>
-        <v>6.0555320304058302E-2</v>
+        <f>(([3]Données!AN5)/100)*-1</f>
+        <v>5.9449229672438812E-2</v>
       </c>
       <c r="AN3" s="2">
-        <f>(([2]Données!AO5)/100)*-1</f>
-        <v>6.1285910820933938E-2</v>
+        <f>(([3]Données!AO5)/100)*-1</f>
+        <v>6.0161600156355854E-2</v>
       </c>
       <c r="AO3" s="2">
-        <f>(([2]Données!AP5)/100)*-1</f>
-        <v>6.1999209769188039E-2</v>
+        <f>(([3]Données!AP5)/100)*-1</f>
+        <v>6.0855962145012106E-2</v>
       </c>
       <c r="AP3" s="2">
-        <f>(([2]Données!AQ5)/100)*-1</f>
-        <v>6.2699584064028979E-2</v>
+        <f>(([3]Données!AQ5)/100)*-1</f>
+        <v>6.1536280510864468E-2</v>
       </c>
       <c r="AQ3" s="2">
-        <f>(([2]Données!AR5)/100)*-1</f>
-        <v>6.3375430839892166E-2</v>
+        <f>(([3]Données!AR5)/100)*-1</f>
+        <v>6.2190933045863532E-2</v>
       </c>
       <c r="AR3" s="2">
-        <f>(([2]Données!AS5)/100)*-1</f>
-        <v>6.4041984514666583E-2</v>
+        <f>(([3]Données!AS5)/100)*-1</f>
+        <v>6.2835066098031023E-2</v>
       </c>
       <c r="AS3" s="2">
-        <f>(([2]Données!AT5)/100)*-1</f>
-        <v>6.4702120871606761E-2</v>
+        <f>(([3]Données!AT5)/100)*-1</f>
+        <v>6.3471463173807252E-2</v>
       </c>
       <c r="AT3" s="2">
-        <f>(([2]Données!AU5)/100)*-1</f>
-        <v>6.5358501296639782E-2</v>
+        <f>(([3]Données!AU5)/100)*-1</f>
+        <v>6.4102710957324671E-2</v>
       </c>
       <c r="AU3" s="2">
-        <f>(([2]Données!AV5)/100)*-1</f>
-        <v>6.6013343336437047E-2</v>
+        <f>(([3]Données!AV5)/100)*-1</f>
+        <v>6.4730962309951678E-2</v>
       </c>
       <c r="AV3" s="2">
-        <f>(([2]Données!AW5)/100)*-1</f>
-        <v>6.6617208449575416E-2</v>
+        <f>(([3]Données!AW5)/100)*-1</f>
+        <v>6.5307300641254673E-2</v>
       </c>
       <c r="AW3" s="2">
-        <f>(([2]Données!AX5)/100)*-1</f>
-        <v>6.7212787141227692E-2</v>
+        <f>(([3]Données!AX5)/100)*-1</f>
+        <v>6.5874374029159188E-2</v>
       </c>
       <c r="AX3" s="2">
-        <f>(([2]Données!AY5)/100)*-1</f>
-        <v>6.7803179119039103E-2</v>
+        <f>(([3]Données!AY5)/100)*-1</f>
+        <v>6.6434968759283564E-2</v>
       </c>
       <c r="AY3" s="2">
-        <f>(([2]Données!AZ5)/100)*-1</f>
-        <v>6.8391735845303669E-2</v>
+        <f>(([3]Données!AZ5)/100)*-1</f>
+        <v>6.6992107040962479E-2</v>
       </c>
       <c r="AZ3" s="4">
-        <f>(([2]Données!BA5)/100)*-1</f>
-        <v>6.8981230170323315E-2</v>
+        <f>(([3]Données!BA5)/100)*-1</f>
+        <v>6.7548297126593604E-2</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.35">
@@ -4208,1463 +4775,1881 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <f>([4]Données!C5/100)*-1</f>
-        <v>1.3878691631188045E-2</v>
+        <f>-0.01*[4]Données!C5</f>
+        <v>1.3734652863725771E-2</v>
       </c>
       <c r="C4" s="2">
         <f>([4]Données!D5/100)*-1</f>
-        <v>1.7559281802439597E-2</v>
+        <v>1.7298565048007308E-2</v>
       </c>
       <c r="D4" s="2">
         <f>([4]Données!E5/100)*-1</f>
-        <v>2.0978964251628707E-2</v>
+        <v>2.0645656708817461E-2</v>
       </c>
       <c r="E4" s="2">
         <f>([4]Données!F5/100)*-1</f>
-        <v>2.3943565545859302E-2</v>
+        <v>2.357633648455304E-2</v>
       </c>
       <c r="F4" s="2">
         <f>([4]Données!G5/100)*-1</f>
-        <v>2.6519237112783922E-2</v>
+        <v>2.6140093324245939E-2</v>
       </c>
       <c r="G4" s="2">
         <f>([4]Données!H5/100)*-1</f>
-        <v>2.8791977291766524E-2</v>
+        <v>2.8407767554473717E-2</v>
       </c>
       <c r="H4" s="2">
         <f>([4]Données!I5/100)*-1</f>
-        <v>3.0856349330678157E-2</v>
+        <v>3.0464601393956126E-2</v>
       </c>
       <c r="I4" s="2">
         <f>([4]Données!J5/100)*-1</f>
-        <v>3.2749100713291068E-2</v>
+        <v>3.2343626267274828E-2</v>
       </c>
       <c r="J4" s="2">
         <f>([4]Données!K5/100)*-1</f>
-        <v>3.4513576987399319E-2</v>
+        <v>3.4088044589155264E-2</v>
       </c>
       <c r="K4" s="2">
         <f>([4]Données!L5/100)*-1</f>
-        <v>3.6186215870805505E-2</v>
+        <v>3.5735780011471041E-2</v>
       </c>
       <c r="L4" s="2">
         <f>([4]Données!M5/100)*-1</f>
-        <v>3.8740905187216068E-2</v>
+        <v>3.8263746283537015E-2</v>
       </c>
       <c r="M4" s="2">
         <f>([4]Données!N5/100)*-1</f>
-        <v>3.9869778110010246E-2</v>
+        <v>3.936158845468507E-2</v>
       </c>
       <c r="N4" s="2">
         <f>([4]Données!O5/100)*-1</f>
-        <v>4.0876115109099394E-2</v>
+        <v>4.0335630799199329E-2</v>
       </c>
       <c r="O4" s="2">
         <f>([4]Données!P5/100)*-1</f>
-        <v>4.1764905258227521E-2</v>
+        <v>4.1191956885294874E-2</v>
       </c>
       <c r="P4" s="2">
         <f>([4]Données!Q5/100)*-1</f>
-        <v>4.2564986174724047E-2</v>
+        <v>4.1960202976913274E-2</v>
       </c>
       <c r="Q4" s="2">
         <f>([4]Données!R5/100)*-1</f>
-        <v>4.3303613971335524E-2</v>
+        <v>4.2668115222945557E-2</v>
       </c>
       <c r="R4" s="2">
         <f>([4]Données!S5/100)*-1</f>
-        <v>4.4050947454435378E-2</v>
+        <v>4.3385282847099305E-2</v>
       </c>
       <c r="S4" s="2">
         <f>([4]Données!T5/100)*-1</f>
-        <v>4.4790098408092671E-2</v>
+        <v>4.4095100887892924E-2</v>
       </c>
       <c r="T4" s="2">
         <f>([4]Données!U5/100)*-1</f>
-        <v>4.5535606178811354E-2</v>
+        <v>4.4812427552597726E-2</v>
       </c>
       <c r="U4" s="2">
         <f>([4]Données!V5/100)*-1</f>
-        <v>4.6297766233334044E-2</v>
+        <v>4.5547781342819116E-2</v>
       </c>
       <c r="V4" s="2">
         <f>([4]Données!W5/100)*-1</f>
-        <v>4.708616376197073E-2</v>
+        <v>4.631109794146681E-2</v>
       </c>
       <c r="W4" s="2">
         <f>([4]Données!X5/100)*-1</f>
-        <v>4.7898956513363282E-2</v>
+        <v>4.7099938027228561E-2</v>
       </c>
       <c r="X4" s="2">
         <f>([4]Données!Y5/100)*-1</f>
-        <v>4.8740905676174284E-2</v>
+        <v>4.791917668963707E-2</v>
       </c>
       <c r="Y4" s="2">
         <f>([4]Données!Z5/100)*-1</f>
-        <v>4.9613142198050471E-2</v>
+        <v>4.8769777598748461E-2</v>
       </c>
       <c r="Z4" s="2">
         <f>([4]Données!AA5/100)*-1</f>
-        <v>5.0514570982640006E-2</v>
+        <v>4.9650464394013112E-2</v>
       </c>
       <c r="AA4" s="2">
         <f>([4]Données!AB5/100)*-1</f>
-        <v>5.1447338143938204E-2</v>
+        <v>5.0564131786857036E-2</v>
       </c>
       <c r="AB4" s="2">
         <f>([4]Données!AC5/100)*-1</f>
-        <v>5.2378674530835771E-2</v>
+        <v>5.1476766199514919E-2</v>
       </c>
       <c r="AC4" s="2">
         <f>([4]Données!AD5/100)*-1</f>
-        <v>5.3322364854814792E-2</v>
+        <v>5.2402349400153196E-2</v>
       </c>
       <c r="AD4" s="2">
         <f>([4]Données!AE5/100)*-1</f>
-        <v>5.4277070818575357E-2</v>
+        <v>5.3339278050197232E-2</v>
       </c>
       <c r="AE4" s="2">
         <f>([4]Données!AF5/100)*-1</f>
-        <v>5.5241238806707837E-2</v>
+        <v>5.4285754760130873E-2</v>
       </c>
       <c r="AF4" s="2">
         <f>([4]Données!AG5/100)*-1</f>
-        <v>5.6212870882486277E-2</v>
+        <v>5.5239595975755229E-2</v>
       </c>
       <c r="AG4" s="2">
         <f>([4]Données!AH5/100)*-1</f>
-        <v>5.7178485260679042E-2</v>
+        <v>5.6187350233234505E-2</v>
       </c>
       <c r="AH4" s="2">
         <f>([4]Données!AI5/100)*-1</f>
-        <v>5.8144543086482321E-2</v>
+        <v>5.7135368368529275E-2</v>
       </c>
       <c r="AI4" s="2">
         <f>([4]Données!AJ5/100)*-1</f>
-        <v>5.9109497872461558E-2</v>
+        <v>5.8081973339606192E-2</v>
       </c>
       <c r="AJ4" s="2">
         <f>([4]Données!AK5/100)*-1</f>
-        <v>6.0072231699979002E-2</v>
+        <v>5.9025940849087973E-2</v>
       </c>
       <c r="AK4" s="2">
         <f>([4]Données!AL5/100)*-1</f>
-        <v>6.1031818886015721E-2</v>
+        <v>5.9966256826181737E-2</v>
       </c>
       <c r="AL4" s="2">
         <f>([4]Données!AM5/100)*-1</f>
-        <v>6.1888335406893091E-2</v>
+        <v>6.0804467910879116E-2</v>
       </c>
       <c r="AM4" s="2">
         <f>([4]Données!AN5/100)*-1</f>
-        <v>6.2718617874111593E-2</v>
+        <v>6.1616942705872917E-2</v>
       </c>
       <c r="AN4" s="2">
         <f>([4]Données!AO5/100)*-1</f>
-        <v>6.3526479659515078E-2</v>
+        <v>6.2406874762081281E-2</v>
       </c>
       <c r="AO4" s="2">
         <f>([4]Données!AP5/100)*-1</f>
-        <v>6.4317838171561115E-2</v>
+        <v>6.3179600181405005E-2</v>
       </c>
       <c r="AP4" s="2">
         <f>([4]Données!AQ5/100)*-1</f>
-        <v>6.5097582722041247E-2</v>
+        <v>6.3939607803403353E-2</v>
       </c>
       <c r="AQ4" s="2">
         <f>([4]Données!AR5/100)*-1</f>
-        <v>6.5853359230707564E-2</v>
+        <v>6.4674527934628911E-2</v>
       </c>
       <c r="AR4" s="2">
         <f>([4]Données!AS5/100)*-1</f>
-        <v>6.6600018684073614E-2</v>
+        <v>6.5399125774206368E-2</v>
       </c>
       <c r="AS4" s="2">
         <f>([4]Données!AT5/100)*-1</f>
-        <v>6.7340376702999083E-2</v>
+        <v>6.6116128037204569E-2</v>
       </c>
       <c r="AT4" s="2">
         <f>([4]Données!AU5/100)*-1</f>
-        <v>6.8077123355999802E-2</v>
+        <v>6.6828151577913664E-2</v>
       </c>
       <c r="AU4" s="2">
         <f>([4]Données!AV5/100)*-1</f>
-        <v>6.8812529999116245E-2</v>
+        <v>6.7537406127560096E-2</v>
       </c>
       <c r="AV4" s="2">
         <f>([4]Données!AW5/100)*-1</f>
-        <v>6.949499281721061E-2</v>
+        <v>6.8192810107848501E-2</v>
       </c>
       <c r="AW4" s="2">
         <f>([4]Données!AX5/100)*-1</f>
-        <v>7.0167271114814467E-2</v>
+        <v>6.8837080079757862E-2</v>
       </c>
       <c r="AX4" s="2">
         <f>([4]Données!AY5/100)*-1</f>
-        <v>7.0833702468528825E-2</v>
+        <v>6.9474240648402019E-2</v>
       </c>
       <c r="AY4" s="2">
         <f>([4]Données!AZ5/100)*-1</f>
-        <v>7.1498659147384402E-2</v>
+        <v>7.0108335681959066E-2</v>
       </c>
       <c r="AZ4" s="4">
         <f>([4]Données!BA5/100)*-1</f>
-        <v>7.2165396597219655E-2</v>
+        <v>7.0742357919410859E-2</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <f>-0.01*[5]Données!C5</f>
+        <v>1.4134377529451903E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <f>-0.01*[5]Données!D5</f>
+        <v>1.793521960439437E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <f>-0.01*[5]Données!E5</f>
+        <v>2.1433063256721785E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <f>-0.01*[5]Données!F5</f>
+        <v>2.4463052308986932E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <f>-0.01*[5]Données!G5</f>
+        <v>2.7093767723510687E-2</v>
+      </c>
+      <c r="G5" s="2">
+        <f>-0.01*[5]Données!H5</f>
+        <v>2.9407512271360292E-2</v>
+      </c>
+      <c r="H5" s="2">
+        <f>-0.01*[5]Données!I5</f>
+        <v>3.1497704598259069E-2</v>
+      </c>
+      <c r="I5" s="2">
+        <f>-0.01*[5]Données!J5</f>
+        <v>3.3401167883251315E-2</v>
+      </c>
+      <c r="J5" s="2">
+        <f>-0.01*[5]Données!K5</f>
+        <v>3.5164428017359417E-2</v>
+      </c>
+      <c r="K5" s="2">
+        <f>-0.01*[5]Données!L5</f>
+        <v>3.682788566089934E-2</v>
+      </c>
+      <c r="L5" s="2">
+        <f>-0.01*[5]Données!M5</f>
+        <v>3.9369483140161643E-2</v>
+      </c>
+      <c r="M5" s="2">
+        <f>-0.01*[5]Données!N5</f>
+        <v>4.0482551339010353E-2</v>
+      </c>
+      <c r="N5" s="2">
+        <f>-0.01*[5]Données!O5</f>
+        <v>4.1473819066695006E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <f>-0.01*[5]Données!P5</f>
+        <v>4.2349535926846205E-2</v>
+      </c>
+      <c r="P5" s="2">
+        <f>-0.01*[5]Données!Q5</f>
+        <v>4.3139404547592131E-2</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>-0.01*[5]Données!R5</f>
+        <v>4.3871121214026247E-2</v>
+      </c>
+      <c r="R5" s="2">
+        <f>-0.01*[5]Données!S5</f>
+        <v>4.4615417243119015E-2</v>
+      </c>
+      <c r="S5" s="2">
+        <f>-0.01*[5]Données!T5</f>
+        <v>4.535498089244494E-2</v>
+      </c>
+      <c r="T5" s="2">
+        <f>-0.01*[5]Données!U5</f>
+        <v>4.6104241154786507E-2</v>
+      </c>
+      <c r="U5" s="2">
+        <f>-0.01*[5]Données!V5</f>
+        <v>4.6873395633610926E-2</v>
+      </c>
+      <c r="V5" s="2">
+        <f>-0.01*[5]Données!W5</f>
+        <v>4.7673156312450837E-2</v>
+      </c>
+      <c r="W5" s="2">
+        <f>-0.01*[5]Données!X5</f>
+        <v>4.8498444305992372E-2</v>
+      </c>
+      <c r="X5" s="2">
+        <f>-0.01*[5]Données!Y5</f>
+        <v>4.9355299079195343E-2</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>-0.01*[5]Données!Z5</f>
+        <v>5.024452868139706E-2</v>
+      </c>
+      <c r="Z5" s="2">
+        <f>-0.01*[5]Données!AA5</f>
+        <v>5.116472084880231E-2</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>-0.01*[5]Données!AB5</f>
+        <v>5.2121771983503096E-2</v>
+      </c>
+      <c r="AB5" s="2">
+        <f>-0.01*[5]Données!AC5</f>
+        <v>5.3075122406260888E-2</v>
+      </c>
+      <c r="AC5" s="2">
+        <f>-0.01*[5]Données!AD5</f>
+        <v>5.4041074122913146E-2</v>
+      </c>
+      <c r="AD5" s="2">
+        <f>-0.01*[5]Données!AE5</f>
+        <v>5.5018075134250284E-2</v>
+      </c>
+      <c r="AE5" s="2">
+        <f>-0.01*[5]Données!AF5</f>
+        <v>5.6004375415494079E-2</v>
+      </c>
+      <c r="AF5" s="2">
+        <f>-0.01*[5]Données!AG5</f>
+        <v>5.6997826557531384E-2</v>
+      </c>
+      <c r="AG5" s="2">
+        <f>-0.01*[5]Données!AH5</f>
+        <v>5.7984634822230263E-2</v>
+      </c>
+      <c r="AH5" s="2">
+        <f>-0.01*[5]Données!AI5</f>
+        <v>5.8971342988124786E-2</v>
+      </c>
+      <c r="AI5" s="2">
+        <f>-0.01*[5]Données!AJ5</f>
+        <v>5.9956382581705443E-2</v>
+      </c>
+      <c r="AJ5" s="2">
+        <f>-0.01*[5]Données!AK5</f>
+        <v>6.0938611164246037E-2</v>
+      </c>
+      <c r="AK5" s="2">
+        <f>-0.01*[5]Données!AL5</f>
+        <v>6.1917080267628877E-2</v>
+      </c>
+      <c r="AL5" s="2">
+        <f>-0.01*[5]Données!AM5</f>
+        <v>6.2790779632635907E-2</v>
+      </c>
+      <c r="AM5" s="2">
+        <f>-0.01*[5]Données!AN5</f>
+        <v>6.3636600616960304E-2</v>
+      </c>
+      <c r="AN5" s="2">
+        <f>-0.01*[5]Données!AO5</f>
+        <v>6.4458492162444814E-2</v>
+      </c>
+      <c r="AO5" s="2">
+        <f>-0.01*[5]Données!AP5</f>
+        <v>6.5262270211267071E-2</v>
+      </c>
+      <c r="AP5" s="2">
+        <f>-0.01*[5]Données!AQ5</f>
+        <v>6.6052765500094202E-2</v>
+      </c>
+      <c r="AQ5" s="2">
+        <f>-0.01*[5]Données!AR5</f>
+        <v>6.6817298427610861E-2</v>
+      </c>
+      <c r="AR5" s="2">
+        <f>-0.01*[5]Données!AS5</f>
+        <v>6.7571094605159754E-2</v>
+      </c>
+      <c r="AS5" s="2">
+        <f>-0.01*[5]Données!AT5</f>
+        <v>6.8317161695697348E-2</v>
+      </c>
+      <c r="AT5" s="2">
+        <f>-0.01*[5]Données!AU5</f>
+        <v>6.9058315740446852E-2</v>
+      </c>
+      <c r="AU5" s="2">
+        <f>-0.01*[5]Données!AV5</f>
+        <v>6.9796909442198962E-2</v>
+      </c>
+      <c r="AV5" s="2">
+        <f>-0.01*[5]Données!AW5</f>
+        <v>7.0479911434117026E-2</v>
+      </c>
+      <c r="AW5" s="2">
+        <f>-0.01*[5]Données!AX5</f>
+        <v>7.1151098686792813E-2</v>
+      </c>
+      <c r="AX5" s="2">
+        <f>-0.01*[5]Données!AY5</f>
+        <v>7.1814955125604873E-2</v>
+      </c>
+      <c r="AY5" s="2">
+        <f>-0.01*[5]Données!AZ5</f>
+        <v>7.2475803820003515E-2</v>
+      </c>
+      <c r="AZ5" s="4">
+        <f>-0.01*[5]Données!BA5</f>
+        <v>7.3136815666987043E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="2">
-        <f>(([3]Données!C5)/100)*-1</f>
-        <v>1.3806021979057337E-2</v>
-      </c>
-      <c r="C5" s="2">
-        <f>(([3]Données!D5)/100)*-1</f>
-        <v>1.7480486286687191E-2</v>
-      </c>
-      <c r="D5" s="2">
-        <f>(([3]Données!E5)/100)*-1</f>
-        <v>2.0891661472786871E-2</v>
-      </c>
-      <c r="E5" s="2">
-        <f>(([3]Données!F5)/100)*-1</f>
-        <v>2.3845793038393404E-2</v>
-      </c>
-      <c r="F5" s="2">
-        <f>(([3]Données!G5)/100)*-1</f>
-        <v>2.641080340774693E-2</v>
-      </c>
-      <c r="G5" s="2">
-        <f>(([3]Données!H5)/100)*-1</f>
-        <v>2.8674419026982645E-2</v>
-      </c>
-      <c r="H5" s="2">
-        <f>(([3]Données!I5)/100)*-1</f>
-        <v>3.0732049106733994E-2</v>
-      </c>
-      <c r="I5" s="2">
-        <f>(([3]Données!J5)/100)*-1</f>
-        <v>3.2620496645927366E-2</v>
-      </c>
-      <c r="J5" s="2">
-        <f>(([3]Données!K5)/100)*-1</f>
-        <v>3.4382447698241725E-2</v>
-      </c>
-      <c r="K5" s="2">
-        <f>(([3]Données!L5)/100)*-1</f>
-        <v>3.6053091816805383E-2</v>
-      </c>
-      <c r="L5" s="2">
-        <f>(([3]Données!M5)/100)*-1</f>
-        <v>3.8605332841323614E-2</v>
-      </c>
-      <c r="M5" s="2">
-        <f>(([3]Données!N5)/100)*-1</f>
-        <v>3.9729931402567087E-2</v>
-      </c>
-      <c r="N5" s="2">
-        <f>(([3]Données!O5)/100)*-1</f>
-        <v>4.0730645930684206E-2</v>
-      </c>
-      <c r="O5" s="2">
-        <f>(([3]Données!P5)/100)*-1</f>
-        <v>4.1612842658112159E-2</v>
-      </c>
-      <c r="P5" s="2">
-        <f>(([3]Données!Q5)/100)*-1</f>
-        <v>4.2405890614810919E-2</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>(([3]Données!R5)/100)*-1</f>
-        <v>4.3137536103815766E-2</v>
-      </c>
-      <c r="R5" s="2">
-        <f>(([3]Données!S5)/100)*-1</f>
-        <v>4.3878096041695895E-2</v>
-      </c>
-      <c r="S5" s="2">
-        <f>(([3]Données!T5)/100)*-1</f>
-        <v>4.461106315736741E-2</v>
-      </c>
-      <c r="T5" s="2">
-        <f>(([3]Données!U5)/100)*-1</f>
-        <v>4.5351085377838496E-2</v>
-      </c>
-      <c r="U5" s="2">
-        <f>(([3]Données!V5)/100)*-1</f>
-        <v>4.6108494006062199E-2</v>
-      </c>
-      <c r="V5" s="2">
-        <f>(([3]Données!W5)/100)*-1</f>
-        <v>4.6892738198556883E-2</v>
-      </c>
-      <c r="W5" s="2">
-        <f>(([3]Données!X5)/100)*-1</f>
-        <v>4.7702100401025509E-2</v>
-      </c>
-      <c r="X5" s="2">
-        <f>(([3]Données!Y5)/100)*-1</f>
-        <v>4.8541150572132159E-2</v>
-      </c>
-      <c r="Y5" s="2">
-        <f>(([3]Données!Z5)/100)*-1</f>
-        <v>4.941090213409572E-2</v>
-      </c>
-      <c r="Z5" s="2">
-        <f>(([3]Données!AA5)/100)*-1</f>
-        <v>5.0310152897432465E-2</v>
-      </c>
-      <c r="AA5" s="2">
-        <f>(([3]Données!AB5)/100)*-1</f>
-        <v>5.1240634534562846E-2</v>
-      </c>
-      <c r="AB5" s="2">
-        <f>(([3]Données!AC5)/100)*-1</f>
-        <v>5.2170075163591401E-2</v>
-      </c>
-      <c r="AC5" s="2">
-        <f>(([3]Données!AD5)/100)*-1</f>
-        <v>5.3111987688361124E-2</v>
-      </c>
-      <c r="AD5" s="2">
-        <f>(([3]Données!AE5)/100)*-1</f>
-        <v>5.4064971725801936E-2</v>
-      </c>
-      <c r="AE5" s="2">
-        <f>(([3]Données!AF5)/100)*-1</f>
-        <v>5.502742944986528E-2</v>
-      </c>
-      <c r="AF5" s="2">
-        <f>(([3]Données!AG5)/100)*-1</f>
-        <v>5.5997344016054162E-2</v>
-      </c>
-      <c r="AG5" s="2">
-        <f>(([3]Données!AH5)/100)*-1</f>
-        <v>5.6961288349583583E-2</v>
-      </c>
-      <c r="AH5" s="2">
-        <f>(([3]Données!AI5)/100)*-1</f>
-        <v>5.7925701399403451E-2</v>
-      </c>
-      <c r="AI5" s="2">
-        <f>(([3]Données!AJ5)/100)*-1</f>
-        <v>5.8889061572018238E-2</v>
-      </c>
-      <c r="AJ5" s="2">
-        <f>(([3]Données!AK5)/100)*-1</f>
-        <v>5.9850274064450752E-2</v>
-      </c>
-      <c r="AK5" s="2">
-        <f>(([3]Données!AL5)/100)*-1</f>
-        <v>6.0808439463491348E-2</v>
-      </c>
-      <c r="AL5" s="2">
-        <f>(([3]Données!AM5)/100)*-1</f>
-        <v>6.1664061587992425E-2</v>
-      </c>
-      <c r="AM5" s="2">
-        <f>(([3]Données!AN5)/100)*-1</f>
-        <v>6.2493723799826102E-2</v>
-      </c>
-      <c r="AN5" s="2">
-        <f>(([3]Données!AO5)/100)*-1</f>
-        <v>6.3301235386888588E-2</v>
-      </c>
-      <c r="AO5" s="2">
-        <f>(([3]Données!AP5)/100)*-1</f>
-        <v>6.4092469543638786E-2</v>
-      </c>
-      <c r="AP5" s="2">
-        <f>(([3]Données!AQ5)/100)*-1</f>
-        <v>6.4872276706564036E-2</v>
-      </c>
-      <c r="AQ5" s="2">
-        <f>(([3]Données!AR5)/100)*-1</f>
-        <v>6.5628351790368078E-2</v>
-      </c>
-      <c r="AR5" s="2">
-        <f>(([3]Données!AS5)/100)*-1</f>
-        <v>6.6375475313916299E-2</v>
-      </c>
-      <c r="AS5" s="2">
-        <f>(([3]Données!AT5)/100)*-1</f>
-        <v>6.7116454172487572E-2</v>
-      </c>
-      <c r="AT5" s="2">
-        <f>(([3]Données!AU5)/100)*-1</f>
-        <v>6.7853971166916494E-2</v>
-      </c>
-      <c r="AU5" s="2">
-        <f>(([3]Données!AV5)/100)*-1</f>
-        <v>6.859029758116808E-2</v>
-      </c>
-      <c r="AV5" s="2">
-        <f>(([3]Données!AW5)/100)*-1</f>
-        <v>6.9274087709707666E-2</v>
-      </c>
-      <c r="AW5" s="2">
-        <f>(([3]Données!AX5)/100)*-1</f>
-        <v>6.9947916420658562E-2</v>
-      </c>
-      <c r="AX5" s="2">
-        <f>(([3]Données!AY5)/100)*-1</f>
-        <v>7.0616110227255446E-2</v>
-      </c>
-      <c r="AY5" s="2">
-        <f>(([3]Données!AZ5)/100)*-1</f>
-        <v>7.1283018366647188E-2</v>
-      </c>
-      <c r="AZ5" s="4">
-        <f>(([3]Données!BA5)/100)*-1</f>
-        <v>7.1951879397782914E-2</v>
+      <c r="B6" s="2">
+        <f>(([1]Données!C5)/100)*-1</f>
+        <v>1.4356607550249811E-2</v>
+      </c>
+      <c r="C6" s="2">
+        <f>(([1]Données!D5)/100)*-1</f>
+        <v>1.8359555756829793E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <f>(([1]Données!E5)/100)*-1</f>
+        <v>2.1979111734358292E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <f>(([1]Données!F5)/100)*-1</f>
+        <v>2.5068879367789454E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <f>(([1]Données!G5)/100)*-1</f>
+        <v>2.7723085374654066E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <f>(([1]Données!H5)/100)*-1</f>
+        <v>3.0045484289630386E-2</v>
+      </c>
+      <c r="H6" s="2">
+        <f>(([1]Données!I5)/100)*-1</f>
+        <v>3.2142934801796197E-2</v>
+      </c>
+      <c r="I6" s="2">
+        <f>(([1]Données!J5)/100)*-1</f>
+        <v>3.4057681683389962E-2</v>
+      </c>
+      <c r="J6" s="2">
+        <f>(([1]Données!K5)/100)*-1</f>
+        <v>3.5837204760872599E-2</v>
+      </c>
+      <c r="K6" s="2">
+        <f>(([1]Données!L5)/100)*-1</f>
+        <v>3.7520252823447842E-2</v>
+      </c>
+      <c r="L6" s="2">
+        <f>(([1]Données!M5)/100)*-1</f>
+        <v>4.0081351725834595E-2</v>
+      </c>
+      <c r="M6" s="2">
+        <f>(([1]Données!N5)/100)*-1</f>
+        <v>4.1216477863235346E-2</v>
+      </c>
+      <c r="N6" s="2">
+        <f>(([1]Données!O5)/100)*-1</f>
+        <v>4.2229563987969287E-2</v>
+      </c>
+      <c r="O6" s="2">
+        <f>(([1]Données!P5)/100)*-1</f>
+        <v>4.3126393087284498E-2</v>
+      </c>
+      <c r="P6" s="2">
+        <f>(([1]Données!Q5)/100)*-1</f>
+        <v>4.3936550525898961E-2</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>(([1]Données!R5)/100)*-1</f>
+        <v>4.4687819847009196E-2</v>
+      </c>
+      <c r="R6" s="2">
+        <f>(([1]Données!S5)/100)*-1</f>
+        <v>4.5451866935080625E-2</v>
+      </c>
+      <c r="S6" s="2">
+        <f>(([1]Données!T5)/100)*-1</f>
+        <v>4.6211401290769845E-2</v>
+      </c>
+      <c r="T6" s="2">
+        <f>(([1]Données!U5)/100)*-1</f>
+        <v>4.6980586975273519E-2</v>
+      </c>
+      <c r="U6" s="2">
+        <f>(([1]Données!V5)/100)*-1</f>
+        <v>4.776938291292588E-2</v>
+      </c>
+      <c r="V6" s="2">
+        <f>(([1]Données!W5)/100)*-1</f>
+        <v>4.8588189167100948E-2</v>
+      </c>
+      <c r="W6" s="2">
+        <f>(([1]Données!X5)/100)*-1</f>
+        <v>4.9432039654755178E-2</v>
+      </c>
+      <c r="X6" s="2">
+        <f>(([1]Données!Y5)/100)*-1</f>
+        <v>5.0307012754312819E-2</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>(([1]Données!Z5)/100)*-1</f>
+        <v>5.121388057047449E-2</v>
+      </c>
+      <c r="Z6" s="2">
+        <f>(([1]Données!AA5)/100)*-1</f>
+        <v>5.2151234582306749E-2</v>
+      </c>
+      <c r="AA6" s="2">
+        <f>(([1]Données!AB5)/100)*-1</f>
+        <v>5.3124301885619118E-2</v>
+      </c>
+      <c r="AB6" s="2">
+        <f>(([1]Données!AC5)/100)*-1</f>
+        <v>5.4092994435144807E-2</v>
+      </c>
+      <c r="AC6" s="2">
+        <f>(([1]Données!AD5)/100)*-1</f>
+        <v>5.5073732374418372E-2</v>
+      </c>
+      <c r="AD6" s="2">
+        <f>(([1]Données!AE5)/100)*-1</f>
+        <v>5.6065126380332009E-2</v>
+      </c>
+      <c r="AE6" s="2">
+        <f>(([1]Données!AF5)/100)*-1</f>
+        <v>5.7065596853837386E-2</v>
+      </c>
+      <c r="AF6" s="2">
+        <f>(([1]Données!AG5)/100)*-1</f>
+        <v>5.8073135619838956E-2</v>
+      </c>
+      <c r="AG6" s="2">
+        <f>(([1]Données!AH5)/100)*-1</f>
+        <v>5.9073929102841483E-2</v>
+      </c>
+      <c r="AH6" s="2">
+        <f>(([1]Données!AI5)/100)*-1</f>
+        <v>6.0074605961998317E-2</v>
+      </c>
+      <c r="AI6" s="2">
+        <f>(([1]Données!AJ5)/100)*-1</f>
+        <v>6.1073754817270502E-2</v>
+      </c>
+      <c r="AJ6" s="2">
+        <f>(([1]Données!AK5)/100)*-1</f>
+        <v>6.2070369634980693E-2</v>
+      </c>
+      <c r="AK6" s="2">
+        <f>(([1]Données!AL5)/100)*-1</f>
+        <v>6.3063627377578424E-2</v>
+      </c>
+      <c r="AL6" s="2">
+        <f>(([1]Données!AM5)/100)*-1</f>
+        <v>6.3951403745941215E-2</v>
+      </c>
+      <c r="AM6" s="2">
+        <f>(([1]Données!AN5)/100)*-1</f>
+        <v>6.4810741844546271E-2</v>
+      </c>
+      <c r="AN6" s="2">
+        <f>(([1]Données!AO5)/100)*-1</f>
+        <v>6.5646312808184004E-2</v>
+      </c>
+      <c r="AO6" s="2">
+        <f>(([1]Données!AP5)/100)*-1</f>
+        <v>6.6464542713124852E-2</v>
+      </c>
+      <c r="AP6" s="2">
+        <f>(([1]Données!AQ5)/100)*-1</f>
+        <v>6.7270680566533958E-2</v>
+      </c>
+      <c r="AQ6" s="2">
+        <f>(([1]Données!AR5)/100)*-1</f>
+        <v>6.8052133812488314E-2</v>
+      </c>
+      <c r="AR6" s="2">
+        <f>(([1]Données!AS5)/100)*-1</f>
+        <v>6.8824193466577088E-2</v>
+      </c>
+      <c r="AS6" s="2">
+        <f>(([1]Données!AT5)/100)*-1</f>
+        <v>6.9589988528039215E-2</v>
+      </c>
+      <c r="AT6" s="2">
+        <f>(([1]Données!AU5)/100)*-1</f>
+        <v>7.0352434940294084E-2</v>
+      </c>
+      <c r="AU6" s="2">
+        <f>(([1]Données!AV5)/100)*-1</f>
+        <v>7.1113972671929981E-2</v>
+      </c>
+      <c r="AV6" s="2">
+        <f>(([1]Données!AW5)/100)*-1</f>
+        <v>7.1821241744193354E-2</v>
+      </c>
+      <c r="AW6" s="2">
+        <f>(([1]Données!AX5)/100)*-1</f>
+        <v>7.2517928035785606E-2</v>
+      </c>
+      <c r="AX6" s="2">
+        <f>(([1]Données!AY5)/100)*-1</f>
+        <v>7.3208842235043092E-2</v>
+      </c>
+      <c r="AY6" s="2">
+        <f>(([1]Données!AZ5)/100)*-1</f>
+        <v>7.3898628273017075E-2</v>
+      </c>
+      <c r="AZ6" s="4">
+        <f>(([1]Données!BA5)/100)*-1</f>
+        <v>7.459070872987239E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="B7" s="1">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
         <f>B1</f>
         <v>42005</v>
       </c>
-      <c r="C7" s="1">
-        <f t="shared" ref="C7:AZ7" si="0">C1</f>
+      <c r="C8" s="1">
+        <f t="shared" ref="C8:AZ8" si="0">C1</f>
         <v>42370</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>42736</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <f t="shared" si="0"/>
         <v>43101</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>43466</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>43831</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>44197</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
         <v>44562</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J8" s="1">
         <f t="shared" si="0"/>
         <v>44927</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K8" s="1">
         <f t="shared" si="0"/>
         <v>45292</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L8" s="1">
         <f t="shared" si="0"/>
         <v>45658</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>46023</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N8" s="1">
         <f t="shared" si="0"/>
         <v>46388</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O8" s="1">
         <f t="shared" si="0"/>
         <v>46753</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P8" s="1">
         <f t="shared" si="0"/>
         <v>47119</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q8" s="1">
         <f t="shared" si="0"/>
         <v>47484</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R8" s="1">
         <f t="shared" si="0"/>
         <v>47849</v>
       </c>
-      <c r="S7" s="1">
+      <c r="S8" s="1">
         <f t="shared" si="0"/>
         <v>48214</v>
       </c>
-      <c r="T7" s="1">
+      <c r="T8" s="1">
         <f t="shared" si="0"/>
         <v>48580</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U8" s="1">
         <f t="shared" si="0"/>
         <v>48945</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V8" s="1">
         <f t="shared" si="0"/>
         <v>49310</v>
       </c>
-      <c r="W7" s="1">
+      <c r="W8" s="1">
         <f t="shared" si="0"/>
         <v>49675</v>
       </c>
-      <c r="X7" s="1">
+      <c r="X8" s="1">
         <f t="shared" si="0"/>
         <v>50041</v>
       </c>
-      <c r="Y7" s="1">
+      <c r="Y8" s="1">
         <f t="shared" si="0"/>
         <v>50406</v>
       </c>
-      <c r="Z7" s="1">
+      <c r="Z8" s="1">
         <f t="shared" si="0"/>
         <v>50771</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="AA8" s="1">
         <f t="shared" si="0"/>
         <v>51136</v>
       </c>
-      <c r="AB7" s="1">
+      <c r="AB8" s="1">
         <f t="shared" si="0"/>
         <v>51502</v>
       </c>
-      <c r="AC7" s="1">
+      <c r="AC8" s="1">
         <f t="shared" si="0"/>
         <v>51867</v>
       </c>
-      <c r="AD7" s="1">
+      <c r="AD8" s="1">
         <f t="shared" si="0"/>
         <v>52232</v>
       </c>
-      <c r="AE7" s="1">
+      <c r="AE8" s="1">
         <f t="shared" si="0"/>
         <v>52597</v>
       </c>
-      <c r="AF7" s="1">
+      <c r="AF8" s="1">
         <f t="shared" si="0"/>
         <v>52963</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AG8" s="1">
         <f t="shared" si="0"/>
         <v>53328</v>
       </c>
-      <c r="AH7" s="1">
+      <c r="AH8" s="1">
         <f t="shared" si="0"/>
         <v>53693</v>
       </c>
-      <c r="AI7" s="1">
+      <c r="AI8" s="1">
         <f t="shared" si="0"/>
         <v>54058</v>
       </c>
-      <c r="AJ7" s="1">
+      <c r="AJ8" s="1">
         <f t="shared" si="0"/>
         <v>54424</v>
       </c>
-      <c r="AK7" s="1">
+      <c r="AK8" s="1">
         <f t="shared" si="0"/>
         <v>54789</v>
       </c>
-      <c r="AL7" s="1">
+      <c r="AL8" s="1">
         <f t="shared" si="0"/>
         <v>55154</v>
       </c>
-      <c r="AM7" s="1">
+      <c r="AM8" s="1">
         <f t="shared" si="0"/>
         <v>55519</v>
       </c>
-      <c r="AN7" s="1">
+      <c r="AN8" s="1">
         <f t="shared" si="0"/>
         <v>55885</v>
       </c>
-      <c r="AO7" s="1">
+      <c r="AO8" s="1">
         <f t="shared" si="0"/>
         <v>56250</v>
       </c>
-      <c r="AP7" s="1">
+      <c r="AP8" s="1">
         <f t="shared" si="0"/>
         <v>56615</v>
       </c>
-      <c r="AQ7" s="1">
+      <c r="AQ8" s="1">
         <f t="shared" si="0"/>
         <v>56980</v>
       </c>
-      <c r="AR7" s="1">
+      <c r="AR8" s="1">
         <f t="shared" si="0"/>
         <v>57346</v>
       </c>
-      <c r="AS7" s="1">
+      <c r="AS8" s="1">
         <f t="shared" si="0"/>
         <v>57711</v>
       </c>
-      <c r="AT7" s="1">
+      <c r="AT8" s="1">
         <f t="shared" si="0"/>
         <v>58076</v>
       </c>
-      <c r="AU7" s="1">
+      <c r="AU8" s="1">
         <f t="shared" si="0"/>
         <v>58441</v>
       </c>
-      <c r="AV7" s="1">
+      <c r="AV8" s="1">
         <f t="shared" si="0"/>
         <v>58807</v>
       </c>
-      <c r="AW7" s="1">
+      <c r="AW8" s="1">
         <f t="shared" si="0"/>
         <v>59172</v>
       </c>
-      <c r="AX7" s="1">
+      <c r="AX8" s="1">
         <f t="shared" si="0"/>
         <v>59537</v>
       </c>
-      <c r="AY7" s="1">
+      <c r="AY8" s="1">
         <f t="shared" si="0"/>
         <v>59902</v>
       </c>
-      <c r="AZ7" s="1">
+      <c r="AZ8" s="1">
         <f t="shared" si="0"/>
         <v>60268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3">
-        <f>B2</f>
-        <v>1.3538601712600906E-2</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" ref="C8:AZ8" si="1">C2</f>
-        <v>1.6912679139984843E-2</v>
-      </c>
-      <c r="D8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.0115560050032899E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.2943774039713705E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.5425308096377663E-2</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.7611418605846372E-2</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="1"/>
-        <v>2.9576927112697438E-2</v>
-      </c>
-      <c r="I8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.1353239073615535E-2</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.2985843392642766E-2</v>
-      </c>
-      <c r="K8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.4516237501799885E-2</v>
-      </c>
-      <c r="L8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.6927247035058564E-2</v>
-      </c>
-      <c r="M8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.7901004681047845E-2</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.8748605891280929E-2</v>
-      </c>
-      <c r="O8" s="3">
-        <f t="shared" si="1"/>
-        <v>3.9477051314678935E-2</v>
-      </c>
-      <c r="P8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.0116488877360634E-2</v>
-      </c>
-      <c r="Q8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.0694640941231978E-2</v>
-      </c>
-      <c r="R8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.1277964002331198E-2</v>
-      </c>
-      <c r="S8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.1849741026071745E-2</v>
-      </c>
-      <c r="T8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.2425458296820991E-2</v>
-      </c>
-      <c r="U8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.3016340742832782E-2</v>
-      </c>
-      <c r="V8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.3633104309372284E-2</v>
-      </c>
-      <c r="W8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.427314031618601E-2</v>
-      </c>
-      <c r="X8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.4941592404026176E-2</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.563947337910957E-2</v>
-      </c>
-      <c r="Z8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.6365522950460585E-2</v>
-      </c>
-      <c r="AA8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.7123697653551948E-2</v>
-      </c>
-      <c r="AB8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.788032119780028E-2</v>
-      </c>
-      <c r="AC8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.8649621572917197E-2</v>
-      </c>
-      <c r="AD8" s="3">
-        <f t="shared" si="1"/>
-        <v>4.9429610515789646E-2</v>
-      </c>
-      <c r="AE8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.0218084317584018E-2</v>
-      </c>
-      <c r="AF8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.1012621214923663E-2</v>
-      </c>
-      <c r="AG8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.1800471640880197E-2</v>
-      </c>
-      <c r="AH8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.2587995224248063E-2</v>
-      </c>
-      <c r="AI8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.337331162577863E-2</v>
-      </c>
-      <c r="AJ8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.4154996240649018E-2</v>
-      </c>
-      <c r="AK8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.4931913241978665E-2</v>
-      </c>
-      <c r="AL8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.5612806592488247E-2</v>
-      </c>
-      <c r="AM8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.6273572035804416E-2</v>
-      </c>
-      <c r="AN8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.6914643529708646E-2</v>
-      </c>
-      <c r="AO8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.753897634474104E-2</v>
-      </c>
-      <c r="AP8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.8149801082812758E-2</v>
-      </c>
-      <c r="AQ8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.8735596987392939E-2</v>
-      </c>
-      <c r="AR8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.9311343796265348E-2</v>
-      </c>
-      <c r="AS8" s="3">
-        <f t="shared" si="1"/>
-        <v>5.9879563848025723E-2</v>
-      </c>
-      <c r="AT8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.0442828733665251E-2</v>
-      </c>
-      <c r="AU8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.1003296850866917E-2</v>
-      </c>
-      <c r="AV8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.1513652453118454E-2</v>
-      </c>
-      <c r="AW8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.2016559531788203E-2</v>
-      </c>
-      <c r="AX8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.251429610217496E-2</v>
-      </c>
-      <c r="AY8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.3009329761051225E-2</v>
-      </c>
-      <c r="AZ8" s="3">
-        <f t="shared" si="1"/>
-        <v>6.3503741189399388E-2</v>
       </c>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="3">
-        <f>B3-B2</f>
-        <v>2.7840212279017784E-4</v>
+        <f>B2</f>
+        <v>1.3538601712600906E-2</v>
       </c>
       <c r="C9" s="3">
-        <f t="shared" ref="C9:AZ9" si="2">C3-C2</f>
-        <v>5.224525962783666E-4</v>
+        <f t="shared" ref="C9:AZ9" si="1">C2</f>
+        <v>1.6912679139984843E-2</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="2"/>
-        <v>6.9534022194739364E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.0115560050032899E-2</v>
       </c>
       <c r="E9" s="3">
-        <f t="shared" si="2"/>
-        <v>8.0445679314089524E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.2943774902325131E-2</v>
       </c>
       <c r="F9" s="3">
-        <f t="shared" si="2"/>
-        <v>8.7831374153535258E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.5425308096377663E-2</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" si="2"/>
-        <v>9.4332704387400934E-4</v>
+        <f t="shared" si="1"/>
+        <v>2.7611418605846372E-2</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.0147871066616965E-3</v>
+        <f t="shared" si="1"/>
+        <v>2.9576927529626262E-2</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.0972397702284642E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.1353239073615535E-2</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.189922651713915E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.2985843392642766E-2</v>
       </c>
       <c r="K9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.289820743303971E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.4516237501799885E-2</v>
       </c>
       <c r="L9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.3906185439738206E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.6927247412231856E-2</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.5004994437428643E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.7901004681047845E-2</v>
       </c>
       <c r="N9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.6132898073157875E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.8748605891280929E-2</v>
       </c>
       <c r="O9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.7274126835205017E-3</v>
+        <f t="shared" si="1"/>
+        <v>3.9477051688237563E-2</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.8416524130396919E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.0116488877360634E-2</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" si="2"/>
-        <v>1.9553201850748408E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.0694640941231978E-2</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.0706062263154898E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.1277964002331198E-2</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.1869310298537961E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.1849741026071745E-2</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.303463453985799E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.2425458296820991E-2</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.4194115546302061E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.3016340742832782E-2</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.5337376518913615E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.3633104309372284E-2</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.647006054314123E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.427314031618601E-2</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.7587936974806659E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.4941592729452529E-2</v>
       </c>
       <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.8691627555110649E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.563947337910957E-2</v>
       </c>
       <c r="Z9" s="3">
-        <f t="shared" si="2"/>
-        <v>2.9782513372484942E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.6365523266142288E-2</v>
       </c>
       <c r="AA9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.0845426854701E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.7123697653551948E-2</v>
       </c>
       <c r="AB9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.1893081092998557E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.788032119780028E-2</v>
       </c>
       <c r="AC9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.2922830336853323E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.8649621572917197E-2</v>
       </c>
       <c r="AD9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.3939862645634492E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.9429610515789646E-2</v>
       </c>
       <c r="AE9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.4949579534206826E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.0218084317584018E-2</v>
       </c>
       <c r="AF9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.5956227016033029E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.1012621505727829E-2</v>
       </c>
       <c r="AG9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.6957206085608263E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.1800471640880197E-2</v>
       </c>
       <c r="AH9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.7954412599580031E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.2587995224248063E-2</v>
       </c>
       <c r="AI9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.8950323936456296E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.33733113615723E-2</v>
       </c>
       <c r="AJ9" s="3">
-        <f t="shared" si="2"/>
-        <v>3.9947226290580826E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.4154996240649018E-2</v>
       </c>
       <c r="AK9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.0946887554384886E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.4931912985350273E-2</v>
       </c>
       <c r="AL9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.1900888256526311E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.5612806592488247E-2</v>
       </c>
       <c r="AM9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.2817482682538863E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.6273572035804416E-2</v>
       </c>
       <c r="AN9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.371267291225292E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.6914643529708646E-2</v>
       </c>
       <c r="AO9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.4602334244469993E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.753897634474104E-2</v>
       </c>
       <c r="AP9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.5497829812162216E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.8149801337017311E-2</v>
       </c>
       <c r="AQ9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.6398338524992269E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.8735596987392939E-2</v>
       </c>
       <c r="AR9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.7306407184012356E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.9311343796265348E-2</v>
       </c>
       <c r="AS9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.822557023581038E-3</v>
+        <f t="shared" si="1"/>
+        <v>5.9879563862663465E-2</v>
       </c>
       <c r="AT9" s="3">
-        <f t="shared" si="2"/>
-        <v>4.915672562974531E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.0442828733665251E-2</v>
       </c>
       <c r="AU9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.0100464855701299E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.1003296850866917E-2</v>
       </c>
       <c r="AV9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.1035559964569613E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.1513652688195419E-2</v>
       </c>
       <c r="AW9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.1962276094394896E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.2016559531788203E-2</v>
       </c>
       <c r="AX9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.2888830168641432E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.2514296331188435E-2</v>
       </c>
       <c r="AY9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.3824060842524446E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.3009329987089857E-2</v>
       </c>
       <c r="AZ9" s="3">
-        <f t="shared" si="2"/>
-        <v>5.477488980923928E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.3503741412501813E-2</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3">
-        <f>B4-B3</f>
-        <v>6.168779579696082E-5</v>
+        <f>B3-B2</f>
+        <v>1.3438789375808113E-4</v>
       </c>
       <c r="C10" s="3">
-        <f t="shared" ref="C10:AZ10" si="3">C4-C3</f>
-        <v>1.2415006617638724E-4</v>
+        <f t="shared" ref="C10:AZ13" si="2">C3-C2</f>
+        <v>2.6181616621756554E-4</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6806397964841402E-4</v>
+        <f t="shared" si="2"/>
+        <v>3.621163355573831E-4</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9533471300470229E-4</v>
+        <f t="shared" si="2"/>
+        <v>4.3724432175051842E-4</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1561527487090615E-4</v>
+        <f t="shared" si="2"/>
+        <v>4.9908398422249256E-4</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.3723164204614289E-4</v>
+        <f t="shared" si="2"/>
+        <v>5.5892513906752317E-4</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.6463511131902262E-4</v>
+        <f t="shared" si="2"/>
+        <v>6.2275232294828342E-4</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.9862186944706881E-4</v>
+        <f t="shared" si="2"/>
+        <v>6.9139740652446324E-4</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="3"/>
-        <v>3.3781094304263792E-4</v>
+        <f t="shared" si="2"/>
+        <v>7.6394908653598659E-4</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="3"/>
-        <v>3.8015762570164924E-4</v>
+        <f t="shared" si="2"/>
+        <v>8.3886924188336653E-4</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" si="3"/>
-        <v>4.2303960818368402E-4</v>
+        <f t="shared" si="2"/>
+        <v>9.1286593600881094E-4</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="3"/>
-        <v>4.6827398521953612E-4</v>
+        <f t="shared" si="2"/>
+        <v>9.9162630619664682E-4</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" si="3"/>
-        <v>5.1421941050267678E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.0720241721557944E-3</v>
       </c>
       <c r="O10" s="3">
-        <f t="shared" si="3"/>
-        <v>5.604412600280842E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.1535640345473608E-3</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="3"/>
-        <v>6.0684488432372063E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.2358563924219634E-3</v>
       </c>
       <c r="Q10" s="3">
-        <f t="shared" si="3"/>
-        <v>6.5365284502870435E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.3187051360760219E-3</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="3"/>
-        <v>7.0237722578869038E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4037302002539651E-3</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" si="3"/>
-        <v>7.5342635216713028E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4906360662765294E-3</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" si="3"/>
-        <v>8.066844280045643E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.5789080261373531E-3</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" si="3"/>
-        <v>8.6201393587105601E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.6679755653525863E-3</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" si="3"/>
-        <v>9.1932180070708469E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.7571472529557333E-3</v>
       </c>
       <c r="W10" s="3">
-        <f t="shared" si="3"/>
-        <v>9.7881014286314849E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.8463864538693642E-3</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.0405195746674423E-3</v>
+        <f t="shared" si="2"/>
+        <v>1.9353816062881446E-3</v>
       </c>
       <c r="Y10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.1045060634298359E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.024025037136272E-3</v>
       </c>
       <c r="Z10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.170796694930927E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.1122705465630581E-3</v>
       </c>
       <c r="AA10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.2390978049161561E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.1993524566710221E-3</v>
       </c>
       <c r="AB10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.3090452237356359E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.2852918106983644E-3</v>
       </c>
       <c r="AC10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.3804602482122633E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.3700224069685902E-3</v>
       </c>
       <c r="AD10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.4534740382222619E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.4537980799140754E-3</v>
       </c>
       <c r="AE10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.5281965357031371E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.5369167545655699E-3</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6046269659593104E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.6196162716446356E-3</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.6822930112380188E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.7016507745774021E-3</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.761106602276255E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.7831101864821406E-3</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.8411538530372987E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.8641228855196335E-3</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="3"/>
-        <v>1.9225128302719011E-3</v>
+        <f t="shared" si="2"/>
+        <v>2.9448077328281183E-3</v>
       </c>
       <c r="AK10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.0052168885985669E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.0252520047377995E-3</v>
       </c>
       <c r="AL10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.0854399887522135E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.1020826789411871E-3</v>
       </c>
       <c r="AM10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.1632975700532908E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.1756576366343964E-3</v>
       </c>
       <c r="AN10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.2405688385811404E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.2469566266472086E-3</v>
       </c>
       <c r="AO10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.3186284023730755E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.3169858002710662E-3</v>
       </c>
       <c r="AP10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.3979986580122681E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.3864791738471567E-3</v>
       </c>
       <c r="AQ10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.4779283908153982E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.4553360584705928E-3</v>
       </c>
       <c r="AR10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.5580341694070308E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.5237223017656749E-3</v>
       </c>
       <c r="AS10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.6382558313923221E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.5918993111437869E-3</v>
       </c>
       <c r="AT10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.7186220593600208E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.6598822236594206E-3</v>
       </c>
       <c r="AU10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.7991866626791984E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.7276654590847613E-3</v>
       </c>
       <c r="AV10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.8777843676351944E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.7936479530592537E-3</v>
       </c>
       <c r="AW10" s="3">
-        <f t="shared" si="3"/>
-        <v>2.9544839735867745E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.8578144973709858E-3</v>
       </c>
       <c r="AX10" s="3">
-        <f t="shared" si="3"/>
-        <v>3.0305233494897221E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.9206724280951288E-3</v>
       </c>
       <c r="AY10" s="3">
-        <f t="shared" si="3"/>
-        <v>3.106923302080733E-3</v>
+        <f t="shared" si="2"/>
+        <v>3.9827770538726215E-3</v>
       </c>
       <c r="AZ10" s="3">
-        <f t="shared" si="3"/>
-        <v>3.1841664268963399E-3</v>
+        <f t="shared" si="2"/>
+        <v>4.0445557140917909E-3</v>
       </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3">
+        <f t="shared" ref="B11:Q13" si="3">B4-B3</f>
+        <v>6.166325736678413E-5</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" si="3"/>
+        <v>1.2406974180489971E-4</v>
+      </c>
+      <c r="D11" s="3">
+        <f t="shared" si="3"/>
+        <v>1.6798032322717926E-4</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="3"/>
+        <v>1.9531726047739006E-4</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="3"/>
+        <v>2.157012436457828E-4</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="3"/>
+        <v>2.3742380955982245E-4</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="3"/>
+        <v>2.6492154138157975E-4</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="3"/>
+        <v>2.9898978713482904E-4</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="3"/>
+        <v>3.3825210997651123E-4</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="3"/>
+        <v>3.8067326778778998E-4</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="3"/>
+        <v>4.2363293529634749E-4</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="3"/>
+        <v>4.6895746744057831E-4</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="3"/>
+        <v>5.1500073576260519E-4</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="3"/>
+        <v>5.6134116250994986E-4</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="3"/>
+        <v>6.0785770713067677E-4</v>
+      </c>
+      <c r="Q11" s="3">
+        <f t="shared" si="3"/>
+        <v>6.5476914563755706E-4</v>
+      </c>
+      <c r="R11" s="3">
+        <f t="shared" si="2"/>
+        <v>7.0358864451414149E-4</v>
+      </c>
+      <c r="S11" s="3">
+        <f t="shared" si="2"/>
+        <v>7.547237955446498E-4</v>
+      </c>
+      <c r="T11" s="3">
+        <f t="shared" si="2"/>
+        <v>8.0806122963938271E-4</v>
+      </c>
+      <c r="U11" s="3">
+        <f t="shared" si="2"/>
+        <v>8.6346503463374802E-4</v>
+      </c>
+      <c r="V11" s="3">
+        <f t="shared" si="2"/>
+        <v>9.2084637913879275E-4</v>
+      </c>
+      <c r="W11" s="3">
+        <f t="shared" si="2"/>
+        <v>9.80411257173186E-4</v>
+      </c>
+      <c r="X11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0422023538963973E-3</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1062791825026189E-3</v>
+      </c>
+      <c r="Z11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1726705813077665E-3</v>
+      </c>
+      <c r="AA11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2410816766340663E-3</v>
+      </c>
+      <c r="AB11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3111531910162746E-3</v>
+      </c>
+      <c r="AC11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3827054202674091E-3</v>
+      </c>
+      <c r="AD11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4558694544935108E-3</v>
+      </c>
+      <c r="AE11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.5307536879812858E-3</v>
+      </c>
+      <c r="AF11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.6073581983827648E-3</v>
+      </c>
+      <c r="AG11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.6852278177769062E-3</v>
+      </c>
+      <c r="AH11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.7642629577990718E-3</v>
+      </c>
+      <c r="AI11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8445390925142593E-3</v>
+      </c>
+      <c r="AJ11" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9261368756108357E-3</v>
+      </c>
+      <c r="AK11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.0090918360936641E-3</v>
+      </c>
+      <c r="AL11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.0895786394496824E-3</v>
+      </c>
+      <c r="AM11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1677130334341044E-3</v>
+      </c>
+      <c r="AN11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2452746057254266E-3</v>
+      </c>
+      <c r="AO11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3236380363928985E-3</v>
+      </c>
+      <c r="AP11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4033272925388857E-3</v>
+      </c>
+      <c r="AQ11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4835948887653794E-3</v>
+      </c>
+      <c r="AR11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5640596761753454E-3</v>
+      </c>
+      <c r="AS11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.6446648633973169E-3</v>
+      </c>
+      <c r="AT11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7254406205889925E-3</v>
+      </c>
+      <c r="AU11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.8064438176084172E-3</v>
+      </c>
+      <c r="AV11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.8855094665938275E-3</v>
+      </c>
+      <c r="AW11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.9627060505986735E-3</v>
+      </c>
+      <c r="AX11" s="3">
+        <f t="shared" si="2"/>
+        <v>3.0392718891184556E-3</v>
+      </c>
+      <c r="AY11" s="3">
+        <f t="shared" si="2"/>
+        <v>3.1162286409965878E-3</v>
+      </c>
+      <c r="AZ11" s="3">
+        <f t="shared" si="2"/>
+        <v>3.1940607928172549E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <f t="shared" si="3"/>
+        <v>3.9972466572613108E-4</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="2"/>
+        <v>6.3665455638706181E-4</v>
+      </c>
+      <c r="D12" s="3">
+        <f t="shared" si="2"/>
+        <v>7.8740654790432352E-4</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="2"/>
+        <v>8.8671582443389241E-4</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="2"/>
+        <v>9.5367439926474784E-4</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="2"/>
+        <v>9.9974471688657474E-4</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0331032043029431E-3</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0575416159764872E-3</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0763834282041529E-3</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0921056494282988E-3</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1057368566246284E-3</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1209628843252828E-3</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1381882674956767E-3</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1575790415513307E-3</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1792015706788561E-3</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2030059910806898E-3</v>
+      </c>
+      <c r="R12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2301343960197109E-3</v>
+      </c>
+      <c r="S12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2598800045520164E-3</v>
+      </c>
+      <c r="T12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2918136021887808E-3</v>
+      </c>
+      <c r="U12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.32561429079181E-3</v>
+      </c>
+      <c r="V12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3620583709840275E-3</v>
+      </c>
+      <c r="W12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3985062787638114E-3</v>
+      </c>
+      <c r="X12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4361223895582725E-3</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4747510826485996E-3</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.5142564547891979E-3</v>
+      </c>
+      <c r="AA12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.5576401966460596E-3</v>
+      </c>
+      <c r="AB12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.5983562067459697E-3</v>
+      </c>
+      <c r="AC12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.6387247227599502E-3</v>
+      </c>
+      <c r="AD12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.6787970840530519E-3</v>
+      </c>
+      <c r="AE12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.7186206553632052E-3</v>
+      </c>
+      <c r="AF12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.7582305817761545E-3</v>
+      </c>
+      <c r="AG12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.7972845889957581E-3</v>
+      </c>
+      <c r="AH12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8359746195955109E-3</v>
+      </c>
+      <c r="AI12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8744092420992509E-3</v>
+      </c>
+      <c r="AJ12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9126703151580646E-3</v>
+      </c>
+      <c r="AK12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9508234414471401E-3</v>
+      </c>
+      <c r="AL12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9863117217567908E-3</v>
+      </c>
+      <c r="AM12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.0196579110873872E-3</v>
+      </c>
+      <c r="AN12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.0516174003635326E-3</v>
+      </c>
+      <c r="AO12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.082670029862066E-3</v>
+      </c>
+      <c r="AP12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1131576966908483E-3</v>
+      </c>
+      <c r="AQ12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1427704929819491E-3</v>
+      </c>
+      <c r="AR12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.1719688309533858E-3</v>
+      </c>
+      <c r="AS12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2010336584927792E-3</v>
+      </c>
+      <c r="AT12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2301641625331881E-3</v>
+      </c>
+      <c r="AU12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2595033146388666E-3</v>
+      </c>
+      <c r="AV12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.2871013262685258E-3</v>
+      </c>
+      <c r="AW12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3140186070349511E-3</v>
+      </c>
+      <c r="AX12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3407144772028543E-3</v>
+      </c>
+      <c r="AY12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3674681380444484E-3</v>
+      </c>
+      <c r="AZ12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.3944577475761841E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="3">
-        <f>B5-B4</f>
-        <v>-7.2669652130707973E-5</v>
-      </c>
-      <c r="C11" s="3">
-        <f t="shared" ref="C11:AZ11" si="4">C5-C4</f>
-        <v>-7.879551575240562E-5</v>
-      </c>
-      <c r="D11" s="3">
-        <f t="shared" si="4"/>
-        <v>-8.7302778841835682E-5</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="4"/>
-        <v>-9.7772507465898606E-5</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.0843370503699212E-4</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.175582647838791E-4</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.2430022394416262E-4</v>
-      </c>
-      <c r="I11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.2860406736370233E-4</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.3112928915759436E-4</v>
-      </c>
-      <c r="K11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.3312405400012217E-4</v>
-      </c>
-      <c r="L11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.3557234589245404E-4</v>
-      </c>
-      <c r="M11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.3984670744315864E-4</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.4546917841518764E-4</v>
-      </c>
-      <c r="O11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.520626001153616E-4</v>
-      </c>
-      <c r="P11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.5909555991312774E-4</v>
-      </c>
-      <c r="Q11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.66077867519758E-4</v>
-      </c>
-      <c r="R11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.7285141273948312E-4</v>
-      </c>
-      <c r="S11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.79035250725261E-4</v>
-      </c>
-      <c r="T11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.84520800972858E-4</v>
-      </c>
-      <c r="U11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.8927222727184445E-4</v>
-      </c>
-      <c r="V11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.9342556341384737E-4</v>
-      </c>
-      <c r="W11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.9685611233777323E-4</v>
-      </c>
-      <c r="X11" s="3">
-        <f t="shared" si="4"/>
-        <v>-1.9975510404212499E-4</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.0224006395475058E-4</v>
-      </c>
-      <c r="Z11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.0441808520754029E-4</v>
-      </c>
-      <c r="AA11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.0670360937535825E-4</v>
-      </c>
-      <c r="AB11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.0859936724437061E-4</v>
-      </c>
-      <c r="AC11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.10377166453668E-4</v>
-      </c>
-      <c r="AD11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1209909277342121E-4</v>
-      </c>
-      <c r="AE11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1380935684255781E-4</v>
-      </c>
-      <c r="AF11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1552686643211416E-4</v>
-      </c>
-      <c r="AG11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1719691109545886E-4</v>
-      </c>
-      <c r="AH11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1884168707887036E-4</v>
-      </c>
-      <c r="AI11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2043630044332047E-4</v>
-      </c>
-      <c r="AJ11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2195763552824987E-4</v>
-      </c>
-      <c r="AK11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2337942252437237E-4</v>
-      </c>
-      <c r="AL11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2427381890066656E-4</v>
-      </c>
-      <c r="AM11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2489407428549074E-4</v>
-      </c>
-      <c r="AN11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2524427262649027E-4</v>
-      </c>
-      <c r="AO11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2536862792232881E-4</v>
-      </c>
-      <c r="AP11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.253060154772113E-4</v>
-      </c>
-      <c r="AQ11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2500744033948639E-4</v>
-      </c>
-      <c r="AR11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2454337015731518E-4</v>
-      </c>
-      <c r="AS11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2392253051151112E-4</v>
-      </c>
-      <c r="AT11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2315218908330881E-4</v>
-      </c>
-      <c r="AU11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2223241794816495E-4</v>
-      </c>
-      <c r="AV11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.2090510750294445E-4</v>
-      </c>
-      <c r="AW11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1935469415590436E-4</v>
-      </c>
-      <c r="AX11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1759224127337884E-4</v>
-      </c>
-      <c r="AY11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.1564078073721404E-4</v>
-      </c>
-      <c r="AZ11" s="3">
-        <f t="shared" si="4"/>
-        <v>-2.135171994367413E-4</v>
+      <c r="B13" s="3">
+        <f t="shared" si="3"/>
+        <v>2.2223002079790888E-4</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2433615243542278E-4</v>
+      </c>
+      <c r="D13" s="3">
+        <f t="shared" si="2"/>
+        <v>5.460484776365071E-4</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.0582705880252163E-4</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.2931765114337956E-4</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.3797201827009431E-4</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.4523020353712823E-4</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.5651380013864724E-4</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.7277674351318151E-4</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="2"/>
+        <v>6.9236716254850172E-4</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.1186858567295203E-4</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.339265242249926E-4</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.5574492127428172E-4</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.7685716043829345E-4</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="2"/>
+        <v>7.9714597830683048E-4</v>
+      </c>
+      <c r="Q13" s="3">
+        <f t="shared" si="2"/>
+        <v>8.1669863298294842E-4</v>
+      </c>
+      <c r="R13" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3644969196160907E-4</v>
+      </c>
+      <c r="S13" s="3">
+        <f t="shared" si="2"/>
+        <v>8.5642039832490441E-4</v>
+      </c>
+      <c r="T13" s="3">
+        <f t="shared" si="2"/>
+        <v>8.7634582048701226E-4</v>
+      </c>
+      <c r="U13" s="3">
+        <f t="shared" si="2"/>
+        <v>8.9598727931495398E-4</v>
+      </c>
+      <c r="V13" s="3">
+        <f t="shared" si="2"/>
+        <v>9.1503285465011075E-4</v>
+      </c>
+      <c r="W13" s="3">
+        <f t="shared" si="2"/>
+        <v>9.335953487628057E-4</v>
+      </c>
+      <c r="X13" s="3">
+        <f t="shared" si="2"/>
+        <v>9.5171367511747568E-4</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>9.6935188907742997E-4</v>
+      </c>
+      <c r="Z13" s="3">
+        <f t="shared" si="2"/>
+        <v>9.8651373350443911E-4</v>
+      </c>
+      <c r="AA13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0025299021160228E-3</v>
+      </c>
+      <c r="AB13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0178720288839191E-3</v>
+      </c>
+      <c r="AC13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0326582515052252E-3</v>
+      </c>
+      <c r="AD13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0470512460817247E-3</v>
+      </c>
+      <c r="AE13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0612214383433072E-3</v>
+      </c>
+      <c r="AF13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0753090623075723E-3</v>
+      </c>
+      <c r="AG13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.0892942806112194E-3</v>
+      </c>
+      <c r="AH13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1032629738735311E-3</v>
+      </c>
+      <c r="AI13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1173722355650589E-3</v>
+      </c>
+      <c r="AJ13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1317584707346562E-3</v>
+      </c>
+      <c r="AK13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1465471099495472E-3</v>
+      </c>
+      <c r="AL13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1606241133053086E-3</v>
+      </c>
+      <c r="AM13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1741412275859675E-3</v>
+      </c>
+      <c r="AN13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1878206457391904E-3</v>
+      </c>
+      <c r="AO13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2022725018577818E-3</v>
+      </c>
+      <c r="AP13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2179150664397564E-3</v>
+      </c>
+      <c r="AQ13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2348353848774529E-3</v>
+      </c>
+      <c r="AR13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2530988614173344E-3</v>
+      </c>
+      <c r="AS13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2728268323418668E-3</v>
+      </c>
+      <c r="AT13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.2941191998472323E-3</v>
+      </c>
+      <c r="AU13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3170632297310192E-3</v>
+      </c>
+      <c r="AV13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3413303100763274E-3</v>
+      </c>
+      <c r="AW13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.366829348992793E-3</v>
+      </c>
+      <c r="AX13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3938871094382188E-3</v>
+      </c>
+      <c r="AY13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4228244530135603E-3</v>
+      </c>
+      <c r="AZ13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4538930628853475E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="B14">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="B16">
         <v>-1</v>
       </c>
     </row>

--- a/results/Dommages.xlsx
+++ b/results/Dommages.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JACQUETINF\Documents\documents\ThreeME_V3-ADEME\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929A55C9-D629-4D11-B1CB-6B9C891370FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5890" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Décompo" sheetId="1" r:id="rId1"/>
@@ -22,10 +23,20 @@
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
   </externalReferences>
-  <calcPr calcId="162913" calcMode="manual"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -55,7 +66,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -157,7 +168,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -385,157 +395,157 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>1.3538601712600906E-2</c:v>
+                  <c:v>1.7105840554810015E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6912679139984843E-2</c:v>
+                  <c:v>2.098056736359466E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.0115560050032899E-2</c:v>
+                  <c:v>2.4532546055058613E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2943774902325131E-2</c:v>
+                  <c:v>2.7517937372380175E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.5425308096377663E-2</c:v>
+                  <c:v>2.9990320526349201E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.7611418605846372E-2</c:v>
+                  <c:v>3.2030280950868795E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.9576927529626262E-2</c:v>
+                  <c:v>3.3733930388557543E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.1353239073615535E-2</c:v>
+                  <c:v>3.51562243585547E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.2985843392642766E-2</c:v>
+                  <c:v>3.6361018719246463E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.4516237501799885E-2</c:v>
+                  <c:v>3.7405791429351631E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.6927247412231856E-2</c:v>
+                  <c:v>3.8334394917893921E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.7901004681047845E-2</c:v>
+                  <c:v>3.925556698553101E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.8748605891280929E-2</c:v>
+                  <c:v>4.0138240489166144E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.9477051688237563E-2</c:v>
+                  <c:v>4.0997975041976102E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.0116488877360634E-2</c:v>
+                  <c:v>4.1844108990118138E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.0694640941231978E-2</c:v>
+                  <c:v>4.2682193718009402E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.1277964002331198E-2</c:v>
+                  <c:v>4.3572346504538013E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.1849741026071745E-2</c:v>
+                  <c:v>4.4465811282116692E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.2425458296820991E-2</c:v>
+                  <c:v>4.5362483138397192E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.3016340742832782E-2</c:v>
+                  <c:v>4.6261021063189967E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.3633104309372284E-2</c:v>
+                  <c:v>4.7163174260623449E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.427314031618601E-2</c:v>
+                  <c:v>4.8060004625971375E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.4941592729452529E-2</c:v>
+                  <c:v>4.8953489734531723E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.563947337910957E-2</c:v>
+                  <c:v>4.9843562098548233E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.6365523266142288E-2</c:v>
+                  <c:v>5.0729292917466084E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.7123697653551948E-2</c:v>
+                  <c:v>5.1616312992447518E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.788032119780028E-2</c:v>
+                  <c:v>5.2470427631295502E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.8649621572917197E-2</c:v>
+                  <c:v>5.3309757047204975E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.9429610515789646E-2</c:v>
+                  <c:v>5.4134537423666911E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>5.0218084317584018E-2</c:v>
+                  <c:v>5.4944750354783627E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.1012621505727829E-2</c:v>
+                  <c:v>5.5740006203695458E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.1800471640880197E-2</c:v>
+                  <c:v>5.6509432844425334E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.2587995224248063E-2</c:v>
+                  <c:v>5.7261280214704439E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5.33733113615723E-2</c:v>
+                  <c:v>5.7995105060567376E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5.4154996240649018E-2</c:v>
+                  <c:v>5.8710724612016547E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.4931912985350273E-2</c:v>
+                  <c:v>5.9408064863598842E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5.5612806592488247E-2</c:v>
+                  <c:v>6.0003827900889546E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.6273572035804416E-2</c:v>
+                  <c:v>6.0571000103954893E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5.6914643529708646E-2</c:v>
+                  <c:v>6.1110748911116231E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.753897634474104E-2</c:v>
+                  <c:v>6.1626563911912131E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.8149801337017311E-2</c:v>
+                  <c:v>6.2122074676719145E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5.8735596987392939E-2</c:v>
+                  <c:v>6.2587962491754912E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5.9311343796265348E-2</c:v>
+                  <c:v>6.3038097195504572E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5.9879563862663465E-2</c:v>
+                  <c:v>6.3475234557170079E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>6.0442828733665251E-2</c:v>
+                  <c:v>6.3901885641366452E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>6.1003296850866917E-2</c:v>
+                  <c:v>6.43201329379125E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6.1513652688195419E-2</c:v>
+                  <c:v>6.4691410532873417E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>6.2016559531788203E-2</c:v>
+                  <c:v>6.5051793926074519E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6.2514296331188435E-2</c:v>
+                  <c:v>6.5403479043005697E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6.3009329987089857E-2</c:v>
+                  <c:v>6.5748713084534671E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6.3503741412501813E-2</c:v>
+                  <c:v>6.6089373105816973E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -738,157 +748,157 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>1.3438789375808113E-4</c:v>
+                  <c:v>1.3324322143182243E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6181616621756554E-4</c:v>
+                  <c:v>2.5936784348279396E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.621163355573831E-4</c:v>
+                  <c:v>3.5867934026390103E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3724432175051842E-4</c:v>
+                  <c:v>4.3321760704773116E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.9908398422249256E-4</c:v>
+                  <c:v>4.9468668139751593E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.5892513906752317E-4</c:v>
+                  <c:v>5.5417555389225548E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.2275232294828342E-4</c:v>
+                  <c:v>6.1757907081383401E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.9139740652446324E-4</c:v>
+                  <c:v>6.8583963207946574E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.6394908653598659E-4</c:v>
+                  <c:v>7.5819410229926998E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3886924188336653E-4</c:v>
+                  <c:v>8.3314302656278816E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.1286593600881094E-4</c:v>
+                  <c:v>9.0941367200969569E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.9162630619664682E-4</c:v>
+                  <c:v>9.8748455042508426E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0720241721557944E-3</c:v>
+                  <c:v>1.0667685359980819E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1535640345473608E-3</c:v>
+                  <c:v>1.1468396075772283E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.2358563924219634E-3</c:v>
+                  <c:v>1.2274375326907297E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.3187051360760219E-3</c:v>
+                  <c:v>1.3085078042389675E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.4037302002539651E-3</c:v>
+                  <c:v>1.3916915929794577E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4906360662765294E-3</c:v>
+                  <c:v>1.4767756078585201E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.5789080261373531E-3</c:v>
+                  <c:v>1.5632585306784019E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.6679755653525863E-3</c:v>
+                  <c:v>1.6505753151656588E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.7571472529557333E-3</c:v>
+                  <c:v>1.7380304818160816E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.8463864538693642E-3</c:v>
+                  <c:v>1.8256020341624879E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.9353816062881446E-3</c:v>
+                  <c:v>1.9129834925784017E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.024025037136272E-3</c:v>
+                  <c:v>2.0000767114388626E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.1122705465630581E-3</c:v>
+                  <c:v>2.0868483862193088E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.1993524566710221E-3</c:v>
+                  <c:v>2.1725348345087298E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.2852918106983644E-3</c:v>
+                  <c:v>2.2571988920424488E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.3700224069685902E-3</c:v>
+                  <c:v>2.3407663910262055E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.4537980799140754E-3</c:v>
+                  <c:v>2.4235085417653249E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.5369167545655699E-3</c:v>
+                  <c:v>2.5057259235543583E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.6196162716446356E-3</c:v>
+                  <c:v>2.5876371226732989E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.7016507745774021E-3</c:v>
+                  <c:v>2.6689904023658936E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.7831101864821406E-3</c:v>
+                  <c:v>2.7498721075444113E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.8641228855196335E-3</c:v>
+                  <c:v>2.8304083889026874E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.9448077328281183E-3</c:v>
+                  <c:v>2.9107162689487737E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>3.0252520047377995E-3</c:v>
+                  <c:v>2.9908803996285815E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>3.1020826789411871E-3</c:v>
+                  <c:v>3.067489871852784E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3.1756576366343964E-3</c:v>
+                  <c:v>3.1409243679222307E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.2469566266472086E-3</c:v>
+                  <c:v>3.2121616789450025E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>3.3169858002710662E-3</c:v>
+                  <c:v>3.2822073507745506E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>3.3864791738471567E-3</c:v>
+                  <c:v>3.3517955131837709E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>3.4553360584705928E-3</c:v>
+                  <c:v>3.4208056641107376E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>3.5237223017656749E-3</c:v>
+                  <c:v>3.489396725786853E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>3.5918993111437869E-3</c:v>
+                  <c:v>3.5577069072368905E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.6598822236594206E-3</c:v>
+                  <c:v>3.6258381577166654E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3.7276654590847613E-3</c:v>
+                  <c:v>3.6938558959118684E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3.7936479530592537E-3</c:v>
+                  <c:v>3.7601128146916851E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3.8578144973709858E-3</c:v>
+                  <c:v>3.8246783854445354E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.9206724280951288E-3</c:v>
+                  <c:v>3.8880748944648547E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.9827770538726215E-3</c:v>
+                  <c:v>3.9508646712963502E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>4.0445557140917909E-3</c:v>
+                  <c:v>4.0134773342603847E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1091,157 +1101,157 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>6.166325736678413E-5</c:v>
+                  <c:v>5.7638045987462583E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2406974180489971E-4</c:v>
+                  <c:v>1.2009166610049693E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.6798032322717926E-4</c:v>
+                  <c:v>1.687411982959075E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9531726047739006E-4</c:v>
+                  <c:v>2.0421975119078173E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.157012436457828E-4</c:v>
+                  <c:v>2.344716659096191E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.3742380955982245E-4</c:v>
+                  <c:v>2.6645718861317835E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.6492154138157975E-4</c:v>
+                  <c:v>3.0382307994003543E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.9898978713482904E-4</c:v>
+                  <c:v>3.4703384205847509E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3825210997651123E-4</c:v>
+                  <c:v>3.9463292062513755E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.8067326778778998E-4</c:v>
+                  <c:v>4.4462244276533003E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.2363293529634749E-4</c:v>
+                  <c:v>4.9535856636317988E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.6895746744057831E-4</c:v>
+                  <c:v>5.4647583905242242E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.1500073576260519E-4</c:v>
+                  <c:v>5.9763944798207902E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.6134116250994986E-4</c:v>
+                  <c:v>6.4849348657292083E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.0785770713067677E-4</c:v>
+                  <c:v>6.9903088351264131E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.5476914563755706E-4</c:v>
+                  <c:v>7.4954679679806874E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.0358864451414149E-4</c:v>
+                  <c:v>8.0157666168491348E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7.547237955446498E-4</c:v>
+                  <c:v>8.5566109907541515E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.0806122963938271E-4</c:v>
+                  <c:v>9.1179353679293057E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.6346503463374802E-4</c:v>
+                  <c:v>9.6993306650561273E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.2084637913879275E-4</c:v>
+                  <c:v>1.0300632197927165E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.80411257173186E-4</c:v>
+                  <c:v>1.0924539061640814E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0422023538963973E-3</c:v>
+                  <c:v>1.1571751287592427E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1062791825026189E-3</c:v>
+                  <c:v>1.2243008983092857E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1726705813077665E-3</c:v>
+                  <c:v>1.2938674026730101E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.2410816766340663E-3</c:v>
+                  <c:v>1.3655834103072501E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.3111531910162746E-3</c:v>
+                  <c:v>1.4391426238076349E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.3827054202674091E-3</c:v>
+                  <c:v>1.5143270412938392E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.4558694544935108E-3</c:v>
+                  <c:v>1.5912321416542419E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.5307536879812858E-3</c:v>
+                  <c:v>1.6699421928104766E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.6073581983827648E-3</c:v>
+                  <c:v>1.7504521528086542E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.6852278177769062E-3</c:v>
+                  <c:v>1.8323106487770982E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.7642629577990718E-3</c:v>
+                  <c:v>1.9153967868150712E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.8445390925142593E-3</c:v>
+                  <c:v>1.9997856099054426E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.9261368756108357E-3</c:v>
+                  <c:v>2.0855621098607793E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2.0090918360936641E-3</c:v>
+                  <c:v>2.1727691065059895E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.0895786394496824E-3</c:v>
+                  <c:v>2.2576642330137675E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.1677130334341044E-3</c:v>
+                  <c:v>2.3403050595077746E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.2452746057254266E-3</c:v>
+                  <c:v>2.4224119145178635E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.3236380363928985E-3</c:v>
+                  <c:v>2.5053133116933468E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.4033272925388857E-3</c:v>
+                  <c:v>2.5895119995650306E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.4835948887653794E-3</c:v>
+                  <c:v>2.6742653688253126E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.5640596761753454E-3</c:v>
+                  <c:v>2.7591957004773349E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.6446648633973169E-3</c:v>
+                  <c:v>2.8442532176052859E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.7254406205889925E-3</c:v>
+                  <c:v>2.9294815834385313E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.8064438176084172E-3</c:v>
+                  <c:v>3.0149562091705828E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.8855094665938275E-3</c:v>
+                  <c:v>3.0985357348083387E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.9627060505986735E-3</c:v>
+                  <c:v>3.1802964182618965E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.0392718891184556E-3</c:v>
+                  <c:v>3.2614553903712595E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.1162286409965878E-3</c:v>
+                  <c:v>3.3430242100392915E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.1940607928172549E-3</c:v>
+                  <c:v>3.4254897640630944E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1446,157 +1456,157 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>3.9972466572613108E-4</c:v>
+                  <c:v>4.014010040395144E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3665455638706181E-4</c:v>
+                  <c:v>6.3762562867408779E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.8740654790432352E-4</c:v>
+                  <c:v>7.8709449617453409E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.8671582443389241E-4</c:v>
+                  <c:v>8.8481089037906191E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.5367439926474784E-4</c:v>
+                  <c:v>9.502334990582062E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.9974471688657474E-4</c:v>
+                  <c:v>9.9507894045069989E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.0331032043029431E-3</c:v>
+                  <c:v>1.0276160048070526E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0575416159764872E-3</c:v>
+                  <c:v>1.0516368655871799E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0763834282041529E-3</c:v>
+                  <c:v>1.0703991665599322E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0921056494282988E-3</c:v>
+                  <c:v>1.0862946219346581E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1057368566246284E-3</c:v>
+                  <c:v>1.0998611542106865E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1209628843252828E-3</c:v>
+                  <c:v>1.1163835919936194E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1381882674956767E-3</c:v>
+                  <c:v>1.1345123579317093E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1575790415513307E-3</c:v>
+                  <c:v>1.1545102582858277E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1792015706788561E-3</c:v>
+                  <c:v>1.1764856315246153E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.2030059910806898E-3</c:v>
+                  <c:v>1.2004344805632769E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.2301343960197109E-3</c:v>
+                  <c:v>1.2275472077650715E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.2598800045520164E-3</c:v>
+                  <c:v>1.2571341706512154E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.2918136021887808E-3</c:v>
+                  <c:v>1.2887948704095667E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.32561429079181E-3</c:v>
+                  <c:v>1.322227372497653E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.3620583709840275E-3</c:v>
+                  <c:v>1.3582232763280563E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.3985062787638114E-3</c:v>
+                  <c:v>1.3941671466480843E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.4361223895582725E-3</c:v>
+                  <c:v>1.4312325344637555E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.4747510826485996E-3</c:v>
+                  <c:v>1.469279157701002E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.5142564547891979E-3</c:v>
+                  <c:v>1.5081846336015836E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.5576401966460596E-3</c:v>
+                  <c:v>1.5509453693839312E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.5983562067459697E-3</c:v>
+                  <c:v>1.5910612637243179E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.6387247227599502E-3</c:v>
+                  <c:v>1.6308560158404539E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.6787970840530519E-3</c:v>
+                  <c:v>1.6703911604041277E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.7186206553632052E-3</c:v>
+                  <c:v>1.7097236875738275E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.7582305817761545E-3</c:v>
+                  <c:v>1.7488957690853305E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.7972845889957581E-3</c:v>
+                  <c:v>1.7875751440025178E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.8359746195955109E-3</c:v>
+                  <c:v>1.8259574704949655E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.8744092420992509E-3</c:v>
+                  <c:v>1.8641541645806337E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.9126703151580646E-3</c:v>
+                  <c:v>1.9022485694611957E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.9508234414471401E-3</c:v>
+                  <c:v>1.9403075903182687E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.9863117217567908E-3</c:v>
+                  <c:v>1.9757933434209063E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.0196579110873872E-3</c:v>
+                  <c:v>2.0092153758880515E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2.0516174003635326E-3</c:v>
+                  <c:v>2.0413199303207508E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.082670029862066E-3</c:v>
+                  <c:v>2.0725801927139464E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.1131576966908483E-3</c:v>
+                  <c:v>2.103330151093874E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.1427704929819491E-3</c:v>
+                  <c:v>2.1332595883019057E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.1719688309533858E-3</c:v>
+                  <c:v>2.1628166483552702E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.2010336584927792E-3</c:v>
+                  <c:v>2.1922774031216674E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.2301641625331881E-3</c:v>
+                  <c:v>2.2218356201946232E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.2595033146388666E-3</c:v>
+                  <c:v>2.2516305007062032E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.2871013262685258E-3</c:v>
+                  <c:v>2.2797248464370146E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.3140186070349511E-3</c:v>
+                  <c:v>2.3071534186777098E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.3407144772028543E-3</c:v>
+                  <c:v>2.3343719520066974E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.3674681380444484E-3</c:v>
+                  <c:v>2.3616564546846686E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2.3944577475761841E-3</c:v>
+                  <c:v>2.3891818233096052E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1799,157 +1809,157 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="51"/>
                 <c:pt idx="0">
-                  <c:v>2.2223002079790888E-4</c:v>
+                  <c:v>2.2243723420811712E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2433615243542278E-4</c:v>
+                  <c:v>4.2333456586218787E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.460484776365071E-4</c:v>
+                  <c:v>5.4416067532780943E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0582705880252163E-4</c:v>
+                  <c:v>6.0363110527583697E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.2931765114337956E-4</c:v>
+                  <c:v>6.2720324913001502E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.3797201827009431E-4</c:v>
+                  <c:v>6.3607743282778628E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.4523020353712823E-4</c:v>
+                  <c:v>6.435470621065642E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.5651380013864724E-4</c:v>
+                  <c:v>6.5498998034063671E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.7277674351318151E-4</c:v>
+                  <c:v>6.7136792078392737E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.9236716254850172E-4</c:v>
+                  <c:v>6.9171932496215477E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.1186858567295203E-4</c:v>
+                  <c:v>7.1430533968352278E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.339265242249926E-4</c:v>
+                  <c:v>7.3914727984803613E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.5574492127428172E-4</c:v>
+                  <c:v>7.6500584549310524E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.7685716043829345E-4</c:v>
+                  <c:v>7.9121226735557465E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.9714597830683048E-4</c:v>
+                  <c:v>8.1732667500866718E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.1669863298294842E-4</c:v>
+                  <c:v>8.4306295223290917E-4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.3644969196160907E-4</c:v>
+                  <c:v>8.6899970740139665E-4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.5642039832490441E-4</c:v>
+                  <c:v>8.9493438715281676E-4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.7634582048701226E-4</c:v>
+                  <c:v>9.2043562006494106E-4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.9598727931495398E-4</c:v>
+                  <c:v>9.4516669452093804E-4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.1503285465011075E-4</c:v>
+                  <c:v>9.6881709693363849E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.335953487628057E-4</c:v>
+                  <c:v>9.9140661068586322E-4</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9.5171367511747568E-4</c:v>
+                  <c:v>1.0130295161511205E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9.6935188907742997E-4</c:v>
+                  <c:v>1.033691239031409E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>9.8651373350443911E-4</c:v>
+                  <c:v>1.0534508742243709E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.0025299021160228E-3</c:v>
+                  <c:v>1.0718887860142814E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.0178720288839191E-3</c:v>
+                  <c:v>1.0892919386841296E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.0326582515052252E-3</c:v>
+                  <c:v>1.1059008542140258E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.0470512460817247E-3</c:v>
+                  <c:v>1.1219316897422907E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.0612214383433072E-3</c:v>
+                  <c:v>1.13760081160863E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.0753090623075723E-3</c:v>
+                  <c:v>1.1530857910740933E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.0892942806112194E-3</c:v>
+                  <c:v>1.1683912037093735E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.1032629738735311E-3</c:v>
+                  <c:v>1.1836276619577868E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.1173722355650589E-3</c:v>
+                  <c:v>1.198956522487582E-3</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.1317584707346562E-3</c:v>
+                  <c:v>1.2145196191616359E-3</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.1465471099495472E-3</c:v>
+                  <c:v>1.2304444634672063E-3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.1606241133053086E-3</c:v>
+                  <c:v>1.2456234673182687E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.1741412275859675E-3</c:v>
+                  <c:v>1.2601897483343061E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.1878206457391904E-3</c:v>
+                  <c:v>1.2748638988242522E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.2022725018577818E-3</c:v>
+                  <c:v>1.2902546661451852E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.2179150664397564E-3</c:v>
+                  <c:v>1.3067780927445982E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.2348353848774529E-3</c:v>
+                  <c:v>1.3245019942423886E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.2530988614173344E-3</c:v>
+                  <c:v>1.3434935981558871E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.2728268323418668E-3</c:v>
+                  <c:v>1.3638659763328675E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.2941191998472323E-3</c:v>
+                  <c:v>1.3857145863834797E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.3170632297310192E-3</c:v>
+                  <c:v>1.4091219941004818E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.3413303100763274E-3</c:v>
+                  <c:v>1.4337019196856149E-3</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.366829348992793E-3</c:v>
+                  <c:v>1.4594038199384762E-3</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.3938871094382188E-3</c:v>
+                  <c:v>1.4865596584855423E-3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.4228244530135603E-3</c:v>
+                  <c:v>1.5154951585009124E-3</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.4538930628853475E-3</c:v>
+                  <c:v>1.5464660346182768E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2027,6 +2037,7 @@
         <c:axId val="582155528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="8.0000000000000016E-2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2091,7 +2102,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2717,7 +2727,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2728,10 +2738,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9291053" cy="6060351"/>
+    <xdr:ext cx="9305636" cy="6084455"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graphique 1"/>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
@@ -2937,160 +2953,181 @@
         </row>
         <row r="5">
           <cell r="C5">
-            <v>-1.4356607550249811</v>
+            <v>-1.7920560060476931</v>
           </cell>
           <cell r="D5">
-            <v>-1.8359555756829793</v>
+            <v>-2.2420987067714226</v>
           </cell>
           <cell r="E5">
-            <v>-2.1979111734358292</v>
+            <v>-2.6391221765120765</v>
           </cell>
           <cell r="F5">
-            <v>-2.5068879367789454</v>
+            <v>-2.9643816726273586</v>
           </cell>
           <cell r="G5">
-            <v>-2.7723085374654066</v>
+            <v>-3.2296915621844557</v>
           </cell>
           <cell r="H5">
-            <v>-3.0045484289630386</v>
+            <v>-3.4482070066652715</v>
           </cell>
           <cell r="I5">
-            <v>-3.2142934801796197</v>
+            <v>-3.6326495606225029</v>
           </cell>
           <cell r="J5">
-            <v>-3.4057681683389962</v>
+            <v>-3.7895724678620457</v>
           </cell>
           <cell r="K5">
-            <v>-3.5837204760872599</v>
+            <v>-3.925561282951473</v>
           </cell>
           <cell r="L5">
-            <v>-3.7520252823447842</v>
+            <v>-4.046157084557656</v>
           </cell>
           <cell r="M5">
-            <v>-4.0081351725834597</v>
+            <v>-4.1553333650161006</v>
           </cell>
           <cell r="N5">
-            <v>-4.1216477863235346</v>
+            <v>-4.2645058246850169</v>
           </cell>
           <cell r="O5">
-            <v>-4.2229563987969287</v>
+            <v>-4.3702166676571119</v>
           </cell>
           <cell r="P5">
-            <v>-4.3126393087284498</v>
+            <v>-4.4739030661767654</v>
           </cell>
           <cell r="Q5">
-            <v>-4.3936550525898959</v>
+            <v>-4.5764389712854792</v>
           </cell>
           <cell r="R5">
-            <v>-4.4687819847009198</v>
+            <v>-4.6783745751842627</v>
           </cell>
           <cell r="S5">
-            <v>-4.5451866935080627</v>
+            <v>-4.7862161674368853</v>
           </cell>
           <cell r="T5">
-            <v>-4.6211401290769842</v>
+            <v>-4.8950316546854662</v>
           </cell>
           <cell r="U5">
-            <v>-4.6980586975273519</v>
+            <v>-5.0046765696343032</v>
           </cell>
           <cell r="V5">
-            <v>-4.7769382912925877</v>
+            <v>-5.1148923511879829</v>
           </cell>
           <cell r="W5">
-            <v>-4.8588189167100948</v>
+            <v>-5.2258308335493941</v>
           </cell>
           <cell r="X5">
-            <v>-4.9432039654755178</v>
+            <v>-5.3363634323631892</v>
           </cell>
           <cell r="Y5">
-            <v>-5.0307012754312819</v>
+            <v>-5.4467910406484243</v>
           </cell>
           <cell r="Z5">
-            <v>-5.121388057047449</v>
+            <v>-5.5570910105028792</v>
           </cell>
           <cell r="AA5">
-            <v>-5.2151234582306749</v>
+            <v>-5.6671644214184358</v>
           </cell>
           <cell r="AB5">
-            <v>-5.3124301885619118</v>
+            <v>-5.7777265392661707</v>
           </cell>
           <cell r="AC5">
-            <v>-5.409299443514481</v>
+            <v>-5.8847122349554031</v>
           </cell>
           <cell r="AD5">
-            <v>-5.5073732374418372</v>
+            <v>-5.99016073495795</v>
           </cell>
           <cell r="AE5">
-            <v>-5.6065126380332009</v>
+            <v>-6.0941600957232893</v>
           </cell>
           <cell r="AF5">
-            <v>-5.7065596853837386</v>
+            <v>-6.1967742970330919</v>
           </cell>
           <cell r="AG5">
-            <v>-5.8073135619838956</v>
+            <v>-6.298007703933683</v>
           </cell>
           <cell r="AH5">
-            <v>-5.9073929102841483</v>
+            <v>-6.3966700243280217</v>
           </cell>
           <cell r="AI5">
-            <v>-6.0074605961998317</v>
+            <v>-6.4936134241516674</v>
           </cell>
           <cell r="AJ5">
-            <v>-6.1073754817270505</v>
+            <v>-6.5888409746443717</v>
           </cell>
           <cell r="AK5">
-            <v>-6.2070369634980693</v>
+            <v>-6.6823771179448936</v>
           </cell>
           <cell r="AL5">
-            <v>-6.3063627377578424</v>
+            <v>-6.7742466423518888</v>
           </cell>
           <cell r="AM5">
-            <v>-6.3951403745941215</v>
+            <v>-6.8550398816495273</v>
           </cell>
           <cell r="AN5">
-            <v>-6.4810741844546271</v>
+            <v>-6.9321634655607252</v>
           </cell>
           <cell r="AO5">
-            <v>-6.5646312808184</v>
+            <v>-7.0061506333724104</v>
           </cell>
           <cell r="AP5">
-            <v>-6.6464542713124857</v>
+            <v>-7.0776919433239165</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.7270680566533958</v>
+            <v>-7.1473490433306424</v>
           </cell>
           <cell r="AR5">
-            <v>-6.8052133812488318</v>
+            <v>-7.2140795107235256</v>
           </cell>
           <cell r="AS5">
-            <v>-6.8824193466577093</v>
+            <v>-7.2792999868279917</v>
           </cell>
           <cell r="AT5">
-            <v>-6.9589988528039211</v>
+            <v>-7.3433338061466795</v>
           </cell>
           <cell r="AU5">
-            <v>-7.0352434940294089</v>
+            <v>-7.4064755589099747</v>
           </cell>
           <cell r="AV5">
-            <v>-7.1113972671929986</v>
+            <v>-7.4689697537801631</v>
           </cell>
           <cell r="AW5">
-            <v>-7.1821241744193358</v>
+            <v>-7.5263485848496074</v>
           </cell>
           <cell r="AX5">
-            <v>-7.2517928035785602</v>
+            <v>-7.5823325968397137</v>
           </cell>
           <cell r="AY5">
-            <v>-7.3208842235043097</v>
+            <v>-7.6373940938334055</v>
           </cell>
           <cell r="AZ5">
-            <v>-7.3898628273017071</v>
+            <v>-7.691975357905589</v>
           </cell>
           <cell r="BA5">
-            <v>-7.4590708729872386</v>
+            <v>-7.7463988062068339</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3127,160 +3164,181 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.3538601712600906</v>
+            <v>-1.7105840554810015</v>
           </cell>
           <cell r="D5">
-            <v>-1.6912679139984843</v>
+            <v>-2.098056736359466</v>
           </cell>
           <cell r="E5">
-            <v>-2.0115560050032899</v>
+            <v>-2.4532546055058613</v>
           </cell>
           <cell r="F5">
-            <v>-2.2943774902325131</v>
+            <v>-2.7517937372380175</v>
           </cell>
           <cell r="G5">
-            <v>-2.5425308096377663</v>
+            <v>-2.9990320526349201</v>
           </cell>
           <cell r="H5">
-            <v>-2.7611418605846372</v>
+            <v>-3.2030280950868795</v>
           </cell>
           <cell r="I5">
-            <v>-2.9576927529626262</v>
+            <v>-3.3733930388557543</v>
           </cell>
           <cell r="J5">
-            <v>-3.1353239073615535</v>
+            <v>-3.51562243585547</v>
           </cell>
           <cell r="K5">
-            <v>-3.2985843392642766</v>
+            <v>-3.6361018719246463</v>
           </cell>
           <cell r="L5">
-            <v>-3.4516237501799885</v>
+            <v>-3.7405791429351631</v>
           </cell>
           <cell r="M5">
-            <v>-3.6927247412231856</v>
+            <v>-3.8334394917893921</v>
           </cell>
           <cell r="N5">
-            <v>-3.7901004681047845</v>
+            <v>-3.925556698553101</v>
           </cell>
           <cell r="O5">
-            <v>-3.8748605891280929</v>
+            <v>-4.0138240489166144</v>
           </cell>
           <cell r="P5">
-            <v>-3.9477051688237563</v>
+            <v>-4.0997975041976105</v>
           </cell>
           <cell r="Q5">
-            <v>-4.0116488877360634</v>
+            <v>-4.1844108990118141</v>
           </cell>
           <cell r="R5">
-            <v>-4.0694640941231981</v>
+            <v>-4.2682193718009405</v>
           </cell>
           <cell r="S5">
-            <v>-4.1277964002331196</v>
+            <v>-4.3572346504538011</v>
           </cell>
           <cell r="T5">
-            <v>-4.1849741026071747</v>
+            <v>-4.446581128211669</v>
           </cell>
           <cell r="U5">
-            <v>-4.2425458296820988</v>
+            <v>-4.5362483138397192</v>
           </cell>
           <cell r="V5">
-            <v>-4.3016340742832782</v>
+            <v>-4.6261021063189967</v>
           </cell>
           <cell r="W5">
-            <v>-4.3633104309372284</v>
+            <v>-4.7163174260623446</v>
           </cell>
           <cell r="X5">
-            <v>-4.427314031618601</v>
+            <v>-4.8060004625971375</v>
           </cell>
           <cell r="Y5">
-            <v>-4.4941592729452529</v>
+            <v>-4.8953489734531725</v>
           </cell>
           <cell r="Z5">
-            <v>-4.5639473379109567</v>
+            <v>-4.9843562098548233</v>
           </cell>
           <cell r="AA5">
-            <v>-4.636552326614229</v>
+            <v>-5.0729292917466084</v>
           </cell>
           <cell r="AB5">
-            <v>-4.712369765355195</v>
+            <v>-5.1616312992447515</v>
           </cell>
           <cell r="AC5">
-            <v>-4.788032119780028</v>
+            <v>-5.2470427631295502</v>
           </cell>
           <cell r="AD5">
-            <v>-4.8649621572917194</v>
+            <v>-5.3309757047204975</v>
           </cell>
           <cell r="AE5">
-            <v>-4.9429610515789646</v>
+            <v>-5.4134537423666913</v>
           </cell>
           <cell r="AF5">
-            <v>-5.0218084317584015</v>
+            <v>-5.4944750354783629</v>
           </cell>
           <cell r="AG5">
-            <v>-5.1012621505727829</v>
+            <v>-5.5740006203695458</v>
           </cell>
           <cell r="AH5">
-            <v>-5.1800471640880197</v>
+            <v>-5.6509432844425334</v>
           </cell>
           <cell r="AI5">
-            <v>-5.2587995224248063</v>
+            <v>-5.7261280214704442</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.3373311361572302</v>
+            <v>-5.7995105060567376</v>
           </cell>
           <cell r="AK5">
-            <v>-5.4154996240649016</v>
+            <v>-5.8710724612016545</v>
           </cell>
           <cell r="AL5">
-            <v>-5.4931912985350273</v>
+            <v>-5.9408064863598842</v>
           </cell>
           <cell r="AM5">
-            <v>-5.5612806592488244</v>
+            <v>-6.0003827900889544</v>
           </cell>
           <cell r="AN5">
-            <v>-5.6273572035804413</v>
+            <v>-6.0571000103954891</v>
           </cell>
           <cell r="AO5">
-            <v>-5.6914643529708648</v>
+            <v>-6.1110748911116231</v>
           </cell>
           <cell r="AP5">
-            <v>-5.7538976344741037</v>
+            <v>-6.1626563911912129</v>
           </cell>
           <cell r="AQ5">
-            <v>-5.8149801337017308</v>
+            <v>-6.2122074676719148</v>
           </cell>
           <cell r="AR5">
-            <v>-5.8735596987392942</v>
+            <v>-6.2587962491754912</v>
           </cell>
           <cell r="AS5">
-            <v>-5.9311343796265348</v>
+            <v>-6.3038097195504577</v>
           </cell>
           <cell r="AT5">
-            <v>-5.9879563862663465</v>
+            <v>-6.3475234557170079</v>
           </cell>
           <cell r="AU5">
-            <v>-6.0442828733665248</v>
+            <v>-6.3901885641366452</v>
           </cell>
           <cell r="AV5">
-            <v>-6.1003296850866917</v>
+            <v>-6.4320132937912504</v>
           </cell>
           <cell r="AW5">
-            <v>-6.1513652688195419</v>
+            <v>-6.4691410532873412</v>
           </cell>
           <cell r="AX5">
-            <v>-6.20165595317882</v>
+            <v>-6.5051793926074524</v>
           </cell>
           <cell r="AY5">
-            <v>-6.2514296331188435</v>
+            <v>-6.5403479043005692</v>
           </cell>
           <cell r="AZ5">
-            <v>-6.3009329987089853</v>
+            <v>-6.5748713084534671</v>
           </cell>
           <cell r="BA5">
-            <v>-6.3503741412501817</v>
+            <v>-6.6089373105816973</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3317,160 +3375,181 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.3672989606358987</v>
+            <v>-1.7239083776241837</v>
           </cell>
           <cell r="D5">
-            <v>-1.7174495306202409</v>
+            <v>-2.1239935207077454</v>
           </cell>
           <cell r="E5">
-            <v>-2.0477676385590282</v>
+            <v>-2.4891225395322514</v>
           </cell>
           <cell r="F5">
-            <v>-2.338101922407565</v>
+            <v>-2.7951154979427906</v>
           </cell>
           <cell r="G5">
-            <v>-2.5924392080600156</v>
+            <v>-3.0485007207746717</v>
           </cell>
           <cell r="H5">
-            <v>-2.8170343744913895</v>
+            <v>-3.258445650476105</v>
           </cell>
           <cell r="I5">
-            <v>-3.0199679852574546</v>
+            <v>-3.4351509459371377</v>
           </cell>
           <cell r="J5">
-            <v>-3.2044636480139999</v>
+            <v>-3.5842063990634165</v>
           </cell>
           <cell r="K5">
-            <v>-3.3749792479178753</v>
+            <v>-3.7119212821545733</v>
           </cell>
           <cell r="L5">
-            <v>-3.5355106743683251</v>
+            <v>-3.823893445591442</v>
           </cell>
           <cell r="M5">
-            <v>-3.7840113348240667</v>
+            <v>-3.9243808589903617</v>
           </cell>
           <cell r="N5">
-            <v>-3.8892630987244492</v>
+            <v>-4.0243051535956091</v>
           </cell>
           <cell r="O5">
-            <v>-3.9820630063436724</v>
+            <v>-4.1205009025164223</v>
           </cell>
           <cell r="P5">
-            <v>-4.0630615722784924</v>
+            <v>-4.214481464955333</v>
           </cell>
           <cell r="Q5">
-            <v>-4.1352345269782598</v>
+            <v>-4.3071546522808868</v>
           </cell>
           <cell r="R5">
-            <v>-4.2013346077308</v>
+            <v>-4.3990701522248372</v>
           </cell>
           <cell r="S5">
-            <v>-4.2681694202585163</v>
+            <v>-4.4964038097517474</v>
           </cell>
           <cell r="T5">
-            <v>-4.3340377092348277</v>
+            <v>-4.5942586889975212</v>
           </cell>
           <cell r="U5">
-            <v>-4.4004366322958344</v>
+            <v>-4.6925741669075594</v>
           </cell>
           <cell r="V5">
-            <v>-4.4684316308185368</v>
+            <v>-4.7911596378355625</v>
           </cell>
           <cell r="W5">
-            <v>-4.5390251562328015</v>
+            <v>-4.890120474243953</v>
           </cell>
           <cell r="X5">
-            <v>-4.6119526770055375</v>
+            <v>-4.9885606660133863</v>
           </cell>
           <cell r="Y5">
-            <v>-4.6876974335740673</v>
+            <v>-5.0866473227110127</v>
           </cell>
           <cell r="Z5">
-            <v>-4.7663498416245842</v>
+            <v>-5.1843638809987098</v>
           </cell>
           <cell r="AA5">
-            <v>-4.8477793812705343</v>
+            <v>-5.2816141303685393</v>
           </cell>
           <cell r="AB5">
-            <v>-4.9323050110222972</v>
+            <v>-5.378884782695625</v>
           </cell>
           <cell r="AC5">
-            <v>-5.0165613008498644</v>
+            <v>-5.4727626523337953</v>
           </cell>
           <cell r="AD5">
-            <v>-5.1019643979885787</v>
+            <v>-5.5650523438231181</v>
           </cell>
           <cell r="AE5">
-            <v>-5.1883408595703724</v>
+            <v>-5.6558045965432235</v>
           </cell>
           <cell r="AF5">
-            <v>-5.2755001072149588</v>
+            <v>-5.7450476278337987</v>
           </cell>
           <cell r="AG5">
-            <v>-5.3632237777372467</v>
+            <v>-5.8327643326368754</v>
           </cell>
           <cell r="AH5">
-            <v>-5.4502122415457599</v>
+            <v>-5.917842324679123</v>
           </cell>
           <cell r="AI5">
-            <v>-5.5371105410730204</v>
+            <v>-6.0011152322248851</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.6237434247091933</v>
+            <v>-6.0825513449470066</v>
           </cell>
           <cell r="AK5">
-            <v>-5.7099803973477137</v>
+            <v>-6.1621440880965324</v>
           </cell>
           <cell r="AL5">
-            <v>-5.7957164990088073</v>
+            <v>-6.2398945263227423</v>
           </cell>
           <cell r="AM5">
-            <v>-5.8714889271429431</v>
+            <v>-6.3071317772742326</v>
           </cell>
           <cell r="AN5">
-            <v>-5.9449229672438815</v>
+            <v>-6.3711924471877124</v>
           </cell>
           <cell r="AO5">
-            <v>-6.0161600156355854</v>
+            <v>-6.4322910590061237</v>
           </cell>
           <cell r="AP5">
-            <v>-6.0855962145012104</v>
+            <v>-6.4908771262686678</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.1536280510864465</v>
+            <v>-6.5473870189902916</v>
           </cell>
           <cell r="AR5">
-            <v>-6.2190933045863535</v>
+            <v>-6.6008768155865649</v>
           </cell>
           <cell r="AS5">
-            <v>-6.2835066098031023</v>
+            <v>-6.6527493921291425</v>
           </cell>
           <cell r="AT5">
-            <v>-6.3471463173807248</v>
+            <v>-6.7032941464406974</v>
           </cell>
           <cell r="AU5">
-            <v>-6.4102710957324671</v>
+            <v>-6.7527723799083113</v>
           </cell>
           <cell r="AV5">
-            <v>-6.4730962309951678</v>
+            <v>-6.8013988833824364</v>
           </cell>
           <cell r="AW5">
-            <v>-6.5307300641254677</v>
+            <v>-6.8451523347565102</v>
           </cell>
           <cell r="AX5">
-            <v>-6.5874374029159188</v>
+            <v>-6.8876472311519059</v>
           </cell>
           <cell r="AY5">
-            <v>-6.6434968759283564</v>
+            <v>-6.9291553937470551</v>
           </cell>
           <cell r="AZ5">
-            <v>-6.6992107040962479</v>
+            <v>-6.9699577755831026</v>
           </cell>
           <cell r="BA5">
-            <v>-6.7548297126593599</v>
+            <v>-7.0102850440077358</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3507,157 +3586,157 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.3734652863725771</v>
+            <v>-1.72967218222293</v>
           </cell>
           <cell r="D5">
-            <v>-1.7298565048007308</v>
+            <v>-2.1360026873177951</v>
           </cell>
           <cell r="E5">
-            <v>-2.0645656708817461</v>
+            <v>-2.5059966593618421</v>
           </cell>
           <cell r="F5">
-            <v>-2.357633648455304</v>
+            <v>-2.8155374730618687</v>
           </cell>
           <cell r="G5">
-            <v>-2.6140093324245939</v>
+            <v>-3.0719478873656336</v>
           </cell>
           <cell r="H5">
-            <v>-2.8407767554473717</v>
+            <v>-3.2850913693374229</v>
           </cell>
           <cell r="I5">
-            <v>-3.0464601393956126</v>
+            <v>-3.4655332539311412</v>
           </cell>
           <cell r="J5">
-            <v>-3.2343626267274828</v>
+            <v>-3.618909783269264</v>
           </cell>
           <cell r="K5">
-            <v>-3.4088044589155264</v>
+            <v>-3.751384574217087</v>
           </cell>
           <cell r="L5">
-            <v>-3.5735780011471041</v>
+            <v>-3.868355689867975</v>
           </cell>
           <cell r="M5">
-            <v>-3.8263746283537015</v>
+            <v>-3.9739167156266797</v>
           </cell>
           <cell r="N5">
-            <v>-3.936158845468507</v>
+            <v>-4.0789527375008516</v>
           </cell>
           <cell r="O5">
-            <v>-4.0335630799199329</v>
+            <v>-4.1802648473146302</v>
           </cell>
           <cell r="P5">
-            <v>-4.1191956885294871</v>
+            <v>-4.2793308136126251</v>
           </cell>
           <cell r="Q5">
-            <v>-4.1960202976913274</v>
+            <v>-4.3770577406321509</v>
           </cell>
           <cell r="R5">
-            <v>-4.2668115222945557</v>
+            <v>-4.4740248319046438</v>
           </cell>
           <cell r="S5">
-            <v>-4.3385282847099305</v>
+            <v>-4.5765614759202382</v>
           </cell>
           <cell r="T5">
-            <v>-4.4095100887892924</v>
+            <v>-4.679824798905063</v>
           </cell>
           <cell r="U5">
-            <v>-4.4812427552597729</v>
+            <v>-4.7837535205868527</v>
           </cell>
           <cell r="V5">
-            <v>-4.5547781342819116</v>
+            <v>-4.8881529444861238</v>
           </cell>
           <cell r="W5">
-            <v>-4.6311097941466812</v>
+            <v>-4.9931267962232244</v>
           </cell>
           <cell r="X5">
-            <v>-4.7099938027228561</v>
+            <v>-5.0978060566297945</v>
           </cell>
           <cell r="Y5">
-            <v>-4.7919176689637073</v>
+            <v>-5.2023648355869367</v>
           </cell>
           <cell r="Z5">
-            <v>-4.8769777598748458</v>
+            <v>-5.3067939708296379</v>
           </cell>
           <cell r="AA5">
-            <v>-4.965046439401311</v>
+            <v>-5.4110008706358403</v>
           </cell>
           <cell r="AB5">
-            <v>-5.0564131786857036</v>
+            <v>-5.5154431237263495</v>
           </cell>
           <cell r="AC5">
-            <v>-5.1476766199514916</v>
+            <v>-5.6166769147145583</v>
           </cell>
           <cell r="AD5">
-            <v>-5.2402349400153199</v>
+            <v>-5.716485047952502</v>
           </cell>
           <cell r="AE5">
-            <v>-5.333927805019723</v>
+            <v>-5.8149278107086477</v>
           </cell>
           <cell r="AF5">
-            <v>-5.4285754760130871</v>
+            <v>-5.9120418471148461</v>
           </cell>
           <cell r="AG5">
-            <v>-5.5239595975755229</v>
+            <v>-6.0078095479177414</v>
           </cell>
           <cell r="AH5">
-            <v>-5.6187350233234508</v>
+            <v>-6.1010733895568325</v>
           </cell>
           <cell r="AI5">
-            <v>-5.7135368368529278</v>
+            <v>-6.1926549109063922</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.808197333960619</v>
+            <v>-6.282529905937551</v>
           </cell>
           <cell r="AK5">
-            <v>-5.902594084908797</v>
+            <v>-6.3707002990826105</v>
           </cell>
           <cell r="AL5">
-            <v>-5.9966256826181734</v>
+            <v>-6.4571714369733417</v>
           </cell>
           <cell r="AM5">
-            <v>-6.0804467910879119</v>
+            <v>-6.5328982005756098</v>
           </cell>
           <cell r="AN5">
-            <v>-6.1616942705872919</v>
+            <v>-6.6052229531384903</v>
           </cell>
           <cell r="AO5">
-            <v>-6.2406874762081284</v>
+            <v>-6.6745322504579097</v>
           </cell>
           <cell r="AP5">
-            <v>-6.3179600181405</v>
+            <v>-6.7414084574380029</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.3939607803403353</v>
+            <v>-6.8063382189467951</v>
           </cell>
           <cell r="AR5">
-            <v>-6.4674527934628916</v>
+            <v>-6.8683033524690966</v>
           </cell>
           <cell r="AS5">
-            <v>-6.5399125774206368</v>
+            <v>-6.928668962176876</v>
           </cell>
           <cell r="AT5">
-            <v>-6.6116128037204565</v>
+            <v>-6.9877194682012256</v>
           </cell>
           <cell r="AU5">
-            <v>-6.6828151577913664</v>
+            <v>-7.0457205382521648</v>
           </cell>
           <cell r="AV5">
-            <v>-6.75374061275601</v>
+            <v>-7.1028945042994955</v>
           </cell>
           <cell r="AW5">
-            <v>-6.8192810107848505</v>
+            <v>-7.1550059082373441</v>
           </cell>
           <cell r="AX5">
-            <v>-6.8837080079757857</v>
+            <v>-7.2056768729780956</v>
           </cell>
           <cell r="AY5">
-            <v>-6.9474240648402024</v>
+            <v>-7.2553009327841806</v>
           </cell>
           <cell r="AZ5">
-            <v>-7.0108335681959062</v>
+            <v>-7.3042601965870313</v>
           </cell>
           <cell r="BA5">
-            <v>-7.0742357919410859</v>
+            <v>-7.3528340204140452</v>
           </cell>
         </row>
       </sheetData>
@@ -3718,160 +3797,181 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>-1.4134377529451903</v>
+            <v>-1.7698122826268814</v>
           </cell>
           <cell r="D5">
-            <v>-1.793521960439437</v>
+            <v>-2.1997652501852039</v>
           </cell>
           <cell r="E5">
-            <v>-2.1433063256721785</v>
+            <v>-2.5847061089792955</v>
           </cell>
           <cell r="F5">
-            <v>-2.4463052308986932</v>
+            <v>-2.9040185620997749</v>
           </cell>
           <cell r="G5">
-            <v>-2.7093767723510687</v>
+            <v>-3.1669712372714542</v>
           </cell>
           <cell r="H5">
-            <v>-2.9407512271360292</v>
+            <v>-3.3845992633824928</v>
           </cell>
           <cell r="I5">
-            <v>-3.1497704598259069</v>
+            <v>-3.5682948544118465</v>
           </cell>
           <cell r="J5">
-            <v>-3.3401167883251315</v>
+            <v>-3.724073469827982</v>
           </cell>
           <cell r="K5">
-            <v>-3.5164428017359417</v>
+            <v>-3.8584244908730803</v>
           </cell>
           <cell r="L5">
-            <v>-3.682788566089934</v>
+            <v>-3.9769851520614408</v>
           </cell>
           <cell r="M5">
-            <v>-3.9369483140161643</v>
+            <v>-4.0839028310477481</v>
           </cell>
           <cell r="N5">
-            <v>-4.0482551339010353</v>
+            <v>-4.1905910967002136</v>
           </cell>
           <cell r="O5">
-            <v>-4.1473819066695006</v>
+            <v>-4.2937160831078014</v>
           </cell>
           <cell r="P5">
-            <v>-4.2349535926846205</v>
+            <v>-4.3947818394412081</v>
           </cell>
           <cell r="Q5">
-            <v>-4.3139404547592131</v>
+            <v>-4.4947063037846124</v>
           </cell>
           <cell r="R5">
-            <v>-4.387112121402625</v>
+            <v>-4.5940682799609718</v>
           </cell>
           <cell r="S5">
-            <v>-4.4615417243119015</v>
+            <v>-4.6993161966967456</v>
           </cell>
           <cell r="T5">
-            <v>-4.535498089244494</v>
+            <v>-4.8055382159701843</v>
           </cell>
           <cell r="U5">
-            <v>-4.6104241154786507</v>
+            <v>-4.9126330076278091</v>
           </cell>
           <cell r="V5">
-            <v>-4.6873395633610926</v>
+            <v>-5.0203756817358887</v>
           </cell>
           <cell r="W5">
-            <v>-4.7673156312450837</v>
+            <v>-5.1289491238560299</v>
           </cell>
           <cell r="X5">
-            <v>-4.8498444305992372</v>
+            <v>-5.2372227712946025</v>
           </cell>
           <cell r="Y5">
-            <v>-4.9355299079195341</v>
+            <v>-5.3454880890333119</v>
           </cell>
           <cell r="Z5">
-            <v>-5.024452868139706</v>
+            <v>-5.4537218865997383</v>
           </cell>
           <cell r="AA5">
-            <v>-5.1164720848802308</v>
+            <v>-5.5618193339959987</v>
           </cell>
           <cell r="AB5">
-            <v>-5.2121771983503091</v>
+            <v>-5.6705376606647429</v>
           </cell>
           <cell r="AC5">
-            <v>-5.3075122406260888</v>
+            <v>-5.7757830410869904</v>
           </cell>
           <cell r="AD5">
-            <v>-5.4041074122913146</v>
+            <v>-5.8795706495365474</v>
           </cell>
           <cell r="AE5">
-            <v>-5.5018075134250282</v>
+            <v>-5.9819669267490605</v>
           </cell>
           <cell r="AF5">
-            <v>-5.6004375415494074</v>
+            <v>-6.0830142158722289</v>
           </cell>
           <cell r="AG5">
-            <v>-5.6997826557531379</v>
+            <v>-6.1826991248262742</v>
           </cell>
           <cell r="AH5">
-            <v>-5.7984634822230259</v>
+            <v>-6.2798309039570839</v>
           </cell>
           <cell r="AI5">
-            <v>-5.8971342988124782</v>
+            <v>-6.3752506579558883</v>
           </cell>
           <cell r="AJ5">
-            <v>-5.9956382581705441</v>
+            <v>-6.4689453223956139</v>
           </cell>
           <cell r="AK5">
-            <v>-6.0938611164246037</v>
+            <v>-6.5609251560287296</v>
           </cell>
           <cell r="AL5">
-            <v>-6.1917080267628872</v>
+            <v>-6.6512021960051682</v>
           </cell>
           <cell r="AM5">
-            <v>-6.2790779632635907</v>
+            <v>-6.7304775349177</v>
           </cell>
           <cell r="AN5">
-            <v>-6.3636600616960308</v>
+            <v>-6.806144490727295</v>
           </cell>
           <cell r="AO5">
-            <v>-6.4458492162444809</v>
+            <v>-6.8786642434899843</v>
           </cell>
           <cell r="AP5">
-            <v>-6.5262270211267071</v>
+            <v>-6.9486664767093975</v>
           </cell>
           <cell r="AQ5">
-            <v>-6.6052765500094202</v>
+            <v>-7.0166712340561821</v>
           </cell>
           <cell r="AR5">
-            <v>-6.6817298427610865</v>
+            <v>-7.0816293112992863</v>
           </cell>
           <cell r="AS5">
-            <v>-6.7571094605159754</v>
+            <v>-7.1449506270124026</v>
           </cell>
           <cell r="AT5">
-            <v>-6.8317161695697344</v>
+            <v>-7.2069472085133928</v>
           </cell>
           <cell r="AU5">
-            <v>-6.9058315740446847</v>
+            <v>-7.2679041002716271</v>
           </cell>
           <cell r="AV5">
-            <v>-6.9796909442198967</v>
+            <v>-7.3280575543701154</v>
           </cell>
           <cell r="AW5">
-            <v>-7.0479911434117026</v>
+            <v>-7.3829783928810455</v>
           </cell>
           <cell r="AX5">
-            <v>-7.1151098686792817</v>
+            <v>-7.4363922148458661</v>
           </cell>
           <cell r="AY5">
-            <v>-7.1814955125604873</v>
+            <v>-7.4887381279848508</v>
           </cell>
           <cell r="AZ5">
-            <v>-7.2475803820003515</v>
+            <v>-7.5404258420554982</v>
           </cell>
           <cell r="BA5">
-            <v>-7.3136815666987047</v>
+            <v>-7.5917522027450062</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4139,7 +4239,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4358,207 +4458,207 @@
       </c>
       <c r="B2" s="2">
         <f>(([2]Données!C5)/100)*-1</f>
-        <v>1.3538601712600906E-2</v>
+        <v>1.7105840554810015E-2</v>
       </c>
       <c r="C2" s="2">
         <f>(([2]Données!D5)/100)*-1</f>
-        <v>1.6912679139984843E-2</v>
+        <v>2.098056736359466E-2</v>
       </c>
       <c r="D2" s="2">
         <f>(([2]Données!E5)/100)*-1</f>
-        <v>2.0115560050032899E-2</v>
+        <v>2.4532546055058613E-2</v>
       </c>
       <c r="E2" s="2">
         <f>(([2]Données!F5)/100)*-1</f>
-        <v>2.2943774902325131E-2</v>
+        <v>2.7517937372380175E-2</v>
       </c>
       <c r="F2" s="2">
         <f>(([2]Données!G5)/100)*-1</f>
-        <v>2.5425308096377663E-2</v>
+        <v>2.9990320526349201E-2</v>
       </c>
       <c r="G2" s="2">
         <f>(([2]Données!H5)/100)*-1</f>
-        <v>2.7611418605846372E-2</v>
+        <v>3.2030280950868795E-2</v>
       </c>
       <c r="H2" s="2">
         <f>(([2]Données!I5)/100)*-1</f>
-        <v>2.9576927529626262E-2</v>
+        <v>3.3733930388557543E-2</v>
       </c>
       <c r="I2" s="2">
         <f>(([2]Données!J5)/100)*-1</f>
-        <v>3.1353239073615535E-2</v>
+        <v>3.51562243585547E-2</v>
       </c>
       <c r="J2" s="2">
         <f>(([2]Données!K5)/100)*-1</f>
-        <v>3.2985843392642766E-2</v>
+        <v>3.6361018719246463E-2</v>
       </c>
       <c r="K2" s="2">
         <f>(([2]Données!L5)/100)*-1</f>
-        <v>3.4516237501799885E-2</v>
+        <v>3.7405791429351631E-2</v>
       </c>
       <c r="L2" s="2">
         <f>(([2]Données!M5)/100)*-1</f>
-        <v>3.6927247412231856E-2</v>
+        <v>3.8334394917893921E-2</v>
       </c>
       <c r="M2" s="2">
         <f>(([2]Données!N5)/100)*-1</f>
-        <v>3.7901004681047845E-2</v>
+        <v>3.925556698553101E-2</v>
       </c>
       <c r="N2" s="2">
         <f>(([2]Données!O5)/100)*-1</f>
-        <v>3.8748605891280929E-2</v>
+        <v>4.0138240489166144E-2</v>
       </c>
       <c r="O2" s="2">
         <f>(([2]Données!P5)/100)*-1</f>
-        <v>3.9477051688237563E-2</v>
+        <v>4.0997975041976102E-2</v>
       </c>
       <c r="P2" s="2">
         <f>(([2]Données!Q5)/100)*-1</f>
-        <v>4.0116488877360634E-2</v>
+        <v>4.1844108990118138E-2</v>
       </c>
       <c r="Q2" s="2">
         <f>(([2]Données!R5)/100)*-1</f>
-        <v>4.0694640941231978E-2</v>
+        <v>4.2682193718009402E-2</v>
       </c>
       <c r="R2" s="2">
         <f>(([2]Données!S5)/100)*-1</f>
-        <v>4.1277964002331198E-2</v>
+        <v>4.3572346504538013E-2</v>
       </c>
       <c r="S2" s="2">
         <f>(([2]Données!T5)/100)*-1</f>
-        <v>4.1849741026071745E-2</v>
+        <v>4.4465811282116692E-2</v>
       </c>
       <c r="T2" s="2">
         <f>(([2]Données!U5)/100)*-1</f>
-        <v>4.2425458296820991E-2</v>
+        <v>4.5362483138397192E-2</v>
       </c>
       <c r="U2" s="2">
         <f>(([2]Données!V5)/100)*-1</f>
-        <v>4.3016340742832782E-2</v>
+        <v>4.6261021063189967E-2</v>
       </c>
       <c r="V2" s="2">
         <f>(([2]Données!W5)/100)*-1</f>
-        <v>4.3633104309372284E-2</v>
+        <v>4.7163174260623449E-2</v>
       </c>
       <c r="W2" s="2">
         <f>(([2]Données!X5)/100)*-1</f>
-        <v>4.427314031618601E-2</v>
+        <v>4.8060004625971375E-2</v>
       </c>
       <c r="X2" s="2">
         <f>(([2]Données!Y5)/100)*-1</f>
-        <v>4.4941592729452529E-2</v>
+        <v>4.8953489734531723E-2</v>
       </c>
       <c r="Y2" s="2">
         <f>(([2]Données!Z5)/100)*-1</f>
-        <v>4.563947337910957E-2</v>
+        <v>4.9843562098548233E-2</v>
       </c>
       <c r="Z2" s="2">
         <f>(([2]Données!AA5)/100)*-1</f>
-        <v>4.6365523266142288E-2</v>
+        <v>5.0729292917466084E-2</v>
       </c>
       <c r="AA2" s="2">
         <f>(([2]Données!AB5)/100)*-1</f>
-        <v>4.7123697653551948E-2</v>
+        <v>5.1616312992447518E-2</v>
       </c>
       <c r="AB2" s="2">
         <f>(([2]Données!AC5)/100)*-1</f>
-        <v>4.788032119780028E-2</v>
+        <v>5.2470427631295502E-2</v>
       </c>
       <c r="AC2" s="2">
         <f>(([2]Données!AD5)/100)*-1</f>
-        <v>4.8649621572917197E-2</v>
+        <v>5.3309757047204975E-2</v>
       </c>
       <c r="AD2" s="2">
         <f>(([2]Données!AE5)/100)*-1</f>
-        <v>4.9429610515789646E-2</v>
+        <v>5.4134537423666911E-2</v>
       </c>
       <c r="AE2" s="2">
         <f>(([2]Données!AF5)/100)*-1</f>
-        <v>5.0218084317584018E-2</v>
+        <v>5.4944750354783627E-2</v>
       </c>
       <c r="AF2" s="2">
         <f>(([2]Données!AG5)/100)*-1</f>
-        <v>5.1012621505727829E-2</v>
+        <v>5.5740006203695458E-2</v>
       </c>
       <c r="AG2" s="2">
         <f>(([2]Données!AH5)/100)*-1</f>
-        <v>5.1800471640880197E-2</v>
+        <v>5.6509432844425334E-2</v>
       </c>
       <c r="AH2" s="2">
         <f>(([2]Données!AI5)/100)*-1</f>
-        <v>5.2587995224248063E-2</v>
+        <v>5.7261280214704439E-2</v>
       </c>
       <c r="AI2" s="2">
         <f>(([2]Données!AJ5)/100)*-1</f>
-        <v>5.33733113615723E-2</v>
+        <v>5.7995105060567376E-2</v>
       </c>
       <c r="AJ2" s="2">
         <f>(([2]Données!AK5)/100)*-1</f>
-        <v>5.4154996240649018E-2</v>
+        <v>5.8710724612016547E-2</v>
       </c>
       <c r="AK2" s="2">
         <f>(([2]Données!AL5)/100)*-1</f>
-        <v>5.4931912985350273E-2</v>
+        <v>5.9408064863598842E-2</v>
       </c>
       <c r="AL2" s="2">
         <f>(([2]Données!AM5)/100)*-1</f>
-        <v>5.5612806592488247E-2</v>
+        <v>6.0003827900889546E-2</v>
       </c>
       <c r="AM2" s="2">
         <f>(([2]Données!AN5)/100)*-1</f>
-        <v>5.6273572035804416E-2</v>
+        <v>6.0571000103954893E-2</v>
       </c>
       <c r="AN2" s="2">
         <f>(([2]Données!AO5)/100)*-1</f>
-        <v>5.6914643529708646E-2</v>
+        <v>6.1110748911116231E-2</v>
       </c>
       <c r="AO2" s="2">
         <f>(([2]Données!AP5)/100)*-1</f>
-        <v>5.753897634474104E-2</v>
+        <v>6.1626563911912131E-2</v>
       </c>
       <c r="AP2" s="2">
         <f>(([2]Données!AQ5)/100)*-1</f>
-        <v>5.8149801337017311E-2</v>
+        <v>6.2122074676719145E-2</v>
       </c>
       <c r="AQ2" s="2">
         <f>(([2]Données!AR5)/100)*-1</f>
-        <v>5.8735596987392939E-2</v>
+        <v>6.2587962491754912E-2</v>
       </c>
       <c r="AR2" s="2">
         <f>(([2]Données!AS5)/100)*-1</f>
-        <v>5.9311343796265348E-2</v>
+        <v>6.3038097195504572E-2</v>
       </c>
       <c r="AS2" s="2">
         <f>(([2]Données!AT5)/100)*-1</f>
-        <v>5.9879563862663465E-2</v>
+        <v>6.3475234557170079E-2</v>
       </c>
       <c r="AT2" s="2">
         <f>(([2]Données!AU5)/100)*-1</f>
-        <v>6.0442828733665251E-2</v>
+        <v>6.3901885641366452E-2</v>
       </c>
       <c r="AU2" s="2">
         <f>(([2]Données!AV5)/100)*-1</f>
-        <v>6.1003296850866917E-2</v>
+        <v>6.43201329379125E-2</v>
       </c>
       <c r="AV2" s="2">
         <f>(([2]Données!AW5)/100)*-1</f>
-        <v>6.1513652688195419E-2</v>
+        <v>6.4691410532873417E-2</v>
       </c>
       <c r="AW2" s="2">
         <f>(([2]Données!AX5)/100)*-1</f>
-        <v>6.2016559531788203E-2</v>
+        <v>6.5051793926074519E-2</v>
       </c>
       <c r="AX2" s="2">
         <f>(([2]Données!AY5)/100)*-1</f>
-        <v>6.2514296331188435E-2</v>
+        <v>6.5403479043005697E-2</v>
       </c>
       <c r="AY2" s="2">
         <f>(([2]Données!AZ5)/100)*-1</f>
-        <v>6.3009329987089857E-2</v>
+        <v>6.5748713084534671E-2</v>
       </c>
       <c r="AZ2" s="4">
         <f>(([2]Données!BA5)/100)*-1</f>
-        <v>6.3503741412501813E-2</v>
+        <v>6.6089373105816973E-2</v>
       </c>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.35">
@@ -4567,207 +4667,207 @@
       </c>
       <c r="B3" s="2">
         <f>(([3]Données!C5)/100)*-1</f>
-        <v>1.3672989606358987E-2</v>
+        <v>1.7239083776241837E-2</v>
       </c>
       <c r="C3" s="2">
         <f>(([3]Données!D5)/100)*-1</f>
-        <v>1.7174495306202409E-2</v>
+        <v>2.1239935207077454E-2</v>
       </c>
       <c r="D3" s="2">
         <f>(([3]Données!E5)/100)*-1</f>
-        <v>2.0477676385590282E-2</v>
+        <v>2.4891225395322514E-2</v>
       </c>
       <c r="E3" s="2">
         <f>(([3]Données!F5)/100)*-1</f>
-        <v>2.338101922407565E-2</v>
+        <v>2.7951154979427906E-2</v>
       </c>
       <c r="F3" s="2">
         <f>(([3]Données!G5)/100)*-1</f>
-        <v>2.5924392080600156E-2</v>
+        <v>3.0485007207746717E-2</v>
       </c>
       <c r="G3" s="2">
         <f>(([3]Données!H5)/100)*-1</f>
-        <v>2.8170343744913895E-2</v>
+        <v>3.258445650476105E-2</v>
       </c>
       <c r="H3" s="2">
         <f>(([3]Données!I5)/100)*-1</f>
-        <v>3.0199679852574546E-2</v>
+        <v>3.4351509459371377E-2</v>
       </c>
       <c r="I3" s="2">
         <f>(([3]Données!J5)/100)*-1</f>
-        <v>3.2044636480139999E-2</v>
+        <v>3.5842063990634165E-2</v>
       </c>
       <c r="J3" s="2">
         <f>(([3]Données!K5)/100)*-1</f>
-        <v>3.3749792479178753E-2</v>
+        <v>3.7119212821545733E-2</v>
       </c>
       <c r="K3" s="2">
         <f>(([3]Données!L5)/100)*-1</f>
-        <v>3.5355106743683251E-2</v>
+        <v>3.823893445591442E-2</v>
       </c>
       <c r="L3" s="2">
         <f>(([3]Données!M5)/100)*-1</f>
-        <v>3.7840113348240667E-2</v>
+        <v>3.9243808589903617E-2</v>
       </c>
       <c r="M3" s="2">
         <f>(([3]Données!N5)/100)*-1</f>
-        <v>3.8892630987244492E-2</v>
+        <v>4.0243051535956094E-2</v>
       </c>
       <c r="N3" s="2">
         <f>(([3]Données!O5)/100)*-1</f>
-        <v>3.9820630063436724E-2</v>
+        <v>4.1205009025164226E-2</v>
       </c>
       <c r="O3" s="2">
         <f>(([3]Données!P5)/100)*-1</f>
-        <v>4.0630615722784924E-2</v>
+        <v>4.214481464955333E-2</v>
       </c>
       <c r="P3" s="2">
         <f>(([3]Données!Q5)/100)*-1</f>
-        <v>4.1352345269782598E-2</v>
+        <v>4.3071546522808868E-2</v>
       </c>
       <c r="Q3" s="2">
         <f>(([3]Données!R5)/100)*-1</f>
-        <v>4.2013346077308E-2</v>
+        <v>4.399070152224837E-2</v>
       </c>
       <c r="R3" s="2">
         <f>(([3]Données!S5)/100)*-1</f>
-        <v>4.2681694202585163E-2</v>
+        <v>4.4964038097517471E-2</v>
       </c>
       <c r="S3" s="2">
         <f>(([3]Données!T5)/100)*-1</f>
-        <v>4.3340377092348274E-2</v>
+        <v>4.5942586889975212E-2</v>
       </c>
       <c r="T3" s="2">
         <f>(([3]Données!U5)/100)*-1</f>
-        <v>4.4004366322958344E-2</v>
+        <v>4.6925741669075594E-2</v>
       </c>
       <c r="U3" s="2">
         <f>(([3]Données!V5)/100)*-1</f>
-        <v>4.4684316308185368E-2</v>
+        <v>4.7911596378355625E-2</v>
       </c>
       <c r="V3" s="2">
         <f>(([3]Données!W5)/100)*-1</f>
-        <v>4.5390251562328017E-2</v>
+        <v>4.890120474243953E-2</v>
       </c>
       <c r="W3" s="2">
         <f>(([3]Données!X5)/100)*-1</f>
-        <v>4.6119526770055375E-2</v>
+        <v>4.9885606660133863E-2</v>
       </c>
       <c r="X3" s="2">
         <f>(([3]Données!Y5)/100)*-1</f>
-        <v>4.6876974335740673E-2</v>
+        <v>5.0866473227110125E-2</v>
       </c>
       <c r="Y3" s="2">
         <f>(([3]Données!Z5)/100)*-1</f>
-        <v>4.7663498416245842E-2</v>
+        <v>5.1843638809987096E-2</v>
       </c>
       <c r="Z3" s="2">
         <f>(([3]Données!AA5)/100)*-1</f>
-        <v>4.8477793812705346E-2</v>
+        <v>5.2816141303685393E-2</v>
       </c>
       <c r="AA3" s="2">
         <f>(([3]Données!AB5)/100)*-1</f>
-        <v>4.932305011022297E-2</v>
+        <v>5.3788847826956247E-2</v>
       </c>
       <c r="AB3" s="2">
         <f>(([3]Données!AC5)/100)*-1</f>
-        <v>5.0165613008498644E-2</v>
+        <v>5.4727626523337951E-2</v>
       </c>
       <c r="AC3" s="2">
         <f>(([3]Données!AD5)/100)*-1</f>
-        <v>5.1019643979885787E-2</v>
+        <v>5.5650523438231181E-2</v>
       </c>
       <c r="AD3" s="2">
         <f>(([3]Données!AE5)/100)*-1</f>
-        <v>5.1883408595703721E-2</v>
+        <v>5.6558045965432235E-2</v>
       </c>
       <c r="AE3" s="2">
         <f>(([3]Données!AF5)/100)*-1</f>
-        <v>5.2755001072149588E-2</v>
+        <v>5.7450476278337985E-2</v>
       </c>
       <c r="AF3" s="2">
         <f>(([3]Données!AG5)/100)*-1</f>
-        <v>5.3632237777372464E-2</v>
+        <v>5.8327643326368757E-2</v>
       </c>
       <c r="AG3" s="2">
         <f>(([3]Données!AH5)/100)*-1</f>
-        <v>5.4502122415457599E-2</v>
+        <v>5.9178423246791227E-2</v>
       </c>
       <c r="AH3" s="2">
         <f>(([3]Données!AI5)/100)*-1</f>
-        <v>5.5371105410730204E-2</v>
+        <v>6.0011152322248851E-2</v>
       </c>
       <c r="AI3" s="2">
         <f>(([3]Données!AJ5)/100)*-1</f>
-        <v>5.6237434247091933E-2</v>
+        <v>6.0825513449470063E-2</v>
       </c>
       <c r="AJ3" s="2">
         <f>(([3]Données!AK5)/100)*-1</f>
-        <v>5.7099803973477137E-2</v>
+        <v>6.1621440880965321E-2</v>
       </c>
       <c r="AK3" s="2">
         <f>(([3]Données!AL5)/100)*-1</f>
-        <v>5.7957164990088073E-2</v>
+        <v>6.2398945263227423E-2</v>
       </c>
       <c r="AL3" s="2">
         <f>(([3]Données!AM5)/100)*-1</f>
-        <v>5.8714889271429434E-2</v>
+        <v>6.307131777274233E-2</v>
       </c>
       <c r="AM3" s="2">
         <f>(([3]Données!AN5)/100)*-1</f>
-        <v>5.9449229672438812E-2</v>
+        <v>6.3711924471877124E-2</v>
       </c>
       <c r="AN3" s="2">
         <f>(([3]Données!AO5)/100)*-1</f>
-        <v>6.0161600156355854E-2</v>
+        <v>6.4322910590061233E-2</v>
       </c>
       <c r="AO3" s="2">
         <f>(([3]Données!AP5)/100)*-1</f>
-        <v>6.0855962145012106E-2</v>
+        <v>6.4908771262686682E-2</v>
       </c>
       <c r="AP3" s="2">
         <f>(([3]Données!AQ5)/100)*-1</f>
-        <v>6.1536280510864468E-2</v>
+        <v>6.5473870189902916E-2</v>
       </c>
       <c r="AQ3" s="2">
         <f>(([3]Données!AR5)/100)*-1</f>
-        <v>6.2190933045863532E-2</v>
+        <v>6.6008768155865649E-2</v>
       </c>
       <c r="AR3" s="2">
         <f>(([3]Données!AS5)/100)*-1</f>
-        <v>6.2835066098031023E-2</v>
+        <v>6.6527493921291425E-2</v>
       </c>
       <c r="AS3" s="2">
         <f>(([3]Données!AT5)/100)*-1</f>
-        <v>6.3471463173807252E-2</v>
+        <v>6.703294146440697E-2</v>
       </c>
       <c r="AT3" s="2">
         <f>(([3]Données!AU5)/100)*-1</f>
-        <v>6.4102710957324671E-2</v>
+        <v>6.7527723799083117E-2</v>
       </c>
       <c r="AU3" s="2">
         <f>(([3]Données!AV5)/100)*-1</f>
-        <v>6.4730962309951678E-2</v>
+        <v>6.8013988833824368E-2</v>
       </c>
       <c r="AV3" s="2">
         <f>(([3]Données!AW5)/100)*-1</f>
-        <v>6.5307300641254673E-2</v>
+        <v>6.8451523347565102E-2</v>
       </c>
       <c r="AW3" s="2">
         <f>(([3]Données!AX5)/100)*-1</f>
-        <v>6.5874374029159188E-2</v>
+        <v>6.8876472311519055E-2</v>
       </c>
       <c r="AX3" s="2">
         <f>(([3]Données!AY5)/100)*-1</f>
-        <v>6.6434968759283564E-2</v>
+        <v>6.9291553937470551E-2</v>
       </c>
       <c r="AY3" s="2">
         <f>(([3]Données!AZ5)/100)*-1</f>
-        <v>6.6992107040962479E-2</v>
+        <v>6.9699577755831021E-2</v>
       </c>
       <c r="AZ3" s="4">
         <f>(([3]Données!BA5)/100)*-1</f>
-        <v>6.7548297126593604E-2</v>
+        <v>7.0102850440077358E-2</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.35">
@@ -4776,207 +4876,207 @@
       </c>
       <c r="B4" s="2">
         <f>-0.01*[4]Données!C5</f>
-        <v>1.3734652863725771E-2</v>
+        <v>1.72967218222293E-2</v>
       </c>
       <c r="C4" s="2">
         <f>([4]Données!D5/100)*-1</f>
-        <v>1.7298565048007308E-2</v>
+        <v>2.1360026873177951E-2</v>
       </c>
       <c r="D4" s="2">
         <f>([4]Données!E5/100)*-1</f>
-        <v>2.0645656708817461E-2</v>
+        <v>2.5059966593618421E-2</v>
       </c>
       <c r="E4" s="2">
         <f>([4]Données!F5/100)*-1</f>
-        <v>2.357633648455304E-2</v>
+        <v>2.8155374730618687E-2</v>
       </c>
       <c r="F4" s="2">
         <f>([4]Données!G5/100)*-1</f>
-        <v>2.6140093324245939E-2</v>
+        <v>3.0719478873656336E-2</v>
       </c>
       <c r="G4" s="2">
         <f>([4]Données!H5/100)*-1</f>
-        <v>2.8407767554473717E-2</v>
+        <v>3.2850913693374229E-2</v>
       </c>
       <c r="H4" s="2">
         <f>([4]Données!I5/100)*-1</f>
-        <v>3.0464601393956126E-2</v>
+        <v>3.4655332539311412E-2</v>
       </c>
       <c r="I4" s="2">
         <f>([4]Données!J5/100)*-1</f>
-        <v>3.2343626267274828E-2</v>
+        <v>3.618909783269264E-2</v>
       </c>
       <c r="J4" s="2">
         <f>([4]Données!K5/100)*-1</f>
-        <v>3.4088044589155264E-2</v>
+        <v>3.751384574217087E-2</v>
       </c>
       <c r="K4" s="2">
         <f>([4]Données!L5/100)*-1</f>
-        <v>3.5735780011471041E-2</v>
+        <v>3.868355689867975E-2</v>
       </c>
       <c r="L4" s="2">
         <f>([4]Données!M5/100)*-1</f>
-        <v>3.8263746283537015E-2</v>
+        <v>3.9739167156266797E-2</v>
       </c>
       <c r="M4" s="2">
         <f>([4]Données!N5/100)*-1</f>
-        <v>3.936158845468507E-2</v>
+        <v>4.0789527375008516E-2</v>
       </c>
       <c r="N4" s="2">
         <f>([4]Données!O5/100)*-1</f>
-        <v>4.0335630799199329E-2</v>
+        <v>4.1802648473146305E-2</v>
       </c>
       <c r="O4" s="2">
         <f>([4]Données!P5/100)*-1</f>
-        <v>4.1191956885294874E-2</v>
+        <v>4.2793308136126251E-2</v>
       </c>
       <c r="P4" s="2">
         <f>([4]Données!Q5/100)*-1</f>
-        <v>4.1960202976913274E-2</v>
+        <v>4.3770577406321509E-2</v>
       </c>
       <c r="Q4" s="2">
         <f>([4]Données!R5/100)*-1</f>
-        <v>4.2668115222945557E-2</v>
+        <v>4.4740248319046438E-2</v>
       </c>
       <c r="R4" s="2">
         <f>([4]Données!S5/100)*-1</f>
-        <v>4.3385282847099305E-2</v>
+        <v>4.5765614759202385E-2</v>
       </c>
       <c r="S4" s="2">
         <f>([4]Données!T5/100)*-1</f>
-        <v>4.4095100887892924E-2</v>
+        <v>4.6798247989050627E-2</v>
       </c>
       <c r="T4" s="2">
         <f>([4]Données!U5/100)*-1</f>
-        <v>4.4812427552597726E-2</v>
+        <v>4.7837535205868524E-2</v>
       </c>
       <c r="U4" s="2">
         <f>([4]Données!V5/100)*-1</f>
-        <v>4.5547781342819116E-2</v>
+        <v>4.8881529444861238E-2</v>
       </c>
       <c r="V4" s="2">
         <f>([4]Données!W5/100)*-1</f>
-        <v>4.631109794146681E-2</v>
+        <v>4.9931267962232247E-2</v>
       </c>
       <c r="W4" s="2">
         <f>([4]Données!X5/100)*-1</f>
-        <v>4.7099938027228561E-2</v>
+        <v>5.0978060566297945E-2</v>
       </c>
       <c r="X4" s="2">
         <f>([4]Données!Y5/100)*-1</f>
-        <v>4.791917668963707E-2</v>
+        <v>5.2023648355869367E-2</v>
       </c>
       <c r="Y4" s="2">
         <f>([4]Données!Z5/100)*-1</f>
-        <v>4.8769777598748461E-2</v>
+        <v>5.3067939708296381E-2</v>
       </c>
       <c r="Z4" s="2">
         <f>([4]Données!AA5/100)*-1</f>
-        <v>4.9650464394013112E-2</v>
+        <v>5.4110008706358403E-2</v>
       </c>
       <c r="AA4" s="2">
         <f>([4]Données!AB5/100)*-1</f>
-        <v>5.0564131786857036E-2</v>
+        <v>5.5154431237263497E-2</v>
       </c>
       <c r="AB4" s="2">
         <f>([4]Données!AC5/100)*-1</f>
-        <v>5.1476766199514919E-2</v>
+        <v>5.6166769147145586E-2</v>
       </c>
       <c r="AC4" s="2">
         <f>([4]Données!AD5/100)*-1</f>
-        <v>5.2402349400153196E-2</v>
+        <v>5.716485047952502E-2</v>
       </c>
       <c r="AD4" s="2">
         <f>([4]Données!AE5/100)*-1</f>
-        <v>5.3339278050197232E-2</v>
+        <v>5.8149278107086477E-2</v>
       </c>
       <c r="AE4" s="2">
         <f>([4]Données!AF5/100)*-1</f>
-        <v>5.4285754760130873E-2</v>
+        <v>5.9120418471148461E-2</v>
       </c>
       <c r="AF4" s="2">
         <f>([4]Données!AG5/100)*-1</f>
-        <v>5.5239595975755229E-2</v>
+        <v>6.0078095479177411E-2</v>
       </c>
       <c r="AG4" s="2">
         <f>([4]Données!AH5/100)*-1</f>
-        <v>5.6187350233234505E-2</v>
+        <v>6.1010733895568325E-2</v>
       </c>
       <c r="AH4" s="2">
         <f>([4]Données!AI5/100)*-1</f>
-        <v>5.7135368368529275E-2</v>
+        <v>6.1926549109063922E-2</v>
       </c>
       <c r="AI4" s="2">
         <f>([4]Données!AJ5/100)*-1</f>
-        <v>5.8081973339606192E-2</v>
+        <v>6.2825299059375506E-2</v>
       </c>
       <c r="AJ4" s="2">
         <f>([4]Données!AK5/100)*-1</f>
-        <v>5.9025940849087973E-2</v>
+        <v>6.37070029908261E-2</v>
       </c>
       <c r="AK4" s="2">
         <f>([4]Données!AL5/100)*-1</f>
-        <v>5.9966256826181737E-2</v>
+        <v>6.4571714369733413E-2</v>
       </c>
       <c r="AL4" s="2">
         <f>([4]Données!AM5/100)*-1</f>
-        <v>6.0804467910879116E-2</v>
+        <v>6.5328982005756098E-2</v>
       </c>
       <c r="AM4" s="2">
         <f>([4]Données!AN5/100)*-1</f>
-        <v>6.1616942705872917E-2</v>
+        <v>6.6052229531384898E-2</v>
       </c>
       <c r="AN4" s="2">
         <f>([4]Données!AO5/100)*-1</f>
-        <v>6.2406874762081281E-2</v>
+        <v>6.6745322504579097E-2</v>
       </c>
       <c r="AO4" s="2">
         <f>([4]Données!AP5/100)*-1</f>
-        <v>6.3179600181405005E-2</v>
+        <v>6.7414084574380029E-2</v>
       </c>
       <c r="AP4" s="2">
         <f>([4]Données!AQ5/100)*-1</f>
-        <v>6.3939607803403353E-2</v>
+        <v>6.8063382189467947E-2</v>
       </c>
       <c r="AQ4" s="2">
         <f>([4]Données!AR5/100)*-1</f>
-        <v>6.4674527934628911E-2</v>
+        <v>6.8683033524690962E-2</v>
       </c>
       <c r="AR4" s="2">
         <f>([4]Données!AS5/100)*-1</f>
-        <v>6.5399125774206368E-2</v>
+        <v>6.928668962176876E-2</v>
       </c>
       <c r="AS4" s="2">
         <f>([4]Données!AT5/100)*-1</f>
-        <v>6.6116128037204569E-2</v>
+        <v>6.9877194682012256E-2</v>
       </c>
       <c r="AT4" s="2">
         <f>([4]Données!AU5/100)*-1</f>
-        <v>6.6828151577913664E-2</v>
+        <v>7.0457205382521648E-2</v>
       </c>
       <c r="AU4" s="2">
         <f>([4]Données!AV5/100)*-1</f>
-        <v>6.7537406127560096E-2</v>
+        <v>7.1028945042994951E-2</v>
       </c>
       <c r="AV4" s="2">
         <f>([4]Données!AW5/100)*-1</f>
-        <v>6.8192810107848501E-2</v>
+        <v>7.1550059082373441E-2</v>
       </c>
       <c r="AW4" s="2">
         <f>([4]Données!AX5/100)*-1</f>
-        <v>6.8837080079757862E-2</v>
+        <v>7.2056768729780951E-2</v>
       </c>
       <c r="AX4" s="2">
         <f>([4]Données!AY5/100)*-1</f>
-        <v>6.9474240648402019E-2</v>
+        <v>7.2553009327841811E-2</v>
       </c>
       <c r="AY4" s="2">
         <f>([4]Données!AZ5/100)*-1</f>
-        <v>7.0108335681959066E-2</v>
+        <v>7.3042601965870313E-2</v>
       </c>
       <c r="AZ4" s="4">
         <f>([4]Données!BA5/100)*-1</f>
-        <v>7.0742357919410859E-2</v>
+        <v>7.3528340204140452E-2</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.35">
@@ -4985,207 +5085,207 @@
       </c>
       <c r="B5" s="2">
         <f>-0.01*[5]Données!C5</f>
-        <v>1.4134377529451903E-2</v>
+        <v>1.7698122826268814E-2</v>
       </c>
       <c r="C5" s="2">
         <f>-0.01*[5]Données!D5</f>
-        <v>1.793521960439437E-2</v>
+        <v>2.1997652501852039E-2</v>
       </c>
       <c r="D5" s="2">
         <f>-0.01*[5]Données!E5</f>
-        <v>2.1433063256721785E-2</v>
+        <v>2.5847061089792955E-2</v>
       </c>
       <c r="E5" s="2">
         <f>-0.01*[5]Données!F5</f>
-        <v>2.4463052308986932E-2</v>
+        <v>2.9040185620997749E-2</v>
       </c>
       <c r="F5" s="2">
         <f>-0.01*[5]Données!G5</f>
-        <v>2.7093767723510687E-2</v>
+        <v>3.1669712372714542E-2</v>
       </c>
       <c r="G5" s="2">
         <f>-0.01*[5]Données!H5</f>
-        <v>2.9407512271360292E-2</v>
+        <v>3.3845992633824928E-2</v>
       </c>
       <c r="H5" s="2">
         <f>-0.01*[5]Données!I5</f>
-        <v>3.1497704598259069E-2</v>
+        <v>3.5682948544118465E-2</v>
       </c>
       <c r="I5" s="2">
         <f>-0.01*[5]Données!J5</f>
-        <v>3.3401167883251315E-2</v>
+        <v>3.724073469827982E-2</v>
       </c>
       <c r="J5" s="2">
         <f>-0.01*[5]Données!K5</f>
-        <v>3.5164428017359417E-2</v>
+        <v>3.8584244908730803E-2</v>
       </c>
       <c r="K5" s="2">
         <f>-0.01*[5]Données!L5</f>
-        <v>3.682788566089934E-2</v>
+        <v>3.9769851520614408E-2</v>
       </c>
       <c r="L5" s="2">
         <f>-0.01*[5]Données!M5</f>
-        <v>3.9369483140161643E-2</v>
+        <v>4.0839028310477483E-2</v>
       </c>
       <c r="M5" s="2">
         <f>-0.01*[5]Données!N5</f>
-        <v>4.0482551339010353E-2</v>
+        <v>4.1905910967002136E-2</v>
       </c>
       <c r="N5" s="2">
         <f>-0.01*[5]Données!O5</f>
-        <v>4.1473819066695006E-2</v>
+        <v>4.2937160831078014E-2</v>
       </c>
       <c r="O5" s="2">
         <f>-0.01*[5]Données!P5</f>
-        <v>4.2349535926846205E-2</v>
+        <v>4.3947818394412079E-2</v>
       </c>
       <c r="P5" s="2">
         <f>-0.01*[5]Données!Q5</f>
-        <v>4.3139404547592131E-2</v>
+        <v>4.4947063037846124E-2</v>
       </c>
       <c r="Q5" s="2">
         <f>-0.01*[5]Données!R5</f>
-        <v>4.3871121214026247E-2</v>
+        <v>4.5940682799609715E-2</v>
       </c>
       <c r="R5" s="2">
         <f>-0.01*[5]Données!S5</f>
-        <v>4.4615417243119015E-2</v>
+        <v>4.6993161966967456E-2</v>
       </c>
       <c r="S5" s="2">
         <f>-0.01*[5]Données!T5</f>
-        <v>4.535498089244494E-2</v>
+        <v>4.8055382159701843E-2</v>
       </c>
       <c r="T5" s="2">
         <f>-0.01*[5]Données!U5</f>
-        <v>4.6104241154786507E-2</v>
+        <v>4.9126330076278091E-2</v>
       </c>
       <c r="U5" s="2">
         <f>-0.01*[5]Données!V5</f>
-        <v>4.6873395633610926E-2</v>
+        <v>5.0203756817358891E-2</v>
       </c>
       <c r="V5" s="2">
         <f>-0.01*[5]Données!W5</f>
-        <v>4.7673156312450837E-2</v>
+        <v>5.1289491238560303E-2</v>
       </c>
       <c r="W5" s="2">
         <f>-0.01*[5]Données!X5</f>
-        <v>4.8498444305992372E-2</v>
+        <v>5.2372227712946029E-2</v>
       </c>
       <c r="X5" s="2">
         <f>-0.01*[5]Données!Y5</f>
-        <v>4.9355299079195343E-2</v>
+        <v>5.3454880890333123E-2</v>
       </c>
       <c r="Y5" s="2">
         <f>-0.01*[5]Données!Z5</f>
-        <v>5.024452868139706E-2</v>
+        <v>5.4537218865997383E-2</v>
       </c>
       <c r="Z5" s="2">
         <f>-0.01*[5]Données!AA5</f>
-        <v>5.116472084880231E-2</v>
+        <v>5.5618193339959987E-2</v>
       </c>
       <c r="AA5" s="2">
         <f>-0.01*[5]Données!AB5</f>
-        <v>5.2121771983503096E-2</v>
+        <v>5.6705376606647429E-2</v>
       </c>
       <c r="AB5" s="2">
         <f>-0.01*[5]Données!AC5</f>
-        <v>5.3075122406260888E-2</v>
+        <v>5.7757830410869904E-2</v>
       </c>
       <c r="AC5" s="2">
         <f>-0.01*[5]Données!AD5</f>
-        <v>5.4041074122913146E-2</v>
+        <v>5.8795706495365474E-2</v>
       </c>
       <c r="AD5" s="2">
         <f>-0.01*[5]Données!AE5</f>
-        <v>5.5018075134250284E-2</v>
+        <v>5.9819669267490605E-2</v>
       </c>
       <c r="AE5" s="2">
         <f>-0.01*[5]Données!AF5</f>
-        <v>5.6004375415494079E-2</v>
+        <v>6.0830142158722289E-2</v>
       </c>
       <c r="AF5" s="2">
         <f>-0.01*[5]Données!AG5</f>
-        <v>5.6997826557531384E-2</v>
+        <v>6.1826991248262742E-2</v>
       </c>
       <c r="AG5" s="2">
         <f>-0.01*[5]Données!AH5</f>
-        <v>5.7984634822230263E-2</v>
+        <v>6.2798309039570843E-2</v>
       </c>
       <c r="AH5" s="2">
         <f>-0.01*[5]Données!AI5</f>
-        <v>5.8971342988124786E-2</v>
+        <v>6.3752506579558887E-2</v>
       </c>
       <c r="AI5" s="2">
         <f>-0.01*[5]Données!AJ5</f>
-        <v>5.9956382581705443E-2</v>
+        <v>6.4689453223956139E-2</v>
       </c>
       <c r="AJ5" s="2">
         <f>-0.01*[5]Données!AK5</f>
-        <v>6.0938611164246037E-2</v>
+        <v>6.5609251560287296E-2</v>
       </c>
       <c r="AK5" s="2">
         <f>-0.01*[5]Données!AL5</f>
-        <v>6.1917080267628877E-2</v>
+        <v>6.6512021960051682E-2</v>
       </c>
       <c r="AL5" s="2">
         <f>-0.01*[5]Données!AM5</f>
-        <v>6.2790779632635907E-2</v>
+        <v>6.7304775349177004E-2</v>
       </c>
       <c r="AM5" s="2">
         <f>-0.01*[5]Données!AN5</f>
-        <v>6.3636600616960304E-2</v>
+        <v>6.806144490727295E-2</v>
       </c>
       <c r="AN5" s="2">
         <f>-0.01*[5]Données!AO5</f>
-        <v>6.4458492162444814E-2</v>
+        <v>6.8786642434899847E-2</v>
       </c>
       <c r="AO5" s="2">
         <f>-0.01*[5]Données!AP5</f>
-        <v>6.5262270211267071E-2</v>
+        <v>6.9486664767093975E-2</v>
       </c>
       <c r="AP5" s="2">
         <f>-0.01*[5]Données!AQ5</f>
-        <v>6.6052765500094202E-2</v>
+        <v>7.0166712340561821E-2</v>
       </c>
       <c r="AQ5" s="2">
         <f>-0.01*[5]Données!AR5</f>
-        <v>6.6817298427610861E-2</v>
+        <v>7.0816293112992867E-2</v>
       </c>
       <c r="AR5" s="2">
         <f>-0.01*[5]Données!AS5</f>
-        <v>6.7571094605159754E-2</v>
+        <v>7.144950627012403E-2</v>
       </c>
       <c r="AS5" s="2">
         <f>-0.01*[5]Données!AT5</f>
-        <v>6.8317161695697348E-2</v>
+        <v>7.2069472085133923E-2</v>
       </c>
       <c r="AT5" s="2">
         <f>-0.01*[5]Données!AU5</f>
-        <v>6.9058315740446852E-2</v>
+        <v>7.2679041002716271E-2</v>
       </c>
       <c r="AU5" s="2">
         <f>-0.01*[5]Données!AV5</f>
-        <v>6.9796909442198962E-2</v>
+        <v>7.3280575543701154E-2</v>
       </c>
       <c r="AV5" s="2">
         <f>-0.01*[5]Données!AW5</f>
-        <v>7.0479911434117026E-2</v>
+        <v>7.3829783928810455E-2</v>
       </c>
       <c r="AW5" s="2">
         <f>-0.01*[5]Données!AX5</f>
-        <v>7.1151098686792813E-2</v>
+        <v>7.4363922148458661E-2</v>
       </c>
       <c r="AX5" s="2">
         <f>-0.01*[5]Données!AY5</f>
-        <v>7.1814955125604873E-2</v>
+        <v>7.4887381279848508E-2</v>
       </c>
       <c r="AY5" s="2">
         <f>-0.01*[5]Données!AZ5</f>
-        <v>7.2475803820003515E-2</v>
+        <v>7.5404258420554982E-2</v>
       </c>
       <c r="AZ5" s="4">
         <f>-0.01*[5]Données!BA5</f>
-        <v>7.3136815666987043E-2</v>
+        <v>7.5917522027450057E-2</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.35">
@@ -5194,207 +5294,207 @@
       </c>
       <c r="B6" s="2">
         <f>(([1]Données!C5)/100)*-1</f>
-        <v>1.4356607550249811E-2</v>
+        <v>1.7920560060476931E-2</v>
       </c>
       <c r="C6" s="2">
         <f>(([1]Données!D5)/100)*-1</f>
-        <v>1.8359555756829793E-2</v>
+        <v>2.2420987067714226E-2</v>
       </c>
       <c r="D6" s="2">
         <f>(([1]Données!E5)/100)*-1</f>
-        <v>2.1979111734358292E-2</v>
+        <v>2.6391221765120765E-2</v>
       </c>
       <c r="E6" s="2">
         <f>(([1]Données!F5)/100)*-1</f>
-        <v>2.5068879367789454E-2</v>
+        <v>2.9643816726273586E-2</v>
       </c>
       <c r="F6" s="2">
         <f>(([1]Données!G5)/100)*-1</f>
-        <v>2.7723085374654066E-2</v>
+        <v>3.2296915621844557E-2</v>
       </c>
       <c r="G6" s="2">
         <f>(([1]Données!H5)/100)*-1</f>
-        <v>3.0045484289630386E-2</v>
+        <v>3.4482070066652715E-2</v>
       </c>
       <c r="H6" s="2">
         <f>(([1]Données!I5)/100)*-1</f>
-        <v>3.2142934801796197E-2</v>
+        <v>3.6326495606225029E-2</v>
       </c>
       <c r="I6" s="2">
         <f>(([1]Données!J5)/100)*-1</f>
-        <v>3.4057681683389962E-2</v>
+        <v>3.7895724678620457E-2</v>
       </c>
       <c r="J6" s="2">
         <f>(([1]Données!K5)/100)*-1</f>
-        <v>3.5837204760872599E-2</v>
+        <v>3.925561282951473E-2</v>
       </c>
       <c r="K6" s="2">
         <f>(([1]Données!L5)/100)*-1</f>
-        <v>3.7520252823447842E-2</v>
+        <v>4.0461570845576562E-2</v>
       </c>
       <c r="L6" s="2">
         <f>(([1]Données!M5)/100)*-1</f>
-        <v>4.0081351725834595E-2</v>
+        <v>4.1553333650161006E-2</v>
       </c>
       <c r="M6" s="2">
         <f>(([1]Données!N5)/100)*-1</f>
-        <v>4.1216477863235346E-2</v>
+        <v>4.2645058246850172E-2</v>
       </c>
       <c r="N6" s="2">
         <f>(([1]Données!O5)/100)*-1</f>
-        <v>4.2229563987969287E-2</v>
+        <v>4.3702166676571119E-2</v>
       </c>
       <c r="O6" s="2">
         <f>(([1]Données!P5)/100)*-1</f>
-        <v>4.3126393087284498E-2</v>
+        <v>4.4739030661767654E-2</v>
       </c>
       <c r="P6" s="2">
         <f>(([1]Données!Q5)/100)*-1</f>
-        <v>4.3936550525898961E-2</v>
+        <v>4.5764389712854792E-2</v>
       </c>
       <c r="Q6" s="2">
         <f>(([1]Données!R5)/100)*-1</f>
-        <v>4.4687819847009196E-2</v>
+        <v>4.6783745751842624E-2</v>
       </c>
       <c r="R6" s="2">
         <f>(([1]Données!S5)/100)*-1</f>
-        <v>4.5451866935080625E-2</v>
+        <v>4.7862161674368853E-2</v>
       </c>
       <c r="S6" s="2">
         <f>(([1]Données!T5)/100)*-1</f>
-        <v>4.6211401290769845E-2</v>
+        <v>4.8950316546854659E-2</v>
       </c>
       <c r="T6" s="2">
         <f>(([1]Données!U5)/100)*-1</f>
-        <v>4.6980586975273519E-2</v>
+        <v>5.0046765696343032E-2</v>
       </c>
       <c r="U6" s="2">
         <f>(([1]Données!V5)/100)*-1</f>
-        <v>4.776938291292588E-2</v>
+        <v>5.1148923511879829E-2</v>
       </c>
       <c r="V6" s="2">
         <f>(([1]Données!W5)/100)*-1</f>
-        <v>4.8588189167100948E-2</v>
+        <v>5.2258308335493941E-2</v>
       </c>
       <c r="W6" s="2">
         <f>(([1]Données!X5)/100)*-1</f>
-        <v>4.9432039654755178E-2</v>
+        <v>5.3363634323631892E-2</v>
       </c>
       <c r="X6" s="2">
         <f>(([1]Données!Y5)/100)*-1</f>
-        <v>5.0307012754312819E-2</v>
+        <v>5.4467910406484243E-2</v>
       </c>
       <c r="Y6" s="2">
         <f>(([1]Données!Z5)/100)*-1</f>
-        <v>5.121388057047449E-2</v>
+        <v>5.5570910105028792E-2</v>
       </c>
       <c r="Z6" s="2">
         <f>(([1]Données!AA5)/100)*-1</f>
-        <v>5.2151234582306749E-2</v>
+        <v>5.6671644214184358E-2</v>
       </c>
       <c r="AA6" s="2">
         <f>(([1]Données!AB5)/100)*-1</f>
-        <v>5.3124301885619118E-2</v>
+        <v>5.777726539266171E-2</v>
       </c>
       <c r="AB6" s="2">
         <f>(([1]Données!AC5)/100)*-1</f>
-        <v>5.4092994435144807E-2</v>
+        <v>5.8847122349554033E-2</v>
       </c>
       <c r="AC6" s="2">
         <f>(([1]Données!AD5)/100)*-1</f>
-        <v>5.5073732374418372E-2</v>
+        <v>5.99016073495795E-2</v>
       </c>
       <c r="AD6" s="2">
         <f>(([1]Données!AE5)/100)*-1</f>
-        <v>5.6065126380332009E-2</v>
+        <v>6.0941600957232896E-2</v>
       </c>
       <c r="AE6" s="2">
         <f>(([1]Données!AF5)/100)*-1</f>
-        <v>5.7065596853837386E-2</v>
+        <v>6.1967742970330919E-2</v>
       </c>
       <c r="AF6" s="2">
         <f>(([1]Données!AG5)/100)*-1</f>
-        <v>5.8073135619838956E-2</v>
+        <v>6.2980077039336835E-2</v>
       </c>
       <c r="AG6" s="2">
         <f>(([1]Données!AH5)/100)*-1</f>
-        <v>5.9073929102841483E-2</v>
+        <v>6.3966700243280217E-2</v>
       </c>
       <c r="AH6" s="2">
         <f>(([1]Données!AI5)/100)*-1</f>
-        <v>6.0074605961998317E-2</v>
+        <v>6.4936134241516674E-2</v>
       </c>
       <c r="AI6" s="2">
         <f>(([1]Données!AJ5)/100)*-1</f>
-        <v>6.1073754817270502E-2</v>
+        <v>6.5888409746443721E-2</v>
       </c>
       <c r="AJ6" s="2">
         <f>(([1]Données!AK5)/100)*-1</f>
-        <v>6.2070369634980693E-2</v>
+        <v>6.6823771179448932E-2</v>
       </c>
       <c r="AK6" s="2">
         <f>(([1]Données!AL5)/100)*-1</f>
-        <v>6.3063627377578424E-2</v>
+        <v>6.7742466423518888E-2</v>
       </c>
       <c r="AL6" s="2">
         <f>(([1]Données!AM5)/100)*-1</f>
-        <v>6.3951403745941215E-2</v>
+        <v>6.8550398816495273E-2</v>
       </c>
       <c r="AM6" s="2">
         <f>(([1]Données!AN5)/100)*-1</f>
-        <v>6.4810741844546271E-2</v>
+        <v>6.9321634655607256E-2</v>
       </c>
       <c r="AN6" s="2">
         <f>(([1]Données!AO5)/100)*-1</f>
-        <v>6.5646312808184004E-2</v>
+        <v>7.00615063337241E-2</v>
       </c>
       <c r="AO6" s="2">
         <f>(([1]Données!AP5)/100)*-1</f>
-        <v>6.6464542713124852E-2</v>
+        <v>7.077691943323916E-2</v>
       </c>
       <c r="AP6" s="2">
         <f>(([1]Données!AQ5)/100)*-1</f>
-        <v>6.7270680566533958E-2</v>
+        <v>7.1473490433306419E-2</v>
       </c>
       <c r="AQ6" s="2">
         <f>(([1]Données!AR5)/100)*-1</f>
-        <v>6.8052133812488314E-2</v>
+        <v>7.2140795107235256E-2</v>
       </c>
       <c r="AR6" s="2">
         <f>(([1]Données!AS5)/100)*-1</f>
-        <v>6.8824193466577088E-2</v>
+        <v>7.2792999868279917E-2</v>
       </c>
       <c r="AS6" s="2">
         <f>(([1]Données!AT5)/100)*-1</f>
-        <v>6.9589988528039215E-2</v>
+        <v>7.3433338061466791E-2</v>
       </c>
       <c r="AT6" s="2">
         <f>(([1]Données!AU5)/100)*-1</f>
-        <v>7.0352434940294084E-2</v>
+        <v>7.4064755589099751E-2</v>
       </c>
       <c r="AU6" s="2">
         <f>(([1]Données!AV5)/100)*-1</f>
-        <v>7.1113972671929981E-2</v>
+        <v>7.4689697537801636E-2</v>
       </c>
       <c r="AV6" s="2">
         <f>(([1]Données!AW5)/100)*-1</f>
-        <v>7.1821241744193354E-2</v>
+        <v>7.526348584849607E-2</v>
       </c>
       <c r="AW6" s="2">
         <f>(([1]Données!AX5)/100)*-1</f>
-        <v>7.2517928035785606E-2</v>
+        <v>7.5823325968397137E-2</v>
       </c>
       <c r="AX6" s="2">
         <f>(([1]Données!AY5)/100)*-1</f>
-        <v>7.3208842235043092E-2</v>
+        <v>7.6373940938334051E-2</v>
       </c>
       <c r="AY6" s="2">
         <f>(([1]Données!AZ5)/100)*-1</f>
-        <v>7.3898628273017075E-2</v>
+        <v>7.6919753579055894E-2</v>
       </c>
       <c r="AZ6" s="4">
         <f>(([1]Données!BA5)/100)*-1</f>
-        <v>7.459070872987239E-2</v>
+        <v>7.7463988062068334E-2</v>
       </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.35">
@@ -5609,207 +5709,207 @@
       </c>
       <c r="B9" s="3">
         <f>B2</f>
-        <v>1.3538601712600906E-2</v>
+        <v>1.7105840554810015E-2</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" ref="C9:AZ9" si="1">C2</f>
-        <v>1.6912679139984843E-2</v>
+        <v>2.098056736359466E-2</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="1"/>
-        <v>2.0115560050032899E-2</v>
+        <v>2.4532546055058613E-2</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="1"/>
-        <v>2.2943774902325131E-2</v>
+        <v>2.7517937372380175E-2</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>2.5425308096377663E-2</v>
+        <v>2.9990320526349201E-2</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="1"/>
-        <v>2.7611418605846372E-2</v>
+        <v>3.2030280950868795E-2</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>2.9576927529626262E-2</v>
+        <v>3.3733930388557543E-2</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="1"/>
-        <v>3.1353239073615535E-2</v>
+        <v>3.51562243585547E-2</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
-        <v>3.2985843392642766E-2</v>
+        <v>3.6361018719246463E-2</v>
       </c>
       <c r="K9" s="3">
         <f t="shared" si="1"/>
-        <v>3.4516237501799885E-2</v>
+        <v>3.7405791429351631E-2</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="1"/>
-        <v>3.6927247412231856E-2</v>
+        <v>3.8334394917893921E-2</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="1"/>
-        <v>3.7901004681047845E-2</v>
+        <v>3.925556698553101E-2</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="1"/>
-        <v>3.8748605891280929E-2</v>
+        <v>4.0138240489166144E-2</v>
       </c>
       <c r="O9" s="3">
         <f t="shared" si="1"/>
-        <v>3.9477051688237563E-2</v>
+        <v>4.0997975041976102E-2</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="1"/>
-        <v>4.0116488877360634E-2</v>
+        <v>4.1844108990118138E-2</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="1"/>
-        <v>4.0694640941231978E-2</v>
+        <v>4.2682193718009402E-2</v>
       </c>
       <c r="R9" s="3">
         <f t="shared" si="1"/>
-        <v>4.1277964002331198E-2</v>
+        <v>4.3572346504538013E-2</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>4.1849741026071745E-2</v>
+        <v>4.4465811282116692E-2</v>
       </c>
       <c r="T9" s="3">
         <f t="shared" si="1"/>
-        <v>4.2425458296820991E-2</v>
+        <v>4.5362483138397192E-2</v>
       </c>
       <c r="U9" s="3">
         <f t="shared" si="1"/>
-        <v>4.3016340742832782E-2</v>
+        <v>4.6261021063189967E-2</v>
       </c>
       <c r="V9" s="3">
         <f t="shared" si="1"/>
-        <v>4.3633104309372284E-2</v>
+        <v>4.7163174260623449E-2</v>
       </c>
       <c r="W9" s="3">
         <f t="shared" si="1"/>
-        <v>4.427314031618601E-2</v>
+        <v>4.8060004625971375E-2</v>
       </c>
       <c r="X9" s="3">
         <f t="shared" si="1"/>
-        <v>4.4941592729452529E-2</v>
+        <v>4.8953489734531723E-2</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="1"/>
-        <v>4.563947337910957E-2</v>
+        <v>4.9843562098548233E-2</v>
       </c>
       <c r="Z9" s="3">
         <f t="shared" si="1"/>
-        <v>4.6365523266142288E-2</v>
+        <v>5.0729292917466084E-2</v>
       </c>
       <c r="AA9" s="3">
         <f t="shared" si="1"/>
-        <v>4.7123697653551948E-2</v>
+        <v>5.1616312992447518E-2</v>
       </c>
       <c r="AB9" s="3">
         <f t="shared" si="1"/>
-        <v>4.788032119780028E-2</v>
+        <v>5.2470427631295502E-2</v>
       </c>
       <c r="AC9" s="3">
         <f t="shared" si="1"/>
-        <v>4.8649621572917197E-2</v>
+        <v>5.3309757047204975E-2</v>
       </c>
       <c r="AD9" s="3">
         <f t="shared" si="1"/>
-        <v>4.9429610515789646E-2</v>
+        <v>5.4134537423666911E-2</v>
       </c>
       <c r="AE9" s="3">
         <f t="shared" si="1"/>
-        <v>5.0218084317584018E-2</v>
+        <v>5.4944750354783627E-2</v>
       </c>
       <c r="AF9" s="3">
         <f t="shared" si="1"/>
-        <v>5.1012621505727829E-2</v>
+        <v>5.5740006203695458E-2</v>
       </c>
       <c r="AG9" s="3">
         <f t="shared" si="1"/>
-        <v>5.1800471640880197E-2</v>
+        <v>5.6509432844425334E-2</v>
       </c>
       <c r="AH9" s="3">
         <f t="shared" si="1"/>
-        <v>5.2587995224248063E-2</v>
+        <v>5.7261280214704439E-2</v>
       </c>
       <c r="AI9" s="3">
         <f t="shared" si="1"/>
-        <v>5.33733113615723E-2</v>
+        <v>5.7995105060567376E-2</v>
       </c>
       <c r="AJ9" s="3">
         <f t="shared" si="1"/>
-        <v>5.4154996240649018E-2</v>
+        <v>5.8710724612016547E-2</v>
       </c>
       <c r="AK9" s="3">
         <f t="shared" si="1"/>
-        <v>5.4931912985350273E-2</v>
+        <v>5.9408064863598842E-2</v>
       </c>
       <c r="AL9" s="3">
         <f t="shared" si="1"/>
-        <v>5.5612806592488247E-2</v>
+        <v>6.0003827900889546E-2</v>
       </c>
       <c r="AM9" s="3">
         <f t="shared" si="1"/>
-        <v>5.6273572035804416E-2</v>
+        <v>6.0571000103954893E-2</v>
       </c>
       <c r="AN9" s="3">
         <f t="shared" si="1"/>
-        <v>5.6914643529708646E-2</v>
+        <v>6.1110748911116231E-2</v>
       </c>
       <c r="AO9" s="3">
         <f t="shared" si="1"/>
-        <v>5.753897634474104E-2</v>
+        <v>6.1626563911912131E-2</v>
       </c>
       <c r="AP9" s="3">
         <f t="shared" si="1"/>
-        <v>5.8149801337017311E-2</v>
+        <v>6.2122074676719145E-2</v>
       </c>
       <c r="AQ9" s="3">
         <f t="shared" si="1"/>
-        <v>5.8735596987392939E-2</v>
+        <v>6.2587962491754912E-2</v>
       </c>
       <c r="AR9" s="3">
         <f t="shared" si="1"/>
-        <v>5.9311343796265348E-2</v>
+        <v>6.3038097195504572E-2</v>
       </c>
       <c r="AS9" s="3">
         <f t="shared" si="1"/>
-        <v>5.9879563862663465E-2</v>
+        <v>6.3475234557170079E-2</v>
       </c>
       <c r="AT9" s="3">
         <f t="shared" si="1"/>
-        <v>6.0442828733665251E-2</v>
+        <v>6.3901885641366452E-2</v>
       </c>
       <c r="AU9" s="3">
         <f t="shared" si="1"/>
-        <v>6.1003296850866917E-2</v>
+        <v>6.43201329379125E-2</v>
       </c>
       <c r="AV9" s="3">
         <f t="shared" si="1"/>
-        <v>6.1513652688195419E-2</v>
+        <v>6.4691410532873417E-2</v>
       </c>
       <c r="AW9" s="3">
         <f t="shared" si="1"/>
-        <v>6.2016559531788203E-2</v>
+        <v>6.5051793926074519E-2</v>
       </c>
       <c r="AX9" s="3">
         <f t="shared" si="1"/>
-        <v>6.2514296331188435E-2</v>
+        <v>6.5403479043005697E-2</v>
       </c>
       <c r="AY9" s="3">
         <f t="shared" si="1"/>
-        <v>6.3009329987089857E-2</v>
+        <v>6.5748713084534671E-2</v>
       </c>
       <c r="AZ9" s="3">
         <f t="shared" si="1"/>
-        <v>6.3503741412501813E-2</v>
+        <v>6.6089373105816973E-2</v>
       </c>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.35">
@@ -5818,207 +5918,207 @@
       </c>
       <c r="B10" s="3">
         <f>B3-B2</f>
-        <v>1.3438789375808113E-4</v>
+        <v>1.3324322143182243E-4</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" ref="C10:AZ13" si="2">C3-C2</f>
-        <v>2.6181616621756554E-4</v>
+        <v>2.5936784348279396E-4</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" si="2"/>
-        <v>3.621163355573831E-4</v>
+        <v>3.5867934026390103E-4</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="2"/>
-        <v>4.3724432175051842E-4</v>
+        <v>4.3321760704773116E-4</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="2"/>
-        <v>4.9908398422249256E-4</v>
+        <v>4.9468668139751593E-4</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>5.5892513906752317E-4</v>
+        <v>5.5417555389225548E-4</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="2"/>
-        <v>6.2275232294828342E-4</v>
+        <v>6.1757907081383401E-4</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="2"/>
-        <v>6.9139740652446324E-4</v>
+        <v>6.8583963207946574E-4</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="2"/>
-        <v>7.6394908653598659E-4</v>
+        <v>7.5819410229926998E-4</v>
       </c>
       <c r="K10" s="3">
         <f t="shared" si="2"/>
-        <v>8.3886924188336653E-4</v>
+        <v>8.3314302656278816E-4</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="2"/>
-        <v>9.1286593600881094E-4</v>
+        <v>9.0941367200969569E-4</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="2"/>
-        <v>9.9162630619664682E-4</v>
+        <v>9.8748455042508426E-4</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="2"/>
-        <v>1.0720241721557944E-3</v>
+        <v>1.0667685359980819E-3</v>
       </c>
       <c r="O10" s="3">
         <f t="shared" si="2"/>
-        <v>1.1535640345473608E-3</v>
+        <v>1.1468396075772283E-3</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" si="2"/>
-        <v>1.2358563924219634E-3</v>
+        <v>1.2274375326907297E-3</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="2"/>
-        <v>1.3187051360760219E-3</v>
+        <v>1.3085078042389675E-3</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="2"/>
-        <v>1.4037302002539651E-3</v>
+        <v>1.3916915929794577E-3</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="2"/>
-        <v>1.4906360662765294E-3</v>
+        <v>1.4767756078585201E-3</v>
       </c>
       <c r="T10" s="3">
         <f t="shared" si="2"/>
-        <v>1.5789080261373531E-3</v>
+        <v>1.5632585306784019E-3</v>
       </c>
       <c r="U10" s="3">
         <f t="shared" si="2"/>
-        <v>1.6679755653525863E-3</v>
+        <v>1.6505753151656588E-3</v>
       </c>
       <c r="V10" s="3">
         <f t="shared" si="2"/>
-        <v>1.7571472529557333E-3</v>
+        <v>1.7380304818160816E-3</v>
       </c>
       <c r="W10" s="3">
         <f t="shared" si="2"/>
-        <v>1.8463864538693642E-3</v>
+        <v>1.8256020341624879E-3</v>
       </c>
       <c r="X10" s="3">
         <f t="shared" si="2"/>
-        <v>1.9353816062881446E-3</v>
+        <v>1.9129834925784017E-3</v>
       </c>
       <c r="Y10" s="3">
         <f t="shared" si="2"/>
-        <v>2.024025037136272E-3</v>
+        <v>2.0000767114388626E-3</v>
       </c>
       <c r="Z10" s="3">
         <f t="shared" si="2"/>
-        <v>2.1122705465630581E-3</v>
+        <v>2.0868483862193088E-3</v>
       </c>
       <c r="AA10" s="3">
         <f t="shared" si="2"/>
-        <v>2.1993524566710221E-3</v>
+        <v>2.1725348345087298E-3</v>
       </c>
       <c r="AB10" s="3">
         <f t="shared" si="2"/>
-        <v>2.2852918106983644E-3</v>
+        <v>2.2571988920424488E-3</v>
       </c>
       <c r="AC10" s="3">
         <f t="shared" si="2"/>
-        <v>2.3700224069685902E-3</v>
+        <v>2.3407663910262055E-3</v>
       </c>
       <c r="AD10" s="3">
         <f t="shared" si="2"/>
-        <v>2.4537980799140754E-3</v>
+        <v>2.4235085417653249E-3</v>
       </c>
       <c r="AE10" s="3">
         <f t="shared" si="2"/>
-        <v>2.5369167545655699E-3</v>
+        <v>2.5057259235543583E-3</v>
       </c>
       <c r="AF10" s="3">
         <f t="shared" si="2"/>
-        <v>2.6196162716446356E-3</v>
+        <v>2.5876371226732989E-3</v>
       </c>
       <c r="AG10" s="3">
         <f t="shared" si="2"/>
-        <v>2.7016507745774021E-3</v>
+        <v>2.6689904023658936E-3</v>
       </c>
       <c r="AH10" s="3">
         <f t="shared" si="2"/>
-        <v>2.7831101864821406E-3</v>
+        <v>2.7498721075444113E-3</v>
       </c>
       <c r="AI10" s="3">
         <f t="shared" si="2"/>
-        <v>2.8641228855196335E-3</v>
+        <v>2.8304083889026874E-3</v>
       </c>
       <c r="AJ10" s="3">
         <f t="shared" si="2"/>
-        <v>2.9448077328281183E-3</v>
+        <v>2.9107162689487737E-3</v>
       </c>
       <c r="AK10" s="3">
         <f t="shared" si="2"/>
-        <v>3.0252520047377995E-3</v>
+        <v>2.9908803996285815E-3</v>
       </c>
       <c r="AL10" s="3">
         <f t="shared" si="2"/>
-        <v>3.1020826789411871E-3</v>
+        <v>3.067489871852784E-3</v>
       </c>
       <c r="AM10" s="3">
         <f t="shared" si="2"/>
-        <v>3.1756576366343964E-3</v>
+        <v>3.1409243679222307E-3</v>
       </c>
       <c r="AN10" s="3">
         <f t="shared" si="2"/>
-        <v>3.2469566266472086E-3</v>
+        <v>3.2121616789450025E-3</v>
       </c>
       <c r="AO10" s="3">
         <f t="shared" si="2"/>
-        <v>3.3169858002710662E-3</v>
+        <v>3.2822073507745506E-3</v>
       </c>
       <c r="AP10" s="3">
         <f t="shared" si="2"/>
-        <v>3.3864791738471567E-3</v>
+        <v>3.3517955131837709E-3</v>
       </c>
       <c r="AQ10" s="3">
         <f t="shared" si="2"/>
-        <v>3.4553360584705928E-3</v>
+        <v>3.4208056641107376E-3</v>
       </c>
       <c r="AR10" s="3">
         <f t="shared" si="2"/>
-        <v>3.5237223017656749E-3</v>
+        <v>3.489396725786853E-3</v>
       </c>
       <c r="AS10" s="3">
         <f t="shared" si="2"/>
-        <v>3.5918993111437869E-3</v>
+        <v>3.5577069072368905E-3</v>
       </c>
       <c r="AT10" s="3">
         <f t="shared" si="2"/>
-        <v>3.6598822236594206E-3</v>
+        <v>3.6258381577166654E-3</v>
       </c>
       <c r="AU10" s="3">
         <f t="shared" si="2"/>
-        <v>3.7276654590847613E-3</v>
+        <v>3.6938558959118684E-3</v>
       </c>
       <c r="AV10" s="3">
         <f t="shared" si="2"/>
-        <v>3.7936479530592537E-3</v>
+        <v>3.7601128146916851E-3</v>
       </c>
       <c r="AW10" s="3">
         <f t="shared" si="2"/>
-        <v>3.8578144973709858E-3</v>
+        <v>3.8246783854445354E-3</v>
       </c>
       <c r="AX10" s="3">
         <f t="shared" si="2"/>
-        <v>3.9206724280951288E-3</v>
+        <v>3.8880748944648547E-3</v>
       </c>
       <c r="AY10" s="3">
         <f t="shared" si="2"/>
-        <v>3.9827770538726215E-3</v>
+        <v>3.9508646712963502E-3</v>
       </c>
       <c r="AZ10" s="3">
         <f t="shared" si="2"/>
-        <v>4.0445557140917909E-3</v>
+        <v>4.0134773342603847E-3</v>
       </c>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.35">
@@ -6027,207 +6127,207 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:Q13" si="3">B4-B3</f>
-        <v>6.166325736678413E-5</v>
+        <v>5.7638045987462583E-5</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
-        <v>1.2406974180489971E-4</v>
+        <v>1.2009166610049693E-4</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" si="3"/>
-        <v>1.6798032322717926E-4</v>
+        <v>1.687411982959075E-4</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="3"/>
-        <v>1.9531726047739006E-4</v>
+        <v>2.0421975119078173E-4</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="3"/>
-        <v>2.157012436457828E-4</v>
+        <v>2.344716659096191E-4</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="3"/>
-        <v>2.3742380955982245E-4</v>
+        <v>2.6645718861317835E-4</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="3"/>
-        <v>2.6492154138157975E-4</v>
+        <v>3.0382307994003543E-4</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="3"/>
-        <v>2.9898978713482904E-4</v>
+        <v>3.4703384205847509E-4</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="3"/>
-        <v>3.3825210997651123E-4</v>
+        <v>3.9463292062513755E-4</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" si="3"/>
-        <v>3.8067326778778998E-4</v>
+        <v>4.4462244276533003E-4</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="3"/>
-        <v>4.2363293529634749E-4</v>
+        <v>4.9535856636317988E-4</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="3"/>
-        <v>4.6895746744057831E-4</v>
+        <v>5.4647583905242242E-4</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="3"/>
-        <v>5.1500073576260519E-4</v>
+        <v>5.9763944798207902E-4</v>
       </c>
       <c r="O11" s="3">
         <f t="shared" si="3"/>
-        <v>5.6134116250994986E-4</v>
+        <v>6.4849348657292083E-4</v>
       </c>
       <c r="P11" s="3">
         <f t="shared" si="3"/>
-        <v>6.0785770713067677E-4</v>
+        <v>6.9903088351264131E-4</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="3"/>
-        <v>6.5476914563755706E-4</v>
+        <v>7.4954679679806874E-4</v>
       </c>
       <c r="R11" s="3">
         <f t="shared" si="2"/>
-        <v>7.0358864451414149E-4</v>
+        <v>8.0157666168491348E-4</v>
       </c>
       <c r="S11" s="3">
         <f t="shared" si="2"/>
-        <v>7.547237955446498E-4</v>
+        <v>8.5566109907541515E-4</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="2"/>
-        <v>8.0806122963938271E-4</v>
+        <v>9.1179353679293057E-4</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="2"/>
-        <v>8.6346503463374802E-4</v>
+        <v>9.6993306650561273E-4</v>
       </c>
       <c r="V11" s="3">
         <f t="shared" si="2"/>
-        <v>9.2084637913879275E-4</v>
+        <v>1.0300632197927165E-3</v>
       </c>
       <c r="W11" s="3">
         <f t="shared" si="2"/>
-        <v>9.80411257173186E-4</v>
+        <v>1.0924539061640814E-3</v>
       </c>
       <c r="X11" s="3">
         <f t="shared" si="2"/>
-        <v>1.0422023538963973E-3</v>
+        <v>1.1571751287592427E-3</v>
       </c>
       <c r="Y11" s="3">
         <f t="shared" si="2"/>
-        <v>1.1062791825026189E-3</v>
+        <v>1.2243008983092857E-3</v>
       </c>
       <c r="Z11" s="3">
         <f t="shared" si="2"/>
-        <v>1.1726705813077665E-3</v>
+        <v>1.2938674026730101E-3</v>
       </c>
       <c r="AA11" s="3">
         <f t="shared" si="2"/>
-        <v>1.2410816766340663E-3</v>
+        <v>1.3655834103072501E-3</v>
       </c>
       <c r="AB11" s="3">
         <f t="shared" si="2"/>
-        <v>1.3111531910162746E-3</v>
+        <v>1.4391426238076349E-3</v>
       </c>
       <c r="AC11" s="3">
         <f t="shared" si="2"/>
-        <v>1.3827054202674091E-3</v>
+        <v>1.5143270412938392E-3</v>
       </c>
       <c r="AD11" s="3">
         <f t="shared" si="2"/>
-        <v>1.4558694544935108E-3</v>
+        <v>1.5912321416542419E-3</v>
       </c>
       <c r="AE11" s="3">
         <f t="shared" si="2"/>
-        <v>1.5307536879812858E-3</v>
+        <v>1.6699421928104766E-3</v>
       </c>
       <c r="AF11" s="3">
         <f t="shared" si="2"/>
-        <v>1.6073581983827648E-3</v>
+        <v>1.7504521528086542E-3</v>
       </c>
       <c r="AG11" s="3">
         <f t="shared" si="2"/>
-        <v>1.6852278177769062E-3</v>
+        <v>1.8323106487770982E-3</v>
       </c>
       <c r="AH11" s="3">
         <f t="shared" si="2"/>
-        <v>1.7642629577990718E-3</v>
+        <v>1.9153967868150712E-3</v>
       </c>
       <c r="AI11" s="3">
         <f t="shared" si="2"/>
-        <v>1.8445390925142593E-3</v>
+        <v>1.9997856099054426E-3</v>
       </c>
       <c r="AJ11" s="3">
         <f t="shared" si="2"/>
-        <v>1.9261368756108357E-3</v>
+        <v>2.0855621098607793E-3</v>
       </c>
       <c r="AK11" s="3">
         <f t="shared" si="2"/>
-        <v>2.0090918360936641E-3</v>
+        <v>2.1727691065059895E-3</v>
       </c>
       <c r="AL11" s="3">
         <f t="shared" si="2"/>
-        <v>2.0895786394496824E-3</v>
+        <v>2.2576642330137675E-3</v>
       </c>
       <c r="AM11" s="3">
         <f t="shared" si="2"/>
-        <v>2.1677130334341044E-3</v>
+        <v>2.3403050595077746E-3</v>
       </c>
       <c r="AN11" s="3">
         <f t="shared" si="2"/>
-        <v>2.2452746057254266E-3</v>
+        <v>2.4224119145178635E-3</v>
       </c>
       <c r="AO11" s="3">
         <f t="shared" si="2"/>
-        <v>2.3236380363928985E-3</v>
+        <v>2.5053133116933468E-3</v>
       </c>
       <c r="AP11" s="3">
         <f t="shared" si="2"/>
-        <v>2.4033272925388857E-3</v>
+        <v>2.5895119995650306E-3</v>
       </c>
       <c r="AQ11" s="3">
         <f t="shared" si="2"/>
-        <v>2.4835948887653794E-3</v>
+        <v>2.6742653688253126E-3</v>
       </c>
       <c r="AR11" s="3">
         <f t="shared" si="2"/>
-        <v>2.5640596761753454E-3</v>
+        <v>2.7591957004773349E-3</v>
       </c>
       <c r="AS11" s="3">
         <f t="shared" si="2"/>
-        <v>2.6446648633973169E-3</v>
+        <v>2.8442532176052859E-3</v>
       </c>
       <c r="AT11" s="3">
         <f t="shared" si="2"/>
-        <v>2.7254406205889925E-3</v>
+        <v>2.9294815834385313E-3</v>
       </c>
       <c r="AU11" s="3">
         <f t="shared" si="2"/>
-        <v>2.8064438176084172E-3</v>
+        <v>3.0149562091705828E-3</v>
       </c>
       <c r="AV11" s="3">
         <f t="shared" si="2"/>
-        <v>2.8855094665938275E-3</v>
+        <v>3.0985357348083387E-3</v>
       </c>
       <c r="AW11" s="3">
         <f t="shared" si="2"/>
-        <v>2.9627060505986735E-3</v>
+        <v>3.1802964182618965E-3</v>
       </c>
       <c r="AX11" s="3">
         <f t="shared" si="2"/>
-        <v>3.0392718891184556E-3</v>
+        <v>3.2614553903712595E-3</v>
       </c>
       <c r="AY11" s="3">
         <f t="shared" si="2"/>
-        <v>3.1162286409965878E-3</v>
+        <v>3.3430242100392915E-3</v>
       </c>
       <c r="AZ11" s="3">
         <f t="shared" si="2"/>
-        <v>3.1940607928172549E-3</v>
+        <v>3.4254897640630944E-3</v>
       </c>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.35">
@@ -6236,207 +6336,207 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" si="3"/>
-        <v>3.9972466572613108E-4</v>
+        <v>4.014010040395144E-4</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="2"/>
-        <v>6.3665455638706181E-4</v>
+        <v>6.3762562867408779E-4</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" si="2"/>
-        <v>7.8740654790432352E-4</v>
+        <v>7.8709449617453409E-4</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="2"/>
-        <v>8.8671582443389241E-4</v>
+        <v>8.8481089037906191E-4</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="2"/>
-        <v>9.5367439926474784E-4</v>
+        <v>9.502334990582062E-4</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>9.9974471688657474E-4</v>
+        <v>9.9507894045069989E-4</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="2"/>
-        <v>1.0331032043029431E-3</v>
+        <v>1.0276160048070526E-3</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="2"/>
-        <v>1.0575416159764872E-3</v>
+        <v>1.0516368655871799E-3</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>1.0763834282041529E-3</v>
+        <v>1.0703991665599322E-3</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" si="2"/>
-        <v>1.0921056494282988E-3</v>
+        <v>1.0862946219346581E-3</v>
       </c>
       <c r="L12" s="3">
         <f t="shared" si="2"/>
-        <v>1.1057368566246284E-3</v>
+        <v>1.0998611542106865E-3</v>
       </c>
       <c r="M12" s="3">
         <f t="shared" si="2"/>
-        <v>1.1209628843252828E-3</v>
+        <v>1.1163835919936194E-3</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="2"/>
-        <v>1.1381882674956767E-3</v>
+        <v>1.1345123579317093E-3</v>
       </c>
       <c r="O12" s="3">
         <f t="shared" si="2"/>
-        <v>1.1575790415513307E-3</v>
+        <v>1.1545102582858277E-3</v>
       </c>
       <c r="P12" s="3">
         <f t="shared" si="2"/>
-        <v>1.1792015706788561E-3</v>
+        <v>1.1764856315246153E-3</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" si="2"/>
-        <v>1.2030059910806898E-3</v>
+        <v>1.2004344805632769E-3</v>
       </c>
       <c r="R12" s="3">
         <f t="shared" si="2"/>
-        <v>1.2301343960197109E-3</v>
+        <v>1.2275472077650715E-3</v>
       </c>
       <c r="S12" s="3">
         <f t="shared" si="2"/>
-        <v>1.2598800045520164E-3</v>
+        <v>1.2571341706512154E-3</v>
       </c>
       <c r="T12" s="3">
         <f t="shared" si="2"/>
-        <v>1.2918136021887808E-3</v>
+        <v>1.2887948704095667E-3</v>
       </c>
       <c r="U12" s="3">
         <f t="shared" si="2"/>
-        <v>1.32561429079181E-3</v>
+        <v>1.322227372497653E-3</v>
       </c>
       <c r="V12" s="3">
         <f t="shared" si="2"/>
-        <v>1.3620583709840275E-3</v>
+        <v>1.3582232763280563E-3</v>
       </c>
       <c r="W12" s="3">
         <f t="shared" si="2"/>
-        <v>1.3985062787638114E-3</v>
+        <v>1.3941671466480843E-3</v>
       </c>
       <c r="X12" s="3">
         <f t="shared" si="2"/>
-        <v>1.4361223895582725E-3</v>
+        <v>1.4312325344637555E-3</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>1.4747510826485996E-3</v>
+        <v>1.469279157701002E-3</v>
       </c>
       <c r="Z12" s="3">
         <f t="shared" si="2"/>
-        <v>1.5142564547891979E-3</v>
+        <v>1.5081846336015836E-3</v>
       </c>
       <c r="AA12" s="3">
         <f t="shared" si="2"/>
-        <v>1.5576401966460596E-3</v>
+        <v>1.5509453693839312E-3</v>
       </c>
       <c r="AB12" s="3">
         <f t="shared" si="2"/>
-        <v>1.5983562067459697E-3</v>
+        <v>1.5910612637243179E-3</v>
       </c>
       <c r="AC12" s="3">
         <f t="shared" si="2"/>
-        <v>1.6387247227599502E-3</v>
+        <v>1.6308560158404539E-3</v>
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="2"/>
-        <v>1.6787970840530519E-3</v>
+        <v>1.6703911604041277E-3</v>
       </c>
       <c r="AE12" s="3">
         <f t="shared" si="2"/>
-        <v>1.7186206553632052E-3</v>
+        <v>1.7097236875738275E-3</v>
       </c>
       <c r="AF12" s="3">
         <f t="shared" si="2"/>
-        <v>1.7582305817761545E-3</v>
+        <v>1.7488957690853305E-3</v>
       </c>
       <c r="AG12" s="3">
         <f t="shared" si="2"/>
-        <v>1.7972845889957581E-3</v>
+        <v>1.7875751440025178E-3</v>
       </c>
       <c r="AH12" s="3">
         <f t="shared" si="2"/>
-        <v>1.8359746195955109E-3</v>
+        <v>1.8259574704949655E-3</v>
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="2"/>
-        <v>1.8744092420992509E-3</v>
+        <v>1.8641541645806337E-3</v>
       </c>
       <c r="AJ12" s="3">
         <f t="shared" si="2"/>
-        <v>1.9126703151580646E-3</v>
+        <v>1.9022485694611957E-3</v>
       </c>
       <c r="AK12" s="3">
         <f t="shared" si="2"/>
-        <v>1.9508234414471401E-3</v>
+        <v>1.9403075903182687E-3</v>
       </c>
       <c r="AL12" s="3">
         <f t="shared" si="2"/>
-        <v>1.9863117217567908E-3</v>
+        <v>1.9757933434209063E-3</v>
       </c>
       <c r="AM12" s="3">
         <f t="shared" si="2"/>
-        <v>2.0196579110873872E-3</v>
+        <v>2.0092153758880515E-3</v>
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="2"/>
-        <v>2.0516174003635326E-3</v>
+        <v>2.0413199303207508E-3</v>
       </c>
       <c r="AO12" s="3">
         <f t="shared" si="2"/>
-        <v>2.082670029862066E-3</v>
+        <v>2.0725801927139464E-3</v>
       </c>
       <c r="AP12" s="3">
         <f t="shared" si="2"/>
-        <v>2.1131576966908483E-3</v>
+        <v>2.103330151093874E-3</v>
       </c>
       <c r="AQ12" s="3">
         <f t="shared" si="2"/>
-        <v>2.1427704929819491E-3</v>
+        <v>2.1332595883019057E-3</v>
       </c>
       <c r="AR12" s="3">
         <f t="shared" si="2"/>
-        <v>2.1719688309533858E-3</v>
+        <v>2.1628166483552702E-3</v>
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="2"/>
-        <v>2.2010336584927792E-3</v>
+        <v>2.1922774031216674E-3</v>
       </c>
       <c r="AT12" s="3">
         <f t="shared" si="2"/>
-        <v>2.2301641625331881E-3</v>
+        <v>2.2218356201946232E-3</v>
       </c>
       <c r="AU12" s="3">
         <f t="shared" si="2"/>
-        <v>2.2595033146388666E-3</v>
+        <v>2.2516305007062032E-3</v>
       </c>
       <c r="AV12" s="3">
         <f t="shared" si="2"/>
-        <v>2.2871013262685258E-3</v>
+        <v>2.2797248464370146E-3</v>
       </c>
       <c r="AW12" s="3">
         <f t="shared" si="2"/>
-        <v>2.3140186070349511E-3</v>
+        <v>2.3071534186777098E-3</v>
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="2"/>
-        <v>2.3407144772028543E-3</v>
+        <v>2.3343719520066974E-3</v>
       </c>
       <c r="AY12" s="3">
         <f t="shared" si="2"/>
-        <v>2.3674681380444484E-3</v>
+        <v>2.3616564546846686E-3</v>
       </c>
       <c r="AZ12" s="3">
         <f t="shared" si="2"/>
-        <v>2.3944577475761841E-3</v>
+        <v>2.3891818233096052E-3</v>
       </c>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.35">
@@ -6445,207 +6545,207 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" si="3"/>
-        <v>2.2223002079790888E-4</v>
+        <v>2.2243723420811712E-4</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="2"/>
-        <v>4.2433615243542278E-4</v>
+        <v>4.2333456586218787E-4</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" si="2"/>
-        <v>5.460484776365071E-4</v>
+        <v>5.4416067532780943E-4</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="2"/>
-        <v>6.0582705880252163E-4</v>
+        <v>6.0363110527583697E-4</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="2"/>
-        <v>6.2931765114337956E-4</v>
+        <v>6.2720324913001502E-4</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="2"/>
-        <v>6.3797201827009431E-4</v>
+        <v>6.3607743282778628E-4</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="2"/>
-        <v>6.4523020353712823E-4</v>
+        <v>6.435470621065642E-4</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="2"/>
-        <v>6.5651380013864724E-4</v>
+        <v>6.5498998034063671E-4</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>6.7277674351318151E-4</v>
+        <v>6.7136792078392737E-4</v>
       </c>
       <c r="K13" s="3">
         <f t="shared" si="2"/>
-        <v>6.9236716254850172E-4</v>
+        <v>6.9171932496215477E-4</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="2"/>
-        <v>7.1186858567295203E-4</v>
+        <v>7.1430533968352278E-4</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="2"/>
-        <v>7.339265242249926E-4</v>
+        <v>7.3914727984803613E-4</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="2"/>
-        <v>7.5574492127428172E-4</v>
+        <v>7.6500584549310524E-4</v>
       </c>
       <c r="O13" s="3">
         <f t="shared" si="2"/>
-        <v>7.7685716043829345E-4</v>
+        <v>7.9121226735557465E-4</v>
       </c>
       <c r="P13" s="3">
         <f t="shared" si="2"/>
-        <v>7.9714597830683048E-4</v>
+        <v>8.1732667500866718E-4</v>
       </c>
       <c r="Q13" s="3">
         <f t="shared" si="2"/>
-        <v>8.1669863298294842E-4</v>
+        <v>8.4306295223290917E-4</v>
       </c>
       <c r="R13" s="3">
         <f t="shared" si="2"/>
-        <v>8.3644969196160907E-4</v>
+        <v>8.6899970740139665E-4</v>
       </c>
       <c r="S13" s="3">
         <f t="shared" si="2"/>
-        <v>8.5642039832490441E-4</v>
+        <v>8.9493438715281676E-4</v>
       </c>
       <c r="T13" s="3">
         <f t="shared" si="2"/>
-        <v>8.7634582048701226E-4</v>
+        <v>9.2043562006494106E-4</v>
       </c>
       <c r="U13" s="3">
         <f t="shared" si="2"/>
-        <v>8.9598727931495398E-4</v>
+        <v>9.4516669452093804E-4</v>
       </c>
       <c r="V13" s="3">
         <f t="shared" si="2"/>
-        <v>9.1503285465011075E-4</v>
+        <v>9.6881709693363849E-4</v>
       </c>
       <c r="W13" s="3">
         <f t="shared" si="2"/>
-        <v>9.335953487628057E-4</v>
+        <v>9.9140661068586322E-4</v>
       </c>
       <c r="X13" s="3">
         <f t="shared" si="2"/>
-        <v>9.5171367511747568E-4</v>
+        <v>1.0130295161511205E-3</v>
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="2"/>
-        <v>9.6935188907742997E-4</v>
+        <v>1.033691239031409E-3</v>
       </c>
       <c r="Z13" s="3">
         <f t="shared" si="2"/>
-        <v>9.8651373350443911E-4</v>
+        <v>1.0534508742243709E-3</v>
       </c>
       <c r="AA13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0025299021160228E-3</v>
+        <v>1.0718887860142814E-3</v>
       </c>
       <c r="AB13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0178720288839191E-3</v>
+        <v>1.0892919386841296E-3</v>
       </c>
       <c r="AC13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0326582515052252E-3</v>
+        <v>1.1059008542140258E-3</v>
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0470512460817247E-3</v>
+        <v>1.1219316897422907E-3</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0612214383433072E-3</v>
+        <v>1.13760081160863E-3</v>
       </c>
       <c r="AF13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0753090623075723E-3</v>
+        <v>1.1530857910740933E-3</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="2"/>
-        <v>1.0892942806112194E-3</v>
+        <v>1.1683912037093735E-3</v>
       </c>
       <c r="AH13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1032629738735311E-3</v>
+        <v>1.1836276619577868E-3</v>
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1173722355650589E-3</v>
+        <v>1.198956522487582E-3</v>
       </c>
       <c r="AJ13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1317584707346562E-3</v>
+        <v>1.2145196191616359E-3</v>
       </c>
       <c r="AK13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1465471099495472E-3</v>
+        <v>1.2304444634672063E-3</v>
       </c>
       <c r="AL13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1606241133053086E-3</v>
+        <v>1.2456234673182687E-3</v>
       </c>
       <c r="AM13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1741412275859675E-3</v>
+        <v>1.2601897483343061E-3</v>
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="2"/>
-        <v>1.1878206457391904E-3</v>
+        <v>1.2748638988242522E-3</v>
       </c>
       <c r="AO13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2022725018577818E-3</v>
+        <v>1.2902546661451852E-3</v>
       </c>
       <c r="AP13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2179150664397564E-3</v>
+        <v>1.3067780927445982E-3</v>
       </c>
       <c r="AQ13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2348353848774529E-3</v>
+        <v>1.3245019942423886E-3</v>
       </c>
       <c r="AR13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2530988614173344E-3</v>
+        <v>1.3434935981558871E-3</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2728268323418668E-3</v>
+        <v>1.3638659763328675E-3</v>
       </c>
       <c r="AT13" s="3">
         <f t="shared" si="2"/>
-        <v>1.2941191998472323E-3</v>
+        <v>1.3857145863834797E-3</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>1.3170632297310192E-3</v>
+        <v>1.4091219941004818E-3</v>
       </c>
       <c r="AV13" s="3">
         <f t="shared" si="2"/>
-        <v>1.3413303100763274E-3</v>
+        <v>1.4337019196856149E-3</v>
       </c>
       <c r="AW13" s="3">
         <f t="shared" si="2"/>
-        <v>1.366829348992793E-3</v>
+        <v>1.4594038199384762E-3</v>
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="2"/>
-        <v>1.3938871094382188E-3</v>
+        <v>1.4865596584855423E-3</v>
       </c>
       <c r="AY13" s="3">
         <f t="shared" si="2"/>
-        <v>1.4228244530135603E-3</v>
+        <v>1.5154951585009124E-3</v>
       </c>
       <c r="AZ13" s="3">
         <f t="shared" si="2"/>
-        <v>1.4538930628853475E-3</v>
+        <v>1.5464660346182768E-3</v>
       </c>
     </row>
     <row r="16" spans="1:52" x14ac:dyDescent="0.35">
